--- a/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
+++ b/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,8 +145,8 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,6 +157,7 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,7 +521,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -797,7 +798,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -805,7 +808,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -851,42 +854,43 @@
           <t>SAR mn</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -1008,23 +1012,23 @@
         <v>621.216217</v>
       </c>
       <c r="F10" s="14">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1039,7 @@
         </is>
       </c>
       <c r="C11" s="19" t="n">
-        <v>1220.387691</v>
+        <v>1486.905974</v>
       </c>
       <c r="D11" s="19" t="n">
         <v>2040.707151</v>
@@ -1051,7 +1055,7 @@
         </is>
       </c>
       <c r="C12" s="19" t="n">
-        <v>2107.644592</v>
+        <v>1841.126309</v>
       </c>
       <c r="D12" s="19" t="n">
         <v>2197.428104</v>
@@ -1121,6 +1125,9 @@
         <is>
           <t>Equity attributable</t>
         </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>2246.744341</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>2624.35365</v>
@@ -1171,23 +1178,23 @@
           <t>Net debt, start of year</t>
         </is>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="29">
         <f>Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="29">
         <f>C24</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="29">
         <f>D24</f>
         <v/>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="29">
         <f>E24</f>
         <v/>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="29">
         <f>F24</f>
         <v/>
       </c>
@@ -1198,24 +1205,24 @@
           <t>Surplus cash</t>
         </is>
       </c>
-      <c r="C18" s="28">
-        <f>Assumptions!$C$51-C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="28">
-        <f>Assumptions!$C$51-D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="28">
-        <f>Assumptions!$C$51-E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="28">
-        <f>Assumptions!$C$51-F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="28">
-        <f>Assumptions!$C$51-G17</f>
+      <c r="C18" s="29">
+        <f>Assumptions!$C$52-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="29">
+        <f>Assumptions!$C$52-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="29">
+        <f>Assumptions!$C$52-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="29">
+        <f>Assumptions!$C$52-F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="29">
+        <f>Assumptions!$C$52-G17</f>
         <v/>
       </c>
     </row>
@@ -1225,24 +1232,24 @@
           <t>Net interest</t>
         </is>
       </c>
-      <c r="C19" s="28">
-        <f>Assumptions!C$32*Assumptions!$C$51-Assumptions!$C$34*MAX(C18,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="28">
-        <f>Assumptions!D$32*Assumptions!$C$51-Assumptions!$C$34*MAX(D18,0)</f>
-        <v/>
-      </c>
-      <c r="E19" s="28">
-        <f>Assumptions!E$32*Assumptions!$C$51-Assumptions!$C$34*MAX(E18,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="28">
-        <f>Assumptions!F$32*Assumptions!$C$51-Assumptions!$C$34*MAX(F18,0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="28">
-        <f>Assumptions!G$32*Assumptions!$C$51-Assumptions!$C$34*MAX(G18,0)</f>
+      <c r="C19" s="29">
+        <f>Assumptions!C$32*Assumptions!$C$52-Assumptions!$C$34*MAX(C18,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>Assumptions!D$32*Assumptions!$C$52-Assumptions!$C$34*MAX(D18,0)</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>Assumptions!E$32*Assumptions!$C$52-Assumptions!$C$34*MAX(E18,0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>Assumptions!F$32*Assumptions!$C$52-Assumptions!$C$34*MAX(F18,0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="29">
+        <f>Assumptions!G$32*Assumptions!$C$52-Assumptions!$C$34*MAX(G18,0)</f>
         <v/>
       </c>
     </row>
@@ -1279,23 +1286,23 @@
           <t>Profit before zakat</t>
         </is>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>C20-C19</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>D20-D19</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>E20-E19</f>
         <v/>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f>F20-F19</f>
         <v/>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f>G20-G19</f>
         <v/>
       </c>
@@ -1306,24 +1313,24 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="C22" s="28">
-        <f>C21*(1-Assumptions!$C$14)*(1-0.004060669885351275)</f>
-        <v/>
-      </c>
-      <c r="D22" s="28">
-        <f>D21*(1-Assumptions!$C$14)*(1-0.004060669885351275)</f>
-        <v/>
-      </c>
-      <c r="E22" s="28">
-        <f>E21*(1-Assumptions!$C$14)*(1-0.004060669885351275)</f>
-        <v/>
-      </c>
-      <c r="F22" s="28">
-        <f>F21*(1-Assumptions!$C$14)*(1-0.004060669885351275)</f>
-        <v/>
-      </c>
-      <c r="G22" s="28">
-        <f>G21*(1-Assumptions!$C$14)*(1-0.004060669885351275)</f>
+      <c r="C22" s="29">
+        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)</f>
+        <v/>
+      </c>
+      <c r="D22" s="29">
+        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)</f>
+        <v/>
+      </c>
+      <c r="E22" s="29">
+        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)</f>
+        <v/>
+      </c>
+      <c r="F22" s="29">
+        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)</f>
+        <v/>
+      </c>
+      <c r="G22" s="29">
+        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)</f>
         <v/>
       </c>
     </row>
@@ -1333,23 +1340,23 @@
           <t>Dividend</t>
         </is>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>Assumptions!$C$33*C22</f>
         <v/>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>Assumptions!$C$33*D22</f>
         <v/>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <f>Assumptions!$C$33*E22</f>
         <v/>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <f>Assumptions!$C$33*F22</f>
         <v/>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <f>Assumptions!$C$33*G22</f>
         <v/>
       </c>
@@ -1360,23 +1367,23 @@
           <t>Net debt, end of year</t>
         </is>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="29">
         <f>C17-(DCF!C27-C19*(1-Assumptions!$C$14))+C23</f>
         <v/>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="29">
         <f>D17-(DCF!D27-D19*(1-Assumptions!$C$14))+D23</f>
         <v/>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="29">
         <f>E17-(DCF!E27-E19*(1-Assumptions!$C$14))+E23</f>
         <v/>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="29">
         <f>F17-(DCF!F27-F19*(1-Assumptions!$C$14))+F23</f>
         <v/>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="29">
         <f>G17-(DCF!G27-G19*(1-Assumptions!$C$14))+G23</f>
         <v/>
       </c>
@@ -1387,29 +1394,31 @@
           <t>Equity attributable</t>
         </is>
       </c>
-      <c r="C25" s="28">
-        <f>Assumptions!$C$52+C22-C23</f>
-        <v/>
-      </c>
-      <c r="D25" s="28">
+      <c r="C25" s="29">
+        <f>Assumptions!$C$53+C22-C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="29">
         <f>C25+D22-D23</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="29">
         <f>D25+E22-E23</f>
         <v/>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="29">
         <f>E25+F22-F23</f>
         <v/>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="29">
         <f>F25+G22-G23</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1417,7 +1426,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1459,27 +1468,28 @@
           <t>SAR mn</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -1653,29 +1663,31 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <f>C9*C10</f>
         <v/>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="29">
         <f>D9*D10</f>
         <v/>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="29">
         <f>E9*E10</f>
         <v/>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="29">
         <f>F9*F10</f>
         <v/>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="29">
         <f>G9*G10</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1683,7 +1695,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1725,27 +1737,28 @@
           <t>SAR mn</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -1785,23 +1798,23 @@
         </is>
       </c>
       <c r="C6" s="14">
-        <f>Segments!C17</f>
+        <f>Segments!C19</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>Segments!D17</f>
+        <f>Segments!D19</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>Segments!E17</f>
+        <f>Segments!E19</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>Segments!F17</f>
+        <f>Segments!F19</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>Segments!G17</f>
+        <f>Segments!G19</f>
         <v/>
       </c>
     </row>
@@ -1914,7 +1927,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1922,7 +1937,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2083,7 +2098,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2091,7 +2108,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2165,111 +2182,113 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=6.88%</t>
+          <t>WACC_t=7.48%</t>
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>161.6870195722353</v>
+        <v>142.7431012135075</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>191.8736371200676</v>
+        <v>164.9510103161226</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>242.7920021776906</v>
+        <v>199.7503161286955</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>328.6054644701809</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>316.2898673502376</v>
+        <v>262.3549098579414</v>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>n.m.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=7.88%</t>
+          <t>WACC_t=8.48%</t>
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>134.9542534346101</v>
+        <v>121.3446604174545</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>153.6462749347582</v>
+        <v>135.7369156695441</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>181.817839760119</v>
+        <v>156.4277477374078</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>229.3284945978041</v>
+        <v>188.8424820913314</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>309.2939518882336</v>
+        <v>247.1468366422771</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=8.88%</t>
+          <t>WACC_t=9.48%</t>
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>115.9875989393748</v>
+        <v>105.6652693207071</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>128.4080357765257</v>
+        <v>115.5320651320001</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>145.8018216575757</v>
+        <v>128.9001658845238</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>172.0099984828811</v>
+        <v>148.1126917464052</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>216.2002968120145</v>
+        <v>178.2037812750351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=9.88%</t>
+          <t>WACC_t=10.48%</t>
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>101.8318835964901</v>
+        <v>93.68221417408712</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>110.4985687882707</v>
+        <v>100.7244384888253</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>122.0196936752806</v>
+        <v>109.8583452566114</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>138.1484649801172</v>
+        <v>122.2284156773896</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>162.4434833151007</v>
+        <v>140.0003338175182</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=10.88%</t>
+          <t>WACC_t=11.48%</t>
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>90.86244771441412</v>
+        <v>84.22599667245792</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>97.12920999823187</v>
+        <v>89.40522709517732</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>105.1403254957291</v>
+        <v>95.90023795914497</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>115.7851086440444</v>
+        <v>104.3199167292194</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>130.6811672133541</v>
+        <v>115.7173612269487</v>
       </c>
     </row>
     <row r="12">
@@ -2286,7 +2305,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>209.3035784772404</v>
+        <v>135.1433046442411</v>
       </c>
     </row>
     <row r="14">
@@ -2296,7 +2315,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>164.1972907373474</v>
+        <v>132.1856078811852</v>
       </c>
     </row>
     <row r="15">
@@ -2306,7 +2325,7 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>130.9006081673441</v>
+        <v>128.9001658845238</v>
       </c>
     </row>
     <row r="16">
@@ -2316,7 +2335,7 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>113.2662678099585</v>
+        <v>126.5148107194236</v>
       </c>
     </row>
     <row r="17">
@@ -2326,7 +2345,7 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>97.50828418400954</v>
+        <v>123.7961150741202</v>
       </c>
     </row>
     <row r="19">
@@ -2343,7 +2362,7 @@
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>158.4002563008479</v>
+        <v>140.3183760368647</v>
       </c>
     </row>
     <row r="21">
@@ -2353,7 +2372,7 @@
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>152.0896788918666</v>
+        <v>134.5979220513759</v>
       </c>
     </row>
     <row r="22">
@@ -2363,7 +2382,7 @@
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>145.8018216575757</v>
+        <v>128.9001658845238</v>
       </c>
     </row>
     <row r="23">
@@ -2373,7 +2392,7 @@
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>139.5341530596548</v>
+        <v>123.2225770227576</v>
       </c>
     </row>
     <row r="24">
@@ -2383,7 +2402,7 @@
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>133.2845824820281</v>
+        <v>117.5630658397253</v>
       </c>
     </row>
     <row r="26">
@@ -2400,7 +2419,7 @@
         </is>
       </c>
       <c r="B27" s="17" t="n">
-        <v>123.3559579612546</v>
+        <v>108.8887041368196</v>
       </c>
     </row>
     <row r="28">
@@ -2410,7 +2429,7 @@
         </is>
       </c>
       <c r="B28" s="17" t="n">
-        <v>132.1837426703699</v>
+        <v>116.759058320275</v>
       </c>
     </row>
     <row r="29">
@@ -2420,7 +2439,7 @@
         </is>
       </c>
       <c r="B29" s="17" t="n">
-        <v>145.8018216575757</v>
+        <v>128.9001658845238</v>
       </c>
     </row>
     <row r="30">
@@ -2430,7 +2449,7 @@
         </is>
       </c>
       <c r="B30" s="17" t="n">
-        <v>150.1532450187395</v>
+        <v>132.779647767494</v>
       </c>
     </row>
     <row r="31">
@@ -2440,7 +2459,7 @@
         </is>
       </c>
       <c r="B31" s="17" t="n">
-        <v>159.2987061984988</v>
+        <v>140.9332204699758</v>
       </c>
     </row>
     <row r="33">
@@ -2457,7 +2476,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>132.9554264400183</v>
+        <v>117.7608569731192</v>
       </c>
     </row>
     <row r="35">
@@ -2467,7 +2486,7 @@
         </is>
       </c>
       <c r="B35" s="17" t="n">
-        <v>139.3834502657949</v>
+        <v>123.3352376150401</v>
       </c>
     </row>
     <row r="36">
@@ -2477,7 +2496,7 @@
         </is>
       </c>
       <c r="B36" s="17" t="n">
-        <v>145.8018216575757</v>
+        <v>128.9001658845238</v>
       </c>
     </row>
     <row r="37">
@@ -2487,7 +2506,7 @@
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>152.2112546307662</v>
+        <v>134.4563415543554</v>
       </c>
     </row>
     <row r="38">
@@ -2497,7 +2516,7 @@
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>158.6123783645118</v>
+        <v>140.004381215677</v>
       </c>
     </row>
     <row r="40">
@@ -2514,7 +2533,7 @@
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>151.7745103839866</v>
+        <v>134.5643347580265</v>
       </c>
     </row>
     <row r="42">
@@ -2524,7 +2543,7 @@
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>148.7881660207811</v>
+        <v>131.7322503212752</v>
       </c>
     </row>
     <row r="43">
@@ -2534,7 +2553,7 @@
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>145.8018216575757</v>
+        <v>128.9001658845238</v>
       </c>
     </row>
     <row r="44">
@@ -2544,7 +2563,7 @@
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>142.8154772943702</v>
+        <v>126.0680814477724</v>
       </c>
     </row>
     <row r="45">
@@ -2554,11 +2573,13 @@
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>139.8291329311647</v>
+        <v>123.235997011021</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2566,7 +2587,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2634,8 +2655,9 @@
           <t>EPS (SAR)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
-        <v>7.216230848097251</v>
+      <c r="B5" s="7">
+        <f>'Income Statement'!E16/Assumptions!$C$6</f>
+        <v/>
       </c>
       <c r="C5" s="15">
         <f>'Balance Sheet'!C22/Assumptions!$C$6</f>
@@ -2665,7 +2687,7 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>Assumptions!$C$52/Assumptions!$C$6</f>
+        <f>Assumptions!$C$53/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C6" s="15">
@@ -2692,11 +2714,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>ROE (%)</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="n">
-        <v>0.3680769183960799</v>
+          <t>ROE (%) — attributable profit / average equity</t>
+        </is>
+      </c>
+      <c r="B7" s="8">
+        <f>'Income Statement'!E16/AVERAGE('Balance Sheet'!D14,'Balance Sheet'!E14)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2705,28 +2728,28 @@
           <t>Net debt / EBITDA (x)</t>
         </is>
       </c>
-      <c r="B8" s="34">
-        <f>Assumptions!$C$7/(Segments!B10*0+1352.0324810000002)</f>
+      <c r="B8" s="30">
+        <f>Assumptions!$C$7/'Income Statement'!E9</f>
         <v/>
       </c>
       <c r="C8" s="34">
-        <f>'Balance Sheet'!F13/Segments!C17</f>
+        <f>'Balance Sheet'!F13/Segments!C19</f>
         <v/>
       </c>
       <c r="D8" s="34">
-        <f>'Balance Sheet'!G13/Segments!D17</f>
+        <f>'Balance Sheet'!G13/Segments!D19</f>
         <v/>
       </c>
       <c r="E8" s="34">
-        <f>'Balance Sheet'!H13/Segments!E17</f>
+        <f>'Balance Sheet'!H13/Segments!E19</f>
         <v/>
       </c>
       <c r="F8" s="34">
-        <f>'Balance Sheet'!I13/Segments!F17</f>
+        <f>'Balance Sheet'!I13/Segments!F19</f>
         <v/>
       </c>
       <c r="G8" s="34">
-        <f>'Balance Sheet'!J13/Segments!G17</f>
+        <f>'Balance Sheet'!J13/Segments!G19</f>
         <v/>
       </c>
     </row>
@@ -2736,8 +2759,9 @@
           <t>Trailing EV/EBITDA (x)</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
-        <v>11.88992678349715</v>
+      <c r="B9" s="30">
+        <f>(Assumptions!$C$5*Assumptions!$C$6+Assumptions!$C$7)/'Income Statement'!E9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -2746,12 +2770,15 @@
           <t>Trailing P/E (x)</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n">
-        <v>14.52281699491824</v>
+      <c r="B10" s="30">
+        <f>Assumptions!$C$5/B5</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2759,7 +2786,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2822,12 +2849,13 @@
           <t>Tadawul</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
-        <v>11.88992678349715</v>
+      <c r="C5" s="30">
+        <f>'Per-Share &amp; Ratios'!B9</f>
+        <v/>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>trailing; ~14.5x P/E</t>
+          <t>trailing; ~14.5x trailing P/E</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2875,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>global cable major</t>
+          <t>developed-market major</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2895,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>global cable major</t>
+          <t>developed-market major</t>
         </is>
       </c>
     </row>
@@ -2931,12 +2959,14 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA applied in the relative lens: 9.0x (mid-range, single-country discount).</t>
+          <t>Justified EV/EBITDA applied in the relative lens: 9.5x (mid-range, single-country discount).</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2944,7 +2974,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3188,7 +3218,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3196,7 +3228,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3286,7 +3318,7 @@
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>Assumptions!$C$39</f>
+        <f>Assumptions!$C$40</f>
         <v/>
       </c>
       <c r="F5" s="15">
@@ -3317,7 +3349,7 @@
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>Assumptions!$C$40</f>
+        <f>Assumptions!$C$41</f>
         <v/>
       </c>
       <c r="F6" s="15">
@@ -3348,7 +3380,7 @@
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>Assumptions!$C$41</f>
+        <f>Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F7" s="15">
@@ -3379,7 +3411,7 @@
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
       <c r="F8" s="15">
@@ -3426,7 +3458,7 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>143.7240895365966</v>
+        <v>126.970585075898</v>
       </c>
     </row>
     <row r="12">
@@ -3471,7 +3503,7 @@
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>159.2987061984988</v>
+        <v>140.9332204699758</v>
       </c>
     </row>
     <row r="17">
@@ -3481,11 +3513,13 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>132.1837426703699</v>
+        <v>116.759058320275</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3493,9 +3527,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3602,7 +3636,7 @@
         </is>
       </c>
       <c r="C9" s="20" t="n">
-        <v>0.0485</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="10">
@@ -3612,7 +3646,7 @@
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>0.0051</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="11">
@@ -3622,7 +3656,7 @@
         </is>
       </c>
       <c r="C11" s="20" t="n">
-        <v>0.0501</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="12">
@@ -3678,7 +3712,7 @@
         </is>
       </c>
       <c r="C16" s="20" t="n">
-        <v>0.0434</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="17">
@@ -3688,7 +3722,7 @@
         </is>
       </c>
       <c r="C17" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="18">
@@ -3952,75 +3986,75 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>NCI share of forecast profit</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>0.004060669885351275</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Lens inputs</t>
         </is>
       </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="n"/>
-      <c r="I35" s="11" t="n"/>
-      <c r="J35" s="11" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C36" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n"/>
+      <c r="I36" s="11" t="n"/>
+      <c r="J36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
+          <t>Justified EV/EBITDA</t>
         </is>
       </c>
       <c r="C37" s="22" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="n">
-        <v>0.28</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="n">
-        <v>0.45</v>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
+          <t>Weight — discounted cash flow</t>
         </is>
       </c>
       <c r="C40" s="23" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
+          <t>Weight — relative</t>
         </is>
       </c>
       <c r="C41" s="23" t="n">
@@ -4030,157 +4064,169 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
           <t>Weight — book</t>
         </is>
       </c>
-      <c r="C42" s="23" t="n">
+      <c r="C43" s="23" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Anchor roll</t>
         </is>
       </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="11" t="n"/>
-      <c r="I43" s="11" t="n"/>
-      <c r="J43" s="11" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Days to the anchor</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="n">
-        <v>230</v>
-      </c>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="11" t="n"/>
+      <c r="I44" s="11" t="n"/>
+      <c r="J44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
+          <t>Days to the anchor</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
           <t>FY2025 dividend per share paid in window</t>
         </is>
       </c>
-      <c r="C45" s="17" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="C46" s="17" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>FY2025 disclosed base (audited)</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="11" t="n"/>
-      <c r="H46" s="11" t="n"/>
-      <c r="I46" s="11" t="n"/>
-      <c r="J46" s="11" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 metal content / materials (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="n">
-        <v>8486.925676999999</v>
-      </c>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="11" t="n"/>
+      <c r="I47" s="11" t="n"/>
+      <c r="J47" s="11" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>FY2025 conversion cost (SAR mn)</t>
+          <t>FY2025 metal content / materials (SAR mn)</t>
         </is>
       </c>
       <c r="C48" s="19" t="n">
-        <v>453.34873</v>
+        <v>8486.925676999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>FY2025 net working capital (SAR mn)</t>
+          <t>FY2025 conversion cost (SAR mn)</t>
         </is>
       </c>
       <c r="C49" s="19" t="n">
-        <v>2933.258925</v>
+        <v>453.34873</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>FY2025 PP&amp;E (SAR mn)</t>
+          <t>FY2025 net working capital (SAR mn)</t>
         </is>
       </c>
       <c r="C50" s="19" t="n">
-        <v>1491.86312</v>
+        <v>2933.258925</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
+          <t>FY2025 PP&amp;E (SAR mn)</t>
         </is>
       </c>
       <c r="C51" s="19" t="n">
-        <v>621.216217</v>
+        <v>1491.86312</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>FY2025 equity attributable (SAR mn)</t>
+          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
         </is>
       </c>
       <c r="C52" s="19" t="n">
-        <v>3246.136935</v>
+        <v>621.216217</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>FY2025 associates carrying value (SAR mn)</t>
+          <t>FY2025 equity attributable (SAR mn)</t>
         </is>
       </c>
       <c r="C53" s="19" t="n">
-        <v>31.851877</v>
+        <v>3246.136935</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>FY2025 non-operating assets (SAR mn)</t>
+          <t>FY2025 associates carrying value (SAR mn)</t>
         </is>
       </c>
       <c r="C54" s="19" t="n">
-        <v>20.40064</v>
+        <v>31.851877</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
+          <t>FY2025 non-operating assets (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="n">
+        <v>20.40064</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
           <t>FY2025 NCI carrying value (SAR mn)</t>
         </is>
       </c>
-      <c r="C55" s="19" t="n">
+      <c r="C56" s="19" t="n">
         <v>62.737156</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4188,7 +4234,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4307,7 +4353,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4315,9 +4363,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4425,7 +4473,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>Assumptions!$C$47/100.0</f>
+        <f>Assumptions!$C$48/100.0</f>
         <v/>
       </c>
       <c r="C6" s="27">
@@ -4456,7 +4504,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>Assumptions!$C$48/100.0</f>
+        <f>Assumptions!$C$49/100.0</f>
         <v/>
       </c>
       <c r="C7" s="27">
@@ -4483,379 +4531,441 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Materials (metal leg)</t>
-        </is>
-      </c>
-      <c r="B8" s="28">
-        <f>B5*B6</f>
-        <v/>
+          <t>Target gross margin (anchor + glide)</t>
+        </is>
       </c>
       <c r="C8" s="28">
-        <f>C5*C6</f>
+        <f>Assumptions!$C$26+Assumptions!C$27</f>
         <v/>
       </c>
       <c r="D8" s="28">
-        <f>D5*D6</f>
+        <f>Assumptions!$C$26+Assumptions!D$27</f>
         <v/>
       </c>
       <c r="E8" s="28">
-        <f>E5*E6</f>
+        <f>Assumptions!$C$26+Assumptions!E$27</f>
         <v/>
       </c>
       <c r="F8" s="28">
-        <f>F5*F6</f>
+        <f>Assumptions!$C$26+Assumptions!F$27</f>
         <v/>
       </c>
       <c r="G8" s="28">
-        <f>G5*G6</f>
+        <f>Assumptions!$C$26+Assumptions!G$27</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Conversion cost</t>
-        </is>
-      </c>
-      <c r="B9" s="28">
-        <f>B5*B7</f>
-        <v/>
-      </c>
-      <c r="C9" s="28">
-        <f>C5*C7</f>
-        <v/>
-      </c>
-      <c r="D9" s="28">
-        <f>D5*D7</f>
-        <v/>
-      </c>
-      <c r="E9" s="28">
-        <f>E5*E7</f>
-        <v/>
-      </c>
-      <c r="F9" s="28">
-        <f>F5*F7</f>
-        <v/>
-      </c>
-      <c r="G9" s="28">
-        <f>G5*G7</f>
+          <t>Gross profit per unit (conversion spread)</t>
+        </is>
+      </c>
+      <c r="B9" s="27">
+        <f>B12/B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="27">
+        <f>C8/(1-C8)*(C6+C7)</f>
+        <v/>
+      </c>
+      <c r="D9" s="27">
+        <f>D8/(1-D8)*(D6+D7)</f>
+        <v/>
+      </c>
+      <c r="E9" s="27">
+        <f>E8/(1-E8)*(E6+E7)</f>
+        <v/>
+      </c>
+      <c r="F9" s="27">
+        <f>F8/(1-F8)*(F6+F7)</f>
+        <v/>
+      </c>
+      <c r="G9" s="27">
+        <f>G8/(1-G8)*(G6+G7)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Cost of revenue</t>
-        </is>
-      </c>
-      <c r="B10" s="28">
-        <f>B8+B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="28">
-        <f>C8+C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="28">
-        <f>D8+D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="28">
-        <f>E8+E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="28">
-        <f>F8+F9</f>
-        <v/>
-      </c>
-      <c r="G10" s="28">
-        <f>G8+G9</f>
+          <t>Materials (metal leg)</t>
+        </is>
+      </c>
+      <c r="B10" s="29">
+        <f>B5*B6</f>
+        <v/>
+      </c>
+      <c r="C10" s="29">
+        <f>C5*C6</f>
+        <v/>
+      </c>
+      <c r="D10" s="29">
+        <f>D5*D6</f>
+        <v/>
+      </c>
+      <c r="E10" s="29">
+        <f>E5*E6</f>
+        <v/>
+      </c>
+      <c r="F10" s="29">
+        <f>F5*F6</f>
+        <v/>
+      </c>
+      <c r="G10" s="29">
+        <f>G5*G6</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Gross margin (target = anchor + glide)</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>0.1623940528853008</v>
+          <t>Conversion cost</t>
+        </is>
+      </c>
+      <c r="B11" s="29">
+        <f>B5*B7</f>
+        <v/>
       </c>
       <c r="C11" s="29">
-        <f>Assumptions!$C$26+Assumptions!C$27</f>
+        <f>C5*C7</f>
         <v/>
       </c>
       <c r="D11" s="29">
-        <f>Assumptions!$C$26+Assumptions!D$27</f>
+        <f>D5*D7</f>
         <v/>
       </c>
       <c r="E11" s="29">
-        <f>Assumptions!$C$26+Assumptions!E$27</f>
+        <f>E5*E7</f>
         <v/>
       </c>
       <c r="F11" s="29">
-        <f>Assumptions!$C$26+Assumptions!F$27</f>
+        <f>F5*F7</f>
         <v/>
       </c>
       <c r="G11" s="29">
-        <f>Assumptions!$C$26+Assumptions!G$27</f>
+        <f>G5*G7</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Gross profit = volume x spread</t>
         </is>
       </c>
       <c r="B12" s="19" t="n">
-        <v>10673.604262</v>
-      </c>
-      <c r="C12" s="28">
-        <f>C10/(1-C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="28">
-        <f>D10/(1-D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="28">
-        <f>E10/(1-E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="28">
-        <f>F10/(1-F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="28">
-        <f>G10/(1-G11)</f>
+        <v>1733.329855</v>
+      </c>
+      <c r="C12" s="29">
+        <f>C5*C9</f>
+        <v/>
+      </c>
+      <c r="D12" s="29">
+        <f>D5*D9</f>
+        <v/>
+      </c>
+      <c r="E12" s="29">
+        <f>E5*E9</f>
+        <v/>
+      </c>
+      <c r="F12" s="29">
+        <f>F5*F9</f>
+        <v/>
+      </c>
+      <c r="G12" s="29">
+        <f>G5*G9</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n">
-        <v>1733.329855</v>
-      </c>
-      <c r="C13" s="28">
-        <f>C12-C10</f>
-        <v/>
-      </c>
-      <c r="D13" s="28">
-        <f>D12-D10</f>
-        <v/>
-      </c>
-      <c r="E13" s="28">
-        <f>E12-E10</f>
-        <v/>
-      </c>
-      <c r="F13" s="28">
-        <f>F12-F10</f>
-        <v/>
-      </c>
-      <c r="G13" s="28">
-        <f>G12-G10</f>
+          <t>Revenue = materials + conversion + gross profit</t>
+        </is>
+      </c>
+      <c r="B13" s="29">
+        <f>B10+B11+B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="29">
+        <f>C10+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="29">
+        <f>D10+D11+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="29">
+        <f>E10+E11+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="29">
+        <f>F10+F11+F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="29">
+        <f>G10+G11+G12</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="C14" s="28">
-        <f>Assumptions!C$28*C12</f>
-        <v/>
-      </c>
-      <c r="D14" s="28">
-        <f>Assumptions!D$28*D12</f>
-        <v/>
-      </c>
-      <c r="E14" s="28">
-        <f>Assumptions!E$28*E12</f>
-        <v/>
-      </c>
-      <c r="F14" s="28">
-        <f>Assumptions!F$28*F12</f>
-        <v/>
-      </c>
-      <c r="G14" s="28">
-        <f>Assumptions!G$28*G12</f>
+          <t>Cost of revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="29">
+        <f>B10+B11</f>
+        <v/>
+      </c>
+      <c r="C14" s="29">
+        <f>C10+C11</f>
+        <v/>
+      </c>
+      <c r="D14" s="29">
+        <f>D10+D11</f>
+        <v/>
+      </c>
+      <c r="E14" s="29">
+        <f>E10+E11</f>
+        <v/>
+      </c>
+      <c r="F14" s="29">
+        <f>F10+F11</f>
+        <v/>
+      </c>
+      <c r="G14" s="29">
+        <f>G10+G11</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Depreciation &amp; amortisation</t>
-        </is>
+          <t>Gross margin (OUTPUT = gross profit / revenue)</t>
+        </is>
+      </c>
+      <c r="B15" s="28">
+        <f>B12/B13</f>
+        <v/>
       </c>
       <c r="C15" s="28">
-        <f>Assumptions!$C$29*C12</f>
+        <f>C12/C13</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>Assumptions!$C$29*D12</f>
+        <f>D12/D13</f>
         <v/>
       </c>
       <c r="E15" s="28">
-        <f>Assumptions!$C$29*E12</f>
+        <f>E12/E13</f>
         <v/>
       </c>
       <c r="F15" s="28">
-        <f>Assumptions!$C$29*F12</f>
+        <f>F12/F13</f>
         <v/>
       </c>
       <c r="G15" s="28">
-        <f>Assumptions!$C$29*G12</f>
+        <f>G12/G13</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C16" s="28">
-        <f>C13-C14</f>
-        <v/>
-      </c>
-      <c r="D16" s="28">
-        <f>D13-D14</f>
-        <v/>
-      </c>
-      <c r="E16" s="28">
-        <f>E13-E14</f>
-        <v/>
-      </c>
-      <c r="F16" s="28">
-        <f>F13-F14</f>
-        <v/>
-      </c>
-      <c r="G16" s="28">
-        <f>G13-G14</f>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C16" s="29">
+        <f>Assumptions!C$28*C13</f>
+        <v/>
+      </c>
+      <c r="D16" s="29">
+        <f>Assumptions!D$28*D13</f>
+        <v/>
+      </c>
+      <c r="E16" s="29">
+        <f>Assumptions!E$28*E13</f>
+        <v/>
+      </c>
+      <c r="F16" s="29">
+        <f>Assumptions!F$28*F13</f>
+        <v/>
+      </c>
+      <c r="G16" s="29">
+        <f>Assumptions!G$28*G13</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="C17" s="28">
-        <f>C16+C15</f>
-        <v/>
-      </c>
-      <c r="D17" s="28">
-        <f>D16+D15</f>
-        <v/>
-      </c>
-      <c r="E17" s="28">
-        <f>E16+E15</f>
-        <v/>
-      </c>
-      <c r="F17" s="28">
-        <f>F16+F15</f>
-        <v/>
-      </c>
-      <c r="G17" s="28">
-        <f>G16+G15</f>
+          <t>Depreciation &amp; amortisation</t>
+        </is>
+      </c>
+      <c r="C17" s="29">
+        <f>Assumptions!$C$29*C13</f>
+        <v/>
+      </c>
+      <c r="D17" s="29">
+        <f>Assumptions!$C$29*D13</f>
+        <v/>
+      </c>
+      <c r="E17" s="29">
+        <f>Assumptions!$C$29*E13</f>
+        <v/>
+      </c>
+      <c r="F17" s="29">
+        <f>Assumptions!$C$29*F13</f>
+        <v/>
+      </c>
+      <c r="G17" s="29">
+        <f>Assumptions!$C$29*G13</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C18" s="29">
+        <f>C12-C16</f>
+        <v/>
+      </c>
+      <c r="D18" s="29">
+        <f>D12-D16</f>
+        <v/>
+      </c>
+      <c r="E18" s="29">
+        <f>E12-E16</f>
+        <v/>
+      </c>
+      <c r="F18" s="29">
+        <f>F12-F16</f>
+        <v/>
+      </c>
+      <c r="G18" s="29">
+        <f>G12-G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C19" s="29">
+        <f>C18+C17</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>D18+D17</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>E18+E17</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>F18+F17</f>
+        <v/>
+      </c>
+      <c r="G19" s="29">
+        <f>G18+G17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="C18" s="29">
-        <f>C17/C12</f>
-        <v/>
-      </c>
-      <c r="D18" s="29">
-        <f>D17/D12</f>
-        <v/>
-      </c>
-      <c r="E18" s="29">
-        <f>E17/E12</f>
-        <v/>
-      </c>
-      <c r="F18" s="29">
-        <f>F17/F12</f>
-        <v/>
-      </c>
-      <c r="G18" s="29">
-        <f>G17/G12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="C20" s="28">
+        <f>C19/C13</f>
+        <v/>
+      </c>
+      <c r="D20" s="28">
+        <f>D19/D13</f>
+        <v/>
+      </c>
+      <c r="E20" s="28">
+        <f>E19/E13</f>
+        <v/>
+      </c>
+      <c r="F20" s="28">
+        <f>F19/F13</f>
+        <v/>
+      </c>
+      <c r="G20" s="28">
+        <f>G19/G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>FY2025 disclosed segment revenue (Note 40)</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Cables and wires</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="n">
-        <v>10414.170668</v>
-      </c>
-      <c r="C21" s="9">
-        <f>B21/B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>High-voltage cables (turnkey projects)</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="n">
-        <v>230.839181</v>
-      </c>
-      <c r="C22" s="9">
-        <f>B22/B12</f>
-        <v/>
-      </c>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>Cables and wires</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>10414.170668</v>
+      </c>
+      <c r="C23" s="9">
+        <f>B23/B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>High-voltage cables (turnkey projects)</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>230.839181</v>
+      </c>
+      <c r="C24" s="9">
+        <f>B24/B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>Other (telephone cables &amp; services)</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B25" s="19" t="n">
         <v>28.594413</v>
       </c>
-      <c r="C23" s="9">
-        <f>B23/B12</f>
+      <c r="C25" s="9">
+        <f>B25/B13</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4863,7 +4973,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4917,7 +5027,7 @@
         </is>
       </c>
       <c r="C5" s="14">
-        <f>Segments!D17</f>
+        <f>Segments!D19</f>
         <v/>
       </c>
     </row>
@@ -4928,7 +5038,7 @@
         </is>
       </c>
       <c r="C6" s="30">
-        <f>Assumptions!$C$36</f>
+        <f>Assumptions!$C$37</f>
         <v/>
       </c>
     </row>
@@ -4950,7 +5060,7 @@
         </is>
       </c>
       <c r="C8" s="32">
-        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$53+Assumptions!$C$54-Assumptions!$C$55)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$54+Assumptions!$C$55-Assumptions!$C$56)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -4961,11 +5071,11 @@
         </is>
       </c>
       <c r="C9" s="15">
-        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$53+Assumptions!$C$54-Assumptions!$C$55)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$54+Assumptions!$C$55-Assumptions!$C$56)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$46</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$53+Assumptions!$C$54-Assumptions!$C$55)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$54+Assumptions!$C$55-Assumptions!$C$56)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -4989,7 +5099,7 @@
         </is>
       </c>
       <c r="C12" s="33">
-        <f>Segments!E18</f>
+        <f>Segments!E20</f>
         <v/>
       </c>
     </row>
@@ -5000,7 +5110,7 @@
         </is>
       </c>
       <c r="C13" s="14">
-        <f>Segments!C12</f>
+        <f>Segments!C13</f>
         <v/>
       </c>
     </row>
@@ -5022,7 +5132,7 @@
         </is>
       </c>
       <c r="C15" s="15">
-        <f>((C12*C13-Assumptions!$C$29*C13)-C14)*(1-Assumptions!$C$14)*(1-0.004060669885351275)/Assumptions!$C$6</f>
+        <f>((C12*C13-Assumptions!$C$29*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5033,7 +5143,7 @@
         </is>
       </c>
       <c r="C16" s="32">
-        <f>(Assumptions!$C$37*C15)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>(Assumptions!$C$38*C15)*DCF!$C$50-Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -5044,11 +5154,11 @@
         </is>
       </c>
       <c r="C17" s="15">
-        <f>(10*C15)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>(10*C15)*DCF!$C$50-Assumptions!$C$46</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>(16*C15)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>(16*C15)*DCF!$C$50-Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -5072,7 +5182,7 @@
         </is>
       </c>
       <c r="C20" s="15">
-        <f>Assumptions!$C$52/Assumptions!$C$6</f>
+        <f>Assumptions!$C$53/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5083,7 +5193,7 @@
         </is>
       </c>
       <c r="C21" s="34">
-        <f>(Assumptions!$C$38-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)</f>
+        <f>(Assumptions!$C$39-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)</f>
         <v/>
       </c>
     </row>
@@ -5094,7 +5204,7 @@
         </is>
       </c>
       <c r="C22" s="32">
-        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -5105,16 +5215,18 @@
         </is>
       </c>
       <c r="C23" s="15">
-        <f>(((Assumptions!$C$38)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>(((Assumptions!$C$39)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$46</f>
         <v/>
       </c>
       <c r="D23" s="15">
-        <f>(((Assumptions!$C$38)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>(((Assumptions!$C$39)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5122,7 +5234,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5178,7 +5290,7 @@
           <t>Normalised risk-free rate rf*</t>
         </is>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="28">
         <f>Assumptions!$C$9-Assumptions!$C$10</f>
         <v/>
       </c>
@@ -5189,7 +5301,7 @@
           <t>Cost of equity Ke</t>
         </is>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="28">
         <f>C5+Assumptions!$C$12*Assumptions!$C$11</f>
         <v/>
       </c>
@@ -5200,7 +5312,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="28">
         <f>Assumptions!$C$13*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -5211,7 +5323,7 @@
           <t>Market capitalisation</t>
         </is>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <f>Assumptions!$C$5*Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5222,7 +5334,7 @@
           <t>Net-debt weight</t>
         </is>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="28">
         <f>Assumptions!$C$7/(Assumptions!$C$7+C8)</f>
         <v/>
       </c>
@@ -5244,7 +5356,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="28">
         <f>Assumptions!$C$16+Assumptions!$C$18*Assumptions!$C$17</f>
         <v/>
       </c>
@@ -5255,7 +5367,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="28">
         <f>Assumptions!$C$19*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -5291,27 +5403,28 @@
           <t>SAR mn</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
@@ -5350,23 +5463,23 @@
           <t>Forward WACC</t>
         </is>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="28">
         <f>C10-(C10-C13)*C17</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="28">
         <f>C10-(C10-C13)*D17</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="28">
         <f>C10-(C10-C13)*E17</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <f>C10-(C10-C13)*F17</f>
         <v/>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <f>C10-(C10-C13)*G17</f>
         <v/>
       </c>
@@ -5405,23 +5518,23 @@
         </is>
       </c>
       <c r="C20" s="14">
-        <f>Segments!C16</f>
+        <f>Segments!C18</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f>Segments!D16</f>
+        <f>Segments!D18</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>Segments!E16</f>
+        <f>Segments!E18</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>Segments!F16</f>
+        <f>Segments!F18</f>
         <v/>
       </c>
       <c r="G20" s="14">
-        <f>Segments!G16</f>
+        <f>Segments!G18</f>
         <v/>
       </c>
     </row>
@@ -5431,23 +5544,23 @@
           <t>NOPAT = EBIT x (1 - tax)</t>
         </is>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>C20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>D20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>E20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f>F20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f>G20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -5459,23 +5572,23 @@
         </is>
       </c>
       <c r="C22" s="14">
-        <f>Segments!C15</f>
+        <f>Segments!C17</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>Segments!D15</f>
+        <f>Segments!D17</f>
         <v/>
       </c>
       <c r="E22" s="14">
-        <f>Segments!E15</f>
+        <f>Segments!E17</f>
         <v/>
       </c>
       <c r="F22" s="14">
-        <f>Segments!F15</f>
+        <f>Segments!F17</f>
         <v/>
       </c>
       <c r="G22" s="14">
-        <f>Segments!G15</f>
+        <f>Segments!G17</f>
         <v/>
       </c>
     </row>
@@ -5486,23 +5599,23 @@
         </is>
       </c>
       <c r="C23" s="14">
-        <f>Segments!C12</f>
+        <f>Segments!C13</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>Segments!D12</f>
+        <f>Segments!D13</f>
         <v/>
       </c>
       <c r="E23" s="14">
-        <f>Segments!E12</f>
+        <f>Segments!E13</f>
         <v/>
       </c>
       <c r="F23" s="14">
-        <f>Segments!F12</f>
+        <f>Segments!F13</f>
         <v/>
       </c>
       <c r="G23" s="14">
-        <f>Segments!G12</f>
+        <f>Segments!G13</f>
         <v/>
       </c>
     </row>
@@ -5512,23 +5625,23 @@
           <t>- Capital expenditure</t>
         </is>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="29">
         <f>Assumptions!C$30*C23</f>
         <v/>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="29">
         <f>Assumptions!D$30*D23</f>
         <v/>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="29">
         <f>Assumptions!E$30*E23</f>
         <v/>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="29">
         <f>Assumptions!F$30*F23</f>
         <v/>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="29">
         <f>Assumptions!G$30*G23</f>
         <v/>
       </c>
@@ -5539,23 +5652,23 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="29">
         <f>Assumptions!$C$31*C23</f>
         <v/>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="29">
         <f>Assumptions!$C$31*D23</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="29">
         <f>Assumptions!$C$31*E23</f>
         <v/>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="29">
         <f>Assumptions!$C$31*F23</f>
         <v/>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="29">
         <f>Assumptions!$C$31*G23</f>
         <v/>
       </c>
@@ -5566,23 +5679,23 @@
           <t>- Change in working capital</t>
         </is>
       </c>
-      <c r="C26" s="28">
-        <f>C25-Assumptions!$C$49</f>
-        <v/>
-      </c>
-      <c r="D26" s="28">
+      <c r="C26" s="29">
+        <f>C25-Assumptions!$C$50</f>
+        <v/>
+      </c>
+      <c r="D26" s="29">
         <f>D25-C25</f>
         <v/>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="29">
         <f>E25-D25</f>
         <v/>
       </c>
-      <c r="F26" s="28">
+      <c r="F26" s="29">
         <f>F25-E25</f>
         <v/>
       </c>
-      <c r="G26" s="28">
+      <c r="G26" s="29">
         <f>G25-F25</f>
         <v/>
       </c>
@@ -5620,23 +5733,23 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="29">
         <f>C27*C19</f>
         <v/>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="29">
         <f>D27*D19</f>
         <v/>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="29">
         <f>E27*E19</f>
         <v/>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="29">
         <f>F27*F19</f>
         <v/>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="29">
         <f>G27*G19</f>
         <v/>
       </c>
@@ -5661,23 +5774,23 @@
           <t>PP&amp;E roll-forward</t>
         </is>
       </c>
-      <c r="C31" s="28">
-        <f>Assumptions!$C$50+C24-C22</f>
-        <v/>
-      </c>
-      <c r="D31" s="28">
+      <c r="C31" s="29">
+        <f>Assumptions!$C$51+C24-C22</f>
+        <v/>
+      </c>
+      <c r="D31" s="29">
         <f>C31+D24-D22</f>
         <v/>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="29">
         <f>D31+E24-E22</f>
         <v/>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="29">
         <f>E31+F24-F22</f>
         <v/>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="29">
         <f>F31+G24-G22</f>
         <v/>
       </c>
@@ -5688,23 +5801,23 @@
           <t>Invested capital = NWC + PP&amp;E</t>
         </is>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="29">
         <f>C25+C31</f>
         <v/>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="29">
         <f>D25+D31</f>
         <v/>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="29">
         <f>E25+E31</f>
         <v/>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="29">
         <f>F25+F31</f>
         <v/>
       </c>
-      <c r="G32" s="28">
+      <c r="G32" s="29">
         <f>G25+G31</f>
         <v/>
       </c>
@@ -5715,23 +5828,23 @@
           <t>ROIC = NOPAT / invested capital</t>
         </is>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="28">
         <f>C21/C32</f>
         <v/>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="28">
         <f>D21/D32</f>
         <v/>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="28">
         <f>E21/E32</f>
         <v/>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="28">
         <f>F21/F32</f>
         <v/>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="28">
         <f>G21/G32</f>
         <v/>
       </c>
@@ -5742,7 +5855,7 @@
           <t>PV of explicit FCFF (5 years)</t>
         </is>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="29">
         <f>SUM(C28:G28)</f>
         <v/>
       </c>
@@ -5753,7 +5866,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="28">
         <f>G21*(1+Assumptions!$C$21)/G32</f>
         <v/>
       </c>
@@ -5764,7 +5877,7 @@
           <t>Terminal reinvestment rate = g / ROIC</t>
         </is>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="28">
         <f>Assumptions!$C$21/C36</f>
         <v/>
       </c>
@@ -5775,7 +5888,7 @@
           <t>Terminal NOPAT (next year)</t>
         </is>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="29">
         <f>G21*(1+Assumptions!$C$21)</f>
         <v/>
       </c>
@@ -5786,7 +5899,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="29">
         <f>C38*(1-C37)/(C13-Assumptions!$C$21)</f>
         <v/>
       </c>
@@ -5797,7 +5910,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="29">
         <f>C39*G19</f>
         <v/>
       </c>
@@ -5844,7 +5957,7 @@
           <t>Less: net financial debt</t>
         </is>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="29">
         <f>-Assumptions!$C$7</f>
         <v/>
       </c>
@@ -5855,8 +5968,8 @@
           <t>Add: associates + non-operating assets</t>
         </is>
       </c>
-      <c r="C46" s="28">
-        <f>Assumptions!$C$53+Assumptions!$C$54</f>
+      <c r="C46" s="29">
+        <f>Assumptions!$C$54+Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -5866,8 +5979,8 @@
           <t>Less: non-controlling interests</t>
         </is>
       </c>
-      <c r="C47" s="28">
-        <f>-Assumptions!$C$55</f>
+      <c r="C47" s="29">
+        <f>-Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
@@ -5900,7 +6013,7 @@
         </is>
       </c>
       <c r="C50" s="36">
-        <f>(1+C6)^(Assumptions!$C$44/365)</f>
+        <f>(1+C6)^(Assumptions!$C$45/365)</f>
         <v/>
       </c>
     </row>
@@ -5911,7 +6024,7 @@
         </is>
       </c>
       <c r="C51" s="32">
-        <f>C49*C50-Assumptions!$C$45</f>
+        <f>C49*C50-Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -5947,7 +6060,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>88.81423921232683</v>
+        <v>81.16296281694119</v>
       </c>
     </row>
     <row r="56">
@@ -5968,11 +6081,13 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>236.7719302390979</v>
+        <v>199.8384804018629</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5980,7 +6095,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6026,42 +6141,43 @@
           <t>SAR mn</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -6083,23 +6199,23 @@
         <v>10673.604262</v>
       </c>
       <c r="F5" s="14">
-        <f>Segments!C12</f>
+        <f>Segments!C13</f>
         <v/>
       </c>
       <c r="G5" s="14">
-        <f>Segments!D12</f>
+        <f>Segments!D13</f>
         <v/>
       </c>
       <c r="H5" s="14">
-        <f>Segments!E12</f>
+        <f>Segments!E13</f>
         <v/>
       </c>
       <c r="I5" s="14">
-        <f>Segments!F12</f>
+        <f>Segments!F13</f>
         <v/>
       </c>
       <c r="J5" s="14">
-        <f>Segments!G12</f>
+        <f>Segments!G13</f>
         <v/>
       </c>
     </row>
@@ -6119,23 +6235,23 @@
         <v>1733.329855</v>
       </c>
       <c r="F6" s="14">
-        <f>Segments!C13</f>
+        <f>Segments!C12</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>Segments!D13</f>
+        <f>Segments!D12</f>
         <v/>
       </c>
       <c r="H6" s="14">
-        <f>Segments!E13</f>
+        <f>Segments!E12</f>
         <v/>
       </c>
       <c r="I6" s="14">
-        <f>Segments!F13</f>
+        <f>Segments!F12</f>
         <v/>
       </c>
       <c r="J6" s="14">
-        <f>Segments!G13</f>
+        <f>Segments!G12</f>
         <v/>
       </c>
     </row>
@@ -6145,35 +6261,35 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="28">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="28">
         <f>D6/D5</f>
         <v/>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="28">
         <f>E6/E5</f>
         <v/>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="28">
         <f>F6/F5</f>
         <v/>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="28">
         <f>G6/G5</f>
         <v/>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="28">
         <f>H6/H5</f>
         <v/>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="28">
         <f>I6/I5</f>
         <v/>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="28">
         <f>J6/J5</f>
         <v/>
       </c>
@@ -6184,36 +6300,36 @@
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <f>C6-C11</f>
         <v/>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f>D6-D11</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>E6-E11</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>Segments!C14</f>
+        <f>Segments!C16</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>Segments!D14</f>
+        <f>Segments!D16</f>
         <v/>
       </c>
       <c r="H8" s="14">
-        <f>Segments!E14</f>
+        <f>Segments!E16</f>
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>Segments!F14</f>
+        <f>Segments!F16</f>
         <v/>
       </c>
       <c r="J8" s="14">
-        <f>Segments!G14</f>
+        <f>Segments!G16</f>
         <v/>
       </c>
     </row>
@@ -6223,36 +6339,36 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <f>C11+C10</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <f>D11+D10</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <f>E11+E10</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>Segments!C17</f>
+        <f>Segments!C19</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>Segments!D17</f>
+        <f>Segments!D19</f>
         <v/>
       </c>
       <c r="H9" s="14">
-        <f>Segments!E17</f>
+        <f>Segments!E19</f>
         <v/>
       </c>
       <c r="I9" s="14">
-        <f>Segments!F17</f>
+        <f>Segments!F19</f>
         <v/>
       </c>
       <c r="J9" s="14">
-        <f>Segments!G17</f>
+        <f>Segments!G19</f>
         <v/>
       </c>
     </row>
@@ -6263,7 +6379,7 @@
         </is>
       </c>
       <c r="C10" s="19" t="n">
-        <v>68.643861</v>
+        <v>66.428122</v>
       </c>
       <c r="D10" s="19" t="n">
         <v>68.643861</v>
@@ -6272,23 +6388,23 @@
         <v>85.39563699999999</v>
       </c>
       <c r="F10" s="14">
-        <f>Segments!C15</f>
+        <f>Segments!C17</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Segments!D15</f>
+        <f>Segments!D17</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Segments!E15</f>
+        <f>Segments!E17</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Segments!F15</f>
+        <f>Segments!F17</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Segments!G15</f>
+        <f>Segments!G17</f>
         <v/>
       </c>
     </row>
@@ -6308,23 +6424,23 @@
         <v>1266.636844</v>
       </c>
       <c r="F11" s="14">
-        <f>Segments!C16</f>
+        <f>Segments!C18</f>
         <v/>
       </c>
       <c r="G11" s="14">
-        <f>Segments!D16</f>
+        <f>Segments!D18</f>
         <v/>
       </c>
       <c r="H11" s="14">
-        <f>Segments!E16</f>
+        <f>Segments!E18</f>
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>Segments!F16</f>
+        <f>Segments!F18</f>
         <v/>
       </c>
       <c r="J11" s="14">
-        <f>Segments!G16</f>
+        <f>Segments!G18</f>
         <v/>
       </c>
     </row>
@@ -6370,35 +6486,35 @@
           <t>Profit before zakat</t>
         </is>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <f>D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="29">
         <f>F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="29">
         <f>G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="29">
         <f>H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="29">
         <f>I11+I12</f>
         <v/>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="29">
         <f>J11+J12</f>
         <v/>
       </c>
@@ -6418,23 +6534,23 @@
       <c r="E14" s="19" t="n">
         <v>-107.681788</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="29">
         <f>-F13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="29">
         <f>-G13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="29">
         <f>-H13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="29">
         <f>-I13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="29">
         <f>-J13*Assumptions!$C$14</f>
         <v/>
       </c>
@@ -6454,23 +6570,23 @@
       <c r="E15" s="19" t="n">
         <v>1084.801061</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="29">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="29">
         <f>I13+I14</f>
         <v/>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="29">
         <f>J13+J14</f>
         <v/>
       </c>
@@ -6506,6 +6622,8 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
+++ b/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
@@ -1012,23 +1012,23 @@
         <v>621.216217</v>
       </c>
       <c r="F10" s="14">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
     </row>
@@ -1206,23 +1206,23 @@
         </is>
       </c>
       <c r="C18" s="29">
-        <f>Assumptions!$C$52-C17</f>
+        <f>Assumptions!$C$60-C17</f>
         <v/>
       </c>
       <c r="D18" s="29">
-        <f>Assumptions!$C$52-D17</f>
+        <f>Assumptions!$C$60-D17</f>
         <v/>
       </c>
       <c r="E18" s="29">
-        <f>Assumptions!$C$52-E17</f>
+        <f>Assumptions!$C$60-E17</f>
         <v/>
       </c>
       <c r="F18" s="29">
-        <f>Assumptions!$C$52-F17</f>
+        <f>Assumptions!$C$60-F17</f>
         <v/>
       </c>
       <c r="G18" s="29">
-        <f>Assumptions!$C$52-G17</f>
+        <f>Assumptions!$C$60-G17</f>
         <v/>
       </c>
     </row>
@@ -1233,23 +1233,23 @@
         </is>
       </c>
       <c r="C19" s="29">
-        <f>Assumptions!C$32*Assumptions!$C$52-Assumptions!$C$34*MAX(C18,0)</f>
+        <f>Assumptions!C$38*Assumptions!$C$60-Assumptions!$C$40*MAX(C18,0)</f>
         <v/>
       </c>
       <c r="D19" s="29">
-        <f>Assumptions!D$32*Assumptions!$C$52-Assumptions!$C$34*MAX(D18,0)</f>
+        <f>Assumptions!D$38*Assumptions!$C$60-Assumptions!$C$40*MAX(D18,0)</f>
         <v/>
       </c>
       <c r="E19" s="29">
-        <f>Assumptions!E$32*Assumptions!$C$52-Assumptions!$C$34*MAX(E18,0)</f>
+        <f>Assumptions!E$38*Assumptions!$C$60-Assumptions!$C$40*MAX(E18,0)</f>
         <v/>
       </c>
       <c r="F19" s="29">
-        <f>Assumptions!F$32*Assumptions!$C$52-Assumptions!$C$34*MAX(F18,0)</f>
+        <f>Assumptions!F$38*Assumptions!$C$60-Assumptions!$C$40*MAX(F18,0)</f>
         <v/>
       </c>
       <c r="G19" s="29">
-        <f>Assumptions!G$32*Assumptions!$C$52-Assumptions!$C$34*MAX(G18,0)</f>
+        <f>Assumptions!G$38*Assumptions!$C$60-Assumptions!$C$40*MAX(G18,0)</f>
         <v/>
       </c>
     </row>
@@ -1314,23 +1314,23 @@
         </is>
       </c>
       <c r="C22" s="29">
-        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)</f>
+        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
         <v/>
       </c>
       <c r="D22" s="29">
-        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)</f>
+        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
         <v/>
       </c>
       <c r="E22" s="29">
-        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)</f>
+        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
         <v/>
       </c>
       <c r="F22" s="29">
-        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)</f>
+        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
         <v/>
       </c>
       <c r="G22" s="29">
-        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)</f>
+        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
         </is>
       </c>
       <c r="C23" s="29">
-        <f>Assumptions!$C$33*C22</f>
+        <f>Assumptions!$C$39*C22</f>
         <v/>
       </c>
       <c r="D23" s="29">
-        <f>Assumptions!$C$33*D22</f>
+        <f>Assumptions!$C$39*D22</f>
         <v/>
       </c>
       <c r="E23" s="29">
-        <f>Assumptions!$C$33*E22</f>
+        <f>Assumptions!$C$39*E22</f>
         <v/>
       </c>
       <c r="F23" s="29">
-        <f>Assumptions!$C$33*F22</f>
+        <f>Assumptions!$C$39*F22</f>
         <v/>
       </c>
       <c r="G23" s="29">
-        <f>Assumptions!$C$33*G22</f>
+        <f>Assumptions!$C$39*G22</f>
         <v/>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="C25" s="29">
-        <f>Assumptions!$C$53+C22-C23</f>
+        <f>Assumptions!$C$61+C22-C23</f>
         <v/>
       </c>
       <c r="D25" s="29">
@@ -1798,23 +1798,23 @@
         </is>
       </c>
       <c r="C6" s="14">
-        <f>Segments!C19</f>
+        <f>Segments!C32</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>Segments!D19</f>
+        <f>Segments!D32</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>Segments!E19</f>
+        <f>Segments!E32</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>Segments!F19</f>
+        <f>Segments!F32</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>Segments!G19</f>
+        <f>Segments!G32</f>
         <v/>
       </c>
     </row>
@@ -2186,16 +2186,16 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>142.7431012135075</v>
+        <v>141.7056057772044</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>164.9510103161226</v>
+        <v>163.715865885987</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>199.7503161286955</v>
+        <v>198.2042805447696</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>262.3549098579414</v>
+        <v>260.2479130974581</v>
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
@@ -2210,19 +2210,19 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>121.3446604174545</v>
+        <v>120.4623841952295</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>135.7369156695441</v>
+        <v>134.7210292900971</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>156.4277477374078</v>
+        <v>155.2188360125738</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>188.8424820913314</v>
+        <v>187.3299521235833</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>247.1468366422771</v>
+        <v>245.0864687133326</v>
       </c>
     </row>
     <row r="8">
@@ -2232,19 +2232,19 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>105.6652693207071</v>
+        <v>104.8967296610403</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>115.5320651320001</v>
+        <v>114.6678051971448</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>128.9001658845238</v>
+        <v>127.905424577565</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>148.1126917464052</v>
+        <v>146.9294453787323</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>178.2037812750351</v>
+        <v>176.7240270270523</v>
       </c>
     </row>
     <row r="9">
@@ -2254,19 +2254,19 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>93.68221417408712</v>
+        <v>93.00059958544631</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>100.7244384888253</v>
+        <v>99.97128853350969</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>109.8583452566114</v>
+        <v>109.0117190503424</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>122.2284156773896</v>
+        <v>121.2543672012037</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>140.0003338175182</v>
+        <v>138.8421999218402</v>
       </c>
     </row>
     <row r="10">
@@ -2276,19 +2276,19 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>84.22599667245792</v>
+        <v>83.61297829887353</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>89.40522709517732</v>
+        <v>88.73699993247544</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>95.90023795914497</v>
+        <v>95.16215451155131</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>104.3199167292194</v>
+        <v>103.4905512602372</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>115.7173612269487</v>
+        <v>114.7635647327278</v>
       </c>
     </row>
     <row r="12">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>135.1433046442411</v>
+        <v>134.1012811749074</v>
       </c>
     </row>
     <row r="14">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>132.1856078811852</v>
+        <v>131.1659864625187</v>
       </c>
     </row>
     <row r="15">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>128.9001658845238</v>
+        <v>127.905424577565</v>
       </c>
     </row>
     <row r="16">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>126.5148107194236</v>
+        <v>125.5381303609279</v>
       </c>
     </row>
     <row r="17">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>123.7961150741202</v>
+        <v>122.8400164516531</v>
       </c>
     </row>
     <row r="19">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>140.3183760368647</v>
+        <v>139.3236347299058</v>
       </c>
     </row>
     <row r="21">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>134.5979220513759</v>
+        <v>133.6031807444171</v>
       </c>
     </row>
     <row r="22">
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>128.9001658845238</v>
+        <v>127.905424577565</v>
       </c>
     </row>
     <row r="23">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>123.2225770227576</v>
+        <v>122.2278357157988</v>
       </c>
     </row>
     <row r="24">
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>117.5630658397253</v>
+        <v>116.5683245327664</v>
       </c>
     </row>
     <row r="26">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="B27" s="17" t="n">
-        <v>108.8887041368196</v>
+        <v>108.4540646253059</v>
       </c>
     </row>
     <row r="28">
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="B28" s="17" t="n">
-        <v>116.759058320275</v>
+        <v>116.1041350901616</v>
       </c>
     </row>
     <row r="29">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="B29" s="17" t="n">
-        <v>128.9001658845238</v>
+        <v>127.905424577565</v>
       </c>
     </row>
     <row r="30">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="B30" s="17" t="n">
-        <v>132.779647767494</v>
+        <v>131.6763234351193</v>
       </c>
     </row>
     <row r="31">
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="B31" s="17" t="n">
-        <v>140.9332204699758</v>
+        <v>139.6016853407702</v>
       </c>
     </row>
     <row r="33">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>117.7608569731192</v>
+        <v>117.0795645368853</v>
       </c>
     </row>
     <row r="35">
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="B35" s="17" t="n">
-        <v>123.3352376150401</v>
+        <v>122.4970935834225</v>
       </c>
     </row>
     <row r="36">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="B36" s="17" t="n">
-        <v>128.9001658845238</v>
+        <v>127.905424577565</v>
       </c>
     </row>
     <row r="37">
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>134.4563415543554</v>
+        <v>133.3052385180974</v>
       </c>
     </row>
     <row r="38">
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>140.004381215677</v>
+        <v>138.6971354501409</v>
       </c>
     </row>
     <row r="40">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>134.5643347580265</v>
+        <v>133.5580939831738</v>
       </c>
     </row>
     <row r="42">
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>131.7322503212752</v>
+        <v>130.7317592803693</v>
       </c>
     </row>
     <row r="43">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>128.9001658845238</v>
+        <v>127.905424577565</v>
       </c>
     </row>
     <row r="44">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>126.0680814477724</v>
+        <v>125.0790898747605</v>
       </c>
     </row>
     <row r="45">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>123.235997011021</v>
+        <v>122.2527551719562</v>
       </c>
     </row>
   </sheetData>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>Assumptions!$C$53/Assumptions!$C$6</f>
+        <f>Assumptions!$C$61/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C6" s="15">
@@ -2733,23 +2733,23 @@
         <v/>
       </c>
       <c r="C8" s="34">
-        <f>'Balance Sheet'!F13/Segments!C19</f>
+        <f>'Balance Sheet'!F13/Segments!C32</f>
         <v/>
       </c>
       <c r="D8" s="34">
-        <f>'Balance Sheet'!G13/Segments!D19</f>
+        <f>'Balance Sheet'!G13/Segments!D32</f>
         <v/>
       </c>
       <c r="E8" s="34">
-        <f>'Balance Sheet'!H13/Segments!E19</f>
+        <f>'Balance Sheet'!H13/Segments!E32</f>
         <v/>
       </c>
       <c r="F8" s="34">
-        <f>'Balance Sheet'!I13/Segments!F19</f>
+        <f>'Balance Sheet'!I13/Segments!F32</f>
         <v/>
       </c>
       <c r="G8" s="34">
-        <f>'Balance Sheet'!J13/Segments!G19</f>
+        <f>'Balance Sheet'!J13/Segments!G32</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>Assumptions!$C$40</f>
+        <f>Assumptions!$C$46</f>
         <v/>
       </c>
       <c r="F5" s="15">
@@ -3349,7 +3349,7 @@
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>Assumptions!$C$41</f>
+        <f>Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="F6" s="15">
@@ -3380,7 +3380,7 @@
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$48</f>
         <v/>
       </c>
       <c r="F7" s="15">
@@ -3411,7 +3411,7 @@
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>Assumptions!$C$43</f>
+        <f>Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="F8" s="15">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>126.970585075898</v>
+        <v>125.9789008877625</v>
       </c>
     </row>
     <row r="12">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>140.9332204699758</v>
+        <v>139.6016853407702</v>
       </c>
     </row>
     <row r="17">
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>116.759058320275</v>
+        <v>116.1041350901616</v>
       </c>
     </row>
   </sheetData>
@@ -3529,7 +3529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3768,7 +3768,7 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Forecast drivers — ground-up cost stack</t>
+          <t>Forecast drivers — Cables &amp; wires leg (metal converter)</t>
         </is>
       </c>
       <c r="B22" s="11" t="n"/>
@@ -3880,346 +3880,462 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Operating expenses / revenue</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>0.042</v>
-      </c>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Forecast drivers — HV turnkey &amp; Other legs</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation / revenue</t>
+          <t>HV turnkey revenue growth</t>
         </is>
       </c>
       <c r="C29" s="20" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.1</v>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure / revenue</t>
+          <t>HV turnkey segment margin</t>
         </is>
       </c>
       <c r="C30" s="20" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="E30" s="20" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v>0.016</v>
+        <v>0.08378233242821985</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Net working capital / revenue</t>
+          <t>Other segment revenue growth</t>
         </is>
       </c>
       <c r="C31" s="20" t="n">
-        <v>0.28</v>
+        <v>0.08</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Cost-of-debt path</t>
+          <t>Other segment margin</t>
         </is>
       </c>
       <c r="C32" s="20" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="D32" s="20" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="E32" s="20" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="F32" s="20" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="G32" s="20" t="n">
-        <v>0.055</v>
+        <v>0.5786820313464731</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Forecast dividend payout ratio</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="n">
-        <v>0.55</v>
-      </c>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Forecast drivers — group</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Yield on surplus cash</t>
+          <t>Operating expenses / revenue</t>
         </is>
       </c>
       <c r="C34" s="20" t="n">
-        <v>0.04</v>
+        <v>0.043</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G34" s="20" t="n">
+        <v>0.042</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>NCI share of forecast profit</t>
+          <t>Depreciation and amortisation / revenue</t>
         </is>
       </c>
       <c r="C35" s="20" t="n">
-        <v>0.004060669885351275</v>
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="11" t="n"/>
-      <c r="I36" s="11" t="n"/>
-      <c r="J36" s="11" t="n"/>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Capital expenditure / revenue</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G36" s="20" t="n">
+        <v>0.016</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C37" s="22" t="n">
-        <v>9.5</v>
+          <t>Net working capital / revenue</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C38" s="22" t="n">
-        <v>13</v>
+          <t>Cost-of-debt path</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="D38" s="20" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E38" s="20" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="G38" s="20" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
+          <t>Forecast dividend payout ratio</t>
         </is>
       </c>
       <c r="C39" s="20" t="n">
-        <v>0.28</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="n">
-        <v>0.45</v>
+          <t>Yield on surplus cash</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="n">
-        <v>0.2</v>
+          <t>NCI share of forecast profit</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="n">
+        <v>0.004060669885351275</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Weight — book</t>
-        </is>
-      </c>
-      <c r="C43" s="23" t="n">
-        <v>0.15</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>Anchor roll</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="11" t="n"/>
-      <c r="I44" s="11" t="n"/>
-      <c r="J44" s="11" t="n"/>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Days to the anchor</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="n">
-        <v>230</v>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>FY2025 dividend per share paid in window</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="n">
-        <v>2.25</v>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>FY2025 disclosed base (audited)</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="11" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="11" t="n"/>
-      <c r="I47" s="11" t="n"/>
-      <c r="J47" s="11" t="n"/>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>FY2025 metal content / materials (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="n">
-        <v>8486.925676999999</v>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>FY2025 conversion cost (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="n">
-        <v>453.34873</v>
+          <t>Weight — book</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 net working capital (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="n">
-        <v>2933.258925</v>
-      </c>
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Anchor roll</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="11" t="n"/>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="11" t="n"/>
+      <c r="I50" s="11" t="n"/>
+      <c r="J50" s="11" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>FY2025 PP&amp;E (SAR mn)</t>
+          <t>Days to the anchor</t>
         </is>
       </c>
       <c r="C51" s="19" t="n">
-        <v>1491.86312</v>
+        <v>230</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C52" s="19" t="n">
-        <v>621.216217</v>
+          <t>FY2025 dividend per share paid in window</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 equity attributable (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C53" s="19" t="n">
-        <v>3246.136935</v>
-      </c>
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>FY2025 disclosed base (audited)</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="11" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="11" t="n"/>
+      <c r="I53" s="11" t="n"/>
+      <c r="J53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>FY2025 associates carrying value (SAR mn)</t>
+          <t>FY2025 cables metal content (SAR mn)</t>
         </is>
       </c>
       <c r="C54" s="19" t="n">
-        <v>31.851877</v>
+        <v>8486.925676999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>FY2025 non-operating assets (SAR mn)</t>
+          <t>FY2025 cables conversion cost (SAR mn)</t>
         </is>
       </c>
       <c r="C55" s="19" t="n">
-        <v>20.40064</v>
+        <v>229.8024540000006</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
+          <t>FY2025 HV turnkey revenue (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="n">
+        <v>230.839181</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 Other segment revenue (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>28.594413</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 net working capital (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="n">
+        <v>2933.258925</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 PP&amp;E (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="n">
+        <v>1491.86312</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>621.216217</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 equity attributable (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="n">
+        <v>3246.136935</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 associates carrying value (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="n">
+        <v>31.851877</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 non-operating assets (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="n">
+        <v>20.40064</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
           <t>FY2025 NCI carrying value (SAR mn)</t>
         </is>
       </c>
-      <c r="C56" s="19" t="n">
+      <c r="C64" s="19" t="n">
         <v>62.737156</v>
       </c>
     </row>
@@ -4365,10 +4481,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -4381,7 +4497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Segments — ground-up cost-stack build</t>
+          <t>Segments — three legs, built to the group</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4395,7 +4511,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Materials on the metal path; conversion on domestic inflation; gross margin is the OUTPUT</t>
+          <t>Each disclosed Note 40 segment on its own driver; the cable leg is the metal converter; group gross margin is the blended OUTPUT</t>
         </is>
       </c>
     </row>
@@ -4437,528 +4553,807 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Cable volume index (FY2025=100)</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="C5" s="26">
-        <f>B5*(1+Assumptions!C$23)</f>
-        <v/>
-      </c>
-      <c r="D5" s="26">
-        <f>C5*(1+Assumptions!D$23)</f>
-        <v/>
-      </c>
-      <c r="E5" s="26">
-        <f>D5*(1+Assumptions!E$23)</f>
-        <v/>
-      </c>
-      <c r="F5" s="26">
-        <f>E5*(1+Assumptions!F$23)</f>
-        <v/>
-      </c>
-      <c r="G5" s="26">
-        <f>F5*(1+Assumptions!G$23)</f>
-        <v/>
-      </c>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Cables &amp; wires — the metal converter</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Metal content per unit</t>
-        </is>
-      </c>
-      <c r="B6" s="27">
-        <f>Assumptions!$C$48/100.0</f>
-        <v/>
-      </c>
-      <c r="C6" s="27">
-        <f>B6*(1+Assumptions!C$24)</f>
-        <v/>
-      </c>
-      <c r="D6" s="27">
-        <f>C6*(1+Assumptions!D$24)</f>
-        <v/>
-      </c>
-      <c r="E6" s="27">
-        <f>D6*(1+Assumptions!E$24)</f>
-        <v/>
-      </c>
-      <c r="F6" s="27">
-        <f>E6*(1+Assumptions!F$24)</f>
-        <v/>
-      </c>
-      <c r="G6" s="27">
-        <f>F6*(1+Assumptions!G$24)</f>
+          <t>Cable volume index (FY2025=100)</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" s="26">
+        <f>B6*(1+Assumptions!C$23)</f>
+        <v/>
+      </c>
+      <c r="D6" s="26">
+        <f>C6*(1+Assumptions!D$23)</f>
+        <v/>
+      </c>
+      <c r="E6" s="26">
+        <f>D6*(1+Assumptions!E$23)</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
+        <f>E6*(1+Assumptions!F$23)</f>
+        <v/>
+      </c>
+      <c r="G6" s="26">
+        <f>F6*(1+Assumptions!G$23)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Conversion cost per unit</t>
+          <t>Metal content per unit</t>
         </is>
       </c>
       <c r="B7" s="27">
-        <f>Assumptions!$C$49/100.0</f>
+        <f>Assumptions!$C$54/100.0</f>
         <v/>
       </c>
       <c r="C7" s="27">
-        <f>B7*(1+Assumptions!C$25)</f>
+        <f>B7*(1+Assumptions!C$24)</f>
         <v/>
       </c>
       <c r="D7" s="27">
-        <f>C7*(1+Assumptions!D$25)</f>
+        <f>C7*(1+Assumptions!D$24)</f>
         <v/>
       </c>
       <c r="E7" s="27">
-        <f>D7*(1+Assumptions!E$25)</f>
+        <f>D7*(1+Assumptions!E$24)</f>
         <v/>
       </c>
       <c r="F7" s="27">
-        <f>E7*(1+Assumptions!F$25)</f>
+        <f>E7*(1+Assumptions!F$24)</f>
         <v/>
       </c>
       <c r="G7" s="27">
-        <f>F7*(1+Assumptions!G$25)</f>
+        <f>F7*(1+Assumptions!G$24)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Target gross margin (anchor + glide)</t>
-        </is>
-      </c>
-      <c r="C8" s="28">
-        <f>Assumptions!$C$26+Assumptions!C$27</f>
-        <v/>
-      </c>
-      <c r="D8" s="28">
-        <f>Assumptions!$C$26+Assumptions!D$27</f>
-        <v/>
-      </c>
-      <c r="E8" s="28">
-        <f>Assumptions!$C$26+Assumptions!E$27</f>
-        <v/>
-      </c>
-      <c r="F8" s="28">
-        <f>Assumptions!$C$26+Assumptions!F$27</f>
-        <v/>
-      </c>
-      <c r="G8" s="28">
-        <f>Assumptions!$C$26+Assumptions!G$27</f>
+          <t>Conversion cost per unit</t>
+        </is>
+      </c>
+      <c r="B8" s="27">
+        <f>Assumptions!$C$55/100.0</f>
+        <v/>
+      </c>
+      <c r="C8" s="27">
+        <f>B8*(1+Assumptions!C$25)</f>
+        <v/>
+      </c>
+      <c r="D8" s="27">
+        <f>C8*(1+Assumptions!D$25)</f>
+        <v/>
+      </c>
+      <c r="E8" s="27">
+        <f>D8*(1+Assumptions!E$25)</f>
+        <v/>
+      </c>
+      <c r="F8" s="27">
+        <f>E8*(1+Assumptions!F$25)</f>
+        <v/>
+      </c>
+      <c r="G8" s="27">
+        <f>F8*(1+Assumptions!G$25)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Gross profit per unit (conversion spread)</t>
-        </is>
-      </c>
-      <c r="B9" s="27">
-        <f>B12/B5</f>
-        <v/>
-      </c>
-      <c r="C9" s="27">
-        <f>C8/(1-C8)*(C6+C7)</f>
-        <v/>
-      </c>
-      <c r="D9" s="27">
-        <f>D8/(1-D8)*(D6+D7)</f>
-        <v/>
-      </c>
-      <c r="E9" s="27">
-        <f>E8/(1-E8)*(E6+E7)</f>
-        <v/>
-      </c>
-      <c r="F9" s="27">
-        <f>F8/(1-F8)*(F6+F7)</f>
-        <v/>
-      </c>
-      <c r="G9" s="27">
-        <f>G8/(1-G8)*(G6+G7)</f>
+          <t>Target gross margin (anchor + glide)</t>
+        </is>
+      </c>
+      <c r="C9" s="28">
+        <f>Assumptions!$C$26+Assumptions!C$27</f>
+        <v/>
+      </c>
+      <c r="D9" s="28">
+        <f>Assumptions!$C$26+Assumptions!D$27</f>
+        <v/>
+      </c>
+      <c r="E9" s="28">
+        <f>Assumptions!$C$26+Assumptions!E$27</f>
+        <v/>
+      </c>
+      <c r="F9" s="28">
+        <f>Assumptions!$C$26+Assumptions!F$27</f>
+        <v/>
+      </c>
+      <c r="G9" s="28">
+        <f>Assumptions!$C$26+Assumptions!G$27</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Materials (metal leg)</t>
-        </is>
-      </c>
-      <c r="B10" s="29">
-        <f>B5*B6</f>
-        <v/>
-      </c>
-      <c r="C10" s="29">
-        <f>C5*C6</f>
-        <v/>
-      </c>
-      <c r="D10" s="29">
-        <f>D5*D6</f>
-        <v/>
-      </c>
-      <c r="E10" s="29">
-        <f>E5*E6</f>
-        <v/>
-      </c>
-      <c r="F10" s="29">
-        <f>F5*F6</f>
-        <v/>
-      </c>
-      <c r="G10" s="29">
-        <f>G5*G6</f>
+          <t>Gross profit per unit (conversion spread)</t>
+        </is>
+      </c>
+      <c r="B10" s="27">
+        <f>B13/B6</f>
+        <v/>
+      </c>
+      <c r="C10" s="27">
+        <f>C9/(1-C9)*(C7+C8)</f>
+        <v/>
+      </c>
+      <c r="D10" s="27">
+        <f>D9/(1-D9)*(D7+D8)</f>
+        <v/>
+      </c>
+      <c r="E10" s="27">
+        <f>E9/(1-E9)*(E7+E8)</f>
+        <v/>
+      </c>
+      <c r="F10" s="27">
+        <f>F9/(1-F9)*(F7+F8)</f>
+        <v/>
+      </c>
+      <c r="G10" s="27">
+        <f>G9/(1-G9)*(G7+G8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Conversion cost</t>
+          <t>Materials (metal leg)</t>
         </is>
       </c>
       <c r="B11" s="29">
-        <f>B5*B7</f>
+        <f>B6*B7</f>
         <v/>
       </c>
       <c r="C11" s="29">
-        <f>C5*C7</f>
+        <f>C6*C7</f>
         <v/>
       </c>
       <c r="D11" s="29">
-        <f>D5*D7</f>
+        <f>D6*D7</f>
         <v/>
       </c>
       <c r="E11" s="29">
-        <f>E5*E7</f>
+        <f>E6*E7</f>
         <v/>
       </c>
       <c r="F11" s="29">
-        <f>F5*F7</f>
+        <f>F6*F7</f>
         <v/>
       </c>
       <c r="G11" s="29">
-        <f>G5*G7</f>
+        <f>G6*G7</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Gross profit = volume x spread</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n">
-        <v>1733.329855</v>
+          <t>Conversion cost</t>
+        </is>
+      </c>
+      <c r="B12" s="29">
+        <f>B6*B8</f>
+        <v/>
       </c>
       <c r="C12" s="29">
-        <f>C5*C9</f>
+        <f>C6*C8</f>
         <v/>
       </c>
       <c r="D12" s="29">
-        <f>D5*D9</f>
+        <f>D6*D8</f>
         <v/>
       </c>
       <c r="E12" s="29">
-        <f>E5*E9</f>
+        <f>E6*E8</f>
         <v/>
       </c>
       <c r="F12" s="29">
-        <f>F5*F9</f>
+        <f>F6*F8</f>
         <v/>
       </c>
       <c r="G12" s="29">
-        <f>G5*G9</f>
+        <f>G6*G8</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Revenue = materials + conversion + gross profit</t>
-        </is>
-      </c>
-      <c r="B13" s="29">
-        <f>B10+B11+B12</f>
-        <v/>
+          <t>Gross profit = volume x spread</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>1697.442537000001</v>
       </c>
       <c r="C13" s="29">
-        <f>C10+C11+C12</f>
+        <f>C6*C10</f>
         <v/>
       </c>
       <c r="D13" s="29">
-        <f>D10+D11+D12</f>
+        <f>D6*D10</f>
         <v/>
       </c>
       <c r="E13" s="29">
-        <f>E10+E11+E12</f>
+        <f>E6*E10</f>
         <v/>
       </c>
       <c r="F13" s="29">
-        <f>F10+F11+F12</f>
+        <f>F6*F10</f>
         <v/>
       </c>
       <c r="G13" s="29">
-        <f>G10+G11+G12</f>
+        <f>G6*G10</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Cost of revenue</t>
+          <t>Cables revenue = materials + conversion + gross profit</t>
         </is>
       </c>
       <c r="B14" s="29">
-        <f>B10+B11</f>
+        <f>B11+B12+B13</f>
         <v/>
       </c>
       <c r="C14" s="29">
-        <f>C10+C11</f>
+        <f>C11+C12+C13</f>
         <v/>
       </c>
       <c r="D14" s="29">
-        <f>D10+D11</f>
+        <f>D11+D12+D13</f>
         <v/>
       </c>
       <c r="E14" s="29">
-        <f>E10+E11</f>
+        <f>E11+E12+E13</f>
         <v/>
       </c>
       <c r="F14" s="29">
-        <f>F10+F11</f>
+        <f>F11+F12+F13</f>
         <v/>
       </c>
       <c r="G14" s="29">
-        <f>G10+G11</f>
+        <f>G11+G12+G13</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Gross margin (OUTPUT = gross profit / revenue)</t>
+          <t>Cables gross margin (OUTPUT)</t>
         </is>
       </c>
       <c r="B15" s="28">
-        <f>B12/B13</f>
+        <f>B13/B14</f>
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>C12/C13</f>
+        <f>C13/C14</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>D12/D13</f>
+        <f>D13/D14</f>
         <v/>
       </c>
       <c r="E15" s="28">
-        <f>E12/E13</f>
+        <f>E13/E14</f>
         <v/>
       </c>
       <c r="F15" s="28">
-        <f>F12/F13</f>
+        <f>F13/F14</f>
         <v/>
       </c>
       <c r="G15" s="28">
-        <f>G12/G13</f>
+        <f>G13/G14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="C16" s="29">
-        <f>Assumptions!C$28*C13</f>
-        <v/>
-      </c>
-      <c r="D16" s="29">
-        <f>Assumptions!D$28*D13</f>
-        <v/>
-      </c>
-      <c r="E16" s="29">
-        <f>Assumptions!E$28*E13</f>
-        <v/>
-      </c>
-      <c r="F16" s="29">
-        <f>Assumptions!F$28*F13</f>
-        <v/>
-      </c>
-      <c r="G16" s="29">
-        <f>Assumptions!G$28*G13</f>
-        <v/>
-      </c>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>HV turnkey projects — own growth, disclosed margin</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Depreciation &amp; amortisation</t>
-        </is>
+          <t>HV revenue (own growth path)</t>
+        </is>
+      </c>
+      <c r="B17" s="29">
+        <f>Assumptions!$C$56</f>
+        <v/>
       </c>
       <c r="C17" s="29">
-        <f>Assumptions!$C$29*C13</f>
+        <f>B17*(1+Assumptions!C$29)</f>
         <v/>
       </c>
       <c r="D17" s="29">
-        <f>Assumptions!$C$29*D13</f>
+        <f>C17*(1+Assumptions!D$29)</f>
         <v/>
       </c>
       <c r="E17" s="29">
-        <f>Assumptions!$C$29*E13</f>
+        <f>D17*(1+Assumptions!E$29)</f>
         <v/>
       </c>
       <c r="F17" s="29">
-        <f>Assumptions!$C$29*F13</f>
+        <f>E17*(1+Assumptions!F$29)</f>
         <v/>
       </c>
       <c r="G17" s="29">
-        <f>Assumptions!$C$29*G13</f>
+        <f>F17*(1+Assumptions!G$29)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C18" s="29">
-        <f>C12-C16</f>
-        <v/>
-      </c>
-      <c r="D18" s="29">
-        <f>D12-D16</f>
-        <v/>
-      </c>
-      <c r="E18" s="29">
-        <f>E12-E16</f>
-        <v/>
-      </c>
-      <c r="F18" s="29">
-        <f>F12-F16</f>
-        <v/>
-      </c>
-      <c r="G18" s="29">
-        <f>G12-G16</f>
+          <t>HV segment margin</t>
+        </is>
+      </c>
+      <c r="B18" s="28">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="C18" s="28">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="D18" s="28">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="E18" s="28">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="F18" s="28">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="G18" s="28">
+        <f>Assumptions!$C$30</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>EBITDA</t>
-        </is>
+          <t>HV gross profit = revenue x margin</t>
+        </is>
+      </c>
+      <c r="B19" s="29">
+        <f>B17*B18</f>
+        <v/>
       </c>
       <c r="C19" s="29">
-        <f>C18+C17</f>
+        <f>C17*C18</f>
         <v/>
       </c>
       <c r="D19" s="29">
-        <f>D18+D17</f>
+        <f>D17*D18</f>
         <v/>
       </c>
       <c r="E19" s="29">
-        <f>E18+E17</f>
+        <f>E17*E18</f>
         <v/>
       </c>
       <c r="F19" s="29">
-        <f>F18+F17</f>
+        <f>F17*F18</f>
         <v/>
       </c>
       <c r="G19" s="29">
-        <f>G18+G17</f>
+        <f>G17*G18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C20" s="28">
-        <f>C19/C13</f>
-        <v/>
-      </c>
-      <c r="D20" s="28">
-        <f>D19/D13</f>
-        <v/>
-      </c>
-      <c r="E20" s="28">
-        <f>E19/E13</f>
-        <v/>
-      </c>
-      <c r="F20" s="28">
-        <f>F19/F13</f>
-        <v/>
-      </c>
-      <c r="G20" s="28">
-        <f>G19/G13</f>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Other (telephone cables &amp; services) — own growth, disclosed margin</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Other revenue (own growth path)</t>
+        </is>
+      </c>
+      <c r="B21" s="29">
+        <f>Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="C21" s="29">
+        <f>B21*(1+Assumptions!C$31)</f>
+        <v/>
+      </c>
+      <c r="D21" s="29">
+        <f>C21*(1+Assumptions!D$31)</f>
+        <v/>
+      </c>
+      <c r="E21" s="29">
+        <f>D21*(1+Assumptions!E$31)</f>
+        <v/>
+      </c>
+      <c r="F21" s="29">
+        <f>E21*(1+Assumptions!F$31)</f>
+        <v/>
+      </c>
+      <c r="G21" s="29">
+        <f>F21*(1+Assumptions!G$31)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>FY2025 disclosed segment revenue (Note 40)</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="n"/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Other segment margin</t>
+        </is>
+      </c>
+      <c r="B22" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="C22" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="E22" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="F22" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="G22" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Cables and wires</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="n">
-        <v>10414.170668</v>
-      </c>
-      <c r="C23" s="9">
-        <f>B23/B13</f>
+          <t>Other gross profit = revenue x margin</t>
+        </is>
+      </c>
+      <c r="B23" s="29">
+        <f>B21*B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="29">
+        <f>C21*C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>D21*D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="29">
+        <f>E21*E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f>F21*F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f>G21*G22</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>High-voltage cables (turnkey projects)</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n">
-        <v>230.839181</v>
-      </c>
-      <c r="C24" s="9">
-        <f>B24/B13</f>
-        <v/>
-      </c>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Group — the sum of the three legs</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Other (telephone cables &amp; services)</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n">
-        <v>28.594413</v>
-      </c>
-      <c r="C25" s="9">
-        <f>B25/B13</f>
+          <t>Revenue (group)</t>
+        </is>
+      </c>
+      <c r="B25" s="29">
+        <f>B14+B17+B21</f>
+        <v/>
+      </c>
+      <c r="C25" s="29">
+        <f>C14+C17+C21</f>
+        <v/>
+      </c>
+      <c r="D25" s="29">
+        <f>D14+D17+D21</f>
+        <v/>
+      </c>
+      <c r="E25" s="29">
+        <f>E14+E17+E21</f>
+        <v/>
+      </c>
+      <c r="F25" s="29">
+        <f>F14+F17+F21</f>
+        <v/>
+      </c>
+      <c r="G25" s="29">
+        <f>G14+G17+G21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Gross profit (group)</t>
+        </is>
+      </c>
+      <c r="B26" s="29">
+        <f>B13+B19+B23</f>
+        <v/>
+      </c>
+      <c r="C26" s="29">
+        <f>C13+C19+C23</f>
+        <v/>
+      </c>
+      <c r="D26" s="29">
+        <f>D13+D19+D23</f>
+        <v/>
+      </c>
+      <c r="E26" s="29">
+        <f>E13+E19+E23</f>
+        <v/>
+      </c>
+      <c r="F26" s="29">
+        <f>F13+F19+F23</f>
+        <v/>
+      </c>
+      <c r="G26" s="29">
+        <f>G13+G19+G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Cost of revenue (group)</t>
+        </is>
+      </c>
+      <c r="B27" s="29">
+        <f>B25-B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="29">
+        <f>C25-C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="29">
+        <f>D25-D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="29">
+        <f>E25-E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="29">
+        <f>F25-F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="29">
+        <f>G25-G26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Gross margin (OUTPUT = group gross profit / group revenue)</t>
+        </is>
+      </c>
+      <c r="B28" s="28">
+        <f>B26/B25</f>
+        <v/>
+      </c>
+      <c r="C28" s="28">
+        <f>C26/C25</f>
+        <v/>
+      </c>
+      <c r="D28" s="28">
+        <f>D26/D25</f>
+        <v/>
+      </c>
+      <c r="E28" s="28">
+        <f>E26/E25</f>
+        <v/>
+      </c>
+      <c r="F28" s="28">
+        <f>F26/F25</f>
+        <v/>
+      </c>
+      <c r="G28" s="28">
+        <f>G26/G25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C29" s="29">
+        <f>Assumptions!C$34*C25</f>
+        <v/>
+      </c>
+      <c r="D29" s="29">
+        <f>Assumptions!D$34*D25</f>
+        <v/>
+      </c>
+      <c r="E29" s="29">
+        <f>Assumptions!E$34*E25</f>
+        <v/>
+      </c>
+      <c r="F29" s="29">
+        <f>Assumptions!F$34*F25</f>
+        <v/>
+      </c>
+      <c r="G29" s="29">
+        <f>Assumptions!G$34*G25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; amortisation</t>
+        </is>
+      </c>
+      <c r="C30" s="29">
+        <f>Assumptions!$C$35*C25</f>
+        <v/>
+      </c>
+      <c r="D30" s="29">
+        <f>Assumptions!$C$35*D25</f>
+        <v/>
+      </c>
+      <c r="E30" s="29">
+        <f>Assumptions!$C$35*E25</f>
+        <v/>
+      </c>
+      <c r="F30" s="29">
+        <f>Assumptions!$C$35*F25</f>
+        <v/>
+      </c>
+      <c r="G30" s="29">
+        <f>Assumptions!$C$35*G25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C31" s="29">
+        <f>C26-C29</f>
+        <v/>
+      </c>
+      <c r="D31" s="29">
+        <f>D26-D29</f>
+        <v/>
+      </c>
+      <c r="E31" s="29">
+        <f>E26-E29</f>
+        <v/>
+      </c>
+      <c r="F31" s="29">
+        <f>F26-F29</f>
+        <v/>
+      </c>
+      <c r="G31" s="29">
+        <f>G26-G29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C32" s="29">
+        <f>C31+C30</f>
+        <v/>
+      </c>
+      <c r="D32" s="29">
+        <f>D31+D30</f>
+        <v/>
+      </c>
+      <c r="E32" s="29">
+        <f>E31+E30</f>
+        <v/>
+      </c>
+      <c r="F32" s="29">
+        <f>F31+F30</f>
+        <v/>
+      </c>
+      <c r="G32" s="29">
+        <f>G31+G30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C33" s="28">
+        <f>C32/C25</f>
+        <v/>
+      </c>
+      <c r="D33" s="28">
+        <f>D32/D25</f>
+        <v/>
+      </c>
+      <c r="E33" s="28">
+        <f>E32/E25</f>
+        <v/>
+      </c>
+      <c r="F33" s="28">
+        <f>F32/F25</f>
+        <v/>
+      </c>
+      <c r="G33" s="28">
+        <f>G32/G25</f>
         <v/>
       </c>
     </row>
@@ -5027,7 +5422,7 @@
         </is>
       </c>
       <c r="C5" s="14">
-        <f>Segments!D19</f>
+        <f>Segments!D32</f>
         <v/>
       </c>
     </row>
@@ -5038,7 +5433,7 @@
         </is>
       </c>
       <c r="C6" s="30">
-        <f>Assumptions!$C$37</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
@@ -5060,7 +5455,7 @@
         </is>
       </c>
       <c r="C8" s="32">
-        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$54+Assumptions!$C$55-Assumptions!$C$56)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$46</f>
+        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5071,11 +5466,11 @@
         </is>
       </c>
       <c r="C9" s="15">
-        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$54+Assumptions!$C$55-Assumptions!$C$56)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$46</f>
+        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$54+Assumptions!$C$55-Assumptions!$C$56)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$46</f>
+        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5099,7 +5494,7 @@
         </is>
       </c>
       <c r="C12" s="33">
-        <f>Segments!E20</f>
+        <f>Segments!E33</f>
         <v/>
       </c>
     </row>
@@ -5110,7 +5505,7 @@
         </is>
       </c>
       <c r="C13" s="14">
-        <f>Segments!C13</f>
+        <f>Segments!C25</f>
         <v/>
       </c>
     </row>
@@ -5132,7 +5527,7 @@
         </is>
       </c>
       <c r="C15" s="15">
-        <f>((C12*C13-Assumptions!$C$29*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$35)/Assumptions!$C$6</f>
+        <f>((C12*C13-Assumptions!$C$35*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5143,7 +5538,7 @@
         </is>
       </c>
       <c r="C16" s="32">
-        <f>(Assumptions!$C$38*C15)*DCF!$C$50-Assumptions!$C$46</f>
+        <f>(Assumptions!$C$44*C15)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5154,11 +5549,11 @@
         </is>
       </c>
       <c r="C17" s="15">
-        <f>(10*C15)*DCF!$C$50-Assumptions!$C$46</f>
+        <f>(10*C15)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>(16*C15)*DCF!$C$50-Assumptions!$C$46</f>
+        <f>(16*C15)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5182,7 +5577,7 @@
         </is>
       </c>
       <c r="C20" s="15">
-        <f>Assumptions!$C$53/Assumptions!$C$6</f>
+        <f>Assumptions!$C$61/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5193,7 +5588,7 @@
         </is>
       </c>
       <c r="C21" s="34">
-        <f>(Assumptions!$C$39-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)</f>
+        <f>(Assumptions!$C$45-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)</f>
         <v/>
       </c>
     </row>
@@ -5204,7 +5599,7 @@
         </is>
       </c>
       <c r="C22" s="32">
-        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$46</f>
+        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5215,11 +5610,11 @@
         </is>
       </c>
       <c r="C23" s="15">
-        <f>(((Assumptions!$C$39)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$46</f>
+        <f>(((Assumptions!$C$45)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="D23" s="15">
-        <f>(((Assumptions!$C$39)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$46</f>
+        <f>(((Assumptions!$C$45)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5437,23 +5832,23 @@
         </is>
       </c>
       <c r="C17" s="36">
-        <f>(Assumptions!C$32-Assumptions!C$32)/(Assumptions!C$32-Assumptions!G$32)</f>
+        <f>(Assumptions!C$38-Assumptions!C$38)/(Assumptions!C$38-Assumptions!G$38)</f>
         <v/>
       </c>
       <c r="D17" s="36">
-        <f>(Assumptions!C$32-Assumptions!D$32)/(Assumptions!C$32-Assumptions!G$32)</f>
+        <f>(Assumptions!C$38-Assumptions!D$38)/(Assumptions!C$38-Assumptions!G$38)</f>
         <v/>
       </c>
       <c r="E17" s="36">
-        <f>(Assumptions!C$32-Assumptions!E$32)/(Assumptions!C$32-Assumptions!G$32)</f>
+        <f>(Assumptions!C$38-Assumptions!E$38)/(Assumptions!C$38-Assumptions!G$38)</f>
         <v/>
       </c>
       <c r="F17" s="36">
-        <f>(Assumptions!C$32-Assumptions!F$32)/(Assumptions!C$32-Assumptions!G$32)</f>
+        <f>(Assumptions!C$38-Assumptions!F$38)/(Assumptions!C$38-Assumptions!G$38)</f>
         <v/>
       </c>
       <c r="G17" s="36">
-        <f>(Assumptions!C$32-Assumptions!G$32)/(Assumptions!C$32-Assumptions!G$32)</f>
+        <f>(Assumptions!C$38-Assumptions!G$38)/(Assumptions!C$38-Assumptions!G$38)</f>
         <v/>
       </c>
     </row>
@@ -5518,23 +5913,23 @@
         </is>
       </c>
       <c r="C20" s="14">
-        <f>Segments!C18</f>
+        <f>Segments!C31</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f>Segments!D18</f>
+        <f>Segments!D31</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>Segments!E18</f>
+        <f>Segments!E31</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>Segments!F18</f>
+        <f>Segments!F31</f>
         <v/>
       </c>
       <c r="G20" s="14">
-        <f>Segments!G18</f>
+        <f>Segments!G31</f>
         <v/>
       </c>
     </row>
@@ -5572,23 +5967,23 @@
         </is>
       </c>
       <c r="C22" s="14">
-        <f>Segments!C17</f>
+        <f>Segments!C30</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>Segments!D17</f>
+        <f>Segments!D30</f>
         <v/>
       </c>
       <c r="E22" s="14">
-        <f>Segments!E17</f>
+        <f>Segments!E30</f>
         <v/>
       </c>
       <c r="F22" s="14">
-        <f>Segments!F17</f>
+        <f>Segments!F30</f>
         <v/>
       </c>
       <c r="G22" s="14">
-        <f>Segments!G17</f>
+        <f>Segments!G30</f>
         <v/>
       </c>
     </row>
@@ -5599,23 +5994,23 @@
         </is>
       </c>
       <c r="C23" s="14">
-        <f>Segments!C13</f>
+        <f>Segments!C25</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>Segments!D13</f>
+        <f>Segments!D25</f>
         <v/>
       </c>
       <c r="E23" s="14">
-        <f>Segments!E13</f>
+        <f>Segments!E25</f>
         <v/>
       </c>
       <c r="F23" s="14">
-        <f>Segments!F13</f>
+        <f>Segments!F25</f>
         <v/>
       </c>
       <c r="G23" s="14">
-        <f>Segments!G13</f>
+        <f>Segments!G25</f>
         <v/>
       </c>
     </row>
@@ -5626,23 +6021,23 @@
         </is>
       </c>
       <c r="C24" s="29">
-        <f>Assumptions!C$30*C23</f>
+        <f>Assumptions!C$36*C23</f>
         <v/>
       </c>
       <c r="D24" s="29">
-        <f>Assumptions!D$30*D23</f>
+        <f>Assumptions!D$36*D23</f>
         <v/>
       </c>
       <c r="E24" s="29">
-        <f>Assumptions!E$30*E23</f>
+        <f>Assumptions!E$36*E23</f>
         <v/>
       </c>
       <c r="F24" s="29">
-        <f>Assumptions!F$30*F23</f>
+        <f>Assumptions!F$36*F23</f>
         <v/>
       </c>
       <c r="G24" s="29">
-        <f>Assumptions!G$30*G23</f>
+        <f>Assumptions!G$36*G23</f>
         <v/>
       </c>
     </row>
@@ -5653,23 +6048,23 @@
         </is>
       </c>
       <c r="C25" s="29">
-        <f>Assumptions!$C$31*C23</f>
+        <f>Assumptions!$C$37*C23</f>
         <v/>
       </c>
       <c r="D25" s="29">
-        <f>Assumptions!$C$31*D23</f>
+        <f>Assumptions!$C$37*D23</f>
         <v/>
       </c>
       <c r="E25" s="29">
-        <f>Assumptions!$C$31*E23</f>
+        <f>Assumptions!$C$37*E23</f>
         <v/>
       </c>
       <c r="F25" s="29">
-        <f>Assumptions!$C$31*F23</f>
+        <f>Assumptions!$C$37*F23</f>
         <v/>
       </c>
       <c r="G25" s="29">
-        <f>Assumptions!$C$31*G23</f>
+        <f>Assumptions!$C$37*G23</f>
         <v/>
       </c>
     </row>
@@ -5680,7 +6075,7 @@
         </is>
       </c>
       <c r="C26" s="29">
-        <f>C25-Assumptions!$C$50</f>
+        <f>C25-Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="D26" s="29">
@@ -5775,7 +6170,7 @@
         </is>
       </c>
       <c r="C31" s="29">
-        <f>Assumptions!$C$51+C24-C22</f>
+        <f>Assumptions!$C$59+C24-C22</f>
         <v/>
       </c>
       <c r="D31" s="29">
@@ -5969,7 +6364,7 @@
         </is>
       </c>
       <c r="C46" s="29">
-        <f>Assumptions!$C$54+Assumptions!$C$55</f>
+        <f>Assumptions!$C$62+Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -5980,7 +6375,7 @@
         </is>
       </c>
       <c r="C47" s="29">
-        <f>-Assumptions!$C$56</f>
+        <f>-Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
@@ -6013,7 +6408,7 @@
         </is>
       </c>
       <c r="C50" s="36">
-        <f>(1+C6)^(Assumptions!$C$45/365)</f>
+        <f>(1+C6)^(Assumptions!$C$51/365)</f>
         <v/>
       </c>
     </row>
@@ -6024,7 +6419,7 @@
         </is>
       </c>
       <c r="C51" s="32">
-        <f>C49*C50-Assumptions!$C$46</f>
+        <f>C49*C50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -6060,7 +6455,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>81.16296281694119</v>
+        <v>80.84906676286525</v>
       </c>
     </row>
     <row r="56">
@@ -6081,7 +6476,7 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>199.8384804018629</v>
+        <v>197.7603327814774</v>
       </c>
     </row>
   </sheetData>
@@ -6199,23 +6594,23 @@
         <v>10673.604262</v>
       </c>
       <c r="F5" s="14">
-        <f>Segments!C13</f>
+        <f>Segments!C25</f>
         <v/>
       </c>
       <c r="G5" s="14">
-        <f>Segments!D13</f>
+        <f>Segments!D25</f>
         <v/>
       </c>
       <c r="H5" s="14">
-        <f>Segments!E13</f>
+        <f>Segments!E25</f>
         <v/>
       </c>
       <c r="I5" s="14">
-        <f>Segments!F13</f>
+        <f>Segments!F25</f>
         <v/>
       </c>
       <c r="J5" s="14">
-        <f>Segments!G13</f>
+        <f>Segments!G25</f>
         <v/>
       </c>
     </row>
@@ -6235,23 +6630,23 @@
         <v>1733.329855</v>
       </c>
       <c r="F6" s="14">
-        <f>Segments!C12</f>
+        <f>Segments!C26</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>Segments!D12</f>
+        <f>Segments!D26</f>
         <v/>
       </c>
       <c r="H6" s="14">
-        <f>Segments!E12</f>
+        <f>Segments!E26</f>
         <v/>
       </c>
       <c r="I6" s="14">
-        <f>Segments!F12</f>
+        <f>Segments!F26</f>
         <v/>
       </c>
       <c r="J6" s="14">
-        <f>Segments!G12</f>
+        <f>Segments!G26</f>
         <v/>
       </c>
     </row>
@@ -6313,23 +6708,23 @@
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>Segments!C16</f>
+        <f>Segments!C29</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>Segments!D16</f>
+        <f>Segments!D29</f>
         <v/>
       </c>
       <c r="H8" s="14">
-        <f>Segments!E16</f>
+        <f>Segments!E29</f>
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>Segments!F16</f>
+        <f>Segments!F29</f>
         <v/>
       </c>
       <c r="J8" s="14">
-        <f>Segments!G16</f>
+        <f>Segments!G29</f>
         <v/>
       </c>
     </row>
@@ -6352,23 +6747,23 @@
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>Segments!C19</f>
+        <f>Segments!C32</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>Segments!D19</f>
+        <f>Segments!D32</f>
         <v/>
       </c>
       <c r="H9" s="14">
-        <f>Segments!E19</f>
+        <f>Segments!E32</f>
         <v/>
       </c>
       <c r="I9" s="14">
-        <f>Segments!F19</f>
+        <f>Segments!F32</f>
         <v/>
       </c>
       <c r="J9" s="14">
-        <f>Segments!G19</f>
+        <f>Segments!G32</f>
         <v/>
       </c>
     </row>
@@ -6388,23 +6783,23 @@
         <v>85.39563699999999</v>
       </c>
       <c r="F10" s="14">
-        <f>Segments!C17</f>
+        <f>Segments!C30</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Segments!D17</f>
+        <f>Segments!D30</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Segments!E17</f>
+        <f>Segments!E30</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Segments!F17</f>
+        <f>Segments!F30</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Segments!G17</f>
+        <f>Segments!G30</f>
         <v/>
       </c>
     </row>
@@ -6424,23 +6819,23 @@
         <v>1266.636844</v>
       </c>
       <c r="F11" s="14">
-        <f>Segments!C18</f>
+        <f>Segments!C31</f>
         <v/>
       </c>
       <c r="G11" s="14">
-        <f>Segments!D18</f>
+        <f>Segments!D31</f>
         <v/>
       </c>
       <c r="H11" s="14">
-        <f>Segments!E18</f>
+        <f>Segments!E31</f>
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>Segments!F18</f>
+        <f>Segments!F31</f>
         <v/>
       </c>
       <c r="J11" s="14">
-        <f>Segments!G18</f>
+        <f>Segments!G31</f>
         <v/>
       </c>
     </row>

--- a/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
+++ b/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -135,28 +135,30 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -522,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="116" customWidth="1" min="1" max="1"/>
@@ -661,83 +663,87 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>bounds, the two pasted framings of the contested gross-margin judgement, and the expert-panel median.</t>
+          <t>bounds, and the pasted alternate framings of the contested gross-margin judgement. Everything else — every</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Everything else — every lens base value, the relative/normalised/book bear and bull bounds, and the anchor</t>
+          <t>lens base value and bound, the whole worked expert panel and its median, every ratio, and the anchor roll —</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>roll — is a live formula. Changing a driver reprices the model but does NOT redraw the engine outputs.</t>
+          <t>is a live formula. Changing a driver reprices the model but does NOT redraw the engine outputs; every</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>pasted grid's base row is asserted at build time to reproduce the live base case.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>How revenue is built. Not as one growth rate. A cable maker is a metal converter: materials (copper and</t>
-        </is>
-      </c>
+      <c r="A24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>aluminium) are 94.9% of cost of revenue. The build prices a tonnage index as metal content — on its own</t>
+          <t>How revenue is built, and how to test it. A cable maker is a metal converter: materials (copper and</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>commodity path — plus a conversion spread whose cost escalates on domestic inflation; gross margin is the</t>
+          <t>aluminium) are 94.9% of cost of revenue. The Segments sheet builds a tonnage index times a metal price on</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>OUTPUT of that stack, not an input. The central judgement is the margin the business sustains once the</t>
+          <t>its own path, plus conversion cost on domestic inflation, plus a CONVERSION SPREAD PER TONNE calibrated to</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>FY2024-25 metal tailwind has passed, anchored on the most recent reviewed actual (H1-2026, 15.26%) rather</t>
+          <t>the margin-anchor path at the BASE metal price and held fixed under metal shocks. The gross margin row is</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>than the higher FY2025 full-year print (16.24%), and computed both ways.</t>
+          <t>therefore an OUTPUT: set the metal price multiplier on Assumptions above 1.00 and watch revenue rise while</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>the margin dilutes and the value falls — the H1-2026 mechanism (flat gross profit on +9.5% revenue). The</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>margin anchor is the reviewed H1-2026 actual (15.26%), not the higher FY2025 print (16.24%), and the</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges.</t>
+          <t>contested judgement is computed both ways plus at the Q2-2026 exit rate (14.99%).</t>
         </is>
       </c>
     </row>
@@ -747,50 +753,98 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Sourcing. FY2022-FY2025 come from the company's own audited consolidated financial statements (KPMG); the</t>
+          <t>Conventions. Year-end discounting, annual compounding (mid-year would raise the DCF lens ~4%). WACC weights</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>FY2026 near-term anchor is the Tadawul-filed reviewed H1-2026 interim. Every input is listed with source and</t>
+          <t>use net financial debt, consistent with the net-debt bridge. Beta 1.129 is a Dimson sum-beta on 185 weekly</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>date in the companion bibliography document. No aggregator or broker figure is a build source.</t>
+          <t>observations (plain OLS 0.928; 90% CI 0.62-1.64 — the grid prices the width). The terminal is discounted</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>all-equity because the model itself forecasts net cash from FY2028E.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Currency. SAR million unless stated. Spot SAR 104.80 (2026-08-18 close). Sheets: READ FIRST · Summary ·</t>
-        </is>
-      </c>
+      <c r="A38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>shown as ranges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sourcing. FY2022-FY2025 come from the company's own audited consolidated financial statements (KPMG); the</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>FY2026 near-term anchor is the Tadawul-filed reviewed H1-2026 interim. Every input is listed with source and</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>date in the companion bibliography document. No aggregator or broker figure is a build source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Currency. SAR million unless stated. Spot SAR 104.90 (2026-08-18 close). Sheets: READ FIRST · Summary ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
           <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
@@ -851,42 +905,43 @@
           <t>SAR mn</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -898,13 +953,13 @@
           <t>Property, plant &amp; equipment</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="23" t="n">
         <v>1206.659875</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="23" t="n">
         <v>1336.038944</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="23" t="n">
         <v>1491.86312</v>
       </c>
       <c r="F5" s="14">
@@ -934,13 +989,13 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="23" t="n">
         <v>1909.11144</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="23" t="n">
         <v>2126.036688</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="23" t="n">
         <v>2411.049305</v>
       </c>
     </row>
@@ -950,13 +1005,13 @@
           <t>Trade &amp; other receivables</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="23" t="n">
         <v>1418.920843</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="23" t="n">
         <v>2112.098567</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="23" t="n">
         <v>2712.677113</v>
       </c>
     </row>
@@ -966,13 +1021,13 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="23" t="n">
         <v>150.051628</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="23" t="n">
         <v>90.672725</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="23" t="n">
         <v>236.043009</v>
       </c>
     </row>
@@ -982,13 +1037,13 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="23" t="n">
         <v>4830.929068</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="23" t="n">
         <v>5811.584098</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="23" t="n">
         <v>7281.581695</v>
       </c>
     </row>
@@ -998,33 +1053,33 @@
           <t>Gross borrowings incl. leases</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="23" t="n">
         <v>730.611837</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="23" t="n">
         <v>440.445599</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="23" t="n">
         <v>621.216217</v>
       </c>
       <c r="F10" s="14">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -1034,13 +1089,13 @@
           <t>Trade &amp; other payables</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n">
-        <v>1220.387691</v>
-      </c>
-      <c r="D11" s="19" t="n">
+      <c r="C11" s="23" t="n">
+        <v>1486.905974</v>
+      </c>
+      <c r="D11" s="23" t="n">
         <v>2040.707151</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="23" t="n">
         <v>2190.467493</v>
       </c>
     </row>
@@ -1050,13 +1105,13 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n">
-        <v>2107.644592</v>
-      </c>
-      <c r="D12" s="19" t="n">
+      <c r="C12" s="23" t="n">
+        <v>1841.126309</v>
+      </c>
+      <c r="D12" s="23" t="n">
         <v>2197.428104</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="23" t="n">
         <v>2933.258925</v>
       </c>
       <c r="F12" s="14">
@@ -1086,13 +1141,13 @@
           <t>Net financial debt</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="23" t="n">
         <v>580.560209</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="23" t="n">
         <v>349.772874</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="23" t="n">
         <v>385.173208</v>
       </c>
       <c r="F13" s="14">
@@ -1122,10 +1177,13 @@
           <t>Equity attributable</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="C14" s="23" t="n">
+        <v>2246.744341</v>
+      </c>
+      <c r="D14" s="23" t="n">
         <v>2624.35365</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="23" t="n">
         <v>3246.136935</v>
       </c>
       <c r="F14" s="14">
@@ -1171,23 +1229,23 @@
           <t>Net debt, start of year</t>
         </is>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="19">
         <f>Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="19">
         <f>C24</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="19">
         <f>D24</f>
         <v/>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="19">
         <f>E24</f>
         <v/>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="19">
         <f>F24</f>
         <v/>
       </c>
@@ -1198,24 +1256,24 @@
           <t>Surplus cash</t>
         </is>
       </c>
-      <c r="C18" s="28">
-        <f>Assumptions!$C$51-C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="28">
-        <f>Assumptions!$C$51-D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="28">
-        <f>Assumptions!$C$51-E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="28">
-        <f>Assumptions!$C$51-F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="28">
-        <f>Assumptions!$C$51-G17</f>
+      <c r="C18" s="19">
+        <f>Assumptions!$C$53-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="19">
+        <f>Assumptions!$C$53-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="19">
+        <f>Assumptions!$C$53-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="19">
+        <f>Assumptions!$C$53-F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="19">
+        <f>Assumptions!$C$53-G17</f>
         <v/>
       </c>
     </row>
@@ -1225,24 +1283,24 @@
           <t>Net interest</t>
         </is>
       </c>
-      <c r="C19" s="28">
-        <f>Assumptions!C$32*Assumptions!$C$51-Assumptions!$C$34*MAX(C18,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="28">
-        <f>Assumptions!D$32*Assumptions!$C$51-Assumptions!$C$34*MAX(D18,0)</f>
-        <v/>
-      </c>
-      <c r="E19" s="28">
-        <f>Assumptions!E$32*Assumptions!$C$51-Assumptions!$C$34*MAX(E18,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="28">
-        <f>Assumptions!F$32*Assumptions!$C$51-Assumptions!$C$34*MAX(F18,0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="28">
-        <f>Assumptions!G$32*Assumptions!$C$51-Assumptions!$C$34*MAX(G18,0)</f>
+      <c r="C19" s="19">
+        <f>Assumptions!C$32*Assumptions!$C$53-Assumptions!$C$34*MAX(C18,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="19">
+        <f>Assumptions!D$32*Assumptions!$C$53-Assumptions!$C$34*MAX(D18,0)</f>
+        <v/>
+      </c>
+      <c r="E19" s="19">
+        <f>Assumptions!E$32*Assumptions!$C$53-Assumptions!$C$34*MAX(E18,0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="19">
+        <f>Assumptions!F$32*Assumptions!$C$53-Assumptions!$C$34*MAX(F18,0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="19">
+        <f>Assumptions!G$32*Assumptions!$C$53-Assumptions!$C$34*MAX(G18,0)</f>
         <v/>
       </c>
     </row>
@@ -1279,23 +1337,23 @@
           <t>Profit before zakat</t>
         </is>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="19">
         <f>C20-C19</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="19">
         <f>D20-D19</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="19">
         <f>E20-E19</f>
         <v/>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="19">
         <f>F20-F19</f>
         <v/>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="19">
         <f>G20-G19</f>
         <v/>
       </c>
@@ -1306,24 +1364,24 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="C22" s="28">
-        <f>C21*(1-Assumptions!$C$14)*(1-0.004060669885351275)</f>
-        <v/>
-      </c>
-      <c r="D22" s="28">
-        <f>D21*(1-Assumptions!$C$14)*(1-0.004060669885351275)</f>
-        <v/>
-      </c>
-      <c r="E22" s="28">
-        <f>E21*(1-Assumptions!$C$14)*(1-0.004060669885351275)</f>
-        <v/>
-      </c>
-      <c r="F22" s="28">
-        <f>F21*(1-Assumptions!$C$14)*(1-0.004060669885351275)</f>
-        <v/>
-      </c>
-      <c r="G22" s="28">
-        <f>G21*(1-Assumptions!$C$14)*(1-0.004060669885351275)</f>
+      <c r="C22" s="19">
+        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
+        <v/>
+      </c>
+      <c r="D22" s="19">
+        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
+        <v/>
+      </c>
+      <c r="E22" s="19">
+        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
+        <v/>
+      </c>
+      <c r="F22" s="19">
+        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
+        <v/>
+      </c>
+      <c r="G22" s="19">
+        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
         <v/>
       </c>
     </row>
@@ -1333,23 +1391,23 @@
           <t>Dividend</t>
         </is>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="19">
         <f>Assumptions!$C$33*C22</f>
         <v/>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="19">
         <f>Assumptions!$C$33*D22</f>
         <v/>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="19">
         <f>Assumptions!$C$33*E22</f>
         <v/>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="19">
         <f>Assumptions!$C$33*F22</f>
         <v/>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="19">
         <f>Assumptions!$C$33*G22</f>
         <v/>
       </c>
@@ -1360,23 +1418,23 @@
           <t>Net debt, end of year</t>
         </is>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="19">
         <f>C17-(DCF!C27-C19*(1-Assumptions!$C$14))+C23</f>
         <v/>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="19">
         <f>D17-(DCF!D27-D19*(1-Assumptions!$C$14))+D23</f>
         <v/>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="19">
         <f>E17-(DCF!E27-E19*(1-Assumptions!$C$14))+E23</f>
         <v/>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="19">
         <f>F17-(DCF!F27-F19*(1-Assumptions!$C$14))+F23</f>
         <v/>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="19">
         <f>G17-(DCF!G27-G19*(1-Assumptions!$C$14))+G23</f>
         <v/>
       </c>
@@ -1387,23 +1445,23 @@
           <t>Equity attributable</t>
         </is>
       </c>
-      <c r="C25" s="28">
-        <f>Assumptions!$C$52+C22-C23</f>
-        <v/>
-      </c>
-      <c r="D25" s="28">
+      <c r="C25" s="19">
+        <f>Assumptions!$C$54+C22-C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="19">
         <f>C25+D22-D23</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="19">
         <f>D25+E22-E23</f>
         <v/>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="19">
         <f>E25+F22-F23</f>
         <v/>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="19">
         <f>F25+G22-G23</f>
         <v/>
       </c>
@@ -1459,27 +1517,28 @@
           <t>SAR mn</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -1599,23 +1658,23 @@
           <t>Free cash flow to firm</t>
         </is>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="38">
         <f>C5+C6+C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="38">
         <f>D5+D6+D7+D8</f>
         <v/>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="38">
         <f>E5+E6+E7+E8</f>
         <v/>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="38">
         <f>F5+F6+F7+F8</f>
         <v/>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="38">
         <f>G5+G6+G7+G8</f>
         <v/>
       </c>
@@ -1626,23 +1685,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="40">
         <f>DCF!C19</f>
         <v/>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="40">
         <f>DCF!D19</f>
         <v/>
       </c>
-      <c r="E10" s="39">
+      <c r="E10" s="40">
         <f>DCF!E19</f>
         <v/>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="40">
         <f>DCF!F19</f>
         <v/>
       </c>
-      <c r="G10" s="39">
+      <c r="G10" s="40">
         <f>DCF!G19</f>
         <v/>
       </c>
@@ -1653,23 +1712,23 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="19">
         <f>C9*C10</f>
         <v/>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="19">
         <f>D9*D10</f>
         <v/>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="19">
         <f>E9*E10</f>
         <v/>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="19">
         <f>F9*F10</f>
         <v/>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="19">
         <f>G9*G10</f>
         <v/>
       </c>
@@ -1725,27 +1784,28 @@
           <t>SAR mn</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -1785,23 +1845,23 @@
         </is>
       </c>
       <c r="C6" s="14">
-        <f>Segments!C17</f>
+        <f>Segments!C20</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>Segments!D17</f>
+        <f>Segments!D20</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>Segments!E17</f>
+        <f>Segments!E20</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>Segments!F17</f>
+        <f>Segments!F20</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>Segments!G17</f>
+        <f>Segments!G20</f>
         <v/>
       </c>
     </row>
@@ -1892,23 +1952,23 @@
           <t>ROIC</t>
         </is>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="18">
         <f>DCF!C33</f>
         <v/>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="18">
         <f>DCF!D33</f>
         <v/>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="18">
         <f>DCF!E33</f>
         <v/>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="18">
         <f>DCF!F33</f>
         <v/>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="18">
         <f>DCF!G33</f>
         <v/>
       </c>
@@ -1978,10 +2038,10 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>87.21321014037129</v>
+        <v>87.25808430972248</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>76.54888951524968</v>
+        <v>76.53735505038735</v>
       </c>
     </row>
     <row r="6">
@@ -1991,10 +2051,10 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>97.61126202615651</v>
+        <v>97.66760169647281</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>92.86909864606133</v>
+        <v>92.86041807876856</v>
       </c>
     </row>
     <row r="7">
@@ -2004,10 +2064,10 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>104.7866044705799</v>
+        <v>104.8512200742135</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>105.0593696127112</v>
+        <v>105.053385509702</v>
       </c>
     </row>
     <row r="8">
@@ -2017,10 +2077,10 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>112.6160892961509</v>
+        <v>112.6900469186186</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>118.7094846328782</v>
+        <v>118.7070159704662</v>
       </c>
     </row>
     <row r="9">
@@ -2030,10 +2090,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>126.1767140981632</v>
+        <v>126.2675579273705</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>144.0563430692076</v>
+        <v>144.0616010928045</v>
       </c>
     </row>
     <row r="10">
@@ -2043,10 +2103,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>104.8</v>
+        <v>104.9</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>104.8</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="11">
@@ -2055,11 +2115,11 @@
           <t>P(above spot)</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
-        <v>0.4997</v>
-      </c>
-      <c r="C11" s="23" t="n">
-        <v>0.50542</v>
+      <c r="B11" s="28" t="n">
+        <v>0.49836</v>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>0.50322</v>
       </c>
     </row>
     <row r="12">
@@ -2068,11 +2128,11 @@
           <t>Annualised vol</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
-        <v>0.3614703996629836</v>
-      </c>
-      <c r="C12" s="23" t="n">
-        <v>0.3670575648854793</v>
+      <c r="B12" s="28" t="n">
+        <v>0.3616713439785802</v>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>0.3671662360524218</v>
       </c>
     </row>
     <row r="14">
@@ -2093,10 +2153,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -2123,12 +2183,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Each cell is a complete revaluation and does NOT redraw when a driver changes</t>
+          <t>Each cell is a complete revaluation and does NOT redraw when a driver changes; every block's base row REPRODUCES the base case (asserted at build time)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>DCF value per share: terminal WACC (rows) x terminal growth (cols)</t>
         </is>
@@ -2165,396 +2225,459 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=6.88%</t>
+          <t>WACC_t=7.72%</t>
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>161.6870195722353</v>
+        <v>136.5639956911652</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>191.8736371200676</v>
+        <v>156.3911656162713</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>242.7920021776906</v>
+        <v>186.7266093183625</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>328.6054644701809</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>316.2898673502376</v>
+        <v>239.1603346397014</v>
+      </c>
+      <c r="F6" s="41" t="inlineStr">
+        <is>
+          <t>n/m</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=7.88%</t>
+          <t>WACC_t=8.72%</t>
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>134.9542534346101</v>
+        <v>116.8034962931929</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>153.6462749347582</v>
+        <v>129.8409494659834</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>181.817839760119</v>
+        <v>148.2860612426722</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>229.3284945978041</v>
+        <v>176.4998466264028</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>309.2939518882336</v>
+        <v>225.2565779778832</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=8.88%</t>
+          <t>WACC_t=9.72%</t>
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>115.9875989393748</v>
+        <v>102.163054852874</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>128.4080357765257</v>
+        <v>111.1904287412299</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>145.8018216575757</v>
+        <v>123.2801134487121</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>172.0099984828811</v>
+        <v>140.3784929705279</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>216.2002968120145</v>
+        <v>166.5248373182366</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=9.88%</t>
+          <t>WACC_t=10.72%</t>
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>101.8318835964901</v>
+        <v>90.88100527108116</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>110.4985687882707</v>
+        <v>97.36966430899766</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>122.0196936752806</v>
+        <v>105.7111587372711</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>138.1484649801172</v>
+        <v>116.8772553690259</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>162.4434833151007</v>
+        <v>132.6632522149492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=10.88%</t>
+          <t>WACC_t=11.72%</t>
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>90.86244771441412</v>
+        <v>81.92065637634063</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>97.12920999823187</v>
+        <v>86.71695307455919</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>105.1403254957291</v>
+        <v>92.68916241571443</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>115.7851086440444</v>
+        <v>100.3622454011173</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>130.6811672133541</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>Beta sensitivity (DCF value/share)</t>
+        <v>110.6282686274013</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>n/m: terminal spread (WACC_t - g) below 2% — the Gordon terminal value is not meaningful there and no number is shown (the first edition printed clamped values).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="n">
-        <v>209.3035784772404</v>
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Risk-free rate (10y SAR; explicit AND terminal move together) — DCF value/share</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>5.02%</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>164.1972907373474</v>
+        <v>136.089531512596</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1.129</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>130.9006081673441</v>
+        <v>123.2801134487121</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>6.02%</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>113.2662678099585</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n">
-        <v>97.50828418400954</v>
+        <v>112.5394948589756</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Beta (explicit-window Ke only; terminal beta held at 1.0 as stated) — DCF value/share</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>Metal price x sensitivity (DCF value/share)</t>
-        </is>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>129.2478439097057</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>158.4002563008479</v>
+        <v>126.4206730646305</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>1.129</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>152.0896788918666</v>
+        <v>123.2801134487121</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>145.8018216575757</v>
+        <v>120.9998758649224</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>139.5341530596548</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>133.2845824820281</v>
+        <v>118.4009111655918</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Metal price x (flat multiplier; spread held — margin is the output) — DCF value/share</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>Sustained gross margin sensitivity (DCF value/share)</t>
-        </is>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>135.7206754924927</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.925</t>
         </is>
       </c>
       <c r="B27" s="17" t="n">
-        <v>123.3559579612546</v>
+        <v>129.5003944706025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="B28" s="17" t="n">
-        <v>132.1837426703699</v>
+        <v>123.2801134487121</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>0.1526</t>
+          <t>1.075</t>
         </is>
       </c>
       <c r="B29" s="17" t="n">
-        <v>145.8018216575757</v>
+        <v>117.0598324268218</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="B30" s="17" t="n">
-        <v>150.1532450187395</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="n">
-        <v>159.2987061984988</v>
+        <v>110.8395514049315</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Sustained gross margin (0.1499 = the Q2-2026 exit rate) — DCF value/share</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>Volume x sensitivity (DCF value/share)</t>
-        </is>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>104.0336994130316</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>132.9554264400183</v>
+        <v>111.6031665507623</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.1499</t>
         </is>
       </c>
       <c r="B35" s="17" t="n">
-        <v>139.3834502657949</v>
+        <v>119.1077739641657</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.1526</t>
         </is>
       </c>
       <c r="B36" s="17" t="n">
-        <v>145.8018216575757</v>
+        <v>123.2801134487121</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>152.2112546307662</v>
+        <v>127.0112805596384</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>158.6123783645118</v>
+        <v>134.8531372449724</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="inlineStr">
-        <is>
-          <t>Net working capital / revenue sensitivity (DCF value/share)</t>
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>Volume x — DCF value/share</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>151.7745103839866</v>
+        <v>112.7169531231438</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>148.7881660207811</v>
+        <v>118.0031768846487</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>145.8018216575757</v>
+        <v>123.2801134487121</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>142.8154772943702</v>
+        <v>128.5484520748093</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>133.8087999793565</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Net working capital / revenue — DCF value/share</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>128.8502974586405</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>126.0652054536764</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>123.2801134487121</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n">
+        <v>120.4950214437479</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>0.32</t>
         </is>
       </c>
-      <c r="B45" s="17" t="n">
-        <v>139.8291329311647</v>
+      <c r="B52" s="17" t="n">
+        <v>117.7099294387837</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>The metal row matches the LIVE Segments sheet: set the metal price multiplier on Assumptions and the whole model reprices the same direction (higher metal dilutes the margin and lowers the value).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2568,7 +2691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2634,8 +2757,9 @@
           <t>EPS (SAR)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
-        <v>7.216230848097251</v>
+      <c r="B5" s="15">
+        <f>Assumptions!$C$58/Assumptions!$C$6</f>
+        <v/>
       </c>
       <c r="C5" s="15">
         <f>'Balance Sheet'!C22/Assumptions!$C$6</f>
@@ -2665,7 +2789,7 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>Assumptions!$C$52/Assumptions!$C$6</f>
+        <f>Assumptions!$C$54/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C6" s="15">
@@ -2692,11 +2816,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>ROE (%)</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="n">
-        <v>0.3680769183960799</v>
+          <t>ROE (%, on average equity)</t>
+        </is>
+      </c>
+      <c r="B7" s="9">
+        <f>Assumptions!$C$58/((Assumptions!$C$59+Assumptions!$C$54)/2)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2705,49 +2830,62 @@
           <t>Net debt / EBITDA (x)</t>
         </is>
       </c>
-      <c r="B8" s="34">
-        <f>Assumptions!$C$7/(Segments!B10*0+1352.0324810000002)</f>
-        <v/>
-      </c>
-      <c r="C8" s="34">
-        <f>'Balance Sheet'!F13/Segments!C17</f>
-        <v/>
-      </c>
-      <c r="D8" s="34">
-        <f>'Balance Sheet'!G13/Segments!D17</f>
-        <v/>
-      </c>
-      <c r="E8" s="34">
-        <f>'Balance Sheet'!H13/Segments!E17</f>
-        <v/>
-      </c>
-      <c r="F8" s="34">
-        <f>'Balance Sheet'!I13/Segments!F17</f>
-        <v/>
-      </c>
-      <c r="G8" s="34">
-        <f>'Balance Sheet'!J13/Segments!G17</f>
+      <c r="B8" s="35">
+        <f>Assumptions!$C$7/'Income Statement'!E9</f>
+        <v/>
+      </c>
+      <c r="C8" s="35">
+        <f>'Balance Sheet'!F13/Segments!C20</f>
+        <v/>
+      </c>
+      <c r="D8" s="35">
+        <f>'Balance Sheet'!G13/Segments!D20</f>
+        <v/>
+      </c>
+      <c r="E8" s="35">
+        <f>'Balance Sheet'!H13/Segments!E20</f>
+        <v/>
+      </c>
+      <c r="F8" s="35">
+        <f>'Balance Sheet'!I13/Segments!F20</f>
+        <v/>
+      </c>
+      <c r="G8" s="35">
+        <f>'Balance Sheet'!J13/Segments!G20</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Trailing EV/EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="n">
-        <v>11.88992678349715</v>
+          <t>EV/EBITDA (FY2025 basis, x)</t>
+        </is>
+      </c>
+      <c r="B9" s="35">
+        <f>(DCF!C8+Assumptions!$C$7)/'Income Statement'!E9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Trailing P/E (x)</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n">
-        <v>14.52281699491824</v>
+          <t>P/E (FY2025 basis, x)</t>
+        </is>
+      </c>
+      <c r="B10" s="35">
+        <f>DCF!C8/Assumptions!$C$58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>P/E (trailing twelve months, x)</t>
+        </is>
+      </c>
+      <c r="B11" s="35">
+        <f>DCF!C8/(Assumptions!$C$58+Assumptions!$C$60-Assumptions!$C$61)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2761,7 +2899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2802,12 +2940,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Fwd EV/EBITDA</t>
+          <t>EV/EBITDA</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Basis &amp; note (each multiple recomputed from the peer's own EV and guidance)</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2960,13 @@
           <t>Tadawul</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
-        <v>11.88992678349715</v>
+      <c r="C5" s="34">
+        <f>'Per-Share &amp; Ratios'!B9</f>
+        <v/>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>trailing; ~14.5x P/E</t>
+          <t>FY2025 basis (TTM P/E 13.9x); see Per-Share &amp; Ratios</t>
         </is>
       </c>
     </row>
@@ -2842,12 +2981,12 @@
           <t>Milan</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
-        <v>8.5</v>
+      <c r="C6" s="27" t="n">
+        <v>14</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>global cable major</t>
+          <t>FY2026E on guidance RAISED 30-Jul-2026 (EUR 2.8-2.9bn) vs ~EUR 40bn EV</t>
         </is>
       </c>
     </row>
@@ -2862,12 +3001,12 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
-        <v>7.5</v>
+      <c r="C7" s="27" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>global cable major</t>
+          <t>FY2026E on guidance raised 29-Jul-2026 (EUR 770-840mn) vs ~EUR 7.1bn EV</t>
         </is>
       </c>
     </row>
@@ -2882,12 +3021,12 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
-        <v>26</v>
+      <c r="C8" s="27" t="n">
+        <v>29</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>high-growth EM premium</t>
+          <t>NTM; high-growth EM premium</t>
         </is>
       </c>
     </row>
@@ -2902,12 +3041,12 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
-        <v>24</v>
+      <c r="C9" s="27" t="n">
+        <v>31</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>high-growth EM premium</t>
+          <t>NTM (~24-25x only on FY-Mar-2028, two years out)</t>
         </is>
       </c>
     </row>
@@ -2931,7 +3070,14 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA applied in the relative lens: 9.0x (mid-range, single-country discount).</t>
+          <t>Justified EV/EBITDA applied in the relative lens: 10.0x — a deliberate DISCOUNT to the corrected developed band (~8.5-14.5x) for single-country and single-customer concentration, not its mid-point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Quotes as of 18-Aug-2026. Cross-check multiples only — never a source for any Riyadh Cables figure.</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3286,7 +3432,7 @@
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>Assumptions!$C$39</f>
+        <f>Assumptions!$C$41</f>
         <v/>
       </c>
       <c r="F5" s="15">
@@ -3317,7 +3463,7 @@
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>Assumptions!$C$40</f>
+        <f>Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F6" s="15">
@@ -3348,7 +3494,7 @@
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>Assumptions!$C$41</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
       <c r="F7" s="15">
@@ -3379,7 +3525,7 @@
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$44</f>
         <v/>
       </c>
       <c r="F8" s="15">
@@ -3422,11 +3568,12 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Expert panel median (whole-model — pasted)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="n">
-        <v>143.7240895365966</v>
+          <t>Expert panel median (live — see the worked panel below)</t>
+        </is>
+      </c>
+      <c r="C11" s="15">
+        <f>MEDIAN(C26,C30,C39)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -3471,7 +3618,7 @@
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>159.2987061984988</v>
+        <v>134.8531372449724</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3628,263 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>132.1837426703699</v>
+        <v>111.6031665507623</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Q2-2026 exit rate (14.99%) sustained — DCF value (pasted re-run)</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>119.1143960075278</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Expert panel — three methods, worked live on the same forecast base</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>E1 mid-cycle EBITDA margin (FY2028E)</t>
+        </is>
+      </c>
+      <c r="C21" s="18">
+        <f>Segments!E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>E1 mid-cycle revenue (FY2028E scale)</t>
+        </is>
+      </c>
+      <c r="C22" s="14">
+        <f>Segments!E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>E1 normalised EBIT (margin x revenue - D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C23" s="19">
+        <f>C21*C22-Assumptions!$C$29*C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>E1 normalised net interest (FY2028 Kd on FY2025 debt less cash yield)</t>
+        </is>
+      </c>
+      <c r="C24" s="19">
+        <f>Assumptions!E$32*Assumptions!$C$53-Assumptions!$C$34*(Assumptions!$C$53-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>E1 earnings per share after tax and minorities</t>
+        </is>
+      </c>
+      <c r="C25" s="15">
+        <f>(C23-C24)*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>Expert 1 — value at anchor (13x; range 10x/16x)</t>
+        </is>
+      </c>
+      <c r="B26" s="15">
+        <f>(10*C25)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="C26" s="21">
+        <f>(13*C25)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="D26" s="15">
+        <f>(16*C25)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>E2 mid-cycle FCFF (average FY2028-30E)</t>
+        </is>
+      </c>
+      <c r="C27" s="14">
+        <f>AVERAGE(DCF!E27:G27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>E2 after-tax net interest (FY2029 Kd basis)</t>
+        </is>
+      </c>
+      <c r="C28" s="19">
+        <f>(Assumptions!F$32*Assumptions!$C$53-Assumptions!$C$34*(Assumptions!$C$53-Assumptions!$C$7))*(1-Assumptions!$C$14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>E2 owner cash (FCFF less after-tax interest, net of minorities)</t>
+        </is>
+      </c>
+      <c r="C29" s="19">
+        <f>(C27-C28)*(1-Assumptions!$C$36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>Expert 2 — value at anchor (perpetuity at terminal Ke; range on rate/growth)</t>
+        </is>
+      </c>
+      <c r="B30" s="15">
+        <f>(C29*1.02/((DCF!C6+DCF!C11)/2-0.02)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="C30" s="21">
+        <f>(C29*(1+Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="D30" s="15">
+        <f>(C29*1.05/(DCF!C11-0.05)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>E3 invested capital, 31-Dec-2025 (NWC + PP&amp;E)</t>
+        </is>
+      </c>
+      <c r="C31" s="19">
+        <f>Assumptions!$C$51+Assumptions!$C$52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of economic profit, FY26E (NOPAT - WACC x opening capital)</t>
+        </is>
+      </c>
+      <c r="C32" s="19">
+        <f>(DCF!C21-DCF!C18*C31)*DCF!C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of economic profit, FY27E (NOPAT - WACC x opening capital)</t>
+        </is>
+      </c>
+      <c r="C33" s="19">
+        <f>(DCF!D21-DCF!D18*DCF!C32)*DCF!D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of economic profit, FY28E (NOPAT - WACC x opening capital)</t>
+        </is>
+      </c>
+      <c r="C34" s="19">
+        <f>(DCF!E21-DCF!E18*DCF!D32)*DCF!E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of economic profit, FY29E (NOPAT - WACC x opening capital)</t>
+        </is>
+      </c>
+      <c r="C35" s="19">
+        <f>(DCF!F21-DCF!F18*DCF!E32)*DCF!F19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of economic profit, FY30E (NOPAT - WACC x opening capital)</t>
+        </is>
+      </c>
+      <c r="C36" s="19">
+        <f>(DCF!G21-DCF!G18*DCF!F32)*DCF!G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of terminal economic profit (reconciles to the DCF terminal value)</t>
+        </is>
+      </c>
+      <c r="C37" s="19">
+        <f>(DCF!G21*(1+Assumptions!$C$21)-DCF!C13*DCF!G32)/(DCF!C13-Assumptions!$C$21)*DCF!G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>E3 enterprise value (capital + PV of excess returns; equals the DCF EV)</t>
+        </is>
+      </c>
+      <c r="C38" s="19">
+        <f>C31+SUM(C32:C36)+C37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>Expert 3 — value at anchor (bridge as the DCF; range on persistence)</t>
+        </is>
+      </c>
+      <c r="B39" s="15">
+        <f>((C31+SUM(C32:C36)*0.7+C37*0.65-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="C39" s="21">
+        <f>((C38-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="D39" s="15">
+        <f>((C31+SUM(C32:C36)*1.15+C37*1.2-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3495,7 +3898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3556,7 +3959,7 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>104.8</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="6">
@@ -3565,7 +3968,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="22" t="n">
         <v>149.7175</v>
       </c>
     </row>
@@ -3575,7 +3978,7 @@
           <t>Net financial debt at FY2025 (SAR mn, disclosed)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="23" t="n">
         <v>385.173208</v>
       </c>
     </row>
@@ -3601,8 +4004,8 @@
           <t>Risk-free rate (10-year SAR sukuk)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
-        <v>0.0485</v>
+      <c r="C9" s="24" t="n">
+        <v>0.0552</v>
       </c>
     </row>
     <row r="10">
@@ -3611,8 +4014,8 @@
           <t>Sovereign default spread (netted out)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
-        <v>0.0051</v>
+      <c r="C10" s="24" t="n">
+        <v>0.0048</v>
       </c>
     </row>
     <row r="11">
@@ -3621,8 +4024,8 @@
           <t>Equity risk premium (rating basis)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
-        <v>0.0501</v>
+      <c r="C11" s="24" t="n">
+        <v>0.0494</v>
       </c>
     </row>
     <row r="12">
@@ -3631,7 +4034,7 @@
           <t>Beta (own-stock vs TASI)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="25" t="n">
         <v>1.129</v>
       </c>
     </row>
@@ -3641,7 +4044,7 @@
           <t>Cost of debt, marginal pre-tax</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="24" t="n">
         <v>0.059</v>
       </c>
     </row>
@@ -3651,7 +4054,7 @@
           <t>Effective zakat and income tax rate</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="24" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -3677,8 +4080,8 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
-        <v>0.0434</v>
+      <c r="C16" s="24" t="n">
+        <v>0.0504</v>
       </c>
     </row>
     <row r="17">
@@ -3687,8 +4090,8 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
-        <v>0.0475</v>
+      <c r="C17" s="24" t="n">
+        <v>0.0468</v>
       </c>
     </row>
     <row r="18">
@@ -3697,7 +4100,7 @@
           <t>Terminal beta</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3707,7 +4110,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="24" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -3717,8 +4120,8 @@
           <t>Terminal net-debt weight</t>
         </is>
       </c>
-      <c r="C20" s="20" t="n">
-        <v>0.05</v>
+      <c r="C20" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3727,7 +4130,7 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="24" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -3753,19 +4156,19 @@
           <t>Cable volume index growth</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="24" t="n">
         <v>0.075</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="24" t="n">
         <v>0.065</v>
       </c>
-      <c r="F23" s="20" t="n">
+      <c r="F23" s="24" t="n">
         <v>0.055</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="24" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -3775,19 +4178,19 @@
           <t>Metal content price growth</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="24" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="20" t="n">
+      <c r="E24" s="24" t="n">
         <v>0.01</v>
       </c>
-      <c r="F24" s="20" t="n">
+      <c r="F24" s="24" t="n">
         <v>0.01</v>
       </c>
-      <c r="G24" s="20" t="n">
+      <c r="G24" s="24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3797,19 +4200,19 @@
           <t>Conversion cost inflation</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="D25" s="20" t="n">
+      <c r="D25" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="E25" s="20" t="n">
+      <c r="E25" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="F25" s="20" t="n">
+      <c r="F25" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="G25" s="20" t="n">
+      <c r="G25" s="24" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -3819,7 +4222,7 @@
           <t>Sustained gross margin (H1-2026 anchor)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="24" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -3829,19 +4232,19 @@
           <t>Gross-margin glide (added to anchor)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="25" t="n">
         <v>0.001</v>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E27" s="25" t="n">
         <v>0.001</v>
       </c>
-      <c r="F27" s="21" t="n">
+      <c r="F27" s="25" t="n">
         <v>0.0015</v>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="25" t="n">
         <v>0.0015</v>
       </c>
     </row>
@@ -3851,19 +4254,19 @@
           <t>Operating expenses / revenue</t>
         </is>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="24" t="n">
         <v>0.043</v>
       </c>
-      <c r="D28" s="20" t="n">
+      <c r="D28" s="24" t="n">
         <v>0.043</v>
       </c>
-      <c r="E28" s="20" t="n">
+      <c r="E28" s="24" t="n">
         <v>0.0425</v>
       </c>
-      <c r="F28" s="20" t="n">
+      <c r="F28" s="24" t="n">
         <v>0.042</v>
       </c>
-      <c r="G28" s="20" t="n">
+      <c r="G28" s="24" t="n">
         <v>0.042</v>
       </c>
     </row>
@@ -3873,7 +4276,7 @@
           <t>Depreciation and amortisation / revenue</t>
         </is>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="24" t="n">
         <v>0.008500000000000001</v>
       </c>
     </row>
@@ -3883,20 +4286,20 @@
           <t>Capital expenditure / revenue</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="24" t="n">
         <v>0.019</v>
       </c>
-      <c r="D30" s="20" t="n">
+      <c r="D30" s="24" t="n">
         <v>0.018</v>
       </c>
-      <c r="E30" s="20" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v>0.016</v>
+      <c r="E30" s="24" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F30" s="24" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>0.0177</v>
       </c>
     </row>
     <row r="31">
@@ -3905,7 +4308,7 @@
           <t>Net working capital / revenue</t>
         </is>
       </c>
-      <c r="C31" s="20" t="n">
+      <c r="C31" s="24" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -3915,19 +4318,19 @@
           <t>Cost-of-debt path</t>
         </is>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="24" t="n">
         <v>0.059</v>
       </c>
-      <c r="D32" s="20" t="n">
+      <c r="D32" s="24" t="n">
         <v>0.058</v>
       </c>
-      <c r="E32" s="20" t="n">
+      <c r="E32" s="24" t="n">
         <v>0.057</v>
       </c>
-      <c r="F32" s="20" t="n">
+      <c r="F32" s="24" t="n">
         <v>0.056</v>
       </c>
-      <c r="G32" s="20" t="n">
+      <c r="G32" s="24" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -3937,7 +4340,7 @@
           <t>Forecast dividend payout ratio</t>
         </is>
       </c>
-      <c r="C33" s="20" t="n">
+      <c r="C33" s="24" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -3947,236 +4350,296 @@
           <t>Yield on surplus cash</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n">
+      <c r="C34" s="24" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="n"/>
-      <c r="I35" s="11" t="n"/>
-      <c r="J35" s="11" t="n"/>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Metal price multiplier (shock; 1.00 = base path)</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C36" s="22" t="n">
-        <v>9</v>
+          <t>NCI share of profit (FY2025)</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="n">
+        <v>0.004060669885351275</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C37" s="22" t="n">
-        <v>13</v>
-      </c>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="n">
-        <v>0.28</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="n">
-        <v>0.45</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C39" s="27" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="n">
-        <v>0.2</v>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="n">
-        <v>0.2</v>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Weight — book</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="n">
-        <v>0.15</v>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>Anchor roll</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="11" t="n"/>
-      <c r="I43" s="11" t="n"/>
-      <c r="J43" s="11" t="n"/>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
+          <t>Weight — book</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Anchor roll</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
           <t>Days to the anchor</t>
         </is>
       </c>
-      <c r="C44" s="19" t="n">
+      <c r="C46" s="23" t="n">
         <v>230</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 dividend per share paid in window</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>FY2025 disclosed base (audited)</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="11" t="n"/>
-      <c r="H46" s="11" t="n"/>
-      <c r="I46" s="11" t="n"/>
-      <c r="J46" s="11" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>FY2025 metal content / materials (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="n">
-        <v>8486.925676999999</v>
+          <t>FY2025 dividend per share paid in window</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 conversion cost (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="n">
-        <v>453.34873</v>
-      </c>
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>FY2025 disclosed base (audited)</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="11" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="11" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>FY2025 net working capital (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="n">
-        <v>2933.258925</v>
+          <t>FY2025 metal content / materials (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="n">
+        <v>8486.925676999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>FY2025 PP&amp;E (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="n">
-        <v>1491.86312</v>
+          <t>FY2025 conversion cost (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="n">
+        <v>453.34873</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="n">
-        <v>621.216217</v>
+          <t>FY2025 net working capital (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="n">
+        <v>2933.258925</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>FY2025 equity attributable (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C52" s="19" t="n">
-        <v>3246.136935</v>
+          <t>FY2025 PP&amp;E (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="n">
+        <v>1491.86312</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>FY2025 associates carrying value (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C53" s="19" t="n">
-        <v>31.851877</v>
+          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>621.216217</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>FY2025 non-operating assets (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="n">
-        <v>20.40064</v>
+          <t>FY2025 equity attributable (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="n">
+        <v>3246.136935</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
+          <t>FY2025 associates carrying value (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="n">
+        <v>31.851877</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 non-operating assets (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="n">
+        <v>20.40064</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
           <t>FY2025 NCI carrying value (SAR mn)</t>
         </is>
       </c>
-      <c r="C55" s="19" t="n">
+      <c r="C57" s="23" t="n">
         <v>62.737156</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 attributable profit (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="n">
+        <v>1080.396042</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>FY2024 equity attributable (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="n">
+        <v>2624.35365</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>H1-2026 attributable profit (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C60" s="23" t="n">
+        <v>588.793</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>H1-2025 attributable profit (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="n">
+        <v>535.4690000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4290,7 +4753,7 @@
           <t>Equity attributable (31-Dec-2025)</t>
         </is>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="29">
         <f>DCF!C48</f>
         <v/>
       </c>
@@ -4301,7 +4764,7 @@
           <t>Value per share at anchor (SAR)</t>
         </is>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="30">
         <f>DCF!C51</f>
         <v/>
       </c>
@@ -4317,7 +4780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4394,26 +4857,26 @@
           <t>Cable volume index (FY2025=100)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="31">
         <f>B5*(1+Assumptions!C$23)</f>
         <v/>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="31">
         <f>C5*(1+Assumptions!D$23)</f>
         <v/>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="31">
         <f>D5*(1+Assumptions!E$23)</f>
         <v/>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="31">
         <f>E5*(1+Assumptions!F$23)</f>
         <v/>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="31">
         <f>F5*(1+Assumptions!G$23)</f>
         <v/>
       </c>
@@ -4421,30 +4884,30 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Metal content per unit</t>
-        </is>
-      </c>
-      <c r="B6" s="27">
-        <f>Assumptions!$C$47/100.0</f>
-        <v/>
-      </c>
-      <c r="C6" s="27">
+          <t>Metal content per unit (base path)</t>
+        </is>
+      </c>
+      <c r="B6" s="32">
+        <f>Assumptions!$C$49/100.0</f>
+        <v/>
+      </c>
+      <c r="C6" s="32">
         <f>B6*(1+Assumptions!C$24)</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="32">
         <f>C6*(1+Assumptions!D$24)</f>
         <v/>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="32">
         <f>D6*(1+Assumptions!E$24)</f>
         <v/>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="32">
         <f>E6*(1+Assumptions!F$24)</f>
         <v/>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="32">
         <f>F6*(1+Assumptions!G$24)</f>
         <v/>
       </c>
@@ -4452,405 +4915,498 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Conversion cost per unit</t>
-        </is>
-      </c>
-      <c r="B7" s="27">
-        <f>Assumptions!$C$48/100.0</f>
-        <v/>
-      </c>
-      <c r="C7" s="27">
-        <f>B7*(1+Assumptions!C$25)</f>
-        <v/>
-      </c>
-      <c r="D7" s="27">
-        <f>C7*(1+Assumptions!D$25)</f>
-        <v/>
-      </c>
-      <c r="E7" s="27">
-        <f>D7*(1+Assumptions!E$25)</f>
-        <v/>
-      </c>
-      <c r="F7" s="27">
-        <f>E7*(1+Assumptions!F$25)</f>
-        <v/>
-      </c>
-      <c r="G7" s="27">
-        <f>F7*(1+Assumptions!G$25)</f>
+          <t>Metal content per unit (after shock multiplier)</t>
+        </is>
+      </c>
+      <c r="B7" s="32">
+        <f>B6*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="C7" s="32">
+        <f>C6*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="D7" s="32">
+        <f>D6*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="E7" s="32">
+        <f>E6*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="F7" s="32">
+        <f>F6*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="G7" s="32">
+        <f>G6*Assumptions!$C$35</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Materials (metal leg)</t>
-        </is>
-      </c>
-      <c r="B8" s="28">
-        <f>B5*B6</f>
-        <v/>
-      </c>
-      <c r="C8" s="28">
-        <f>C5*C6</f>
-        <v/>
-      </c>
-      <c r="D8" s="28">
-        <f>D5*D6</f>
-        <v/>
-      </c>
-      <c r="E8" s="28">
-        <f>E5*E6</f>
-        <v/>
-      </c>
-      <c r="F8" s="28">
-        <f>F5*F6</f>
-        <v/>
-      </c>
-      <c r="G8" s="28">
-        <f>G5*G6</f>
+          <t>Conversion cost per unit</t>
+        </is>
+      </c>
+      <c r="B8" s="32">
+        <f>Assumptions!$C$50/100.0</f>
+        <v/>
+      </c>
+      <c r="C8" s="32">
+        <f>B8*(1+Assumptions!C$25)</f>
+        <v/>
+      </c>
+      <c r="D8" s="32">
+        <f>C8*(1+Assumptions!D$25)</f>
+        <v/>
+      </c>
+      <c r="E8" s="32">
+        <f>D8*(1+Assumptions!E$25)</f>
+        <v/>
+      </c>
+      <c r="F8" s="32">
+        <f>E8*(1+Assumptions!F$25)</f>
+        <v/>
+      </c>
+      <c r="G8" s="32">
+        <f>F8*(1+Assumptions!G$25)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Conversion cost</t>
-        </is>
-      </c>
-      <c r="B9" s="28">
-        <f>B5*B7</f>
-        <v/>
-      </c>
-      <c r="C9" s="28">
-        <f>C5*C7</f>
-        <v/>
-      </c>
-      <c r="D9" s="28">
-        <f>D5*D7</f>
-        <v/>
-      </c>
-      <c r="E9" s="28">
-        <f>E5*E7</f>
-        <v/>
-      </c>
-      <c r="F9" s="28">
-        <f>F5*F7</f>
-        <v/>
-      </c>
-      <c r="G9" s="28">
-        <f>G5*G7</f>
+          <t>Margin anchor path (calibrates the spread at base metal)</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="n">
+        <v>0.1623940528853008</v>
+      </c>
+      <c r="C9" s="33">
+        <f>Assumptions!$C$26+Assumptions!C$27</f>
+        <v/>
+      </c>
+      <c r="D9" s="33">
+        <f>Assumptions!$C$26+Assumptions!D$27</f>
+        <v/>
+      </c>
+      <c r="E9" s="33">
+        <f>Assumptions!$C$26+Assumptions!E$27</f>
+        <v/>
+      </c>
+      <c r="F9" s="33">
+        <f>Assumptions!$C$26+Assumptions!F$27</f>
+        <v/>
+      </c>
+      <c r="G9" s="33">
+        <f>Assumptions!$C$26+Assumptions!G$27</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Cost of revenue</t>
-        </is>
-      </c>
-      <c r="B10" s="28">
-        <f>B8+B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="28">
-        <f>C8+C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="28">
-        <f>D8+D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="28">
-        <f>E8+E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="28">
-        <f>F8+F9</f>
-        <v/>
-      </c>
-      <c r="G10" s="28">
-        <f>G8+G9</f>
+          <t>Conversion spread per unit (calibrated at base metal, held under shocks)</t>
+        </is>
+      </c>
+      <c r="B10" s="32">
+        <f>B9/(1-B9)*(B6+B8)</f>
+        <v/>
+      </c>
+      <c r="C10" s="32">
+        <f>C9/(1-C9)*(C6+C8)</f>
+        <v/>
+      </c>
+      <c r="D10" s="32">
+        <f>D9/(1-D9)*(D6+D8)</f>
+        <v/>
+      </c>
+      <c r="E10" s="32">
+        <f>E9/(1-E9)*(E6+E8)</f>
+        <v/>
+      </c>
+      <c r="F10" s="32">
+        <f>F9/(1-F9)*(F6+F8)</f>
+        <v/>
+      </c>
+      <c r="G10" s="32">
+        <f>G9/(1-G9)*(G6+G8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Gross margin (target = anchor + glide)</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>0.1623940528853008</v>
-      </c>
-      <c r="C11" s="29">
-        <f>Assumptions!$C$26+Assumptions!C$27</f>
-        <v/>
-      </c>
-      <c r="D11" s="29">
-        <f>Assumptions!$C$26+Assumptions!D$27</f>
-        <v/>
-      </c>
-      <c r="E11" s="29">
-        <f>Assumptions!$C$26+Assumptions!E$27</f>
-        <v/>
-      </c>
-      <c r="F11" s="29">
-        <f>Assumptions!$C$26+Assumptions!F$27</f>
-        <v/>
-      </c>
-      <c r="G11" s="29">
-        <f>Assumptions!$C$26+Assumptions!G$27</f>
+          <t>Materials (metal leg, shocked)</t>
+        </is>
+      </c>
+      <c r="B11" s="19">
+        <f>B5*B7</f>
+        <v/>
+      </c>
+      <c r="C11" s="19">
+        <f>C5*C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="19">
+        <f>D5*D7</f>
+        <v/>
+      </c>
+      <c r="E11" s="19">
+        <f>E5*E7</f>
+        <v/>
+      </c>
+      <c r="F11" s="19">
+        <f>F5*F7</f>
+        <v/>
+      </c>
+      <c r="G11" s="19">
+        <f>G5*G7</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n">
-        <v>10673.604262</v>
-      </c>
-      <c r="C12" s="28">
-        <f>C10/(1-C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="28">
-        <f>D10/(1-D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="28">
-        <f>E10/(1-E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="28">
-        <f>F10/(1-F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="28">
-        <f>G10/(1-G11)</f>
+          <t>Conversion cost</t>
+        </is>
+      </c>
+      <c r="B12" s="19">
+        <f>B5*B8</f>
+        <v/>
+      </c>
+      <c r="C12" s="19">
+        <f>C5*C8</f>
+        <v/>
+      </c>
+      <c r="D12" s="19">
+        <f>D5*D8</f>
+        <v/>
+      </c>
+      <c r="E12" s="19">
+        <f>E5*E8</f>
+        <v/>
+      </c>
+      <c r="F12" s="19">
+        <f>F5*F8</f>
+        <v/>
+      </c>
+      <c r="G12" s="19">
+        <f>G5*G8</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n">
-        <v>1733.329855</v>
-      </c>
-      <c r="C13" s="28">
-        <f>C12-C10</f>
-        <v/>
-      </c>
-      <c r="D13" s="28">
-        <f>D12-D10</f>
-        <v/>
-      </c>
-      <c r="E13" s="28">
-        <f>E12-E10</f>
-        <v/>
-      </c>
-      <c r="F13" s="28">
-        <f>F12-F10</f>
-        <v/>
-      </c>
-      <c r="G13" s="28">
-        <f>G12-G10</f>
+          <t>Cost of revenue</t>
+        </is>
+      </c>
+      <c r="B13" s="19">
+        <f>B11+B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="19">
+        <f>C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="19">
+        <f>D11+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="19">
+        <f>E11+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="19">
+        <f>F11+F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="19">
+        <f>G11+G12</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="C14" s="28">
-        <f>Assumptions!C$28*C12</f>
-        <v/>
-      </c>
-      <c r="D14" s="28">
-        <f>Assumptions!D$28*D12</f>
-        <v/>
-      </c>
-      <c r="E14" s="28">
-        <f>Assumptions!E$28*E12</f>
-        <v/>
-      </c>
-      <c r="F14" s="28">
-        <f>Assumptions!F$28*F12</f>
-        <v/>
-      </c>
-      <c r="G14" s="28">
-        <f>Assumptions!G$28*G12</f>
+          <t>Gross profit = volume x spread</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>1733.329855</v>
+      </c>
+      <c r="C14" s="19">
+        <f>C5*C10</f>
+        <v/>
+      </c>
+      <c r="D14" s="19">
+        <f>D5*D10</f>
+        <v/>
+      </c>
+      <c r="E14" s="19">
+        <f>E5*E10</f>
+        <v/>
+      </c>
+      <c r="F14" s="19">
+        <f>F5*F10</f>
+        <v/>
+      </c>
+      <c r="G14" s="19">
+        <f>G5*G10</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Depreciation &amp; amortisation</t>
-        </is>
-      </c>
-      <c r="C15" s="28">
-        <f>Assumptions!$C$29*C12</f>
-        <v/>
-      </c>
-      <c r="D15" s="28">
-        <f>Assumptions!$C$29*D12</f>
-        <v/>
-      </c>
-      <c r="E15" s="28">
-        <f>Assumptions!$C$29*E12</f>
-        <v/>
-      </c>
-      <c r="F15" s="28">
-        <f>Assumptions!$C$29*F12</f>
-        <v/>
-      </c>
-      <c r="G15" s="28">
-        <f>Assumptions!$C$29*G12</f>
+          <t>Revenue = materials + conversion + spread</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>10673.604262</v>
+      </c>
+      <c r="C15" s="19">
+        <f>C13+C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="19">
+        <f>D13+D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="19">
+        <f>E13+E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="19">
+        <f>F13+F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="19">
+        <f>G13+G14</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C16" s="28">
-        <f>C13-C14</f>
-        <v/>
-      </c>
-      <c r="D16" s="28">
-        <f>D13-D14</f>
-        <v/>
-      </c>
-      <c r="E16" s="28">
-        <f>E13-E14</f>
-        <v/>
-      </c>
-      <c r="F16" s="28">
-        <f>F13-F14</f>
-        <v/>
-      </c>
-      <c r="G16" s="28">
-        <f>G13-G14</f>
+          <t>Gross margin — OUTPUT (dilutes when metal rises)</t>
+        </is>
+      </c>
+      <c r="B16" s="33">
+        <f>B14/B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="33">
+        <f>C14/C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="33">
+        <f>D14/D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="33">
+        <f>E14/E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="33">
+        <f>F14/F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="33">
+        <f>G14/G15</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="C17" s="28">
-        <f>C16+C15</f>
-        <v/>
-      </c>
-      <c r="D17" s="28">
-        <f>D16+D15</f>
-        <v/>
-      </c>
-      <c r="E17" s="28">
-        <f>E16+E15</f>
-        <v/>
-      </c>
-      <c r="F17" s="28">
-        <f>F16+F15</f>
-        <v/>
-      </c>
-      <c r="G17" s="28">
-        <f>G16+G15</f>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C17" s="19">
+        <f>Assumptions!C$28*C15</f>
+        <v/>
+      </c>
+      <c r="D17" s="19">
+        <f>Assumptions!D$28*D15</f>
+        <v/>
+      </c>
+      <c r="E17" s="19">
+        <f>Assumptions!E$28*E15</f>
+        <v/>
+      </c>
+      <c r="F17" s="19">
+        <f>Assumptions!F$28*F15</f>
+        <v/>
+      </c>
+      <c r="G17" s="19">
+        <f>Assumptions!G$28*G15</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C18" s="29">
-        <f>C17/C12</f>
-        <v/>
-      </c>
-      <c r="D18" s="29">
-        <f>D17/D12</f>
-        <v/>
-      </c>
-      <c r="E18" s="29">
-        <f>E17/E12</f>
-        <v/>
-      </c>
-      <c r="F18" s="29">
-        <f>F17/F12</f>
-        <v/>
-      </c>
-      <c r="G18" s="29">
-        <f>G17/G12</f>
+          <t>Depreciation &amp; amortisation</t>
+        </is>
+      </c>
+      <c r="C18" s="19">
+        <f>Assumptions!$C$29*C15</f>
+        <v/>
+      </c>
+      <c r="D18" s="19">
+        <f>Assumptions!$C$29*D15</f>
+        <v/>
+      </c>
+      <c r="E18" s="19">
+        <f>Assumptions!$C$29*E15</f>
+        <v/>
+      </c>
+      <c r="F18" s="19">
+        <f>Assumptions!$C$29*F15</f>
+        <v/>
+      </c>
+      <c r="G18" s="19">
+        <f>Assumptions!$C$29*G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C19" s="19">
+        <f>C14-C17</f>
+        <v/>
+      </c>
+      <c r="D19" s="19">
+        <f>D14-D17</f>
+        <v/>
+      </c>
+      <c r="E19" s="19">
+        <f>E14-E17</f>
+        <v/>
+      </c>
+      <c r="F19" s="19">
+        <f>F14-F17</f>
+        <v/>
+      </c>
+      <c r="G19" s="19">
+        <f>G14-G17</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>FY2025 disclosed segment revenue (Note 40)</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C20" s="19">
+        <f>C19+C18</f>
+        <v/>
+      </c>
+      <c r="D20" s="19">
+        <f>D19+D18</f>
+        <v/>
+      </c>
+      <c r="E20" s="19">
+        <f>E19+E18</f>
+        <v/>
+      </c>
+      <c r="F20" s="19">
+        <f>F19+F18</f>
+        <v/>
+      </c>
+      <c r="G20" s="19">
+        <f>G19+G18</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C21" s="33">
+        <f>C20/C15</f>
+        <v/>
+      </c>
+      <c r="D21" s="33">
+        <f>D20/D15</f>
+        <v/>
+      </c>
+      <c r="E21" s="33">
+        <f>E20/E15</f>
+        <v/>
+      </c>
+      <c r="F21" s="33">
+        <f>F20/F15</f>
+        <v/>
+      </c>
+      <c r="G21" s="33">
+        <f>G20/G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>FY2025 disclosed segment revenue (Note 40)</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="11" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>Cables and wires</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B24" s="23" t="n">
         <v>10414.170668</v>
       </c>
-      <c r="C21" s="9">
-        <f>B21/B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="C24" s="9">
+        <f>B24/B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>High-voltage cables (turnkey projects)</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B25" s="23" t="n">
         <v>230.839181</v>
       </c>
-      <c r="C22" s="9">
-        <f>B22/B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="C25" s="9">
+        <f>B25/B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Other (telephone cables &amp; services)</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B26" s="23" t="n">
         <v>28.594413</v>
       </c>
-      <c r="C23" s="9">
-        <f>B23/B12</f>
+      <c r="C26" s="9">
+        <f>B26/B15</f>
         <v/>
       </c>
     </row>
@@ -4917,7 +5473,7 @@
         </is>
       </c>
       <c r="C5" s="14">
-        <f>Segments!D17</f>
+        <f>Segments!D20</f>
         <v/>
       </c>
     </row>
@@ -4927,8 +5483,8 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="30">
-        <f>Assumptions!$C$36</f>
+      <c r="C6" s="34">
+        <f>Assumptions!$C$38</f>
         <v/>
       </c>
     </row>
@@ -4944,28 +5500,28 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Relative lens — implied value (base)</t>
         </is>
       </c>
-      <c r="C8" s="32">
-        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$53+Assumptions!$C$54-Assumptions!$C$55)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$45</f>
+      <c r="C8" s="21">
+        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Bear (7.5x) / Bull (11.0x)</t>
+          <t>Bear (8.0x) / Bull (12.0x)</t>
         </is>
       </c>
       <c r="C9" s="15">
-        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$53+Assumptions!$C$54-Assumptions!$C$55)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>((8*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$53+Assumptions!$C$54-Assumptions!$C$55)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>((12*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -4988,8 +5544,8 @@
           <t>Mid-cycle EBITDA margin (FY2028E)</t>
         </is>
       </c>
-      <c r="C12" s="33">
-        <f>Segments!E18</f>
+      <c r="C12" s="18">
+        <f>Segments!E21</f>
         <v/>
       </c>
     </row>
@@ -5000,7 +5556,7 @@
         </is>
       </c>
       <c r="C13" s="14">
-        <f>Segments!C12</f>
+        <f>Segments!C15</f>
         <v/>
       </c>
     </row>
@@ -5022,18 +5578,18 @@
         </is>
       </c>
       <c r="C15" s="15">
-        <f>((C12*C13-Assumptions!$C$29*C13)-C14)*(1-Assumptions!$C$14)*(1-0.004060669885351275)/Assumptions!$C$6</f>
+        <f>((C12*C13-Assumptions!$C$29*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Normalised lens — implied value (base)</t>
         </is>
       </c>
-      <c r="C16" s="32">
-        <f>(Assumptions!$C$37*C15)*DCF!$C$50-Assumptions!$C$45</f>
+      <c r="C16" s="21">
+        <f>(Assumptions!$C$39*C15)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5044,11 +5600,11 @@
         </is>
       </c>
       <c r="C17" s="15">
-        <f>(10*C15)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>(10*C15)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>(16*C15)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>(16*C15)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5072,7 +5628,7 @@
         </is>
       </c>
       <c r="C20" s="15">
-        <f>Assumptions!$C$52/Assumptions!$C$6</f>
+        <f>Assumptions!$C$54/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5082,19 +5638,19 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C21" s="34">
-        <f>(Assumptions!$C$38-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)</f>
+      <c r="C21" s="35">
+        <f>(Assumptions!$C$40-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Book lens — implied value (base)</t>
         </is>
       </c>
-      <c r="C22" s="32">
-        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$45</f>
+      <c r="C22" s="21">
+        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5105,11 +5661,11 @@
         </is>
       </c>
       <c r="C23" s="15">
-        <f>(((Assumptions!$C$38)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>(((Assumptions!$C$40)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="D23" s="15">
-        <f>(((Assumptions!$C$38)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$45</f>
+        <f>(((Assumptions!$C$40)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5178,7 +5734,7 @@
           <t>Normalised risk-free rate rf*</t>
         </is>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="33">
         <f>Assumptions!$C$9-Assumptions!$C$10</f>
         <v/>
       </c>
@@ -5189,7 +5745,7 @@
           <t>Cost of equity Ke</t>
         </is>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="33">
         <f>C5+Assumptions!$C$12*Assumptions!$C$11</f>
         <v/>
       </c>
@@ -5200,7 +5756,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="33">
         <f>Assumptions!$C$13*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -5211,7 +5767,7 @@
           <t>Market capitalisation</t>
         </is>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="19">
         <f>Assumptions!$C$5*Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5222,18 +5778,18 @@
           <t>Net-debt weight</t>
         </is>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="33">
         <f>Assumptions!$C$7/(Assumptions!$C$7+C8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>WACC — explicit window</t>
         </is>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="36">
         <f>(1-C9)*C6+C9*C7</f>
         <v/>
       </c>
@@ -5244,7 +5800,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="33">
         <f>Assumptions!$C$16+Assumptions!$C$18*Assumptions!$C$17</f>
         <v/>
       </c>
@@ -5255,18 +5811,18 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="33">
         <f>Assumptions!$C$19*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>WACC — terminal</t>
         </is>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="36">
         <f>(1-Assumptions!$C$20)*C11+Assumptions!$C$20*C12</f>
         <v/>
       </c>
@@ -5291,27 +5847,28 @@
           <t>SAR mn</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
@@ -5323,23 +5880,23 @@
           <t>Glide fraction (from Kd path)</t>
         </is>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="37">
         <f>(Assumptions!C$32-Assumptions!C$32)/(Assumptions!C$32-Assumptions!G$32)</f>
         <v/>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="37">
         <f>(Assumptions!C$32-Assumptions!D$32)/(Assumptions!C$32-Assumptions!G$32)</f>
         <v/>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="37">
         <f>(Assumptions!C$32-Assumptions!E$32)/(Assumptions!C$32-Assumptions!G$32)</f>
         <v/>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="37">
         <f>(Assumptions!C$32-Assumptions!F$32)/(Assumptions!C$32-Assumptions!G$32)</f>
         <v/>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="37">
         <f>(Assumptions!C$32-Assumptions!G$32)/(Assumptions!C$32-Assumptions!G$32)</f>
         <v/>
       </c>
@@ -5350,23 +5907,23 @@
           <t>Forward WACC</t>
         </is>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="33">
         <f>C10-(C10-C13)*C17</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="33">
         <f>C10-(C10-C13)*D17</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="33">
         <f>C10-(C10-C13)*E17</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="33">
         <f>C10-(C10-C13)*F17</f>
         <v/>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="33">
         <f>C10-(C10-C13)*G17</f>
         <v/>
       </c>
@@ -5377,23 +5934,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="37">
         <f>1/(1+C18)</f>
         <v/>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="37">
         <f>C19/(1+D18)</f>
         <v/>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="37">
         <f>D19/(1+E18)</f>
         <v/>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="37">
         <f>E19/(1+F18)</f>
         <v/>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="37">
         <f>F19/(1+G18)</f>
         <v/>
       </c>
@@ -5405,23 +5962,23 @@
         </is>
       </c>
       <c r="C20" s="14">
-        <f>Segments!C16</f>
+        <f>Segments!C19</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f>Segments!D16</f>
+        <f>Segments!D19</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>Segments!E16</f>
+        <f>Segments!E19</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>Segments!F16</f>
+        <f>Segments!F19</f>
         <v/>
       </c>
       <c r="G20" s="14">
-        <f>Segments!G16</f>
+        <f>Segments!G19</f>
         <v/>
       </c>
     </row>
@@ -5431,23 +5988,23 @@
           <t>NOPAT = EBIT x (1 - tax)</t>
         </is>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="19">
         <f>C20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="19">
         <f>D20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="19">
         <f>E20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="19">
         <f>F20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="19">
         <f>G20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -5459,23 +6016,23 @@
         </is>
       </c>
       <c r="C22" s="14">
-        <f>Segments!C15</f>
+        <f>Segments!C18</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>Segments!D15</f>
+        <f>Segments!D18</f>
         <v/>
       </c>
       <c r="E22" s="14">
-        <f>Segments!E15</f>
+        <f>Segments!E18</f>
         <v/>
       </c>
       <c r="F22" s="14">
-        <f>Segments!F15</f>
+        <f>Segments!F18</f>
         <v/>
       </c>
       <c r="G22" s="14">
-        <f>Segments!G15</f>
+        <f>Segments!G18</f>
         <v/>
       </c>
     </row>
@@ -5486,23 +6043,23 @@
         </is>
       </c>
       <c r="C23" s="14">
-        <f>Segments!C12</f>
+        <f>Segments!C15</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>Segments!D12</f>
+        <f>Segments!D15</f>
         <v/>
       </c>
       <c r="E23" s="14">
-        <f>Segments!E12</f>
+        <f>Segments!E15</f>
         <v/>
       </c>
       <c r="F23" s="14">
-        <f>Segments!F12</f>
+        <f>Segments!F15</f>
         <v/>
       </c>
       <c r="G23" s="14">
-        <f>Segments!G12</f>
+        <f>Segments!G15</f>
         <v/>
       </c>
     </row>
@@ -5512,23 +6069,23 @@
           <t>- Capital expenditure</t>
         </is>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="19">
         <f>Assumptions!C$30*C23</f>
         <v/>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="19">
         <f>Assumptions!D$30*D23</f>
         <v/>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="19">
         <f>Assumptions!E$30*E23</f>
         <v/>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="19">
         <f>Assumptions!F$30*F23</f>
         <v/>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="19">
         <f>Assumptions!G$30*G23</f>
         <v/>
       </c>
@@ -5539,23 +6096,23 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="19">
         <f>Assumptions!$C$31*C23</f>
         <v/>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="19">
         <f>Assumptions!$C$31*D23</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="19">
         <f>Assumptions!$C$31*E23</f>
         <v/>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="19">
         <f>Assumptions!$C$31*F23</f>
         <v/>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="19">
         <f>Assumptions!$C$31*G23</f>
         <v/>
       </c>
@@ -5566,50 +6123,50 @@
           <t>- Change in working capital</t>
         </is>
       </c>
-      <c r="C26" s="28">
-        <f>C25-Assumptions!$C$49</f>
-        <v/>
-      </c>
-      <c r="D26" s="28">
+      <c r="C26" s="19">
+        <f>C25-Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="D26" s="19">
         <f>D25-C25</f>
         <v/>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="19">
         <f>E25-D25</f>
         <v/>
       </c>
-      <c r="F26" s="28">
+      <c r="F26" s="19">
         <f>F25-E25</f>
         <v/>
       </c>
-      <c r="G26" s="28">
+      <c r="G26" s="19">
         <f>G25-F25</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Free cash flow to firm</t>
         </is>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="38">
         <f>C21+C22-C24-C26</f>
         <v/>
       </c>
-      <c r="D27" s="37">
+      <c r="D27" s="38">
         <f>D21+D22-D24-D26</f>
         <v/>
       </c>
-      <c r="E27" s="37">
+      <c r="E27" s="38">
         <f>E21+E22-E24-E26</f>
         <v/>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="38">
         <f>F21+F22-F24-F26</f>
         <v/>
       </c>
-      <c r="G27" s="37">
+      <c r="G27" s="38">
         <f>G21+G22-G24-G26</f>
         <v/>
       </c>
@@ -5620,23 +6177,23 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="19">
         <f>C27*C19</f>
         <v/>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="19">
         <f>D27*D19</f>
         <v/>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="19">
         <f>E27*E19</f>
         <v/>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="19">
         <f>F27*F19</f>
         <v/>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="19">
         <f>G27*G19</f>
         <v/>
       </c>
@@ -5661,23 +6218,23 @@
           <t>PP&amp;E roll-forward</t>
         </is>
       </c>
-      <c r="C31" s="28">
-        <f>Assumptions!$C$50+C24-C22</f>
-        <v/>
-      </c>
-      <c r="D31" s="28">
+      <c r="C31" s="19">
+        <f>Assumptions!$C$52+C24-C22</f>
+        <v/>
+      </c>
+      <c r="D31" s="19">
         <f>C31+D24-D22</f>
         <v/>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="19">
         <f>D31+E24-E22</f>
         <v/>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="19">
         <f>E31+F24-F22</f>
         <v/>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="19">
         <f>F31+G24-G22</f>
         <v/>
       </c>
@@ -5688,23 +6245,23 @@
           <t>Invested capital = NWC + PP&amp;E</t>
         </is>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="19">
         <f>C25+C31</f>
         <v/>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="19">
         <f>D25+D31</f>
         <v/>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="19">
         <f>E25+E31</f>
         <v/>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="19">
         <f>F25+F31</f>
         <v/>
       </c>
-      <c r="G32" s="28">
+      <c r="G32" s="19">
         <f>G25+G31</f>
         <v/>
       </c>
@@ -5715,23 +6272,23 @@
           <t>ROIC = NOPAT / invested capital</t>
         </is>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="33">
         <f>C21/C32</f>
         <v/>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="33">
         <f>D21/D32</f>
         <v/>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="33">
         <f>E21/E32</f>
         <v/>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="33">
         <f>F21/F32</f>
         <v/>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="33">
         <f>G21/G32</f>
         <v/>
       </c>
@@ -5742,7 +6299,7 @@
           <t>PV of explicit FCFF (5 years)</t>
         </is>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="19">
         <f>SUM(C28:G28)</f>
         <v/>
       </c>
@@ -5753,7 +6310,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="33">
         <f>G21*(1+Assumptions!$C$21)/G32</f>
         <v/>
       </c>
@@ -5764,7 +6321,7 @@
           <t>Terminal reinvestment rate = g / ROIC</t>
         </is>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="33">
         <f>Assumptions!$C$21/C36</f>
         <v/>
       </c>
@@ -5775,7 +6332,7 @@
           <t>Terminal NOPAT (next year)</t>
         </is>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="19">
         <f>G21*(1+Assumptions!$C$21)</f>
         <v/>
       </c>
@@ -5786,7 +6343,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="19">
         <f>C38*(1-C37)/(C13-Assumptions!$C$21)</f>
         <v/>
       </c>
@@ -5797,29 +6354,29 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="19">
         <f>C39*G19</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C41" s="37">
+      <c r="C41" s="38">
         <f>C35+C40</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="31" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Terminal value as % of EV</t>
         </is>
       </c>
-      <c r="C42" s="38">
+      <c r="C42" s="39">
         <f>C40/C41</f>
         <v/>
       </c>
@@ -5844,7 +6401,7 @@
           <t>Less: net financial debt</t>
         </is>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="19">
         <f>-Assumptions!$C$7</f>
         <v/>
       </c>
@@ -5855,8 +6412,8 @@
           <t>Add: associates + non-operating assets</t>
         </is>
       </c>
-      <c r="C46" s="28">
-        <f>Assumptions!$C$53+Assumptions!$C$54</f>
+      <c r="C46" s="19">
+        <f>Assumptions!$C$55+Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
@@ -5866,18 +6423,18 @@
           <t>Less: non-controlling interests</t>
         </is>
       </c>
-      <c r="C47" s="28">
-        <f>-Assumptions!$C$55</f>
+      <c r="C47" s="19">
+        <f>-Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>Equity attributable (31-Dec-2025)</t>
         </is>
       </c>
-      <c r="C48" s="37">
+      <c r="C48" s="38">
         <f>C41+C45+C46+C47</f>
         <v/>
       </c>
@@ -5899,19 +6456,19 @@
           <t>Anchor accretion factor</t>
         </is>
       </c>
-      <c r="C50" s="36">
-        <f>(1+C6)^(Assumptions!$C$44/365)</f>
+      <c r="C50" s="37">
+        <f>(1+C6)^(Assumptions!$C$46/365)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>Value per share at anchor (18-Aug-2026)</t>
         </is>
       </c>
-      <c r="C51" s="32">
-        <f>C49*C50-Assumptions!$C$45</f>
+      <c r="C51" s="21">
+        <f>C49*C50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5947,7 +6504,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>88.81423921232683</v>
+        <v>78.52014039378953</v>
       </c>
     </row>
     <row r="56">
@@ -5968,7 +6525,7 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>236.7719302390979</v>
+        <v>188.2848029277439</v>
       </c>
     </row>
   </sheetData>
@@ -6026,42 +6583,43 @@
           <t>SAR mn</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -6073,33 +6631,33 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="23" t="n">
         <v>7825.378127</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="23" t="n">
         <v>9007.360866999999</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="23" t="n">
         <v>10673.604262</v>
       </c>
       <c r="F5" s="14">
-        <f>Segments!C12</f>
+        <f>Segments!C15</f>
         <v/>
       </c>
       <c r="G5" s="14">
-        <f>Segments!D12</f>
+        <f>Segments!D15</f>
         <v/>
       </c>
       <c r="H5" s="14">
-        <f>Segments!E12</f>
+        <f>Segments!E15</f>
         <v/>
       </c>
       <c r="I5" s="14">
-        <f>Segments!F12</f>
+        <f>Segments!F15</f>
         <v/>
       </c>
       <c r="J5" s="14">
-        <f>Segments!G12</f>
+        <f>Segments!G15</f>
         <v/>
       </c>
     </row>
@@ -6109,33 +6667,33 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="23" t="n">
         <v>972.763438</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="23" t="n">
         <v>1286.522351</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="23" t="n">
         <v>1733.329855</v>
       </c>
       <c r="F6" s="14">
-        <f>Segments!C13</f>
+        <f>Segments!C14</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>Segments!D13</f>
+        <f>Segments!D14</f>
         <v/>
       </c>
       <c r="H6" s="14">
-        <f>Segments!E13</f>
+        <f>Segments!E14</f>
         <v/>
       </c>
       <c r="I6" s="14">
-        <f>Segments!F13</f>
+        <f>Segments!F14</f>
         <v/>
       </c>
       <c r="J6" s="14">
-        <f>Segments!G13</f>
+        <f>Segments!G14</f>
         <v/>
       </c>
     </row>
@@ -6145,35 +6703,35 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="33">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="33">
         <f>D6/D5</f>
         <v/>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="33">
         <f>E6/E5</f>
         <v/>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="33">
         <f>F6/F5</f>
         <v/>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="33">
         <f>G6/G5</f>
         <v/>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="33">
         <f>H6/H5</f>
         <v/>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="33">
         <f>I6/I5</f>
         <v/>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="33">
         <f>J6/J5</f>
         <v/>
       </c>
@@ -6184,36 +6742,36 @@
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="19">
         <f>C6-C11</f>
         <v/>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="19">
         <f>D6-D11</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="19">
         <f>E6-E11</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>Segments!C14</f>
+        <f>Segments!C17</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>Segments!D14</f>
+        <f>Segments!D17</f>
         <v/>
       </c>
       <c r="H8" s="14">
-        <f>Segments!E14</f>
+        <f>Segments!E17</f>
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>Segments!F14</f>
+        <f>Segments!F17</f>
         <v/>
       </c>
       <c r="J8" s="14">
-        <f>Segments!G14</f>
+        <f>Segments!G17</f>
         <v/>
       </c>
     </row>
@@ -6223,36 +6781,36 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="19">
         <f>C11+C10</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="19">
         <f>D11+D10</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="19">
         <f>E11+E10</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>Segments!C17</f>
+        <f>Segments!C20</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>Segments!D17</f>
+        <f>Segments!D20</f>
         <v/>
       </c>
       <c r="H9" s="14">
-        <f>Segments!E17</f>
+        <f>Segments!E20</f>
         <v/>
       </c>
       <c r="I9" s="14">
-        <f>Segments!F17</f>
+        <f>Segments!F20</f>
         <v/>
       </c>
       <c r="J9" s="14">
-        <f>Segments!G17</f>
+        <f>Segments!G20</f>
         <v/>
       </c>
     </row>
@@ -6262,33 +6820,33 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="23" t="n">
+        <v>66.428122</v>
+      </c>
+      <c r="D10" s="23" t="n">
         <v>68.643861</v>
       </c>
-      <c r="D10" s="19" t="n">
-        <v>68.643861</v>
-      </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="23" t="n">
         <v>85.39563699999999</v>
       </c>
       <c r="F10" s="14">
-        <f>Segments!C15</f>
+        <f>Segments!C18</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Segments!D15</f>
+        <f>Segments!D18</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Segments!E15</f>
+        <f>Segments!E18</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Segments!F15</f>
+        <f>Segments!F18</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Segments!G15</f>
+        <f>Segments!G18</f>
         <v/>
       </c>
     </row>
@@ -6298,33 +6856,33 @@
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="23" t="n">
         <v>647.606782</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="23" t="n">
         <v>968.439154</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="23" t="n">
         <v>1266.636844</v>
       </c>
       <c r="F11" s="14">
-        <f>Segments!C16</f>
+        <f>Segments!C19</f>
         <v/>
       </c>
       <c r="G11" s="14">
-        <f>Segments!D16</f>
+        <f>Segments!D19</f>
         <v/>
       </c>
       <c r="H11" s="14">
-        <f>Segments!E16</f>
+        <f>Segments!E19</f>
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>Segments!F16</f>
+        <f>Segments!F19</f>
         <v/>
       </c>
       <c r="J11" s="14">
-        <f>Segments!G16</f>
+        <f>Segments!G19</f>
         <v/>
       </c>
     </row>
@@ -6334,13 +6892,13 @@
           <t>Net finance cost</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="23" t="n">
         <v>-89.01433400000001</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="23" t="n">
         <v>-87.66669899999999</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="23" t="n">
         <v>-74.15399499999999</v>
       </c>
       <c r="F12" s="14">
@@ -6370,35 +6928,35 @@
           <t>Profit before zakat</t>
         </is>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="19">
         <f>C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="19">
         <f>D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="19">
         <f>E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="19">
         <f>F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="19">
         <f>G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="19">
         <f>H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="19">
         <f>I11+I12</f>
         <v/>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="19">
         <f>J11+J12</f>
         <v/>
       </c>
@@ -6409,32 +6967,32 @@
           <t>Zakat &amp; income tax</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="23" t="n">
         <v>-39.126206</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="23" t="n">
         <v>-63.891298</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="23" t="n">
         <v>-107.681788</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="19">
         <f>-F13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="19">
         <f>-G13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="19">
         <f>-H13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="19">
         <f>-I13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="19">
         <f>-J13*Assumptions!$C$14</f>
         <v/>
       </c>
@@ -6445,32 +7003,32 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="23" t="n">
         <v>518.492623</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="23" t="n">
         <v>816.881157</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="23" t="n">
         <v>1084.801061</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="19">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="19">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="19">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="19">
         <f>I13+I14</f>
         <v/>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="19">
         <f>J13+J14</f>
         <v/>
       </c>
@@ -6481,7 +7039,7 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="23" t="n">
         <v>1080.396042</v>
       </c>
       <c r="F16" s="14">

--- a/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
+++ b/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -135,10 +135,15 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,11 +151,7 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -521,9 +522,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="116" customWidth="1" min="1" max="1"/>
@@ -662,83 +663,87 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>bounds, the two pasted framings of the contested gross-margin judgement, and the expert-panel median.</t>
+          <t>bounds, and the pasted alternate framings of the contested gross-margin judgement. Everything else — every</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Everything else — every lens base value, the relative/normalised/book bear and bull bounds, and the anchor</t>
+          <t>lens base value and bound, the whole worked expert panel and its median, every ratio, and the anchor roll —</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>roll — is a live formula. Changing a driver reprices the model but does NOT redraw the engine outputs.</t>
+          <t>is a live formula. Changing a driver reprices the model but does NOT redraw the engine outputs; every</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>pasted grid's base row is asserted at build time to reproduce the live base case.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>How revenue is built. Not as one growth rate. A cable maker is a metal converter: materials (copper and</t>
-        </is>
-      </c>
+      <c r="A24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>aluminium) are 94.9% of cost of revenue. The build prices a tonnage index as metal content — on its own</t>
+          <t>How revenue is built, and how to test it. A cable maker is a metal converter: materials (copper and</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>commodity path — plus a conversion spread whose cost escalates on domestic inflation; gross margin is the</t>
+          <t>aluminium) are 94.9% of cost of revenue. The Segments sheet builds a tonnage index times a metal price on</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>OUTPUT of that stack, not an input. The central judgement is the margin the business sustains once the</t>
+          <t>its own path, plus conversion cost on domestic inflation, plus a CONVERSION SPREAD PER TONNE calibrated to</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>FY2024-25 metal tailwind has passed, anchored on the most recent reviewed actual (H1-2026, 15.26%) rather</t>
+          <t>the margin-anchor path at the BASE metal price and held fixed under metal shocks. The gross margin row is</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>than the higher FY2025 full-year print (16.24%), and computed both ways.</t>
+          <t>therefore an OUTPUT: set the metal price multiplier on Assumptions above 1.00 and watch revenue rise while</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>the margin dilutes and the value falls — the H1-2026 mechanism (flat gross profit on +9.5% revenue). The</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>margin anchor is the reviewed H1-2026 actual (15.26%), not the higher FY2025 print (16.24%), and the</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges.</t>
+          <t>contested judgement is computed both ways plus at the Q2-2026 exit rate (14.99%).</t>
         </is>
       </c>
     </row>
@@ -748,59 +753,105 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Sourcing. FY2022-FY2025 come from the company's own audited consolidated financial statements (KPMG); the</t>
+          <t>Conventions. Year-end discounting, annual compounding (mid-year would raise the DCF lens ~4%). WACC weights</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>FY2026 near-term anchor is the Tadawul-filed reviewed H1-2026 interim. Every input is listed with source and</t>
+          <t>use net financial debt, consistent with the net-debt bridge. Beta 1.129 is a Dimson sum-beta on 185 weekly</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>date in the companion bibliography document. No aggregator or broker figure is a build source.</t>
+          <t>observations (plain OLS 0.928; 90% CI 0.62-1.64 — the grid prices the width). The terminal is discounted</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>all-equity because the model itself forecasts net cash from FY2028E.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Currency. SAR million unless stated. Spot SAR 104.80 (2026-08-18 close). Sheets: READ FIRST · Summary ·</t>
-        </is>
-      </c>
+      <c r="A38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>shown as ranges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sourcing. FY2022-FY2025 come from the company's own audited consolidated financial statements (KPMG); the</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>FY2026 near-term anchor is the Tadawul-filed reviewed H1-2026 interim. Every input is listed with source and</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>date in the companion bibliography document. No aggregator or broker figure is a build source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Currency. SAR million unless stated. Spot SAR 104.90 (2026-08-18 close). Sheets: READ FIRST · Summary ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
           <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -808,7 +859,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -902,13 +953,13 @@
           <t>Property, plant &amp; equipment</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="23" t="n">
         <v>1206.659875</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="23" t="n">
         <v>1336.038944</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="23" t="n">
         <v>1491.86312</v>
       </c>
       <c r="F5" s="14">
@@ -938,13 +989,13 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="23" t="n">
         <v>1909.11144</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="23" t="n">
         <v>2126.036688</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="23" t="n">
         <v>2411.049305</v>
       </c>
     </row>
@@ -954,13 +1005,13 @@
           <t>Trade &amp; other receivables</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="23" t="n">
         <v>1418.920843</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="23" t="n">
         <v>2112.098567</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="23" t="n">
         <v>2712.677113</v>
       </c>
     </row>
@@ -970,13 +1021,13 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="23" t="n">
         <v>150.051628</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="23" t="n">
         <v>90.672725</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="23" t="n">
         <v>236.043009</v>
       </c>
     </row>
@@ -986,13 +1037,13 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="23" t="n">
         <v>4830.929068</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="23" t="n">
         <v>5811.584098</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="23" t="n">
         <v>7281.581695</v>
       </c>
     </row>
@@ -1002,33 +1053,33 @@
           <t>Gross borrowings incl. leases</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="23" t="n">
         <v>730.611837</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="23" t="n">
         <v>440.445599</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="23" t="n">
         <v>621.216217</v>
       </c>
       <c r="F10" s="14">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
@@ -1038,13 +1089,13 @@
           <t>Trade &amp; other payables</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="23" t="n">
         <v>1486.905974</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="23" t="n">
         <v>2040.707151</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="23" t="n">
         <v>2190.467493</v>
       </c>
     </row>
@@ -1054,13 +1105,13 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="23" t="n">
         <v>1841.126309</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="23" t="n">
         <v>2197.428104</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="23" t="n">
         <v>2933.258925</v>
       </c>
       <c r="F12" s="14">
@@ -1090,13 +1141,13 @@
           <t>Net financial debt</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="23" t="n">
         <v>580.560209</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="23" t="n">
         <v>349.772874</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="23" t="n">
         <v>385.173208</v>
       </c>
       <c r="F13" s="14">
@@ -1126,13 +1177,13 @@
           <t>Equity attributable</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="23" t="n">
         <v>2246.744341</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="23" t="n">
         <v>2624.35365</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="23" t="n">
         <v>3246.136935</v>
       </c>
       <c r="F14" s="14">
@@ -1178,23 +1229,23 @@
           <t>Net debt, start of year</t>
         </is>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="19">
         <f>Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="19">
         <f>C24</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="19">
         <f>D24</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="19">
         <f>E24</f>
         <v/>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="19">
         <f>F24</f>
         <v/>
       </c>
@@ -1205,24 +1256,24 @@
           <t>Surplus cash</t>
         </is>
       </c>
-      <c r="C18" s="29">
-        <f>Assumptions!$C$60-C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="29">
-        <f>Assumptions!$C$60-D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="29">
-        <f>Assumptions!$C$60-E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="29">
-        <f>Assumptions!$C$60-F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="29">
-        <f>Assumptions!$C$60-G17</f>
+      <c r="C18" s="19">
+        <f>Assumptions!$C$53-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="19">
+        <f>Assumptions!$C$53-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="19">
+        <f>Assumptions!$C$53-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="19">
+        <f>Assumptions!$C$53-F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="19">
+        <f>Assumptions!$C$53-G17</f>
         <v/>
       </c>
     </row>
@@ -1232,24 +1283,24 @@
           <t>Net interest</t>
         </is>
       </c>
-      <c r="C19" s="29">
-        <f>Assumptions!C$38*Assumptions!$C$60-Assumptions!$C$40*MAX(C18,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="29">
-        <f>Assumptions!D$38*Assumptions!$C$60-Assumptions!$C$40*MAX(D18,0)</f>
-        <v/>
-      </c>
-      <c r="E19" s="29">
-        <f>Assumptions!E$38*Assumptions!$C$60-Assumptions!$C$40*MAX(E18,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="29">
-        <f>Assumptions!F$38*Assumptions!$C$60-Assumptions!$C$40*MAX(F18,0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="29">
-        <f>Assumptions!G$38*Assumptions!$C$60-Assumptions!$C$40*MAX(G18,0)</f>
+      <c r="C19" s="19">
+        <f>Assumptions!C$32*Assumptions!$C$53-Assumptions!$C$34*MAX(C18,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="19">
+        <f>Assumptions!D$32*Assumptions!$C$53-Assumptions!$C$34*MAX(D18,0)</f>
+        <v/>
+      </c>
+      <c r="E19" s="19">
+        <f>Assumptions!E$32*Assumptions!$C$53-Assumptions!$C$34*MAX(E18,0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="19">
+        <f>Assumptions!F$32*Assumptions!$C$53-Assumptions!$C$34*MAX(F18,0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="19">
+        <f>Assumptions!G$32*Assumptions!$C$53-Assumptions!$C$34*MAX(G18,0)</f>
         <v/>
       </c>
     </row>
@@ -1286,23 +1337,23 @@
           <t>Profit before zakat</t>
         </is>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="19">
         <f>C20-C19</f>
         <v/>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="19">
         <f>D20-D19</f>
         <v/>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="19">
         <f>E20-E19</f>
         <v/>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="19">
         <f>F20-F19</f>
         <v/>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="19">
         <f>G20-G19</f>
         <v/>
       </c>
@@ -1313,24 +1364,24 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="C22" s="29">
-        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
-        <v/>
-      </c>
-      <c r="D22" s="29">
-        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
-        <v/>
-      </c>
-      <c r="E22" s="29">
-        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
-        <v/>
-      </c>
-      <c r="F22" s="29">
-        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
-        <v/>
-      </c>
-      <c r="G22" s="29">
-        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
+      <c r="C22" s="19">
+        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
+        <v/>
+      </c>
+      <c r="D22" s="19">
+        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
+        <v/>
+      </c>
+      <c r="E22" s="19">
+        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
+        <v/>
+      </c>
+      <c r="F22" s="19">
+        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
+        <v/>
+      </c>
+      <c r="G22" s="19">
+        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
         <v/>
       </c>
     </row>
@@ -1340,24 +1391,24 @@
           <t>Dividend</t>
         </is>
       </c>
-      <c r="C23" s="29">
-        <f>Assumptions!$C$39*C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="29">
-        <f>Assumptions!$C$39*D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="29">
-        <f>Assumptions!$C$39*E22</f>
-        <v/>
-      </c>
-      <c r="F23" s="29">
-        <f>Assumptions!$C$39*F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="29">
-        <f>Assumptions!$C$39*G22</f>
+      <c r="C23" s="19">
+        <f>Assumptions!$C$33*C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="19">
+        <f>Assumptions!$C$33*D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="19">
+        <f>Assumptions!$C$33*E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="19">
+        <f>Assumptions!$C$33*F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="19">
+        <f>Assumptions!$C$33*G22</f>
         <v/>
       </c>
     </row>
@@ -1367,23 +1418,23 @@
           <t>Net debt, end of year</t>
         </is>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="19">
         <f>C17-(DCF!C27-C19*(1-Assumptions!$C$14))+C23</f>
         <v/>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="19">
         <f>D17-(DCF!D27-D19*(1-Assumptions!$C$14))+D23</f>
         <v/>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="19">
         <f>E17-(DCF!E27-E19*(1-Assumptions!$C$14))+E23</f>
         <v/>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="19">
         <f>F17-(DCF!F27-F19*(1-Assumptions!$C$14))+F23</f>
         <v/>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="19">
         <f>G17-(DCF!G27-G19*(1-Assumptions!$C$14))+G23</f>
         <v/>
       </c>
@@ -1394,31 +1445,29 @@
           <t>Equity attributable</t>
         </is>
       </c>
-      <c r="C25" s="29">
-        <f>Assumptions!$C$61+C22-C23</f>
-        <v/>
-      </c>
-      <c r="D25" s="29">
+      <c r="C25" s="19">
+        <f>Assumptions!$C$54+C22-C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="19">
         <f>C25+D22-D23</f>
         <v/>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="19">
         <f>D25+E22-E23</f>
         <v/>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="19">
         <f>E25+F22-F23</f>
         <v/>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="19">
         <f>F25+G22-G23</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1426,7 +1475,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1609,23 +1658,23 @@
           <t>Free cash flow to firm</t>
         </is>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="38">
         <f>C5+C6+C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="38">
         <f>D5+D6+D7+D8</f>
         <v/>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="38">
         <f>E5+E6+E7+E8</f>
         <v/>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="38">
         <f>F5+F6+F7+F8</f>
         <v/>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="38">
         <f>G5+G6+G7+G8</f>
         <v/>
       </c>
@@ -1636,23 +1685,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="40">
         <f>DCF!C19</f>
         <v/>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="40">
         <f>DCF!D19</f>
         <v/>
       </c>
-      <c r="E10" s="39">
+      <c r="E10" s="40">
         <f>DCF!E19</f>
         <v/>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="40">
         <f>DCF!F19</f>
         <v/>
       </c>
-      <c r="G10" s="39">
+      <c r="G10" s="40">
         <f>DCF!G19</f>
         <v/>
       </c>
@@ -1663,31 +1712,29 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="19">
         <f>C9*C10</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="19">
         <f>D9*D10</f>
         <v/>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="19">
         <f>E9*E10</f>
         <v/>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="19">
         <f>F9*F10</f>
         <v/>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="19">
         <f>G9*G10</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1695,7 +1742,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1798,23 +1845,23 @@
         </is>
       </c>
       <c r="C6" s="14">
-        <f>Segments!C32</f>
+        <f>Segments!C20</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>Segments!D32</f>
+        <f>Segments!D20</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>Segments!E32</f>
+        <f>Segments!E20</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>Segments!F32</f>
+        <f>Segments!F20</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>Segments!G32</f>
+        <f>Segments!G20</f>
         <v/>
       </c>
     </row>
@@ -1905,31 +1952,29 @@
           <t>ROIC</t>
         </is>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="18">
         <f>DCF!C33</f>
         <v/>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="18">
         <f>DCF!D33</f>
         <v/>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="18">
         <f>DCF!E33</f>
         <v/>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="18">
         <f>DCF!F33</f>
         <v/>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="18">
         <f>DCF!G33</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1937,7 +1982,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1993,10 +2038,10 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>87.21321014037129</v>
+        <v>87.25808430972248</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>76.54888951524968</v>
+        <v>76.53735505038735</v>
       </c>
     </row>
     <row r="6">
@@ -2006,10 +2051,10 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>97.61126202615651</v>
+        <v>97.66760169647281</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>92.86909864606133</v>
+        <v>92.86041807876856</v>
       </c>
     </row>
     <row r="7">
@@ -2019,10 +2064,10 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>104.7866044705799</v>
+        <v>104.8512200742135</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>105.0593696127112</v>
+        <v>105.053385509702</v>
       </c>
     </row>
     <row r="8">
@@ -2032,10 +2077,10 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>112.6160892961509</v>
+        <v>112.6900469186186</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>118.7094846328782</v>
+        <v>118.7070159704662</v>
       </c>
     </row>
     <row r="9">
@@ -2045,10 +2090,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>126.1767140981632</v>
+        <v>126.2675579273705</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>144.0563430692076</v>
+        <v>144.0616010928045</v>
       </c>
     </row>
     <row r="10">
@@ -2058,10 +2103,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>104.8</v>
+        <v>104.9</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>104.8</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="11">
@@ -2070,11 +2115,11 @@
           <t>P(above spot)</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
-        <v>0.4997</v>
-      </c>
-      <c r="C11" s="23" t="n">
-        <v>0.50542</v>
+      <c r="B11" s="28" t="n">
+        <v>0.49836</v>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>0.50322</v>
       </c>
     </row>
     <row r="12">
@@ -2083,11 +2128,11 @@
           <t>Annualised vol</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
-        <v>0.3614703996629836</v>
-      </c>
-      <c r="C12" s="23" t="n">
-        <v>0.3670575648854793</v>
+      <c r="B12" s="28" t="n">
+        <v>0.3616713439785802</v>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>0.3671662360524218</v>
       </c>
     </row>
     <row r="14">
@@ -2098,9 +2143,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2108,12 +2151,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -2140,12 +2183,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Each cell is a complete revaluation and does NOT redraw when a driver changes</t>
+          <t>Each cell is a complete revaluation and does NOT redraw when a driver changes; every block's base row REPRODUCES the base case (asserted at build time)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>DCF value per share: terminal WACC (rows) x terminal growth (cols)</t>
         </is>
@@ -2182,404 +2225,463 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=7.48%</t>
+          <t>WACC_t=7.72%</t>
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>141.7056057772044</v>
+        <v>136.5639956911652</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>163.715865885987</v>
+        <v>156.3911656162713</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>198.2042805447696</v>
+        <v>186.7266093183625</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>260.2479130974581</v>
-      </c>
-      <c r="F6" s="40" t="inlineStr">
-        <is>
-          <t>n.m.</t>
+        <v>239.1603346397014</v>
+      </c>
+      <c r="F6" s="41" t="inlineStr">
+        <is>
+          <t>n/m</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=8.48%</t>
+          <t>WACC_t=8.72%</t>
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>120.4623841952295</v>
+        <v>116.8034962931929</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>134.7210292900971</v>
+        <v>129.8409494659834</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>155.2188360125738</v>
+        <v>148.2860612426722</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>187.3299521235833</v>
+        <v>176.4998466264028</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>245.0864687133326</v>
+        <v>225.2565779778832</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=9.48%</t>
+          <t>WACC_t=9.72%</t>
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>104.8967296610403</v>
+        <v>102.163054852874</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>114.6678051971448</v>
+        <v>111.1904287412299</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>127.905424577565</v>
+        <v>123.2801134487121</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>146.9294453787323</v>
+        <v>140.3784929705279</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>176.7240270270523</v>
+        <v>166.5248373182366</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=10.48%</t>
+          <t>WACC_t=10.72%</t>
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>93.00059958544631</v>
+        <v>90.88100527108116</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>99.97128853350969</v>
+        <v>97.36966430899766</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>109.0117190503424</v>
+        <v>105.7111587372711</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>121.2543672012037</v>
+        <v>116.8772553690259</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>138.8421999218402</v>
+        <v>132.6632522149492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=11.48%</t>
+          <t>WACC_t=11.72%</t>
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>83.61297829887353</v>
+        <v>81.92065637634063</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>88.73699993247544</v>
+        <v>86.71695307455919</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>95.16215451155131</v>
+        <v>92.68916241571443</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>103.4905512602372</v>
+        <v>100.3622454011173</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>114.7635647327278</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>Beta sensitivity (DCF value/share)</t>
+        <v>110.6282686274013</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>n/m: terminal spread (WACC_t - g) below 2% — the Gordon terminal value is not meaningful there and no number is shown (the first edition printed clamped values).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="n">
-        <v>134.1012811749074</v>
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Risk-free rate (10y SAR; explicit AND terminal move together) — DCF value/share</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>5.02%</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>131.1659864625187</v>
+        <v>136.089531512596</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1.129</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>127.905424577565</v>
+        <v>123.2801134487121</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>6.02%</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>125.5381303609279</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n">
-        <v>122.8400164516531</v>
+        <v>112.5394948589756</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Beta (explicit-window Ke only; terminal beta held at 1.0 as stated) — DCF value/share</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>Metal price x sensitivity (DCF value/share)</t>
-        </is>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>129.2478439097057</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>139.3236347299058</v>
+        <v>126.4206730646305</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>1.129</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>133.6031807444171</v>
+        <v>123.2801134487121</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>127.905424577565</v>
+        <v>120.9998758649224</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>122.2278357157988</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>116.5683245327664</v>
+        <v>118.4009111655918</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Metal price x (flat multiplier; spread held — margin is the output) — DCF value/share</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>Sustained gross margin sensitivity (DCF value/share)</t>
-        </is>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>135.7206754924927</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.925</t>
         </is>
       </c>
       <c r="B27" s="17" t="n">
-        <v>108.4540646253059</v>
+        <v>129.5003944706025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="B28" s="17" t="n">
-        <v>116.1041350901616</v>
+        <v>123.2801134487121</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>0.1526</t>
+          <t>1.075</t>
         </is>
       </c>
       <c r="B29" s="17" t="n">
-        <v>127.905424577565</v>
+        <v>117.0598324268218</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="B30" s="17" t="n">
-        <v>131.6763234351193</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="n">
-        <v>139.6016853407702</v>
+        <v>110.8395514049315</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Sustained gross margin (0.1499 = the Q2-2026 exit rate) — DCF value/share</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>Volume x sensitivity (DCF value/share)</t>
-        </is>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>104.0336994130316</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>117.0795645368853</v>
+        <v>111.6031665507623</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.1499</t>
         </is>
       </c>
       <c r="B35" s="17" t="n">
-        <v>122.4970935834225</v>
+        <v>119.1077739641657</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.1526</t>
         </is>
       </c>
       <c r="B36" s="17" t="n">
-        <v>127.905424577565</v>
+        <v>123.2801134487121</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>133.3052385180974</v>
+        <v>127.0112805596384</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>138.6971354501409</v>
+        <v>134.8531372449724</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="inlineStr">
-        <is>
-          <t>Net working capital / revenue sensitivity (DCF value/share)</t>
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>Volume x — DCF value/share</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>133.5580939831738</v>
+        <v>112.7169531231438</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>130.7317592803693</v>
+        <v>118.0031768846487</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>127.905424577565</v>
+        <v>123.2801134487121</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>125.0790898747605</v>
+        <v>128.5484520748093</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>133.8087999793565</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Net working capital / revenue — DCF value/share</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>128.8502974586405</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>126.0652054536764</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>123.2801134487121</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n">
+        <v>120.4950214437479</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>0.32</t>
         </is>
       </c>
-      <c r="B45" s="17" t="n">
-        <v>122.2527551719562</v>
+      <c r="B52" s="17" t="n">
+        <v>117.7099294387837</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>The metal row matches the LIVE Segments sheet: set the metal price multiplier on Assumptions and the whole model reprices the same direction (higher metal dilutes the margin and lowers the value).</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2587,9 +2689,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2655,8 +2757,8 @@
           <t>EPS (SAR)</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>'Income Statement'!E16/Assumptions!$C$6</f>
+      <c r="B5" s="15">
+        <f>Assumptions!$C$58/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C5" s="15">
@@ -2687,7 +2789,7 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>Assumptions!$C$61/Assumptions!$C$6</f>
+        <f>Assumptions!$C$54/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C6" s="15">
@@ -2714,11 +2816,11 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>ROE (%) — attributable profit / average equity</t>
-        </is>
-      </c>
-      <c r="B7" s="8">
-        <f>'Income Statement'!E16/AVERAGE('Balance Sheet'!D14,'Balance Sheet'!E14)</f>
+          <t>ROE (%, on average equity)</t>
+        </is>
+      </c>
+      <c r="B7" s="9">
+        <f>Assumptions!$C$58/((Assumptions!$C$59+Assumptions!$C$54)/2)</f>
         <v/>
       </c>
     </row>
@@ -2728,57 +2830,66 @@
           <t>Net debt / EBITDA (x)</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="35">
         <f>Assumptions!$C$7/'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="C8" s="34">
-        <f>'Balance Sheet'!F13/Segments!C32</f>
-        <v/>
-      </c>
-      <c r="D8" s="34">
-        <f>'Balance Sheet'!G13/Segments!D32</f>
-        <v/>
-      </c>
-      <c r="E8" s="34">
-        <f>'Balance Sheet'!H13/Segments!E32</f>
-        <v/>
-      </c>
-      <c r="F8" s="34">
-        <f>'Balance Sheet'!I13/Segments!F32</f>
-        <v/>
-      </c>
-      <c r="G8" s="34">
-        <f>'Balance Sheet'!J13/Segments!G32</f>
+      <c r="C8" s="35">
+        <f>'Balance Sheet'!F13/Segments!C20</f>
+        <v/>
+      </c>
+      <c r="D8" s="35">
+        <f>'Balance Sheet'!G13/Segments!D20</f>
+        <v/>
+      </c>
+      <c r="E8" s="35">
+        <f>'Balance Sheet'!H13/Segments!E20</f>
+        <v/>
+      </c>
+      <c r="F8" s="35">
+        <f>'Balance Sheet'!I13/Segments!F20</f>
+        <v/>
+      </c>
+      <c r="G8" s="35">
+        <f>'Balance Sheet'!J13/Segments!G20</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Trailing EV/EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="B9" s="30">
-        <f>(Assumptions!$C$5*Assumptions!$C$6+Assumptions!$C$7)/'Income Statement'!E9</f>
+          <t>EV/EBITDA (FY2025 basis, x)</t>
+        </is>
+      </c>
+      <c r="B9" s="35">
+        <f>(DCF!C8+Assumptions!$C$7)/'Income Statement'!E9</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Trailing P/E (x)</t>
-        </is>
-      </c>
-      <c r="B10" s="30">
-        <f>Assumptions!$C$5/B5</f>
+          <t>P/E (FY2025 basis, x)</t>
+        </is>
+      </c>
+      <c r="B10" s="35">
+        <f>DCF!C8/Assumptions!$C$58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>P/E (trailing twelve months, x)</t>
+        </is>
+      </c>
+      <c r="B11" s="35">
+        <f>DCF!C8/(Assumptions!$C$58+Assumptions!$C$60-Assumptions!$C$61)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2786,9 +2897,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2829,12 +2940,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Fwd EV/EBITDA</t>
+          <t>EV/EBITDA</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Basis &amp; note (each multiple recomputed from the peer's own EV and guidance)</t>
         </is>
       </c>
     </row>
@@ -2849,13 +2960,13 @@
           <t>Tadawul</t>
         </is>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="34">
         <f>'Per-Share &amp; Ratios'!B9</f>
         <v/>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>trailing; ~14.5x trailing P/E</t>
+          <t>FY2025 basis (TTM P/E 13.9x); see Per-Share &amp; Ratios</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2981,12 @@
           <t>Milan</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
-        <v>8.5</v>
+      <c r="C6" s="27" t="n">
+        <v>14</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>developed-market major</t>
+          <t>FY2026E on guidance RAISED 30-Jul-2026 (EUR 2.8-2.9bn) vs ~EUR 40bn EV</t>
         </is>
       </c>
     </row>
@@ -2890,12 +3001,12 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
-        <v>7.5</v>
+      <c r="C7" s="27" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>developed-market major</t>
+          <t>FY2026E on guidance raised 29-Jul-2026 (EUR 770-840mn) vs ~EUR 7.1bn EV</t>
         </is>
       </c>
     </row>
@@ -2910,12 +3021,12 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
-        <v>26</v>
+      <c r="C8" s="27" t="n">
+        <v>29</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>high-growth EM premium</t>
+          <t>NTM; high-growth EM premium</t>
         </is>
       </c>
     </row>
@@ -2930,12 +3041,12 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
-        <v>24</v>
+      <c r="C9" s="27" t="n">
+        <v>31</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>high-growth EM premium</t>
+          <t>NTM (~24-25x only on FY-Mar-2028, two years out)</t>
         </is>
       </c>
     </row>
@@ -2959,14 +3070,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA applied in the relative lens: 9.5x (mid-range, single-country discount).</t>
+          <t>Justified EV/EBITDA applied in the relative lens: 10.0x — a deliberate DISCOUNT to the corrected developed band (~8.5-14.5x) for single-country and single-customer concentration, not its mid-point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Quotes as of 18-Aug-2026. Cross-check multiples only — never a source for any Riyadh Cables figure.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2974,7 +3090,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3218,9 +3334,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3228,9 +3342,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3318,7 +3432,7 @@
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$41</f>
         <v/>
       </c>
       <c r="F5" s="15">
@@ -3349,7 +3463,7 @@
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F6" s="15">
@@ -3380,7 +3494,7 @@
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>Assumptions!$C$48</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
       <c r="F7" s="15">
@@ -3411,7 +3525,7 @@
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>Assumptions!$C$49</f>
+        <f>Assumptions!$C$44</f>
         <v/>
       </c>
       <c r="F8" s="15">
@@ -3454,11 +3568,12 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Expert panel median (whole-model — pasted)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="n">
-        <v>125.9789008877625</v>
+          <t>Expert panel median (live — see the worked panel below)</t>
+        </is>
+      </c>
+      <c r="C11" s="15">
+        <f>MEDIAN(C26,C30,C39)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -3503,7 +3618,7 @@
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>139.6016853407702</v>
+        <v>134.8531372449724</v>
       </c>
     </row>
     <row r="17">
@@ -3513,13 +3628,267 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>116.1041350901616</v>
+        <v>111.6031665507623</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Q2-2026 exit rate (14.99%) sustained — DCF value (pasted re-run)</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>119.1143960075278</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Expert panel — three methods, worked live on the same forecast base</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>E1 mid-cycle EBITDA margin (FY2028E)</t>
+        </is>
+      </c>
+      <c r="C21" s="18">
+        <f>Segments!E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>E1 mid-cycle revenue (FY2028E scale)</t>
+        </is>
+      </c>
+      <c r="C22" s="14">
+        <f>Segments!E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>E1 normalised EBIT (margin x revenue - D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C23" s="19">
+        <f>C21*C22-Assumptions!$C$29*C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>E1 normalised net interest (FY2028 Kd on FY2025 debt less cash yield)</t>
+        </is>
+      </c>
+      <c r="C24" s="19">
+        <f>Assumptions!E$32*Assumptions!$C$53-Assumptions!$C$34*(Assumptions!$C$53-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>E1 earnings per share after tax and minorities</t>
+        </is>
+      </c>
+      <c r="C25" s="15">
+        <f>(C23-C24)*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>Expert 1 — value at anchor (13x; range 10x/16x)</t>
+        </is>
+      </c>
+      <c r="B26" s="15">
+        <f>(10*C25)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="C26" s="21">
+        <f>(13*C25)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="D26" s="15">
+        <f>(16*C25)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>E2 mid-cycle FCFF (average FY2028-30E)</t>
+        </is>
+      </c>
+      <c r="C27" s="14">
+        <f>AVERAGE(DCF!E27:G27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>E2 after-tax net interest (FY2029 Kd basis)</t>
+        </is>
+      </c>
+      <c r="C28" s="19">
+        <f>(Assumptions!F$32*Assumptions!$C$53-Assumptions!$C$34*(Assumptions!$C$53-Assumptions!$C$7))*(1-Assumptions!$C$14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>E2 owner cash (FCFF less after-tax interest, net of minorities)</t>
+        </is>
+      </c>
+      <c r="C29" s="19">
+        <f>(C27-C28)*(1-Assumptions!$C$36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>Expert 2 — value at anchor (perpetuity at terminal Ke; range on rate/growth)</t>
+        </is>
+      </c>
+      <c r="B30" s="15">
+        <f>(C29*1.02/((DCF!C6+DCF!C11)/2-0.02)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="C30" s="21">
+        <f>(C29*(1+Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="D30" s="15">
+        <f>(C29*1.05/(DCF!C11-0.05)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>E3 invested capital, 31-Dec-2025 (NWC + PP&amp;E)</t>
+        </is>
+      </c>
+      <c r="C31" s="19">
+        <f>Assumptions!$C$51+Assumptions!$C$52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of economic profit, FY26E (NOPAT - WACC x opening capital)</t>
+        </is>
+      </c>
+      <c r="C32" s="19">
+        <f>(DCF!C21-DCF!C18*C31)*DCF!C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of economic profit, FY27E (NOPAT - WACC x opening capital)</t>
+        </is>
+      </c>
+      <c r="C33" s="19">
+        <f>(DCF!D21-DCF!D18*DCF!C32)*DCF!D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of economic profit, FY28E (NOPAT - WACC x opening capital)</t>
+        </is>
+      </c>
+      <c r="C34" s="19">
+        <f>(DCF!E21-DCF!E18*DCF!D32)*DCF!E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of economic profit, FY29E (NOPAT - WACC x opening capital)</t>
+        </is>
+      </c>
+      <c r="C35" s="19">
+        <f>(DCF!F21-DCF!F18*DCF!E32)*DCF!F19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of economic profit, FY30E (NOPAT - WACC x opening capital)</t>
+        </is>
+      </c>
+      <c r="C36" s="19">
+        <f>(DCF!G21-DCF!G18*DCF!F32)*DCF!G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>E3 PV of terminal economic profit (reconciles to the DCF terminal value)</t>
+        </is>
+      </c>
+      <c r="C37" s="19">
+        <f>(DCF!G21*(1+Assumptions!$C$21)-DCF!C13*DCF!G32)/(DCF!C13-Assumptions!$C$21)*DCF!G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>E3 enterprise value (capital + PV of excess returns; equals the DCF EV)</t>
+        </is>
+      </c>
+      <c r="C38" s="19">
+        <f>C31+SUM(C32:C36)+C37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>Expert 3 — value at anchor (bridge as the DCF; range on persistence)</t>
+        </is>
+      </c>
+      <c r="B39" s="15">
+        <f>((C31+SUM(C32:C36)*0.7+C37*0.65-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="C39" s="21">
+        <f>((C38-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
+      </c>
+      <c r="D39" s="15">
+        <f>((C31+SUM(C32:C36)*1.15+C37*1.2-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3527,9 +3896,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3590,7 +3959,7 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>104.8</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="6">
@@ -3599,7 +3968,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="22" t="n">
         <v>149.7175</v>
       </c>
     </row>
@@ -3609,7 +3978,7 @@
           <t>Net financial debt at FY2025 (SAR mn, disclosed)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="23" t="n">
         <v>385.173208</v>
       </c>
     </row>
@@ -3635,8 +4004,8 @@
           <t>Risk-free rate (10-year SAR sukuk)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
-        <v>0.055</v>
+      <c r="C9" s="24" t="n">
+        <v>0.0552</v>
       </c>
     </row>
     <row r="10">
@@ -3645,7 +4014,7 @@
           <t>Sovereign default spread (netted out)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="24" t="n">
         <v>0.0048</v>
       </c>
     </row>
@@ -3655,7 +4024,7 @@
           <t>Equity risk premium (rating basis)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="24" t="n">
         <v>0.0494</v>
       </c>
     </row>
@@ -3665,7 +4034,7 @@
           <t>Beta (own-stock vs TASI)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="25" t="n">
         <v>1.129</v>
       </c>
     </row>
@@ -3675,7 +4044,7 @@
           <t>Cost of debt, marginal pre-tax</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="24" t="n">
         <v>0.059</v>
       </c>
     </row>
@@ -3685,7 +4054,7 @@
           <t>Effective zakat and income tax rate</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="24" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -3711,8 +4080,8 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
-        <v>0.0502</v>
+      <c r="C16" s="24" t="n">
+        <v>0.0504</v>
       </c>
     </row>
     <row r="17">
@@ -3721,8 +4090,8 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
-        <v>0.047</v>
+      <c r="C17" s="24" t="n">
+        <v>0.0468</v>
       </c>
     </row>
     <row r="18">
@@ -3731,7 +4100,7 @@
           <t>Terminal beta</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3741,7 +4110,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="24" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -3751,8 +4120,8 @@
           <t>Terminal net-debt weight</t>
         </is>
       </c>
-      <c r="C20" s="20" t="n">
-        <v>0.05</v>
+      <c r="C20" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3761,14 +4130,14 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="24" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Forecast drivers — Cables &amp; wires leg (metal converter)</t>
+          <t>Forecast drivers — ground-up cost stack</t>
         </is>
       </c>
       <c r="B22" s="11" t="n"/>
@@ -3787,19 +4156,19 @@
           <t>Cable volume index growth</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="24" t="n">
         <v>0.075</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="24" t="n">
         <v>0.065</v>
       </c>
-      <c r="F23" s="20" t="n">
+      <c r="F23" s="24" t="n">
         <v>0.055</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="24" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -3809,19 +4178,19 @@
           <t>Metal content price growth</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="24" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="20" t="n">
+      <c r="E24" s="24" t="n">
         <v>0.01</v>
       </c>
-      <c r="F24" s="20" t="n">
+      <c r="F24" s="24" t="n">
         <v>0.01</v>
       </c>
-      <c r="G24" s="20" t="n">
+      <c r="G24" s="24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3831,19 +4200,19 @@
           <t>Conversion cost inflation</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="D25" s="20" t="n">
+      <c r="D25" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="E25" s="20" t="n">
+      <c r="E25" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="F25" s="20" t="n">
+      <c r="F25" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="G25" s="20" t="n">
+      <c r="G25" s="24" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -3853,7 +4222,7 @@
           <t>Sustained gross margin (H1-2026 anchor)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="24" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -3863,486 +4232,418 @@
           <t>Gross-margin glide (added to anchor)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="25" t="n">
         <v>0.001</v>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E27" s="25" t="n">
         <v>0.001</v>
       </c>
-      <c r="F27" s="21" t="n">
+      <c r="F27" s="25" t="n">
         <v>0.0015</v>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="25" t="n">
         <v>0.0015</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Forecast drivers — HV turnkey &amp; Other legs</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="11" t="n"/>
-      <c r="I28" s="11" t="n"/>
-      <c r="J28" s="11" t="n"/>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Operating expenses / revenue</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="F28" s="24" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G28" s="24" t="n">
+        <v>0.042</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>HV turnkey revenue growth</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D29" s="20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E29" s="20" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G29" s="20" t="n">
-        <v>0.08</v>
+          <t>Depreciation and amortisation / revenue</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="n">
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>HV turnkey segment margin</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="n">
-        <v>0.08378233242821985</v>
+          <t>Capital expenditure / revenue</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="D30" s="24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F30" s="24" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>0.0177</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Other segment revenue growth</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>0.06</v>
+          <t>Net working capital / revenue</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Other segment margin</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="n">
-        <v>0.5786820313464731</v>
+          <t>Cost-of-debt path</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="F32" s="24" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="G32" s="24" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Forecast drivers — group</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="11" t="n"/>
-      <c r="J33" s="11" t="n"/>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Forecast dividend payout ratio</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Operating expenses / revenue</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D34" s="20" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="E34" s="20" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="F34" s="20" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="G34" s="20" t="n">
-        <v>0.042</v>
+          <t>Yield on surplus cash</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation / revenue</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="n">
-        <v>0.008500000000000001</v>
+          <t>Metal price multiplier (shock; 1.00 = base path)</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure / revenue</t>
-        </is>
-      </c>
-      <c r="C36" s="20" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="D36" s="20" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="E36" s="20" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="F36" s="20" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="G36" s="20" t="n">
-        <v>0.016</v>
+          <t>NCI share of profit (FY2025)</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="n">
+        <v>0.004060669885351275</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Net working capital / revenue</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="n">
-        <v>0.28</v>
-      </c>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Cost-of-debt path</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="D38" s="20" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="E38" s="20" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="F38" s="20" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="G38" s="20" t="n">
-        <v>0.055</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Forecast dividend payout ratio</t>
-        </is>
-      </c>
-      <c r="C39" s="20" t="n">
-        <v>0.55</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C39" s="27" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Yield on surplus cash</t>
-        </is>
-      </c>
-      <c r="C40" s="20" t="n">
-        <v>0.04</v>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>NCI share of forecast profit</t>
-        </is>
-      </c>
-      <c r="C41" s="20" t="n">
-        <v>0.004060669885351275</v>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="11" t="n"/>
-      <c r="H42" s="11" t="n"/>
-      <c r="I42" s="11" t="n"/>
-      <c r="J42" s="11" t="n"/>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C43" s="22" t="n">
-        <v>9.5</v>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C44" s="22" t="n">
-        <v>13</v>
+          <t>Weight — book</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="n">
-        <v>0.28</v>
-      </c>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Anchor roll</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="11" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
+          <t>Days to the anchor</t>
         </is>
       </c>
       <c r="C46" s="23" t="n">
-        <v>0.45</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="n">
-        <v>0.2</v>
+          <t>FY2025 dividend per share paid in window</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C48" s="23" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>FY2025 disclosed base (audited)</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="11" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="11" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Weight — book</t>
+          <t>FY2025 metal content / materials (SAR mn)</t>
         </is>
       </c>
       <c r="C49" s="23" t="n">
-        <v>0.15</v>
+        <v>8486.925676999999</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>Anchor roll</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n"/>
-      <c r="C50" s="11" t="n"/>
-      <c r="D50" s="11" t="n"/>
-      <c r="E50" s="11" t="n"/>
-      <c r="F50" s="11" t="n"/>
-      <c r="G50" s="11" t="n"/>
-      <c r="H50" s="11" t="n"/>
-      <c r="I50" s="11" t="n"/>
-      <c r="J50" s="11" t="n"/>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 conversion cost (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="n">
+        <v>453.34873</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Days to the anchor</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="n">
-        <v>230</v>
+          <t>FY2025 net working capital (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="n">
+        <v>2933.258925</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>FY2025 dividend per share paid in window</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="n">
-        <v>2.25</v>
+          <t>FY2025 PP&amp;E (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="n">
+        <v>1491.86312</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>FY2025 disclosed base (audited)</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n"/>
-      <c r="C53" s="11" t="n"/>
-      <c r="D53" s="11" t="n"/>
-      <c r="E53" s="11" t="n"/>
-      <c r="F53" s="11" t="n"/>
-      <c r="G53" s="11" t="n"/>
-      <c r="H53" s="11" t="n"/>
-      <c r="I53" s="11" t="n"/>
-      <c r="J53" s="11" t="n"/>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>621.216217</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>FY2025 cables metal content (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="n">
-        <v>8486.925676999999</v>
+          <t>FY2025 equity attributable (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="n">
+        <v>3246.136935</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>FY2025 cables conversion cost (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="n">
-        <v>229.8024540000006</v>
+          <t>FY2025 associates carrying value (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="n">
+        <v>31.851877</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>FY2025 HV turnkey revenue (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C56" s="19" t="n">
-        <v>230.839181</v>
+          <t>FY2025 non-operating assets (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="n">
+        <v>20.40064</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>FY2025 Other segment revenue (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C57" s="19" t="n">
-        <v>28.594413</v>
+          <t>FY2025 NCI carrying value (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="n">
+        <v>62.737156</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>FY2025 net working capital (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C58" s="19" t="n">
-        <v>2933.258925</v>
+          <t>FY2025 attributable profit (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="n">
+        <v>1080.396042</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>FY2025 PP&amp;E (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C59" s="19" t="n">
-        <v>1491.86312</v>
+          <t>FY2024 equity attributable (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="n">
+        <v>2624.35365</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="n">
-        <v>621.216217</v>
+          <t>H1-2026 attributable profit (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C60" s="23" t="n">
+        <v>588.793</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>FY2025 equity attributable (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="n">
-        <v>3246.136935</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 associates carrying value (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C62" s="19" t="n">
-        <v>31.851877</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 non-operating assets (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="n">
-        <v>20.40064</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 NCI carrying value (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C64" s="19" t="n">
-        <v>62.737156</v>
+          <t>H1-2025 attributable profit (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="n">
+        <v>535.4690000000001</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4350,7 +4651,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4452,7 +4753,7 @@
           <t>Equity attributable (31-Dec-2025)</t>
         </is>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="29">
         <f>DCF!C48</f>
         <v/>
       </c>
@@ -4463,15 +4764,13 @@
           <t>Value per share at anchor (SAR)</t>
         </is>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="30">
         <f>DCF!C51</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4479,12 +4778,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -4497,7 +4796,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Segments — three legs, built to the group</t>
+          <t>Segments — ground-up cost-stack build</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4511,7 +4810,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Each disclosed Note 40 segment on its own driver; the cable leg is the metal converter; group gross margin is the blended OUTPUT</t>
+          <t>Materials on the metal path; conversion on domestic inflation; gross margin is the OUTPUT</t>
         </is>
       </c>
     </row>
@@ -4553,77 +4852,94 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Cables &amp; wires — the metal converter</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cable volume index (FY2025=100)</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" s="31">
+        <f>B5*(1+Assumptions!C$23)</f>
+        <v/>
+      </c>
+      <c r="D5" s="31">
+        <f>C5*(1+Assumptions!D$23)</f>
+        <v/>
+      </c>
+      <c r="E5" s="31">
+        <f>D5*(1+Assumptions!E$23)</f>
+        <v/>
+      </c>
+      <c r="F5" s="31">
+        <f>E5*(1+Assumptions!F$23)</f>
+        <v/>
+      </c>
+      <c r="G5" s="31">
+        <f>F5*(1+Assumptions!G$23)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Cable volume index (FY2025=100)</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="C6" s="26">
-        <f>B6*(1+Assumptions!C$23)</f>
-        <v/>
-      </c>
-      <c r="D6" s="26">
-        <f>C6*(1+Assumptions!D$23)</f>
-        <v/>
-      </c>
-      <c r="E6" s="26">
-        <f>D6*(1+Assumptions!E$23)</f>
-        <v/>
-      </c>
-      <c r="F6" s="26">
-        <f>E6*(1+Assumptions!F$23)</f>
-        <v/>
-      </c>
-      <c r="G6" s="26">
-        <f>F6*(1+Assumptions!G$23)</f>
+          <t>Metal content per unit (base path)</t>
+        </is>
+      </c>
+      <c r="B6" s="32">
+        <f>Assumptions!$C$49/100.0</f>
+        <v/>
+      </c>
+      <c r="C6" s="32">
+        <f>B6*(1+Assumptions!C$24)</f>
+        <v/>
+      </c>
+      <c r="D6" s="32">
+        <f>C6*(1+Assumptions!D$24)</f>
+        <v/>
+      </c>
+      <c r="E6" s="32">
+        <f>D6*(1+Assumptions!E$24)</f>
+        <v/>
+      </c>
+      <c r="F6" s="32">
+        <f>E6*(1+Assumptions!F$24)</f>
+        <v/>
+      </c>
+      <c r="G6" s="32">
+        <f>F6*(1+Assumptions!G$24)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Metal content per unit</t>
-        </is>
-      </c>
-      <c r="B7" s="27">
-        <f>Assumptions!$C$54/100.0</f>
-        <v/>
-      </c>
-      <c r="C7" s="27">
-        <f>B7*(1+Assumptions!C$24)</f>
-        <v/>
-      </c>
-      <c r="D7" s="27">
-        <f>C7*(1+Assumptions!D$24)</f>
-        <v/>
-      </c>
-      <c r="E7" s="27">
-        <f>D7*(1+Assumptions!E$24)</f>
-        <v/>
-      </c>
-      <c r="F7" s="27">
-        <f>E7*(1+Assumptions!F$24)</f>
-        <v/>
-      </c>
-      <c r="G7" s="27">
-        <f>F7*(1+Assumptions!G$24)</f>
+          <t>Metal content per unit (after shock multiplier)</t>
+        </is>
+      </c>
+      <c r="B7" s="32">
+        <f>B6*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="C7" s="32">
+        <f>C6*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="D7" s="32">
+        <f>D6*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="E7" s="32">
+        <f>E6*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="F7" s="32">
+        <f>F6*Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="G7" s="32">
+        <f>G6*Assumptions!$C$35</f>
         <v/>
       </c>
     </row>
@@ -4633,27 +4949,27 @@
           <t>Conversion cost per unit</t>
         </is>
       </c>
-      <c r="B8" s="27">
-        <f>Assumptions!$C$55/100.0</f>
-        <v/>
-      </c>
-      <c r="C8" s="27">
+      <c r="B8" s="32">
+        <f>Assumptions!$C$50/100.0</f>
+        <v/>
+      </c>
+      <c r="C8" s="32">
         <f>B8*(1+Assumptions!C$25)</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="32">
         <f>C8*(1+Assumptions!D$25)</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="32">
         <f>D8*(1+Assumptions!E$25)</f>
         <v/>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="32">
         <f>E8*(1+Assumptions!F$25)</f>
         <v/>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="32">
         <f>F8*(1+Assumptions!G$25)</f>
         <v/>
       </c>
@@ -4661,26 +4977,29 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Target gross margin (anchor + glide)</t>
-        </is>
-      </c>
-      <c r="C9" s="28">
+          <t>Margin anchor path (calibrates the spread at base metal)</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="n">
+        <v>0.1623940528853008</v>
+      </c>
+      <c r="C9" s="33">
         <f>Assumptions!$C$26+Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="33">
         <f>Assumptions!$C$26+Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="33">
         <f>Assumptions!$C$26+Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="33">
         <f>Assumptions!$C$26+Assumptions!F$27</f>
         <v/>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="33">
         <f>Assumptions!$C$26+Assumptions!G$27</f>
         <v/>
       </c>
@@ -4688,62 +5007,62 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Gross profit per unit (conversion spread)</t>
-        </is>
-      </c>
-      <c r="B10" s="27">
-        <f>B13/B6</f>
-        <v/>
-      </c>
-      <c r="C10" s="27">
-        <f>C9/(1-C9)*(C7+C8)</f>
-        <v/>
-      </c>
-      <c r="D10" s="27">
-        <f>D9/(1-D9)*(D7+D8)</f>
-        <v/>
-      </c>
-      <c r="E10" s="27">
-        <f>E9/(1-E9)*(E7+E8)</f>
-        <v/>
-      </c>
-      <c r="F10" s="27">
-        <f>F9/(1-F9)*(F7+F8)</f>
-        <v/>
-      </c>
-      <c r="G10" s="27">
-        <f>G9/(1-G9)*(G7+G8)</f>
+          <t>Conversion spread per unit (calibrated at base metal, held under shocks)</t>
+        </is>
+      </c>
+      <c r="B10" s="32">
+        <f>B9/(1-B9)*(B6+B8)</f>
+        <v/>
+      </c>
+      <c r="C10" s="32">
+        <f>C9/(1-C9)*(C6+C8)</f>
+        <v/>
+      </c>
+      <c r="D10" s="32">
+        <f>D9/(1-D9)*(D6+D8)</f>
+        <v/>
+      </c>
+      <c r="E10" s="32">
+        <f>E9/(1-E9)*(E6+E8)</f>
+        <v/>
+      </c>
+      <c r="F10" s="32">
+        <f>F9/(1-F9)*(F6+F8)</f>
+        <v/>
+      </c>
+      <c r="G10" s="32">
+        <f>G9/(1-G9)*(G6+G8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Materials (metal leg)</t>
-        </is>
-      </c>
-      <c r="B11" s="29">
-        <f>B6*B7</f>
-        <v/>
-      </c>
-      <c r="C11" s="29">
-        <f>C6*C7</f>
-        <v/>
-      </c>
-      <c r="D11" s="29">
-        <f>D6*D7</f>
-        <v/>
-      </c>
-      <c r="E11" s="29">
-        <f>E6*E7</f>
-        <v/>
-      </c>
-      <c r="F11" s="29">
-        <f>F6*F7</f>
-        <v/>
-      </c>
-      <c r="G11" s="29">
-        <f>G6*G7</f>
+          <t>Materials (metal leg, shocked)</t>
+        </is>
+      </c>
+      <c r="B11" s="19">
+        <f>B5*B7</f>
+        <v/>
+      </c>
+      <c r="C11" s="19">
+        <f>C5*C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="19">
+        <f>D5*D7</f>
+        <v/>
+      </c>
+      <c r="E11" s="19">
+        <f>E5*E7</f>
+        <v/>
+      </c>
+      <c r="F11" s="19">
+        <f>F5*F7</f>
+        <v/>
+      </c>
+      <c r="G11" s="19">
+        <f>G5*G7</f>
         <v/>
       </c>
     </row>
@@ -4753,614 +5072,346 @@
           <t>Conversion cost</t>
         </is>
       </c>
-      <c r="B12" s="29">
-        <f>B6*B8</f>
-        <v/>
-      </c>
-      <c r="C12" s="29">
-        <f>C6*C8</f>
-        <v/>
-      </c>
-      <c r="D12" s="29">
-        <f>D6*D8</f>
-        <v/>
-      </c>
-      <c r="E12" s="29">
-        <f>E6*E8</f>
-        <v/>
-      </c>
-      <c r="F12" s="29">
-        <f>F6*F8</f>
-        <v/>
-      </c>
-      <c r="G12" s="29">
-        <f>G6*G8</f>
+      <c r="B12" s="19">
+        <f>B5*B8</f>
+        <v/>
+      </c>
+      <c r="C12" s="19">
+        <f>C5*C8</f>
+        <v/>
+      </c>
+      <c r="D12" s="19">
+        <f>D5*D8</f>
+        <v/>
+      </c>
+      <c r="E12" s="19">
+        <f>E5*E8</f>
+        <v/>
+      </c>
+      <c r="F12" s="19">
+        <f>F5*F8</f>
+        <v/>
+      </c>
+      <c r="G12" s="19">
+        <f>G5*G8</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Gross profit = volume x spread</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n">
-        <v>1697.442537000001</v>
-      </c>
-      <c r="C13" s="29">
-        <f>C6*C10</f>
-        <v/>
-      </c>
-      <c r="D13" s="29">
-        <f>D6*D10</f>
-        <v/>
-      </c>
-      <c r="E13" s="29">
-        <f>E6*E10</f>
-        <v/>
-      </c>
-      <c r="F13" s="29">
-        <f>F6*F10</f>
-        <v/>
-      </c>
-      <c r="G13" s="29">
-        <f>G6*G10</f>
+          <t>Cost of revenue</t>
+        </is>
+      </c>
+      <c r="B13" s="19">
+        <f>B11+B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="19">
+        <f>C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="19">
+        <f>D11+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="19">
+        <f>E11+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="19">
+        <f>F11+F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="19">
+        <f>G11+G12</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Cables revenue = materials + conversion + gross profit</t>
-        </is>
-      </c>
-      <c r="B14" s="29">
-        <f>B11+B12+B13</f>
-        <v/>
-      </c>
-      <c r="C14" s="29">
-        <f>C11+C12+C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="29">
-        <f>D11+D12+D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="29">
-        <f>E11+E12+E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="29">
-        <f>F11+F12+F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="29">
-        <f>G11+G12+G13</f>
+          <t>Gross profit = volume x spread</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>1733.329855</v>
+      </c>
+      <c r="C14" s="19">
+        <f>C5*C10</f>
+        <v/>
+      </c>
+      <c r="D14" s="19">
+        <f>D5*D10</f>
+        <v/>
+      </c>
+      <c r="E14" s="19">
+        <f>E5*E10</f>
+        <v/>
+      </c>
+      <c r="F14" s="19">
+        <f>F5*F10</f>
+        <v/>
+      </c>
+      <c r="G14" s="19">
+        <f>G5*G10</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Cables gross margin (OUTPUT)</t>
-        </is>
-      </c>
-      <c r="B15" s="28">
-        <f>B13/B14</f>
-        <v/>
-      </c>
-      <c r="C15" s="28">
-        <f>C13/C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="28">
-        <f>D13/D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="28">
-        <f>E13/E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="28">
-        <f>F13/F14</f>
-        <v/>
-      </c>
-      <c r="G15" s="28">
-        <f>G13/G14</f>
+          <t>Revenue = materials + conversion + spread</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>10673.604262</v>
+      </c>
+      <c r="C15" s="19">
+        <f>C13+C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="19">
+        <f>D13+D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="19">
+        <f>E13+E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="19">
+        <f>F13+F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="19">
+        <f>G13+G14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>HV turnkey projects — own growth, disclosed margin</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Gross margin — OUTPUT (dilutes when metal rises)</t>
+        </is>
+      </c>
+      <c r="B16" s="33">
+        <f>B14/B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="33">
+        <f>C14/C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="33">
+        <f>D14/D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="33">
+        <f>E14/E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="33">
+        <f>F14/F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="33">
+        <f>G14/G15</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>HV revenue (own growth path)</t>
-        </is>
-      </c>
-      <c r="B17" s="29">
-        <f>Assumptions!$C$56</f>
-        <v/>
-      </c>
-      <c r="C17" s="29">
-        <f>B17*(1+Assumptions!C$29)</f>
-        <v/>
-      </c>
-      <c r="D17" s="29">
-        <f>C17*(1+Assumptions!D$29)</f>
-        <v/>
-      </c>
-      <c r="E17" s="29">
-        <f>D17*(1+Assumptions!E$29)</f>
-        <v/>
-      </c>
-      <c r="F17" s="29">
-        <f>E17*(1+Assumptions!F$29)</f>
-        <v/>
-      </c>
-      <c r="G17" s="29">
-        <f>F17*(1+Assumptions!G$29)</f>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C17" s="19">
+        <f>Assumptions!C$28*C15</f>
+        <v/>
+      </c>
+      <c r="D17" s="19">
+        <f>Assumptions!D$28*D15</f>
+        <v/>
+      </c>
+      <c r="E17" s="19">
+        <f>Assumptions!E$28*E15</f>
+        <v/>
+      </c>
+      <c r="F17" s="19">
+        <f>Assumptions!F$28*F15</f>
+        <v/>
+      </c>
+      <c r="G17" s="19">
+        <f>Assumptions!G$28*G15</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>HV segment margin</t>
-        </is>
-      </c>
-      <c r="B18" s="28">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="C18" s="28">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="D18" s="28">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="E18" s="28">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="F18" s="28">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="G18" s="28">
-        <f>Assumptions!$C$30</f>
+          <t>Depreciation &amp; amortisation</t>
+        </is>
+      </c>
+      <c r="C18" s="19">
+        <f>Assumptions!$C$29*C15</f>
+        <v/>
+      </c>
+      <c r="D18" s="19">
+        <f>Assumptions!$C$29*D15</f>
+        <v/>
+      </c>
+      <c r="E18" s="19">
+        <f>Assumptions!$C$29*E15</f>
+        <v/>
+      </c>
+      <c r="F18" s="19">
+        <f>Assumptions!$C$29*F15</f>
+        <v/>
+      </c>
+      <c r="G18" s="19">
+        <f>Assumptions!$C$29*G15</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>HV gross profit = revenue x margin</t>
-        </is>
-      </c>
-      <c r="B19" s="29">
-        <f>B17*B18</f>
-        <v/>
-      </c>
-      <c r="C19" s="29">
-        <f>C17*C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="29">
-        <f>D17*D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="29">
-        <f>E17*E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="29">
-        <f>F17*F18</f>
-        <v/>
-      </c>
-      <c r="G19" s="29">
-        <f>G17*G18</f>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C19" s="19">
+        <f>C14-C17</f>
+        <v/>
+      </c>
+      <c r="D19" s="19">
+        <f>D14-D17</f>
+        <v/>
+      </c>
+      <c r="E19" s="19">
+        <f>E14-E17</f>
+        <v/>
+      </c>
+      <c r="F19" s="19">
+        <f>F14-F17</f>
+        <v/>
+      </c>
+      <c r="G19" s="19">
+        <f>G14-G17</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Other (telephone cables &amp; services) — own growth, disclosed margin</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C20" s="19">
+        <f>C19+C18</f>
+        <v/>
+      </c>
+      <c r="D20" s="19">
+        <f>D19+D18</f>
+        <v/>
+      </c>
+      <c r="E20" s="19">
+        <f>E19+E18</f>
+        <v/>
+      </c>
+      <c r="F20" s="19">
+        <f>F19+F18</f>
+        <v/>
+      </c>
+      <c r="G20" s="19">
+        <f>G19+G18</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Other revenue (own growth path)</t>
-        </is>
-      </c>
-      <c r="B21" s="29">
-        <f>Assumptions!$C$57</f>
-        <v/>
-      </c>
-      <c r="C21" s="29">
-        <f>B21*(1+Assumptions!C$31)</f>
-        <v/>
-      </c>
-      <c r="D21" s="29">
-        <f>C21*(1+Assumptions!D$31)</f>
-        <v/>
-      </c>
-      <c r="E21" s="29">
-        <f>D21*(1+Assumptions!E$31)</f>
-        <v/>
-      </c>
-      <c r="F21" s="29">
-        <f>E21*(1+Assumptions!F$31)</f>
-        <v/>
-      </c>
-      <c r="G21" s="29">
-        <f>F21*(1+Assumptions!G$31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Other segment margin</t>
-        </is>
-      </c>
-      <c r="B22" s="28">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="C22" s="28">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="D22" s="28">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="E22" s="28">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="F22" s="28">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="G22" s="28">
-        <f>Assumptions!$C$32</f>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C21" s="33">
+        <f>C20/C15</f>
+        <v/>
+      </c>
+      <c r="D21" s="33">
+        <f>D20/D15</f>
+        <v/>
+      </c>
+      <c r="E21" s="33">
+        <f>E20/E15</f>
+        <v/>
+      </c>
+      <c r="F21" s="33">
+        <f>F20/F15</f>
+        <v/>
+      </c>
+      <c r="G21" s="33">
+        <f>G20/G15</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Other gross profit = revenue x margin</t>
-        </is>
-      </c>
-      <c r="B23" s="29">
-        <f>B21*B22</f>
-        <v/>
-      </c>
-      <c r="C23" s="29">
-        <f>C21*C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="29">
-        <f>D21*D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="29">
-        <f>E21*E22</f>
-        <v/>
-      </c>
-      <c r="F23" s="29">
-        <f>F21*F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="29">
-        <f>G21*G22</f>
-        <v/>
-      </c>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>FY2025 disclosed segment revenue (Note 40)</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="11" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Group — the sum of the three legs</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="n"/>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Cables and wires</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>10414.170668</v>
+      </c>
+      <c r="C24" s="9">
+        <f>B24/B15</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Revenue (group)</t>
-        </is>
-      </c>
-      <c r="B25" s="29">
-        <f>B14+B17+B21</f>
-        <v/>
-      </c>
-      <c r="C25" s="29">
-        <f>C14+C17+C21</f>
-        <v/>
-      </c>
-      <c r="D25" s="29">
-        <f>D14+D17+D21</f>
-        <v/>
-      </c>
-      <c r="E25" s="29">
-        <f>E14+E17+E21</f>
-        <v/>
-      </c>
-      <c r="F25" s="29">
-        <f>F14+F17+F21</f>
-        <v/>
-      </c>
-      <c r="G25" s="29">
-        <f>G14+G17+G21</f>
+          <t>High-voltage cables (turnkey projects)</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="n">
+        <v>230.839181</v>
+      </c>
+      <c r="C25" s="9">
+        <f>B25/B15</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Gross profit (group)</t>
-        </is>
-      </c>
-      <c r="B26" s="29">
-        <f>B13+B19+B23</f>
-        <v/>
-      </c>
-      <c r="C26" s="29">
-        <f>C13+C19+C23</f>
-        <v/>
-      </c>
-      <c r="D26" s="29">
-        <f>D13+D19+D23</f>
-        <v/>
-      </c>
-      <c r="E26" s="29">
-        <f>E13+E19+E23</f>
-        <v/>
-      </c>
-      <c r="F26" s="29">
-        <f>F13+F19+F23</f>
-        <v/>
-      </c>
-      <c r="G26" s="29">
-        <f>G13+G19+G23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Cost of revenue (group)</t>
-        </is>
-      </c>
-      <c r="B27" s="29">
-        <f>B25-B26</f>
-        <v/>
-      </c>
-      <c r="C27" s="29">
-        <f>C25-C26</f>
-        <v/>
-      </c>
-      <c r="D27" s="29">
-        <f>D25-D26</f>
-        <v/>
-      </c>
-      <c r="E27" s="29">
-        <f>E25-E26</f>
-        <v/>
-      </c>
-      <c r="F27" s="29">
-        <f>F25-F26</f>
-        <v/>
-      </c>
-      <c r="G27" s="29">
-        <f>G25-G26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Gross margin (OUTPUT = group gross profit / group revenue)</t>
-        </is>
-      </c>
-      <c r="B28" s="28">
-        <f>B26/B25</f>
-        <v/>
-      </c>
-      <c r="C28" s="28">
-        <f>C26/C25</f>
-        <v/>
-      </c>
-      <c r="D28" s="28">
-        <f>D26/D25</f>
-        <v/>
-      </c>
-      <c r="E28" s="28">
-        <f>E26/E25</f>
-        <v/>
-      </c>
-      <c r="F28" s="28">
-        <f>F26/F25</f>
-        <v/>
-      </c>
-      <c r="G28" s="28">
-        <f>G26/G25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="C29" s="29">
-        <f>Assumptions!C$34*C25</f>
-        <v/>
-      </c>
-      <c r="D29" s="29">
-        <f>Assumptions!D$34*D25</f>
-        <v/>
-      </c>
-      <c r="E29" s="29">
-        <f>Assumptions!E$34*E25</f>
-        <v/>
-      </c>
-      <c r="F29" s="29">
-        <f>Assumptions!F$34*F25</f>
-        <v/>
-      </c>
-      <c r="G29" s="29">
-        <f>Assumptions!G$34*G25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation &amp; amortisation</t>
-        </is>
-      </c>
-      <c r="C30" s="29">
-        <f>Assumptions!$C$35*C25</f>
-        <v/>
-      </c>
-      <c r="D30" s="29">
-        <f>Assumptions!$C$35*D25</f>
-        <v/>
-      </c>
-      <c r="E30" s="29">
-        <f>Assumptions!$C$35*E25</f>
-        <v/>
-      </c>
-      <c r="F30" s="29">
-        <f>Assumptions!$C$35*F25</f>
-        <v/>
-      </c>
-      <c r="G30" s="29">
-        <f>Assumptions!$C$35*G25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C31" s="29">
-        <f>C26-C29</f>
-        <v/>
-      </c>
-      <c r="D31" s="29">
-        <f>D26-D29</f>
-        <v/>
-      </c>
-      <c r="E31" s="29">
-        <f>E26-E29</f>
-        <v/>
-      </c>
-      <c r="F31" s="29">
-        <f>F26-F29</f>
-        <v/>
-      </c>
-      <c r="G31" s="29">
-        <f>G26-G29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="C32" s="29">
-        <f>C31+C30</f>
-        <v/>
-      </c>
-      <c r="D32" s="29">
-        <f>D31+D30</f>
-        <v/>
-      </c>
-      <c r="E32" s="29">
-        <f>E31+E30</f>
-        <v/>
-      </c>
-      <c r="F32" s="29">
-        <f>F31+F30</f>
-        <v/>
-      </c>
-      <c r="G32" s="29">
-        <f>G31+G30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C33" s="28">
-        <f>C32/C25</f>
-        <v/>
-      </c>
-      <c r="D33" s="28">
-        <f>D32/D25</f>
-        <v/>
-      </c>
-      <c r="E33" s="28">
-        <f>E32/E25</f>
-        <v/>
-      </c>
-      <c r="F33" s="28">
-        <f>F32/F25</f>
-        <v/>
-      </c>
-      <c r="G33" s="28">
-        <f>G32/G25</f>
+          <t>Other (telephone cables &amp; services)</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="n">
+        <v>28.594413</v>
+      </c>
+      <c r="C26" s="9">
+        <f>B26/B15</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5368,7 +5419,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5422,7 +5473,7 @@
         </is>
       </c>
       <c r="C5" s="14">
-        <f>Segments!D32</f>
+        <f>Segments!D20</f>
         <v/>
       </c>
     </row>
@@ -5432,8 +5483,8 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="30">
-        <f>Assumptions!$C$43</f>
+      <c r="C6" s="34">
+        <f>Assumptions!$C$38</f>
         <v/>
       </c>
     </row>
@@ -5449,28 +5500,28 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Relative lens — implied value (base)</t>
         </is>
       </c>
-      <c r="C8" s="32">
-        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
+      <c r="C8" s="21">
+        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Bear (7.5x) / Bull (11.0x)</t>
+          <t>Bear (8.0x) / Bull (12.0x)</t>
         </is>
       </c>
       <c r="C9" s="15">
-        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
+        <f>((8*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
+        <f>((12*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5493,8 +5544,8 @@
           <t>Mid-cycle EBITDA margin (FY2028E)</t>
         </is>
       </c>
-      <c r="C12" s="33">
-        <f>Segments!E33</f>
+      <c r="C12" s="18">
+        <f>Segments!E21</f>
         <v/>
       </c>
     </row>
@@ -5505,7 +5556,7 @@
         </is>
       </c>
       <c r="C13" s="14">
-        <f>Segments!C25</f>
+        <f>Segments!C15</f>
         <v/>
       </c>
     </row>
@@ -5527,18 +5578,18 @@
         </is>
       </c>
       <c r="C15" s="15">
-        <f>((C12*C13-Assumptions!$C$35*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)/Assumptions!$C$6</f>
+        <f>((C12*C13-Assumptions!$C$29*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Normalised lens — implied value (base)</t>
         </is>
       </c>
-      <c r="C16" s="32">
-        <f>(Assumptions!$C$44*C15)*DCF!$C$50-Assumptions!$C$52</f>
+      <c r="C16" s="21">
+        <f>(Assumptions!$C$39*C15)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5549,11 +5600,11 @@
         </is>
       </c>
       <c r="C17" s="15">
-        <f>(10*C15)*DCF!$C$50-Assumptions!$C$52</f>
+        <f>(10*C15)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>(16*C15)*DCF!$C$50-Assumptions!$C$52</f>
+        <f>(16*C15)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5577,7 +5628,7 @@
         </is>
       </c>
       <c r="C20" s="15">
-        <f>Assumptions!$C$61/Assumptions!$C$6</f>
+        <f>Assumptions!$C$54/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5587,19 +5638,19 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C21" s="34">
-        <f>(Assumptions!$C$45-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)</f>
+      <c r="C21" s="35">
+        <f>(Assumptions!$C$40-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Book lens — implied value (base)</t>
         </is>
       </c>
-      <c r="C22" s="32">
-        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$52</f>
+      <c r="C22" s="21">
+        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5610,18 +5661,16 @@
         </is>
       </c>
       <c r="C23" s="15">
-        <f>(((Assumptions!$C$45)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$52</f>
+        <f>(((Assumptions!$C$40)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="D23" s="15">
-        <f>(((Assumptions!$C$45)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$52</f>
+        <f>(((Assumptions!$C$40)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5629,7 +5678,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5685,7 +5734,7 @@
           <t>Normalised risk-free rate rf*</t>
         </is>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="33">
         <f>Assumptions!$C$9-Assumptions!$C$10</f>
         <v/>
       </c>
@@ -5696,7 +5745,7 @@
           <t>Cost of equity Ke</t>
         </is>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="33">
         <f>C5+Assumptions!$C$12*Assumptions!$C$11</f>
         <v/>
       </c>
@@ -5707,7 +5756,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="33">
         <f>Assumptions!$C$13*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -5718,7 +5767,7 @@
           <t>Market capitalisation</t>
         </is>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="19">
         <f>Assumptions!$C$5*Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5729,18 +5778,18 @@
           <t>Net-debt weight</t>
         </is>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="33">
         <f>Assumptions!$C$7/(Assumptions!$C$7+C8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>WACC — explicit window</t>
         </is>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="36">
         <f>(1-C9)*C6+C9*C7</f>
         <v/>
       </c>
@@ -5751,7 +5800,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="33">
         <f>Assumptions!$C$16+Assumptions!$C$18*Assumptions!$C$17</f>
         <v/>
       </c>
@@ -5762,18 +5811,18 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="33">
         <f>Assumptions!$C$19*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>WACC — terminal</t>
         </is>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="36">
         <f>(1-Assumptions!$C$20)*C11+Assumptions!$C$20*C12</f>
         <v/>
       </c>
@@ -5831,24 +5880,24 @@
           <t>Glide fraction (from Kd path)</t>
         </is>
       </c>
-      <c r="C17" s="36">
-        <f>(Assumptions!C$38-Assumptions!C$38)/(Assumptions!C$38-Assumptions!G$38)</f>
-        <v/>
-      </c>
-      <c r="D17" s="36">
-        <f>(Assumptions!C$38-Assumptions!D$38)/(Assumptions!C$38-Assumptions!G$38)</f>
-        <v/>
-      </c>
-      <c r="E17" s="36">
-        <f>(Assumptions!C$38-Assumptions!E$38)/(Assumptions!C$38-Assumptions!G$38)</f>
-        <v/>
-      </c>
-      <c r="F17" s="36">
-        <f>(Assumptions!C$38-Assumptions!F$38)/(Assumptions!C$38-Assumptions!G$38)</f>
-        <v/>
-      </c>
-      <c r="G17" s="36">
-        <f>(Assumptions!C$38-Assumptions!G$38)/(Assumptions!C$38-Assumptions!G$38)</f>
+      <c r="C17" s="37">
+        <f>(Assumptions!C$32-Assumptions!C$32)/(Assumptions!C$32-Assumptions!G$32)</f>
+        <v/>
+      </c>
+      <c r="D17" s="37">
+        <f>(Assumptions!C$32-Assumptions!D$32)/(Assumptions!C$32-Assumptions!G$32)</f>
+        <v/>
+      </c>
+      <c r="E17" s="37">
+        <f>(Assumptions!C$32-Assumptions!E$32)/(Assumptions!C$32-Assumptions!G$32)</f>
+        <v/>
+      </c>
+      <c r="F17" s="37">
+        <f>(Assumptions!C$32-Assumptions!F$32)/(Assumptions!C$32-Assumptions!G$32)</f>
+        <v/>
+      </c>
+      <c r="G17" s="37">
+        <f>(Assumptions!C$32-Assumptions!G$32)/(Assumptions!C$32-Assumptions!G$32)</f>
         <v/>
       </c>
     </row>
@@ -5858,23 +5907,23 @@
           <t>Forward WACC</t>
         </is>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="33">
         <f>C10-(C10-C13)*C17</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="33">
         <f>C10-(C10-C13)*D17</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="33">
         <f>C10-(C10-C13)*E17</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="33">
         <f>C10-(C10-C13)*F17</f>
         <v/>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="33">
         <f>C10-(C10-C13)*G17</f>
         <v/>
       </c>
@@ -5885,23 +5934,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="37">
         <f>1/(1+C18)</f>
         <v/>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="37">
         <f>C19/(1+D18)</f>
         <v/>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="37">
         <f>D19/(1+E18)</f>
         <v/>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="37">
         <f>E19/(1+F18)</f>
         <v/>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="37">
         <f>F19/(1+G18)</f>
         <v/>
       </c>
@@ -5913,23 +5962,23 @@
         </is>
       </c>
       <c r="C20" s="14">
-        <f>Segments!C31</f>
+        <f>Segments!C19</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f>Segments!D31</f>
+        <f>Segments!D19</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>Segments!E31</f>
+        <f>Segments!E19</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>Segments!F31</f>
+        <f>Segments!F19</f>
         <v/>
       </c>
       <c r="G20" s="14">
-        <f>Segments!G31</f>
+        <f>Segments!G19</f>
         <v/>
       </c>
     </row>
@@ -5939,23 +5988,23 @@
           <t>NOPAT = EBIT x (1 - tax)</t>
         </is>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="19">
         <f>C20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="19">
         <f>D20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="19">
         <f>E20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="19">
         <f>F20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="19">
         <f>G20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -5967,23 +6016,23 @@
         </is>
       </c>
       <c r="C22" s="14">
-        <f>Segments!C30</f>
+        <f>Segments!C18</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>Segments!D30</f>
+        <f>Segments!D18</f>
         <v/>
       </c>
       <c r="E22" s="14">
-        <f>Segments!E30</f>
+        <f>Segments!E18</f>
         <v/>
       </c>
       <c r="F22" s="14">
-        <f>Segments!F30</f>
+        <f>Segments!F18</f>
         <v/>
       </c>
       <c r="G22" s="14">
-        <f>Segments!G30</f>
+        <f>Segments!G18</f>
         <v/>
       </c>
     </row>
@@ -5994,23 +6043,23 @@
         </is>
       </c>
       <c r="C23" s="14">
-        <f>Segments!C25</f>
+        <f>Segments!C15</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>Segments!D25</f>
+        <f>Segments!D15</f>
         <v/>
       </c>
       <c r="E23" s="14">
-        <f>Segments!E25</f>
+        <f>Segments!E15</f>
         <v/>
       </c>
       <c r="F23" s="14">
-        <f>Segments!F25</f>
+        <f>Segments!F15</f>
         <v/>
       </c>
       <c r="G23" s="14">
-        <f>Segments!G25</f>
+        <f>Segments!G15</f>
         <v/>
       </c>
     </row>
@@ -6020,24 +6069,24 @@
           <t>- Capital expenditure</t>
         </is>
       </c>
-      <c r="C24" s="29">
-        <f>Assumptions!C$36*C23</f>
-        <v/>
-      </c>
-      <c r="D24" s="29">
-        <f>Assumptions!D$36*D23</f>
-        <v/>
-      </c>
-      <c r="E24" s="29">
-        <f>Assumptions!E$36*E23</f>
-        <v/>
-      </c>
-      <c r="F24" s="29">
-        <f>Assumptions!F$36*F23</f>
-        <v/>
-      </c>
-      <c r="G24" s="29">
-        <f>Assumptions!G$36*G23</f>
+      <c r="C24" s="19">
+        <f>Assumptions!C$30*C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="19">
+        <f>Assumptions!D$30*D23</f>
+        <v/>
+      </c>
+      <c r="E24" s="19">
+        <f>Assumptions!E$30*E23</f>
+        <v/>
+      </c>
+      <c r="F24" s="19">
+        <f>Assumptions!F$30*F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="19">
+        <f>Assumptions!G$30*G23</f>
         <v/>
       </c>
     </row>
@@ -6047,24 +6096,24 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="C25" s="29">
-        <f>Assumptions!$C$37*C23</f>
-        <v/>
-      </c>
-      <c r="D25" s="29">
-        <f>Assumptions!$C$37*D23</f>
-        <v/>
-      </c>
-      <c r="E25" s="29">
-        <f>Assumptions!$C$37*E23</f>
-        <v/>
-      </c>
-      <c r="F25" s="29">
-        <f>Assumptions!$C$37*F23</f>
-        <v/>
-      </c>
-      <c r="G25" s="29">
-        <f>Assumptions!$C$37*G23</f>
+      <c r="C25" s="19">
+        <f>Assumptions!$C$31*C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="19">
+        <f>Assumptions!$C$31*D23</f>
+        <v/>
+      </c>
+      <c r="E25" s="19">
+        <f>Assumptions!$C$31*E23</f>
+        <v/>
+      </c>
+      <c r="F25" s="19">
+        <f>Assumptions!$C$31*F23</f>
+        <v/>
+      </c>
+      <c r="G25" s="19">
+        <f>Assumptions!$C$31*G23</f>
         <v/>
       </c>
     </row>
@@ -6074,50 +6123,50 @@
           <t>- Change in working capital</t>
         </is>
       </c>
-      <c r="C26" s="29">
-        <f>C25-Assumptions!$C$58</f>
-        <v/>
-      </c>
-      <c r="D26" s="29">
+      <c r="C26" s="19">
+        <f>C25-Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="D26" s="19">
         <f>D25-C25</f>
         <v/>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="19">
         <f>E25-D25</f>
         <v/>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="19">
         <f>F25-E25</f>
         <v/>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="19">
         <f>G25-F25</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Free cash flow to firm</t>
         </is>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="38">
         <f>C21+C22-C24-C26</f>
         <v/>
       </c>
-      <c r="D27" s="37">
+      <c r="D27" s="38">
         <f>D21+D22-D24-D26</f>
         <v/>
       </c>
-      <c r="E27" s="37">
+      <c r="E27" s="38">
         <f>E21+E22-E24-E26</f>
         <v/>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="38">
         <f>F21+F22-F24-F26</f>
         <v/>
       </c>
-      <c r="G27" s="37">
+      <c r="G27" s="38">
         <f>G21+G22-G24-G26</f>
         <v/>
       </c>
@@ -6128,23 +6177,23 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="19">
         <f>C27*C19</f>
         <v/>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="19">
         <f>D27*D19</f>
         <v/>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="19">
         <f>E27*E19</f>
         <v/>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="19">
         <f>F27*F19</f>
         <v/>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="19">
         <f>G27*G19</f>
         <v/>
       </c>
@@ -6169,23 +6218,23 @@
           <t>PP&amp;E roll-forward</t>
         </is>
       </c>
-      <c r="C31" s="29">
-        <f>Assumptions!$C$59+C24-C22</f>
-        <v/>
-      </c>
-      <c r="D31" s="29">
+      <c r="C31" s="19">
+        <f>Assumptions!$C$52+C24-C22</f>
+        <v/>
+      </c>
+      <c r="D31" s="19">
         <f>C31+D24-D22</f>
         <v/>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="19">
         <f>D31+E24-E22</f>
         <v/>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="19">
         <f>E31+F24-F22</f>
         <v/>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="19">
         <f>F31+G24-G22</f>
         <v/>
       </c>
@@ -6196,23 +6245,23 @@
           <t>Invested capital = NWC + PP&amp;E</t>
         </is>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="19">
         <f>C25+C31</f>
         <v/>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="19">
         <f>D25+D31</f>
         <v/>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="19">
         <f>E25+E31</f>
         <v/>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="19">
         <f>F25+F31</f>
         <v/>
       </c>
-      <c r="G32" s="29">
+      <c r="G32" s="19">
         <f>G25+G31</f>
         <v/>
       </c>
@@ -6223,23 +6272,23 @@
           <t>ROIC = NOPAT / invested capital</t>
         </is>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="33">
         <f>C21/C32</f>
         <v/>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="33">
         <f>D21/D32</f>
         <v/>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="33">
         <f>E21/E32</f>
         <v/>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="33">
         <f>F21/F32</f>
         <v/>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="33">
         <f>G21/G32</f>
         <v/>
       </c>
@@ -6250,7 +6299,7 @@
           <t>PV of explicit FCFF (5 years)</t>
         </is>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="19">
         <f>SUM(C28:G28)</f>
         <v/>
       </c>
@@ -6261,7 +6310,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="33">
         <f>G21*(1+Assumptions!$C$21)/G32</f>
         <v/>
       </c>
@@ -6272,7 +6321,7 @@
           <t>Terminal reinvestment rate = g / ROIC</t>
         </is>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="33">
         <f>Assumptions!$C$21/C36</f>
         <v/>
       </c>
@@ -6283,7 +6332,7 @@
           <t>Terminal NOPAT (next year)</t>
         </is>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="19">
         <f>G21*(1+Assumptions!$C$21)</f>
         <v/>
       </c>
@@ -6294,7 +6343,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="19">
         <f>C38*(1-C37)/(C13-Assumptions!$C$21)</f>
         <v/>
       </c>
@@ -6305,29 +6354,29 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="19">
         <f>C39*G19</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C41" s="37">
+      <c r="C41" s="38">
         <f>C35+C40</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="31" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Terminal value as % of EV</t>
         </is>
       </c>
-      <c r="C42" s="38">
+      <c r="C42" s="39">
         <f>C40/C41</f>
         <v/>
       </c>
@@ -6352,7 +6401,7 @@
           <t>Less: net financial debt</t>
         </is>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="19">
         <f>-Assumptions!$C$7</f>
         <v/>
       </c>
@@ -6363,8 +6412,8 @@
           <t>Add: associates + non-operating assets</t>
         </is>
       </c>
-      <c r="C46" s="29">
-        <f>Assumptions!$C$62+Assumptions!$C$63</f>
+      <c r="C46" s="19">
+        <f>Assumptions!$C$55+Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
@@ -6374,18 +6423,18 @@
           <t>Less: non-controlling interests</t>
         </is>
       </c>
-      <c r="C47" s="29">
-        <f>-Assumptions!$C$64</f>
+      <c r="C47" s="19">
+        <f>-Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>Equity attributable (31-Dec-2025)</t>
         </is>
       </c>
-      <c r="C48" s="37">
+      <c r="C48" s="38">
         <f>C41+C45+C46+C47</f>
         <v/>
       </c>
@@ -6407,19 +6456,19 @@
           <t>Anchor accretion factor</t>
         </is>
       </c>
-      <c r="C50" s="36">
-        <f>(1+C6)^(Assumptions!$C$51/365)</f>
+      <c r="C50" s="37">
+        <f>(1+C6)^(Assumptions!$C$46/365)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>Value per share at anchor (18-Aug-2026)</t>
         </is>
       </c>
-      <c r="C51" s="32">
-        <f>C49*C50-Assumptions!$C$52</f>
+      <c r="C51" s="21">
+        <f>C49*C50-Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -6455,7 +6504,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>80.84906676286525</v>
+        <v>78.52014039378953</v>
       </c>
     </row>
     <row r="56">
@@ -6476,13 +6525,11 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>197.7603327814774</v>
+        <v>188.2848029277439</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6490,7 +6537,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6584,33 +6631,33 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="23" t="n">
         <v>7825.378127</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="23" t="n">
         <v>9007.360866999999</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="23" t="n">
         <v>10673.604262</v>
       </c>
       <c r="F5" s="14">
-        <f>Segments!C25</f>
+        <f>Segments!C15</f>
         <v/>
       </c>
       <c r="G5" s="14">
-        <f>Segments!D25</f>
+        <f>Segments!D15</f>
         <v/>
       </c>
       <c r="H5" s="14">
-        <f>Segments!E25</f>
+        <f>Segments!E15</f>
         <v/>
       </c>
       <c r="I5" s="14">
-        <f>Segments!F25</f>
+        <f>Segments!F15</f>
         <v/>
       </c>
       <c r="J5" s="14">
-        <f>Segments!G25</f>
+        <f>Segments!G15</f>
         <v/>
       </c>
     </row>
@@ -6620,33 +6667,33 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="23" t="n">
         <v>972.763438</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="23" t="n">
         <v>1286.522351</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="23" t="n">
         <v>1733.329855</v>
       </c>
       <c r="F6" s="14">
-        <f>Segments!C26</f>
+        <f>Segments!C14</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>Segments!D26</f>
+        <f>Segments!D14</f>
         <v/>
       </c>
       <c r="H6" s="14">
-        <f>Segments!E26</f>
+        <f>Segments!E14</f>
         <v/>
       </c>
       <c r="I6" s="14">
-        <f>Segments!F26</f>
+        <f>Segments!F14</f>
         <v/>
       </c>
       <c r="J6" s="14">
-        <f>Segments!G26</f>
+        <f>Segments!G14</f>
         <v/>
       </c>
     </row>
@@ -6656,35 +6703,35 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="33">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="33">
         <f>D6/D5</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="33">
         <f>E6/E5</f>
         <v/>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="33">
         <f>F6/F5</f>
         <v/>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="33">
         <f>G6/G5</f>
         <v/>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="33">
         <f>H6/H5</f>
         <v/>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="33">
         <f>I6/I5</f>
         <v/>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="33">
         <f>J6/J5</f>
         <v/>
       </c>
@@ -6695,36 +6742,36 @@
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="19">
         <f>C6-C11</f>
         <v/>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="19">
         <f>D6-D11</f>
         <v/>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="19">
         <f>E6-E11</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>Segments!C29</f>
+        <f>Segments!C17</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>Segments!D29</f>
+        <f>Segments!D17</f>
         <v/>
       </c>
       <c r="H8" s="14">
-        <f>Segments!E29</f>
+        <f>Segments!E17</f>
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>Segments!F29</f>
+        <f>Segments!F17</f>
         <v/>
       </c>
       <c r="J8" s="14">
-        <f>Segments!G29</f>
+        <f>Segments!G17</f>
         <v/>
       </c>
     </row>
@@ -6734,36 +6781,36 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="19">
         <f>C11+C10</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="19">
         <f>D11+D10</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="19">
         <f>E11+E10</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>Segments!C32</f>
+        <f>Segments!C20</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>Segments!D32</f>
+        <f>Segments!D20</f>
         <v/>
       </c>
       <c r="H9" s="14">
-        <f>Segments!E32</f>
+        <f>Segments!E20</f>
         <v/>
       </c>
       <c r="I9" s="14">
-        <f>Segments!F32</f>
+        <f>Segments!F20</f>
         <v/>
       </c>
       <c r="J9" s="14">
-        <f>Segments!G32</f>
+        <f>Segments!G20</f>
         <v/>
       </c>
     </row>
@@ -6773,33 +6820,33 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="23" t="n">
         <v>66.428122</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="23" t="n">
         <v>68.643861</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="23" t="n">
         <v>85.39563699999999</v>
       </c>
       <c r="F10" s="14">
-        <f>Segments!C30</f>
+        <f>Segments!C18</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Segments!D30</f>
+        <f>Segments!D18</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Segments!E30</f>
+        <f>Segments!E18</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Segments!F30</f>
+        <f>Segments!F18</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Segments!G30</f>
+        <f>Segments!G18</f>
         <v/>
       </c>
     </row>
@@ -6809,33 +6856,33 @@
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="23" t="n">
         <v>647.606782</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="23" t="n">
         <v>968.439154</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="23" t="n">
         <v>1266.636844</v>
       </c>
       <c r="F11" s="14">
-        <f>Segments!C31</f>
+        <f>Segments!C19</f>
         <v/>
       </c>
       <c r="G11" s="14">
-        <f>Segments!D31</f>
+        <f>Segments!D19</f>
         <v/>
       </c>
       <c r="H11" s="14">
-        <f>Segments!E31</f>
+        <f>Segments!E19</f>
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>Segments!F31</f>
+        <f>Segments!F19</f>
         <v/>
       </c>
       <c r="J11" s="14">
-        <f>Segments!G31</f>
+        <f>Segments!G19</f>
         <v/>
       </c>
     </row>
@@ -6845,13 +6892,13 @@
           <t>Net finance cost</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="23" t="n">
         <v>-89.01433400000001</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="23" t="n">
         <v>-87.66669899999999</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="23" t="n">
         <v>-74.15399499999999</v>
       </c>
       <c r="F12" s="14">
@@ -6881,35 +6928,35 @@
           <t>Profit before zakat</t>
         </is>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="19">
         <f>C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="19">
         <f>D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="19">
         <f>E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="19">
         <f>F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="19">
         <f>G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="19">
         <f>H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="19">
         <f>I11+I12</f>
         <v/>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="19">
         <f>J11+J12</f>
         <v/>
       </c>
@@ -6920,32 +6967,32 @@
           <t>Zakat &amp; income tax</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="23" t="n">
         <v>-39.126206</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="23" t="n">
         <v>-63.891298</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="23" t="n">
         <v>-107.681788</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="19">
         <f>-F13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="19">
         <f>-G13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="19">
         <f>-H13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="19">
         <f>-I13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="J14" s="29">
+      <c r="J14" s="19">
         <f>-J13*Assumptions!$C$14</f>
         <v/>
       </c>
@@ -6956,32 +7003,32 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="23" t="n">
         <v>518.492623</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="23" t="n">
         <v>816.881157</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="23" t="n">
         <v>1084.801061</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="19">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="19">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="19">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="19">
         <f>I13+I14</f>
         <v/>
       </c>
-      <c r="J15" s="29">
+      <c r="J15" s="19">
         <f>J13+J14</f>
         <v/>
       </c>
@@ -6992,7 +7039,7 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="23" t="n">
         <v>1080.396042</v>
       </c>
       <c r="F16" s="14">
@@ -7017,8 +7064,6 @@
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
+++ b/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -135,15 +135,10 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -151,7 +146,11 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -522,9 +521,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="116" customWidth="1" min="1" max="1"/>
@@ -663,87 +662,83 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>bounds, and the pasted alternate framings of the contested gross-margin judgement. Everything else — every</t>
+          <t>bounds, the two pasted framings of the contested gross-margin judgement, and the expert-panel median.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>lens base value and bound, the whole worked expert panel and its median, every ratio, and the anchor roll —</t>
+          <t>Everything else — every lens base value, the relative/normalised/book bear and bull bounds, and the anchor</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>is a live formula. Changing a driver reprices the model but does NOT redraw the engine outputs; every</t>
+          <t>roll — is a live formula. Changing a driver reprices the model but does NOT redraw the engine outputs.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>pasted grid's base row is asserted at build time to reproduce the live base case.</t>
-        </is>
-      </c>
+      <c r="A23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>How revenue is built. Not as one growth rate. A cable maker is a metal converter: materials (copper and</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>How revenue is built, and how to test it. A cable maker is a metal converter: materials (copper and</t>
+          <t>aluminium) are 94.9% of cost of revenue. The build prices a tonnage index as metal content — on its own</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>aluminium) are 94.9% of cost of revenue. The Segments sheet builds a tonnage index times a metal price on</t>
+          <t>commodity path — plus a conversion spread whose cost escalates on domestic inflation; gross margin is the</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>its own path, plus conversion cost on domestic inflation, plus a CONVERSION SPREAD PER TONNE calibrated to</t>
+          <t>OUTPUT of that stack, not an input. The central judgement is the margin the business sustains once the</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>the margin-anchor path at the BASE metal price and held fixed under metal shocks. The gross margin row is</t>
+          <t>FY2024-25 metal tailwind has passed, anchored on the most recent reviewed actual (H1-2026, 15.26%) rather</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>therefore an OUTPUT: set the metal price multiplier on Assumptions above 1.00 and watch revenue rise while</t>
+          <t>than the higher FY2025 full-year print (16.24%), and computed both ways.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>the margin dilutes and the value falls — the H1-2026 mechanism (flat gross profit on +9.5% revenue). The</t>
-        </is>
-      </c>
+      <c r="A30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>margin anchor is the reviewed H1-2026 actual (15.26%), not the higher FY2025 print (16.24%), and the</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>contested judgement is computed both ways plus at the Q2-2026 exit rate (14.99%).</t>
+          <t>shown as ranges.</t>
         </is>
       </c>
     </row>
@@ -753,105 +748,59 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Conventions. Year-end discounting, annual compounding (mid-year would raise the DCF lens ~4%). WACC weights</t>
+          <t>Sourcing. FY2022-FY2025 come from the company's own audited consolidated financial statements (KPMG); the</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>use net financial debt, consistent with the net-debt bridge. Beta 1.129 is a Dimson sum-beta on 185 weekly</t>
+          <t>FY2026 near-term anchor is the Tadawul-filed reviewed H1-2026 interim. Every input is listed with source and</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>observations (plain OLS 0.928; 90% CI 0.62-1.64 — the grid prices the width). The terminal is discounted</t>
+          <t>date in the companion bibliography document. No aggregator or broker figure is a build source.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>all-equity because the model itself forecasts net cash from FY2028E.</t>
-        </is>
-      </c>
+      <c r="A37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr"/>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Currency. SAR million unless stated. Spot SAR 104.80 (2026-08-18 close). Sheets: READ FIRST · Summary ·</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges.</t>
+          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Sourcing. FY2022-FY2025 come from the company's own audited consolidated financial statements (KPMG); the</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>FY2026 near-term anchor is the Tadawul-filed reviewed H1-2026 interim. Every input is listed with source and</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>date in the companion bibliography document. No aggregator or broker figure is a build source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Currency. SAR million unless stated. Spot SAR 104.90 (2026-08-18 close). Sheets: READ FIRST · Summary ·</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -859,7 +808,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -953,13 +902,13 @@
           <t>Property, plant &amp; equipment</t>
         </is>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="19" t="n">
         <v>1206.659875</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="19" t="n">
         <v>1336.038944</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="19" t="n">
         <v>1491.86312</v>
       </c>
       <c r="F5" s="14">
@@ -989,13 +938,13 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="19" t="n">
         <v>1909.11144</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="19" t="n">
         <v>2126.036688</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="19" t="n">
         <v>2411.049305</v>
       </c>
     </row>
@@ -1005,13 +954,13 @@
           <t>Trade &amp; other receivables</t>
         </is>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="19" t="n">
         <v>1418.920843</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="19" t="n">
         <v>2112.098567</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="19" t="n">
         <v>2712.677113</v>
       </c>
     </row>
@@ -1021,13 +970,13 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="19" t="n">
         <v>150.051628</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="19" t="n">
         <v>90.672725</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="19" t="n">
         <v>236.043009</v>
       </c>
     </row>
@@ -1037,13 +986,13 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="19" t="n">
         <v>4830.929068</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="19" t="n">
         <v>5811.584098</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="19" t="n">
         <v>7281.581695</v>
       </c>
     </row>
@@ -1053,33 +1002,33 @@
           <t>Gross borrowings incl. leases</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="19" t="n">
         <v>730.611837</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="19" t="n">
         <v>440.445599</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="19" t="n">
         <v>621.216217</v>
       </c>
       <c r="F10" s="14">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
     </row>
@@ -1089,13 +1038,13 @@
           <t>Trade &amp; other payables</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="19" t="n">
         <v>1486.905974</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="19" t="n">
         <v>2040.707151</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="19" t="n">
         <v>2190.467493</v>
       </c>
     </row>
@@ -1105,13 +1054,13 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="19" t="n">
         <v>1841.126309</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="19" t="n">
         <v>2197.428104</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="19" t="n">
         <v>2933.258925</v>
       </c>
       <c r="F12" s="14">
@@ -1141,13 +1090,13 @@
           <t>Net financial debt</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="19" t="n">
         <v>580.560209</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="19" t="n">
         <v>349.772874</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="19" t="n">
         <v>385.173208</v>
       </c>
       <c r="F13" s="14">
@@ -1177,13 +1126,13 @@
           <t>Equity attributable</t>
         </is>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="19" t="n">
         <v>2246.744341</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="19" t="n">
         <v>2624.35365</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="19" t="n">
         <v>3246.136935</v>
       </c>
       <c r="F14" s="14">
@@ -1229,23 +1178,23 @@
           <t>Net debt, start of year</t>
         </is>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="29">
         <f>Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="29">
         <f>C24</f>
         <v/>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="29">
         <f>D24</f>
         <v/>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="29">
         <f>E24</f>
         <v/>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="29">
         <f>F24</f>
         <v/>
       </c>
@@ -1256,24 +1205,24 @@
           <t>Surplus cash</t>
         </is>
       </c>
-      <c r="C18" s="19">
-        <f>Assumptions!$C$53-C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="19">
-        <f>Assumptions!$C$53-D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="19">
-        <f>Assumptions!$C$53-E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="19">
-        <f>Assumptions!$C$53-F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="19">
-        <f>Assumptions!$C$53-G17</f>
+      <c r="C18" s="29">
+        <f>Assumptions!$C$60-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="29">
+        <f>Assumptions!$C$60-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="29">
+        <f>Assumptions!$C$60-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="29">
+        <f>Assumptions!$C$60-F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="29">
+        <f>Assumptions!$C$60-G17</f>
         <v/>
       </c>
     </row>
@@ -1283,24 +1232,24 @@
           <t>Net interest</t>
         </is>
       </c>
-      <c r="C19" s="19">
-        <f>Assumptions!C$32*Assumptions!$C$53-Assumptions!$C$34*MAX(C18,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="19">
-        <f>Assumptions!D$32*Assumptions!$C$53-Assumptions!$C$34*MAX(D18,0)</f>
-        <v/>
-      </c>
-      <c r="E19" s="19">
-        <f>Assumptions!E$32*Assumptions!$C$53-Assumptions!$C$34*MAX(E18,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="19">
-        <f>Assumptions!F$32*Assumptions!$C$53-Assumptions!$C$34*MAX(F18,0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="19">
-        <f>Assumptions!G$32*Assumptions!$C$53-Assumptions!$C$34*MAX(G18,0)</f>
+      <c r="C19" s="29">
+        <f>Assumptions!C$38*Assumptions!$C$60-Assumptions!$C$40*MAX(C18,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>Assumptions!D$38*Assumptions!$C$60-Assumptions!$C$40*MAX(D18,0)</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>Assumptions!E$38*Assumptions!$C$60-Assumptions!$C$40*MAX(E18,0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>Assumptions!F$38*Assumptions!$C$60-Assumptions!$C$40*MAX(F18,0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="29">
+        <f>Assumptions!G$38*Assumptions!$C$60-Assumptions!$C$40*MAX(G18,0)</f>
         <v/>
       </c>
     </row>
@@ -1337,23 +1286,23 @@
           <t>Profit before zakat</t>
         </is>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="29">
         <f>C20-C19</f>
         <v/>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="29">
         <f>D20-D19</f>
         <v/>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="29">
         <f>E20-E19</f>
         <v/>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="29">
         <f>F20-F19</f>
         <v/>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="29">
         <f>G20-G19</f>
         <v/>
       </c>
@@ -1364,24 +1313,24 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="C22" s="19">
-        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
-        <v/>
-      </c>
-      <c r="D22" s="19">
-        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
-        <v/>
-      </c>
-      <c r="E22" s="19">
-        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
-        <v/>
-      </c>
-      <c r="F22" s="19">
-        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
-        <v/>
-      </c>
-      <c r="G22" s="19">
-        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)</f>
+      <c r="C22" s="29">
+        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
+        <v/>
+      </c>
+      <c r="D22" s="29">
+        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
+        <v/>
+      </c>
+      <c r="E22" s="29">
+        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
+        <v/>
+      </c>
+      <c r="F22" s="29">
+        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
+        <v/>
+      </c>
+      <c r="G22" s="29">
+        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
         <v/>
       </c>
     </row>
@@ -1391,24 +1340,24 @@
           <t>Dividend</t>
         </is>
       </c>
-      <c r="C23" s="19">
-        <f>Assumptions!$C$33*C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="19">
-        <f>Assumptions!$C$33*D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="19">
-        <f>Assumptions!$C$33*E22</f>
-        <v/>
-      </c>
-      <c r="F23" s="19">
-        <f>Assumptions!$C$33*F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="19">
-        <f>Assumptions!$C$33*G22</f>
+      <c r="C23" s="29">
+        <f>Assumptions!$C$39*C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>Assumptions!$C$39*D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="29">
+        <f>Assumptions!$C$39*E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f>Assumptions!$C$39*F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f>Assumptions!$C$39*G22</f>
         <v/>
       </c>
     </row>
@@ -1418,23 +1367,23 @@
           <t>Net debt, end of year</t>
         </is>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="29">
         <f>C17-(DCF!C27-C19*(1-Assumptions!$C$14))+C23</f>
         <v/>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="29">
         <f>D17-(DCF!D27-D19*(1-Assumptions!$C$14))+D23</f>
         <v/>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="29">
         <f>E17-(DCF!E27-E19*(1-Assumptions!$C$14))+E23</f>
         <v/>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="29">
         <f>F17-(DCF!F27-F19*(1-Assumptions!$C$14))+F23</f>
         <v/>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="29">
         <f>G17-(DCF!G27-G19*(1-Assumptions!$C$14))+G23</f>
         <v/>
       </c>
@@ -1445,29 +1394,31 @@
           <t>Equity attributable</t>
         </is>
       </c>
-      <c r="C25" s="19">
-        <f>Assumptions!$C$54+C22-C23</f>
-        <v/>
-      </c>
-      <c r="D25" s="19">
+      <c r="C25" s="29">
+        <f>Assumptions!$C$61+C22-C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="29">
         <f>C25+D22-D23</f>
         <v/>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="29">
         <f>D25+E22-E23</f>
         <v/>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="29">
         <f>E25+F22-F23</f>
         <v/>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="29">
         <f>F25+G22-G23</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1475,7 +1426,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1658,23 +1609,23 @@
           <t>Free cash flow to firm</t>
         </is>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="37">
         <f>C5+C6+C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="37">
         <f>D5+D6+D7+D8</f>
         <v/>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="37">
         <f>E5+E6+E7+E8</f>
         <v/>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="37">
         <f>F5+F6+F7+F8</f>
         <v/>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="37">
         <f>G5+G6+G7+G8</f>
         <v/>
       </c>
@@ -1685,23 +1636,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="39">
         <f>DCF!C19</f>
         <v/>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="39">
         <f>DCF!D19</f>
         <v/>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="39">
         <f>DCF!E19</f>
         <v/>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="39">
         <f>DCF!F19</f>
         <v/>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="39">
         <f>DCF!G19</f>
         <v/>
       </c>
@@ -1712,29 +1663,31 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="29">
         <f>C9*C10</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="29">
         <f>D9*D10</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="29">
         <f>E9*E10</f>
         <v/>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="29">
         <f>F9*F10</f>
         <v/>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="29">
         <f>G9*G10</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1742,7 +1695,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1845,23 +1798,23 @@
         </is>
       </c>
       <c r="C6" s="14">
-        <f>Segments!C20</f>
+        <f>Segments!C32</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>Segments!D20</f>
+        <f>Segments!D32</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>Segments!E20</f>
+        <f>Segments!E32</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>Segments!F20</f>
+        <f>Segments!F32</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>Segments!G20</f>
+        <f>Segments!G32</f>
         <v/>
       </c>
     </row>
@@ -1952,29 +1905,31 @@
           <t>ROIC</t>
         </is>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="33">
         <f>DCF!C33</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="33">
         <f>DCF!D33</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="33">
         <f>DCF!E33</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="33">
         <f>DCF!F33</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="33">
         <f>DCF!G33</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1982,7 +1937,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2038,10 +1993,10 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>87.25808430972248</v>
+        <v>87.21321014037129</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>76.53735505038735</v>
+        <v>76.54888951524968</v>
       </c>
     </row>
     <row r="6">
@@ -2051,10 +2006,10 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>97.66760169647281</v>
+        <v>97.61126202615651</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>92.86041807876856</v>
+        <v>92.86909864606133</v>
       </c>
     </row>
     <row r="7">
@@ -2064,10 +2019,10 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>104.8512200742135</v>
+        <v>104.7866044705799</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>105.053385509702</v>
+        <v>105.0593696127112</v>
       </c>
     </row>
     <row r="8">
@@ -2077,10 +2032,10 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>112.6900469186186</v>
+        <v>112.6160892961509</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>118.7070159704662</v>
+        <v>118.7094846328782</v>
       </c>
     </row>
     <row r="9">
@@ -2090,10 +2045,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>126.2675579273705</v>
+        <v>126.1767140981632</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>144.0616010928045</v>
+        <v>144.0563430692076</v>
       </c>
     </row>
     <row r="10">
@@ -2103,10 +2058,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>104.9</v>
+        <v>104.8</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>104.9</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="11">
@@ -2115,11 +2070,11 @@
           <t>P(above spot)</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
-        <v>0.49836</v>
-      </c>
-      <c r="C11" s="28" t="n">
-        <v>0.50322</v>
+      <c r="B11" s="23" t="n">
+        <v>0.4997</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>0.50542</v>
       </c>
     </row>
     <row r="12">
@@ -2128,11 +2083,11 @@
           <t>Annualised vol</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
-        <v>0.3616713439785802</v>
-      </c>
-      <c r="C12" s="28" t="n">
-        <v>0.3671662360524218</v>
+      <c r="B12" s="23" t="n">
+        <v>0.3614703996629836</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>0.3670575648854793</v>
       </c>
     </row>
     <row r="14">
@@ -2143,7 +2098,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2151,12 +2108,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -2183,12 +2140,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Each cell is a complete revaluation and does NOT redraw when a driver changes; every block's base row REPRODUCES the base case (asserted at build time)</t>
+          <t>Each cell is a complete revaluation and does NOT redraw when a driver changes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>DCF value per share: terminal WACC (rows) x terminal growth (cols)</t>
         </is>
@@ -2225,463 +2182,404 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=7.72%</t>
+          <t>WACC_t=7.48%</t>
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>136.5639956911652</v>
+        <v>141.7056057772044</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>156.3911656162713</v>
+        <v>163.715865885987</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>186.7266093183625</v>
+        <v>198.2042805447696</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>239.1603346397014</v>
-      </c>
-      <c r="F6" s="41" t="inlineStr">
-        <is>
-          <t>n/m</t>
+        <v>260.2479130974581</v>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>n.m.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=8.72%</t>
+          <t>WACC_t=8.48%</t>
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>116.8034962931929</v>
+        <v>120.4623841952295</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>129.8409494659834</v>
+        <v>134.7210292900971</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>148.2860612426722</v>
+        <v>155.2188360125738</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>176.4998466264028</v>
+        <v>187.3299521235833</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>225.2565779778832</v>
+        <v>245.0864687133326</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=9.72%</t>
+          <t>WACC_t=9.48%</t>
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>102.163054852874</v>
+        <v>104.8967296610403</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>111.1904287412299</v>
+        <v>114.6678051971448</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>123.2801134487121</v>
+        <v>127.905424577565</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>140.3784929705279</v>
+        <v>146.9294453787323</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>166.5248373182366</v>
+        <v>176.7240270270523</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=10.72%</t>
+          <t>WACC_t=10.48%</t>
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>90.88100527108116</v>
+        <v>93.00059958544631</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>97.36966430899766</v>
+        <v>99.97128853350969</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>105.7111587372711</v>
+        <v>109.0117190503424</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>116.8772553690259</v>
+        <v>121.2543672012037</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>132.6632522149492</v>
+        <v>138.8421999218402</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>WACC_t=11.72%</t>
+          <t>WACC_t=11.48%</t>
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>81.92065637634063</v>
+        <v>83.61297829887353</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>86.71695307455919</v>
+        <v>88.73699993247544</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>92.68916241571443</v>
+        <v>95.16215451155131</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>100.3622454011173</v>
+        <v>103.4905512602372</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>110.6282686274013</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>n/m: terminal spread (WACC_t - g) below 2% — the Gordon terminal value is not meaningful there and no number is shown (the first edition printed clamped values).</t>
+        <v>114.7635647327278</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Beta sensitivity (DCF value/share)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Risk-free rate (10y SAR; explicit AND terminal move together) — DCF value/share</t>
-        </is>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>134.1012811749074</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>136.089531512596</v>
+        <v>131.1659864625187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>1.129</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>123.2801134487121</v>
+        <v>127.905424577565</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>6.02%</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>112.5394948589756</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Beta (explicit-window Ke only; terminal beta held at 1.0 as stated) — DCF value/share</t>
-        </is>
+        <v>125.5381303609279</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>122.8400164516531</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n">
-        <v>129.2478439097057</v>
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Metal price x sensitivity (DCF value/share)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>126.4206730646305</v>
+        <v>139.3236347299058</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1.129</t>
+          <t>0.925</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>123.2801134487121</v>
+        <v>133.6031807444171</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>120.9998758649224</v>
+        <v>127.905424577565</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.075</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>118.4009111655918</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>Metal price x (flat multiplier; spread held — margin is the output) — DCF value/share</t>
-        </is>
+        <v>122.2278357157988</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>116.5683245327664</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="n">
-        <v>135.7206754924927</v>
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Sustained gross margin sensitivity (DCF value/share)</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="B27" s="17" t="n">
-        <v>129.5003944706025</v>
+        <v>108.4540646253059</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="B28" s="17" t="n">
-        <v>123.2801134487121</v>
+        <v>116.1041350901616</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>0.1526</t>
         </is>
       </c>
       <c r="B29" s="17" t="n">
-        <v>117.0598324268218</v>
+        <v>127.905424577565</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="B30" s="17" t="n">
-        <v>110.8395514049315</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>Sustained gross margin (0.1499 = the Q2-2026 exit rate) — DCF value/share</t>
-        </is>
+        <v>131.6763234351193</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>139.6016853407702</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="n">
-        <v>104.0336994130316</v>
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>Volume x sensitivity (DCF value/share)</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>111.6031665507623</v>
+        <v>117.0795645368853</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>0.1499</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="B35" s="17" t="n">
-        <v>119.1077739641657</v>
+        <v>122.4970935834225</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>0.1526</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="B36" s="17" t="n">
-        <v>123.2801134487121</v>
+        <v>127.905424577565</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>127.0112805596384</v>
+        <v>133.3052385180974</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>134.8531372449724</v>
+        <v>138.6971354501409</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>Volume x — DCF value/share</t>
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>Net working capital / revenue sensitivity (DCF value/share)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>112.7169531231438</v>
+        <v>133.5580939831738</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>118.0031768846487</v>
+        <v>130.7317592803693</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>123.2801134487121</v>
+        <v>127.905424577565</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>128.5484520748093</v>
+        <v>125.0790898747605</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>133.8087999793565</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>Net working capital / revenue — DCF value/share</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="n">
-        <v>128.8502974586405</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="n">
-        <v>126.0652054536764</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="n">
-        <v>123.2801134487121</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="n">
-        <v>120.4950214437479</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="n">
-        <v>117.7099294387837</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>The metal row matches the LIVE Segments sheet: set the metal price multiplier on Assumptions and the whole model reprices the same direction (higher metal dilutes the margin and lowers the value).</t>
-        </is>
+        <v>122.2527551719562</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2689,9 +2587,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2757,8 +2655,8 @@
           <t>EPS (SAR)</t>
         </is>
       </c>
-      <c r="B5" s="15">
-        <f>Assumptions!$C$58/Assumptions!$C$6</f>
+      <c r="B5" s="7">
+        <f>'Income Statement'!E16/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C5" s="15">
@@ -2789,7 +2687,7 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>Assumptions!$C$54/Assumptions!$C$6</f>
+        <f>Assumptions!$C$61/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C6" s="15">
@@ -2816,11 +2714,11 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>ROE (%, on average equity)</t>
-        </is>
-      </c>
-      <c r="B7" s="9">
-        <f>Assumptions!$C$58/((Assumptions!$C$59+Assumptions!$C$54)/2)</f>
+          <t>ROE (%) — attributable profit / average equity</t>
+        </is>
+      </c>
+      <c r="B7" s="8">
+        <f>'Income Statement'!E16/AVERAGE('Balance Sheet'!D14,'Balance Sheet'!E14)</f>
         <v/>
       </c>
     </row>
@@ -2830,66 +2728,57 @@
           <t>Net debt / EBITDA (x)</t>
         </is>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="30">
         <f>Assumptions!$C$7/'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="C8" s="35">
-        <f>'Balance Sheet'!F13/Segments!C20</f>
-        <v/>
-      </c>
-      <c r="D8" s="35">
-        <f>'Balance Sheet'!G13/Segments!D20</f>
-        <v/>
-      </c>
-      <c r="E8" s="35">
-        <f>'Balance Sheet'!H13/Segments!E20</f>
-        <v/>
-      </c>
-      <c r="F8" s="35">
-        <f>'Balance Sheet'!I13/Segments!F20</f>
-        <v/>
-      </c>
-      <c r="G8" s="35">
-        <f>'Balance Sheet'!J13/Segments!G20</f>
+      <c r="C8" s="34">
+        <f>'Balance Sheet'!F13/Segments!C32</f>
+        <v/>
+      </c>
+      <c r="D8" s="34">
+        <f>'Balance Sheet'!G13/Segments!D32</f>
+        <v/>
+      </c>
+      <c r="E8" s="34">
+        <f>'Balance Sheet'!H13/Segments!E32</f>
+        <v/>
+      </c>
+      <c r="F8" s="34">
+        <f>'Balance Sheet'!I13/Segments!F32</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>'Balance Sheet'!J13/Segments!G32</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>EV/EBITDA (FY2025 basis, x)</t>
-        </is>
-      </c>
-      <c r="B9" s="35">
-        <f>(DCF!C8+Assumptions!$C$7)/'Income Statement'!E9</f>
+          <t>Trailing EV/EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="B9" s="30">
+        <f>(Assumptions!$C$5*Assumptions!$C$6+Assumptions!$C$7)/'Income Statement'!E9</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>P/E (FY2025 basis, x)</t>
-        </is>
-      </c>
-      <c r="B10" s="35">
-        <f>DCF!C8/Assumptions!$C$58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>P/E (trailing twelve months, x)</t>
-        </is>
-      </c>
-      <c r="B11" s="35">
-        <f>DCF!C8/(Assumptions!$C$58+Assumptions!$C$60-Assumptions!$C$61)</f>
+          <t>Trailing P/E (x)</t>
+        </is>
+      </c>
+      <c r="B10" s="30">
+        <f>Assumptions!$C$5/B5</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2897,9 +2786,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2940,12 +2829,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>EV/EBITDA</t>
+          <t>Fwd EV/EBITDA</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Basis &amp; note (each multiple recomputed from the peer's own EV and guidance)</t>
+          <t>Note</t>
         </is>
       </c>
     </row>
@@ -2960,13 +2849,13 @@
           <t>Tadawul</t>
         </is>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="30">
         <f>'Per-Share &amp; Ratios'!B9</f>
         <v/>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>FY2025 basis (TTM P/E 13.9x); see Per-Share &amp; Ratios</t>
+          <t>trailing; ~14.5x trailing P/E</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2870,12 @@
           <t>Milan</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
-        <v>14</v>
+      <c r="C6" s="22" t="n">
+        <v>8.5</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>FY2026E on guidance RAISED 30-Jul-2026 (EUR 2.8-2.9bn) vs ~EUR 40bn EV</t>
+          <t>developed-market major</t>
         </is>
       </c>
     </row>
@@ -3001,12 +2890,12 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
-        <v>8.699999999999999</v>
+      <c r="C7" s="22" t="n">
+        <v>7.5</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>FY2026E on guidance raised 29-Jul-2026 (EUR 770-840mn) vs ~EUR 7.1bn EV</t>
+          <t>developed-market major</t>
         </is>
       </c>
     </row>
@@ -3021,12 +2910,12 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
-        <v>29</v>
+      <c r="C8" s="22" t="n">
+        <v>26</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>NTM; high-growth EM premium</t>
+          <t>high-growth EM premium</t>
         </is>
       </c>
     </row>
@@ -3041,12 +2930,12 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
-        <v>31</v>
+      <c r="C9" s="22" t="n">
+        <v>24</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>NTM (~24-25x only on FY-Mar-2028, two years out)</t>
+          <t>high-growth EM premium</t>
         </is>
       </c>
     </row>
@@ -3070,19 +2959,14 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA applied in the relative lens: 10.0x — a deliberate DISCOUNT to the corrected developed band (~8.5-14.5x) for single-country and single-customer concentration, not its mid-point.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Quotes as of 18-Aug-2026. Cross-check multiples only — never a source for any Riyadh Cables figure.</t>
+          <t>Justified EV/EBITDA applied in the relative lens: 9.5x (mid-range, single-country discount).</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3090,7 +2974,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3334,7 +3218,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3342,9 +3228,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3432,7 +3318,7 @@
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>Assumptions!$C$41</f>
+        <f>Assumptions!$C$46</f>
         <v/>
       </c>
       <c r="F5" s="15">
@@ -3463,7 +3349,7 @@
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="F6" s="15">
@@ -3494,7 +3380,7 @@
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>Assumptions!$C$43</f>
+        <f>Assumptions!$C$48</f>
         <v/>
       </c>
       <c r="F7" s="15">
@@ -3525,7 +3411,7 @@
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>Assumptions!$C$44</f>
+        <f>Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="F8" s="15">
@@ -3568,12 +3454,11 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Expert panel median (live — see the worked panel below)</t>
-        </is>
-      </c>
-      <c r="C11" s="15">
-        <f>MEDIAN(C26,C30,C39)</f>
-        <v/>
+          <t>Expert panel median (whole-model — pasted)</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>125.9789008877625</v>
       </c>
     </row>
     <row r="12">
@@ -3618,7 +3503,7 @@
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>134.8531372449724</v>
+        <v>139.6016853407702</v>
       </c>
     </row>
     <row r="17">
@@ -3628,267 +3513,13 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>111.6031665507623</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Q2-2026 exit rate (14.99%) sustained — DCF value (pasted re-run)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>119.1143960075278</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Expert panel — three methods, worked live on the same forecast base</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>E1 mid-cycle EBITDA margin (FY2028E)</t>
-        </is>
-      </c>
-      <c r="C21" s="18">
-        <f>Segments!E21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>E1 mid-cycle revenue (FY2028E scale)</t>
-        </is>
-      </c>
-      <c r="C22" s="14">
-        <f>Segments!E15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>E1 normalised EBIT (margin x revenue - D&amp;A)</t>
-        </is>
-      </c>
-      <c r="C23" s="19">
-        <f>C21*C22-Assumptions!$C$29*C22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>E1 normalised net interest (FY2028 Kd on FY2025 debt less cash yield)</t>
-        </is>
-      </c>
-      <c r="C24" s="19">
-        <f>Assumptions!E$32*Assumptions!$C$53-Assumptions!$C$34*(Assumptions!$C$53-Assumptions!$C$7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>E1 earnings per share after tax and minorities</t>
-        </is>
-      </c>
-      <c r="C25" s="15">
-        <f>(C23-C24)*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)/Assumptions!$C$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>Expert 1 — value at anchor (13x; range 10x/16x)</t>
-        </is>
-      </c>
-      <c r="B26" s="15">
-        <f>(10*C25)*DCF!$C$50-Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="C26" s="21">
-        <f>(13*C25)*DCF!$C$50-Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="D26" s="15">
-        <f>(16*C25)*DCF!$C$50-Assumptions!$C$47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>E2 mid-cycle FCFF (average FY2028-30E)</t>
-        </is>
-      </c>
-      <c r="C27" s="14">
-        <f>AVERAGE(DCF!E27:G27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>E2 after-tax net interest (FY2029 Kd basis)</t>
-        </is>
-      </c>
-      <c r="C28" s="19">
-        <f>(Assumptions!F$32*Assumptions!$C$53-Assumptions!$C$34*(Assumptions!$C$53-Assumptions!$C$7))*(1-Assumptions!$C$14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>E2 owner cash (FCFF less after-tax interest, net of minorities)</t>
-        </is>
-      </c>
-      <c r="C29" s="19">
-        <f>(C27-C28)*(1-Assumptions!$C$36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>Expert 2 — value at anchor (perpetuity at terminal Ke; range on rate/growth)</t>
-        </is>
-      </c>
-      <c r="B30" s="15">
-        <f>(C29*1.02/((DCF!C6+DCF!C11)/2-0.02)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="C30" s="21">
-        <f>(C29*(1+Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="D30" s="15">
-        <f>(C29*1.05/(DCF!C11-0.05)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>E3 invested capital, 31-Dec-2025 (NWC + PP&amp;E)</t>
-        </is>
-      </c>
-      <c r="C31" s="19">
-        <f>Assumptions!$C$51+Assumptions!$C$52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>E3 PV of economic profit, FY26E (NOPAT - WACC x opening capital)</t>
-        </is>
-      </c>
-      <c r="C32" s="19">
-        <f>(DCF!C21-DCF!C18*C31)*DCF!C19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>E3 PV of economic profit, FY27E (NOPAT - WACC x opening capital)</t>
-        </is>
-      </c>
-      <c r="C33" s="19">
-        <f>(DCF!D21-DCF!D18*DCF!C32)*DCF!D19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>E3 PV of economic profit, FY28E (NOPAT - WACC x opening capital)</t>
-        </is>
-      </c>
-      <c r="C34" s="19">
-        <f>(DCF!E21-DCF!E18*DCF!D32)*DCF!E19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>E3 PV of economic profit, FY29E (NOPAT - WACC x opening capital)</t>
-        </is>
-      </c>
-      <c r="C35" s="19">
-        <f>(DCF!F21-DCF!F18*DCF!E32)*DCF!F19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>E3 PV of economic profit, FY30E (NOPAT - WACC x opening capital)</t>
-        </is>
-      </c>
-      <c r="C36" s="19">
-        <f>(DCF!G21-DCF!G18*DCF!F32)*DCF!G19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>E3 PV of terminal economic profit (reconciles to the DCF terminal value)</t>
-        </is>
-      </c>
-      <c r="C37" s="19">
-        <f>(DCF!G21*(1+Assumptions!$C$21)-DCF!C13*DCF!G32)/(DCF!C13-Assumptions!$C$21)*DCF!G19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>E3 enterprise value (capital + PV of excess returns; equals the DCF EV)</t>
-        </is>
-      </c>
-      <c r="C38" s="19">
-        <f>C31+SUM(C32:C36)+C37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>Expert 3 — value at anchor (bridge as the DCF; range on persistence)</t>
-        </is>
-      </c>
-      <c r="B39" s="15">
-        <f>((C31+SUM(C32:C36)*0.7+C37*0.65-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="C39" s="21">
-        <f>((C38-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="D39" s="15">
-        <f>((C31+SUM(C32:C36)*1.15+C37*1.2-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
-        <v/>
+        <v>116.1041350901616</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3896,9 +3527,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3959,7 +3590,7 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>104.9</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="6">
@@ -3968,7 +3599,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="18" t="n">
         <v>149.7175</v>
       </c>
     </row>
@@ -3978,7 +3609,7 @@
           <t>Net financial debt at FY2025 (SAR mn, disclosed)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="19" t="n">
         <v>385.173208</v>
       </c>
     </row>
@@ -4004,8 +3635,8 @@
           <t>Risk-free rate (10-year SAR sukuk)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n">
-        <v>0.0552</v>
+      <c r="C9" s="20" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="10">
@@ -4014,7 +3645,7 @@
           <t>Sovereign default spread (netted out)</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="20" t="n">
         <v>0.0048</v>
       </c>
     </row>
@@ -4024,7 +3655,7 @@
           <t>Equity risk premium (rating basis)</t>
         </is>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="20" t="n">
         <v>0.0494</v>
       </c>
     </row>
@@ -4034,7 +3665,7 @@
           <t>Beta (own-stock vs TASI)</t>
         </is>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="21" t="n">
         <v>1.129</v>
       </c>
     </row>
@@ -4044,7 +3675,7 @@
           <t>Cost of debt, marginal pre-tax</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="20" t="n">
         <v>0.059</v>
       </c>
     </row>
@@ -4054,7 +3685,7 @@
           <t>Effective zakat and income tax rate</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="20" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -4080,8 +3711,8 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C16" s="24" t="n">
-        <v>0.0504</v>
+      <c r="C16" s="20" t="n">
+        <v>0.0502</v>
       </c>
     </row>
     <row r="17">
@@ -4090,8 +3721,8 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C17" s="24" t="n">
-        <v>0.0468</v>
+      <c r="C17" s="20" t="n">
+        <v>0.047</v>
       </c>
     </row>
     <row r="18">
@@ -4100,7 +3731,7 @@
           <t>Terminal beta</t>
         </is>
       </c>
-      <c r="C18" s="25" t="n">
+      <c r="C18" s="21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4110,7 +3741,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C19" s="20" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -4120,8 +3751,8 @@
           <t>Terminal net-debt weight</t>
         </is>
       </c>
-      <c r="C20" s="24" t="n">
-        <v>0</v>
+      <c r="C20" s="20" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="21">
@@ -4130,14 +3761,14 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C21" s="24" t="n">
+      <c r="C21" s="20" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Forecast drivers — ground-up cost stack</t>
+          <t>Forecast drivers — Cables &amp; wires leg (metal converter)</t>
         </is>
       </c>
       <c r="B22" s="11" t="n"/>
@@ -4156,19 +3787,19 @@
           <t>Cable volume index growth</t>
         </is>
       </c>
-      <c r="C23" s="24" t="n">
+      <c r="C23" s="20" t="n">
         <v>0.1</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D23" s="20" t="n">
         <v>0.075</v>
       </c>
-      <c r="E23" s="24" t="n">
+      <c r="E23" s="20" t="n">
         <v>0.065</v>
       </c>
-      <c r="F23" s="24" t="n">
+      <c r="F23" s="20" t="n">
         <v>0.055</v>
       </c>
-      <c r="G23" s="24" t="n">
+      <c r="G23" s="20" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4178,19 +3809,19 @@
           <t>Metal content price growth</t>
         </is>
       </c>
-      <c r="C24" s="24" t="n">
+      <c r="C24" s="20" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D24" s="24" t="n">
+      <c r="D24" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="24" t="n">
+      <c r="E24" s="20" t="n">
         <v>0.01</v>
       </c>
-      <c r="F24" s="24" t="n">
+      <c r="F24" s="20" t="n">
         <v>0.01</v>
       </c>
-      <c r="G24" s="24" t="n">
+      <c r="G24" s="20" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4200,19 +3831,19 @@
           <t>Conversion cost inflation</t>
         </is>
       </c>
-      <c r="C25" s="24" t="n">
+      <c r="C25" s="20" t="n">
         <v>0.03</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="20" t="n">
         <v>0.03</v>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="20" t="n">
         <v>0.03</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="20" t="n">
         <v>0.03</v>
       </c>
-      <c r="G25" s="24" t="n">
+      <c r="G25" s="20" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -4222,7 +3853,7 @@
           <t>Sustained gross margin (H1-2026 anchor)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="n">
+      <c r="C26" s="20" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -4232,418 +3863,486 @@
           <t>Gross-margin glide (added to anchor)</t>
         </is>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="25" t="n">
+      <c r="D27" s="21" t="n">
         <v>0.001</v>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="21" t="n">
         <v>0.001</v>
       </c>
-      <c r="F27" s="25" t="n">
+      <c r="F27" s="21" t="n">
         <v>0.0015</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="21" t="n">
         <v>0.0015</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Operating expenses / revenue</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D28" s="24" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="E28" s="24" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="F28" s="24" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="G28" s="24" t="n">
-        <v>0.042</v>
-      </c>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Forecast drivers — HV turnkey &amp; Other legs</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation / revenue</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="n">
-        <v>0.008500000000000001</v>
+          <t>HV turnkey revenue growth</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure / revenue</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="D30" s="24" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="E30" s="24" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="F30" s="24" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="G30" s="24" t="n">
-        <v>0.0177</v>
+          <t>HV turnkey segment margin</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="n">
+        <v>0.08378233242821985</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Net working capital / revenue</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="n">
-        <v>0.28</v>
+          <t>Other segment revenue growth</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Cost-of-debt path</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="D32" s="24" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="E32" s="24" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="F32" s="24" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="G32" s="24" t="n">
-        <v>0.055</v>
+          <t>Other segment margin</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="n">
+        <v>0.5786820313464731</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Forecast dividend payout ratio</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="n">
-        <v>0.55</v>
-      </c>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Forecast drivers — group</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Yield on surplus cash</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="n">
-        <v>0.04</v>
+          <t>Operating expenses / revenue</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G34" s="20" t="n">
+        <v>0.042</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Metal price multiplier (shock; 1.00 = base path)</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="n">
-        <v>1</v>
+          <t>Depreciation and amortisation / revenue</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>NCI share of profit (FY2025)</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="n">
-        <v>0.004060669885351275</v>
+          <t>Capital expenditure / revenue</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G36" s="20" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="11" t="n"/>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Net working capital / revenue</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C38" s="27" t="n">
-        <v>10</v>
+          <t>Cost-of-debt path</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="D38" s="20" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E38" s="20" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="G38" s="20" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C39" s="27" t="n">
-        <v>13</v>
+          <t>Forecast dividend payout ratio</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="n">
-        <v>0.28</v>
+          <t>Yield on surplus cash</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C41" s="28" t="n">
-        <v>0.45</v>
+          <t>NCI share of forecast profit</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="n">
+        <v>0.004060669885351275</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C42" s="28" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C43" s="28" t="n">
-        <v>0.2</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Weight — book</t>
-        </is>
-      </c>
-      <c r="C44" s="28" t="n">
-        <v>0.15</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Anchor roll</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="11" t="n"/>
-      <c r="I45" s="11" t="n"/>
-      <c r="J45" s="11" t="n"/>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Days to the anchor</t>
+          <t>Weight — discounted cash flow</t>
         </is>
       </c>
       <c r="C46" s="23" t="n">
-        <v>230</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>FY2025 dividend per share paid in window</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="n">
-        <v>2.25</v>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>FY2025 disclosed base (audited)</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="11" t="n"/>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="11" t="n"/>
-      <c r="I48" s="11" t="n"/>
-      <c r="J48" s="11" t="n"/>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>FY2025 metal content / materials (SAR mn)</t>
+          <t>Weight — book</t>
         </is>
       </c>
       <c r="C49" s="23" t="n">
-        <v>8486.925676999999</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 conversion cost (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C50" s="23" t="n">
-        <v>453.34873</v>
-      </c>
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Anchor roll</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="11" t="n"/>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="11" t="n"/>
+      <c r="I50" s="11" t="n"/>
+      <c r="J50" s="11" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>FY2025 net working capital (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C51" s="23" t="n">
-        <v>2933.258925</v>
+          <t>Days to the anchor</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>230</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>FY2025 PP&amp;E (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C52" s="23" t="n">
-        <v>1491.86312</v>
+          <t>FY2025 dividend per share paid in window</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C53" s="23" t="n">
-        <v>621.216217</v>
-      </c>
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>FY2025 disclosed base (audited)</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="11" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="11" t="n"/>
+      <c r="I53" s="11" t="n"/>
+      <c r="J53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>FY2025 equity attributable (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C54" s="23" t="n">
-        <v>3246.136935</v>
+          <t>FY2025 cables metal content (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="n">
+        <v>8486.925676999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>FY2025 associates carrying value (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C55" s="23" t="n">
-        <v>31.851877</v>
+          <t>FY2025 cables conversion cost (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="n">
+        <v>229.8024540000006</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>FY2025 non-operating assets (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C56" s="23" t="n">
-        <v>20.40064</v>
+          <t>FY2025 HV turnkey revenue (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="n">
+        <v>230.839181</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>FY2025 NCI carrying value (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C57" s="23" t="n">
-        <v>62.737156</v>
+          <t>FY2025 Other segment revenue (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>28.594413</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>FY2025 attributable profit (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C58" s="23" t="n">
-        <v>1080.396042</v>
+          <t>FY2025 net working capital (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="n">
+        <v>2933.258925</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>FY2024 equity attributable (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C59" s="23" t="n">
-        <v>2624.35365</v>
+          <t>FY2025 PP&amp;E (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="n">
+        <v>1491.86312</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>H1-2026 attributable profit (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C60" s="23" t="n">
-        <v>588.793</v>
+          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>621.216217</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>H1-2025 attributable profit (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C61" s="23" t="n">
-        <v>535.4690000000001</v>
+          <t>FY2025 equity attributable (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="n">
+        <v>3246.136935</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 associates carrying value (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="n">
+        <v>31.851877</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 non-operating assets (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="n">
+        <v>20.40064</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 NCI carrying value (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="n">
+        <v>62.737156</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4651,7 +4350,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4753,7 +4452,7 @@
           <t>Equity attributable (31-Dec-2025)</t>
         </is>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="24">
         <f>DCF!C48</f>
         <v/>
       </c>
@@ -4764,13 +4463,15 @@
           <t>Value per share at anchor (SAR)</t>
         </is>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="25">
         <f>DCF!C51</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4778,12 +4479,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -4796,7 +4497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Segments — ground-up cost-stack build</t>
+          <t>Segments — three legs, built to the group</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4810,7 +4511,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Materials on the metal path; conversion on domestic inflation; gross margin is the OUTPUT</t>
+          <t>Each disclosed Note 40 segment on its own driver; the cable leg is the metal converter; group gross margin is the blended OUTPUT</t>
         </is>
       </c>
     </row>
@@ -4852,94 +4553,77 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Cable volume index (FY2025=100)</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="C5" s="31">
-        <f>B5*(1+Assumptions!C$23)</f>
-        <v/>
-      </c>
-      <c r="D5" s="31">
-        <f>C5*(1+Assumptions!D$23)</f>
-        <v/>
-      </c>
-      <c r="E5" s="31">
-        <f>D5*(1+Assumptions!E$23)</f>
-        <v/>
-      </c>
-      <c r="F5" s="31">
-        <f>E5*(1+Assumptions!F$23)</f>
-        <v/>
-      </c>
-      <c r="G5" s="31">
-        <f>F5*(1+Assumptions!G$23)</f>
-        <v/>
-      </c>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Cables &amp; wires — the metal converter</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Metal content per unit (base path)</t>
-        </is>
-      </c>
-      <c r="B6" s="32">
-        <f>Assumptions!$C$49/100.0</f>
-        <v/>
-      </c>
-      <c r="C6" s="32">
-        <f>B6*(1+Assumptions!C$24)</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>C6*(1+Assumptions!D$24)</f>
-        <v/>
-      </c>
-      <c r="E6" s="32">
-        <f>D6*(1+Assumptions!E$24)</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>E6*(1+Assumptions!F$24)</f>
-        <v/>
-      </c>
-      <c r="G6" s="32">
-        <f>F6*(1+Assumptions!G$24)</f>
+          <t>Cable volume index (FY2025=100)</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" s="26">
+        <f>B6*(1+Assumptions!C$23)</f>
+        <v/>
+      </c>
+      <c r="D6" s="26">
+        <f>C6*(1+Assumptions!D$23)</f>
+        <v/>
+      </c>
+      <c r="E6" s="26">
+        <f>D6*(1+Assumptions!E$23)</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
+        <f>E6*(1+Assumptions!F$23)</f>
+        <v/>
+      </c>
+      <c r="G6" s="26">
+        <f>F6*(1+Assumptions!G$23)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Metal content per unit (after shock multiplier)</t>
-        </is>
-      </c>
-      <c r="B7" s="32">
-        <f>B6*Assumptions!$C$35</f>
-        <v/>
-      </c>
-      <c r="C7" s="32">
-        <f>C6*Assumptions!$C$35</f>
-        <v/>
-      </c>
-      <c r="D7" s="32">
-        <f>D6*Assumptions!$C$35</f>
-        <v/>
-      </c>
-      <c r="E7" s="32">
-        <f>E6*Assumptions!$C$35</f>
-        <v/>
-      </c>
-      <c r="F7" s="32">
-        <f>F6*Assumptions!$C$35</f>
-        <v/>
-      </c>
-      <c r="G7" s="32">
-        <f>G6*Assumptions!$C$35</f>
+          <t>Metal content per unit</t>
+        </is>
+      </c>
+      <c r="B7" s="27">
+        <f>Assumptions!$C$54/100.0</f>
+        <v/>
+      </c>
+      <c r="C7" s="27">
+        <f>B7*(1+Assumptions!C$24)</f>
+        <v/>
+      </c>
+      <c r="D7" s="27">
+        <f>C7*(1+Assumptions!D$24)</f>
+        <v/>
+      </c>
+      <c r="E7" s="27">
+        <f>D7*(1+Assumptions!E$24)</f>
+        <v/>
+      </c>
+      <c r="F7" s="27">
+        <f>E7*(1+Assumptions!F$24)</f>
+        <v/>
+      </c>
+      <c r="G7" s="27">
+        <f>F7*(1+Assumptions!G$24)</f>
         <v/>
       </c>
     </row>
@@ -4949,27 +4633,27 @@
           <t>Conversion cost per unit</t>
         </is>
       </c>
-      <c r="B8" s="32">
-        <f>Assumptions!$C$50/100.0</f>
-        <v/>
-      </c>
-      <c r="C8" s="32">
+      <c r="B8" s="27">
+        <f>Assumptions!$C$55/100.0</f>
+        <v/>
+      </c>
+      <c r="C8" s="27">
         <f>B8*(1+Assumptions!C$25)</f>
         <v/>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="27">
         <f>C8*(1+Assumptions!D$25)</f>
         <v/>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="27">
         <f>D8*(1+Assumptions!E$25)</f>
         <v/>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="27">
         <f>E8*(1+Assumptions!F$25)</f>
         <v/>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="27">
         <f>F8*(1+Assumptions!G$25)</f>
         <v/>
       </c>
@@ -4977,29 +4661,26 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Margin anchor path (calibrates the spread at base metal)</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="n">
-        <v>0.1623940528853008</v>
-      </c>
-      <c r="C9" s="33">
+          <t>Target gross margin (anchor + glide)</t>
+        </is>
+      </c>
+      <c r="C9" s="28">
         <f>Assumptions!$C$26+Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="28">
         <f>Assumptions!$C$26+Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="28">
         <f>Assumptions!$C$26+Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="28">
         <f>Assumptions!$C$26+Assumptions!F$27</f>
         <v/>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="28">
         <f>Assumptions!$C$26+Assumptions!G$27</f>
         <v/>
       </c>
@@ -5007,62 +4688,62 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Conversion spread per unit (calibrated at base metal, held under shocks)</t>
-        </is>
-      </c>
-      <c r="B10" s="32">
-        <f>B9/(1-B9)*(B6+B8)</f>
-        <v/>
-      </c>
-      <c r="C10" s="32">
-        <f>C9/(1-C9)*(C6+C8)</f>
-        <v/>
-      </c>
-      <c r="D10" s="32">
-        <f>D9/(1-D9)*(D6+D8)</f>
-        <v/>
-      </c>
-      <c r="E10" s="32">
-        <f>E9/(1-E9)*(E6+E8)</f>
-        <v/>
-      </c>
-      <c r="F10" s="32">
-        <f>F9/(1-F9)*(F6+F8)</f>
-        <v/>
-      </c>
-      <c r="G10" s="32">
-        <f>G9/(1-G9)*(G6+G8)</f>
+          <t>Gross profit per unit (conversion spread)</t>
+        </is>
+      </c>
+      <c r="B10" s="27">
+        <f>B13/B6</f>
+        <v/>
+      </c>
+      <c r="C10" s="27">
+        <f>C9/(1-C9)*(C7+C8)</f>
+        <v/>
+      </c>
+      <c r="D10" s="27">
+        <f>D9/(1-D9)*(D7+D8)</f>
+        <v/>
+      </c>
+      <c r="E10" s="27">
+        <f>E9/(1-E9)*(E7+E8)</f>
+        <v/>
+      </c>
+      <c r="F10" s="27">
+        <f>F9/(1-F9)*(F7+F8)</f>
+        <v/>
+      </c>
+      <c r="G10" s="27">
+        <f>G9/(1-G9)*(G7+G8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Materials (metal leg, shocked)</t>
-        </is>
-      </c>
-      <c r="B11" s="19">
-        <f>B5*B7</f>
-        <v/>
-      </c>
-      <c r="C11" s="19">
-        <f>C5*C7</f>
-        <v/>
-      </c>
-      <c r="D11" s="19">
-        <f>D5*D7</f>
-        <v/>
-      </c>
-      <c r="E11" s="19">
-        <f>E5*E7</f>
-        <v/>
-      </c>
-      <c r="F11" s="19">
-        <f>F5*F7</f>
-        <v/>
-      </c>
-      <c r="G11" s="19">
-        <f>G5*G7</f>
+          <t>Materials (metal leg)</t>
+        </is>
+      </c>
+      <c r="B11" s="29">
+        <f>B6*B7</f>
+        <v/>
+      </c>
+      <c r="C11" s="29">
+        <f>C6*C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="29">
+        <f>D6*D7</f>
+        <v/>
+      </c>
+      <c r="E11" s="29">
+        <f>E6*E7</f>
+        <v/>
+      </c>
+      <c r="F11" s="29">
+        <f>F6*F7</f>
+        <v/>
+      </c>
+      <c r="G11" s="29">
+        <f>G6*G7</f>
         <v/>
       </c>
     </row>
@@ -5072,346 +4753,614 @@
           <t>Conversion cost</t>
         </is>
       </c>
-      <c r="B12" s="19">
-        <f>B5*B8</f>
-        <v/>
-      </c>
-      <c r="C12" s="19">
-        <f>C5*C8</f>
-        <v/>
-      </c>
-      <c r="D12" s="19">
-        <f>D5*D8</f>
-        <v/>
-      </c>
-      <c r="E12" s="19">
-        <f>E5*E8</f>
-        <v/>
-      </c>
-      <c r="F12" s="19">
-        <f>F5*F8</f>
-        <v/>
-      </c>
-      <c r="G12" s="19">
-        <f>G5*G8</f>
+      <c r="B12" s="29">
+        <f>B6*B8</f>
+        <v/>
+      </c>
+      <c r="C12" s="29">
+        <f>C6*C8</f>
+        <v/>
+      </c>
+      <c r="D12" s="29">
+        <f>D6*D8</f>
+        <v/>
+      </c>
+      <c r="E12" s="29">
+        <f>E6*E8</f>
+        <v/>
+      </c>
+      <c r="F12" s="29">
+        <f>F6*F8</f>
+        <v/>
+      </c>
+      <c r="G12" s="29">
+        <f>G6*G8</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Cost of revenue</t>
-        </is>
-      </c>
-      <c r="B13" s="19">
-        <f>B11+B12</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>C11+C12</f>
-        <v/>
-      </c>
-      <c r="D13" s="19">
-        <f>D11+D12</f>
-        <v/>
-      </c>
-      <c r="E13" s="19">
-        <f>E11+E12</f>
-        <v/>
-      </c>
-      <c r="F13" s="19">
-        <f>F11+F12</f>
-        <v/>
-      </c>
-      <c r="G13" s="19">
-        <f>G11+G12</f>
+          <t>Gross profit = volume x spread</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>1697.442537000001</v>
+      </c>
+      <c r="C13" s="29">
+        <f>C6*C10</f>
+        <v/>
+      </c>
+      <c r="D13" s="29">
+        <f>D6*D10</f>
+        <v/>
+      </c>
+      <c r="E13" s="29">
+        <f>E6*E10</f>
+        <v/>
+      </c>
+      <c r="F13" s="29">
+        <f>F6*F10</f>
+        <v/>
+      </c>
+      <c r="G13" s="29">
+        <f>G6*G10</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Gross profit = volume x spread</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="n">
-        <v>1733.329855</v>
-      </c>
-      <c r="C14" s="19">
-        <f>C5*C10</f>
-        <v/>
-      </c>
-      <c r="D14" s="19">
-        <f>D5*D10</f>
-        <v/>
-      </c>
-      <c r="E14" s="19">
-        <f>E5*E10</f>
-        <v/>
-      </c>
-      <c r="F14" s="19">
-        <f>F5*F10</f>
-        <v/>
-      </c>
-      <c r="G14" s="19">
-        <f>G5*G10</f>
+          <t>Cables revenue = materials + conversion + gross profit</t>
+        </is>
+      </c>
+      <c r="B14" s="29">
+        <f>B11+B12+B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="29">
+        <f>C11+C12+C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="29">
+        <f>D11+D12+D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="29">
+        <f>E11+E12+E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="29">
+        <f>F11+F12+F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="29">
+        <f>G11+G12+G13</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Revenue = materials + conversion + spread</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="n">
-        <v>10673.604262</v>
-      </c>
-      <c r="C15" s="19">
-        <f>C13+C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="19">
-        <f>D13+D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="19">
-        <f>E13+E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="19">
-        <f>F13+F14</f>
-        <v/>
-      </c>
-      <c r="G15" s="19">
-        <f>G13+G14</f>
+          <t>Cables gross margin (OUTPUT)</t>
+        </is>
+      </c>
+      <c r="B15" s="28">
+        <f>B13/B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="28">
+        <f>C13/C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="28">
+        <f>D13/D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="28">
+        <f>E13/E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="28">
+        <f>F13/F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="28">
+        <f>G13/G14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Gross margin — OUTPUT (dilutes when metal rises)</t>
-        </is>
-      </c>
-      <c r="B16" s="33">
-        <f>B14/B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="33">
-        <f>C14/C15</f>
-        <v/>
-      </c>
-      <c r="D16" s="33">
-        <f>D14/D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="33">
-        <f>E14/E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="33">
-        <f>F14/F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="33">
-        <f>G14/G15</f>
-        <v/>
-      </c>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>HV turnkey projects — own growth, disclosed margin</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="C17" s="19">
-        <f>Assumptions!C$28*C15</f>
-        <v/>
-      </c>
-      <c r="D17" s="19">
-        <f>Assumptions!D$28*D15</f>
-        <v/>
-      </c>
-      <c r="E17" s="19">
-        <f>Assumptions!E$28*E15</f>
-        <v/>
-      </c>
-      <c r="F17" s="19">
-        <f>Assumptions!F$28*F15</f>
-        <v/>
-      </c>
-      <c r="G17" s="19">
-        <f>Assumptions!G$28*G15</f>
+          <t>HV revenue (own growth path)</t>
+        </is>
+      </c>
+      <c r="B17" s="29">
+        <f>Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="C17" s="29">
+        <f>B17*(1+Assumptions!C$29)</f>
+        <v/>
+      </c>
+      <c r="D17" s="29">
+        <f>C17*(1+Assumptions!D$29)</f>
+        <v/>
+      </c>
+      <c r="E17" s="29">
+        <f>D17*(1+Assumptions!E$29)</f>
+        <v/>
+      </c>
+      <c r="F17" s="29">
+        <f>E17*(1+Assumptions!F$29)</f>
+        <v/>
+      </c>
+      <c r="G17" s="29">
+        <f>F17*(1+Assumptions!G$29)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Depreciation &amp; amortisation</t>
-        </is>
-      </c>
-      <c r="C18" s="19">
-        <f>Assumptions!$C$29*C15</f>
-        <v/>
-      </c>
-      <c r="D18" s="19">
-        <f>Assumptions!$C$29*D15</f>
-        <v/>
-      </c>
-      <c r="E18" s="19">
-        <f>Assumptions!$C$29*E15</f>
-        <v/>
-      </c>
-      <c r="F18" s="19">
-        <f>Assumptions!$C$29*F15</f>
-        <v/>
-      </c>
-      <c r="G18" s="19">
-        <f>Assumptions!$C$29*G15</f>
+          <t>HV segment margin</t>
+        </is>
+      </c>
+      <c r="B18" s="28">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="C18" s="28">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="D18" s="28">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="E18" s="28">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="F18" s="28">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="G18" s="28">
+        <f>Assumptions!$C$30</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C19" s="19">
-        <f>C14-C17</f>
-        <v/>
-      </c>
-      <c r="D19" s="19">
-        <f>D14-D17</f>
-        <v/>
-      </c>
-      <c r="E19" s="19">
-        <f>E14-E17</f>
-        <v/>
-      </c>
-      <c r="F19" s="19">
-        <f>F14-F17</f>
-        <v/>
-      </c>
-      <c r="G19" s="19">
-        <f>G14-G17</f>
+          <t>HV gross profit = revenue x margin</t>
+        </is>
+      </c>
+      <c r="B19" s="29">
+        <f>B17*B18</f>
+        <v/>
+      </c>
+      <c r="C19" s="29">
+        <f>C17*C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>D17*D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>E17*E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>F17*F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="29">
+        <f>G17*G18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="C20" s="19">
-        <f>C19+C18</f>
-        <v/>
-      </c>
-      <c r="D20" s="19">
-        <f>D19+D18</f>
-        <v/>
-      </c>
-      <c r="E20" s="19">
-        <f>E19+E18</f>
-        <v/>
-      </c>
-      <c r="F20" s="19">
-        <f>F19+F18</f>
-        <v/>
-      </c>
-      <c r="G20" s="19">
-        <f>G19+G18</f>
-        <v/>
-      </c>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Other (telephone cables &amp; services) — own growth, disclosed margin</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C21" s="33">
-        <f>C20/C15</f>
-        <v/>
-      </c>
-      <c r="D21" s="33">
-        <f>D20/D15</f>
-        <v/>
-      </c>
-      <c r="E21" s="33">
-        <f>E20/E15</f>
-        <v/>
-      </c>
-      <c r="F21" s="33">
-        <f>F20/F15</f>
-        <v/>
-      </c>
-      <c r="G21" s="33">
-        <f>G20/G15</f>
+          <t>Other revenue (own growth path)</t>
+        </is>
+      </c>
+      <c r="B21" s="29">
+        <f>Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="C21" s="29">
+        <f>B21*(1+Assumptions!C$31)</f>
+        <v/>
+      </c>
+      <c r="D21" s="29">
+        <f>C21*(1+Assumptions!D$31)</f>
+        <v/>
+      </c>
+      <c r="E21" s="29">
+        <f>D21*(1+Assumptions!E$31)</f>
+        <v/>
+      </c>
+      <c r="F21" s="29">
+        <f>E21*(1+Assumptions!F$31)</f>
+        <v/>
+      </c>
+      <c r="G21" s="29">
+        <f>F21*(1+Assumptions!G$31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Other segment margin</t>
+        </is>
+      </c>
+      <c r="B22" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="C22" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="E22" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="F22" s="28">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="G22" s="28">
+        <f>Assumptions!$C$32</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>FY2025 disclosed segment revenue (Note 40)</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Other gross profit = revenue x margin</t>
+        </is>
+      </c>
+      <c r="B23" s="29">
+        <f>B21*B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="29">
+        <f>C21*C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>D21*D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="29">
+        <f>E21*E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f>F21*F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f>G21*G22</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Cables and wires</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="n">
-        <v>10414.170668</v>
-      </c>
-      <c r="C24" s="9">
-        <f>B24/B15</f>
-        <v/>
-      </c>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Group — the sum of the three legs</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>High-voltage cables (turnkey projects)</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="n">
-        <v>230.839181</v>
-      </c>
-      <c r="C25" s="9">
-        <f>B25/B15</f>
+          <t>Revenue (group)</t>
+        </is>
+      </c>
+      <c r="B25" s="29">
+        <f>B14+B17+B21</f>
+        <v/>
+      </c>
+      <c r="C25" s="29">
+        <f>C14+C17+C21</f>
+        <v/>
+      </c>
+      <c r="D25" s="29">
+        <f>D14+D17+D21</f>
+        <v/>
+      </c>
+      <c r="E25" s="29">
+        <f>E14+E17+E21</f>
+        <v/>
+      </c>
+      <c r="F25" s="29">
+        <f>F14+F17+F21</f>
+        <v/>
+      </c>
+      <c r="G25" s="29">
+        <f>G14+G17+G21</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Other (telephone cables &amp; services)</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="n">
-        <v>28.594413</v>
-      </c>
-      <c r="C26" s="9">
-        <f>B26/B15</f>
+          <t>Gross profit (group)</t>
+        </is>
+      </c>
+      <c r="B26" s="29">
+        <f>B13+B19+B23</f>
+        <v/>
+      </c>
+      <c r="C26" s="29">
+        <f>C13+C19+C23</f>
+        <v/>
+      </c>
+      <c r="D26" s="29">
+        <f>D13+D19+D23</f>
+        <v/>
+      </c>
+      <c r="E26" s="29">
+        <f>E13+E19+E23</f>
+        <v/>
+      </c>
+      <c r="F26" s="29">
+        <f>F13+F19+F23</f>
+        <v/>
+      </c>
+      <c r="G26" s="29">
+        <f>G13+G19+G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Cost of revenue (group)</t>
+        </is>
+      </c>
+      <c r="B27" s="29">
+        <f>B25-B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="29">
+        <f>C25-C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="29">
+        <f>D25-D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="29">
+        <f>E25-E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="29">
+        <f>F25-F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="29">
+        <f>G25-G26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Gross margin (OUTPUT = group gross profit / group revenue)</t>
+        </is>
+      </c>
+      <c r="B28" s="28">
+        <f>B26/B25</f>
+        <v/>
+      </c>
+      <c r="C28" s="28">
+        <f>C26/C25</f>
+        <v/>
+      </c>
+      <c r="D28" s="28">
+        <f>D26/D25</f>
+        <v/>
+      </c>
+      <c r="E28" s="28">
+        <f>E26/E25</f>
+        <v/>
+      </c>
+      <c r="F28" s="28">
+        <f>F26/F25</f>
+        <v/>
+      </c>
+      <c r="G28" s="28">
+        <f>G26/G25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C29" s="29">
+        <f>Assumptions!C$34*C25</f>
+        <v/>
+      </c>
+      <c r="D29" s="29">
+        <f>Assumptions!D$34*D25</f>
+        <v/>
+      </c>
+      <c r="E29" s="29">
+        <f>Assumptions!E$34*E25</f>
+        <v/>
+      </c>
+      <c r="F29" s="29">
+        <f>Assumptions!F$34*F25</f>
+        <v/>
+      </c>
+      <c r="G29" s="29">
+        <f>Assumptions!G$34*G25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; amortisation</t>
+        </is>
+      </c>
+      <c r="C30" s="29">
+        <f>Assumptions!$C$35*C25</f>
+        <v/>
+      </c>
+      <c r="D30" s="29">
+        <f>Assumptions!$C$35*D25</f>
+        <v/>
+      </c>
+      <c r="E30" s="29">
+        <f>Assumptions!$C$35*E25</f>
+        <v/>
+      </c>
+      <c r="F30" s="29">
+        <f>Assumptions!$C$35*F25</f>
+        <v/>
+      </c>
+      <c r="G30" s="29">
+        <f>Assumptions!$C$35*G25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C31" s="29">
+        <f>C26-C29</f>
+        <v/>
+      </c>
+      <c r="D31" s="29">
+        <f>D26-D29</f>
+        <v/>
+      </c>
+      <c r="E31" s="29">
+        <f>E26-E29</f>
+        <v/>
+      </c>
+      <c r="F31" s="29">
+        <f>F26-F29</f>
+        <v/>
+      </c>
+      <c r="G31" s="29">
+        <f>G26-G29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C32" s="29">
+        <f>C31+C30</f>
+        <v/>
+      </c>
+      <c r="D32" s="29">
+        <f>D31+D30</f>
+        <v/>
+      </c>
+      <c r="E32" s="29">
+        <f>E31+E30</f>
+        <v/>
+      </c>
+      <c r="F32" s="29">
+        <f>F31+F30</f>
+        <v/>
+      </c>
+      <c r="G32" s="29">
+        <f>G31+G30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C33" s="28">
+        <f>C32/C25</f>
+        <v/>
+      </c>
+      <c r="D33" s="28">
+        <f>D32/D25</f>
+        <v/>
+      </c>
+      <c r="E33" s="28">
+        <f>E32/E25</f>
+        <v/>
+      </c>
+      <c r="F33" s="28">
+        <f>F32/F25</f>
+        <v/>
+      </c>
+      <c r="G33" s="28">
+        <f>G32/G25</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5419,7 +5368,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5473,7 +5422,7 @@
         </is>
       </c>
       <c r="C5" s="14">
-        <f>Segments!D20</f>
+        <f>Segments!D32</f>
         <v/>
       </c>
     </row>
@@ -5483,8 +5432,8 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="34">
-        <f>Assumptions!$C$38</f>
+      <c r="C6" s="30">
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
@@ -5500,28 +5449,28 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Relative lens — implied value (base)</t>
         </is>
       </c>
-      <c r="C8" s="21">
-        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+      <c r="C8" s="32">
+        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Bear (8.0x) / Bull (12.0x)</t>
+          <t>Bear (7.5x) / Bull (11.0x)</t>
         </is>
       </c>
       <c r="C9" s="15">
-        <f>((8*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>((12*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$55+Assumptions!$C$56-Assumptions!$C$57)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$47</f>
+        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5544,8 +5493,8 @@
           <t>Mid-cycle EBITDA margin (FY2028E)</t>
         </is>
       </c>
-      <c r="C12" s="18">
-        <f>Segments!E21</f>
+      <c r="C12" s="33">
+        <f>Segments!E33</f>
         <v/>
       </c>
     </row>
@@ -5556,7 +5505,7 @@
         </is>
       </c>
       <c r="C13" s="14">
-        <f>Segments!C15</f>
+        <f>Segments!C25</f>
         <v/>
       </c>
     </row>
@@ -5578,18 +5527,18 @@
         </is>
       </c>
       <c r="C15" s="15">
-        <f>((C12*C13-Assumptions!$C$29*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$36)/Assumptions!$C$6</f>
+        <f>((C12*C13-Assumptions!$C$35*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>Normalised lens — implied value (base)</t>
         </is>
       </c>
-      <c r="C16" s="21">
-        <f>(Assumptions!$C$39*C15)*DCF!$C$50-Assumptions!$C$47</f>
+      <c r="C16" s="32">
+        <f>(Assumptions!$C$44*C15)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5600,11 +5549,11 @@
         </is>
       </c>
       <c r="C17" s="15">
-        <f>(10*C15)*DCF!$C$50-Assumptions!$C$47</f>
+        <f>(10*C15)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>(16*C15)*DCF!$C$50-Assumptions!$C$47</f>
+        <f>(16*C15)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5628,7 +5577,7 @@
         </is>
       </c>
       <c r="C20" s="15">
-        <f>Assumptions!$C$54/Assumptions!$C$6</f>
+        <f>Assumptions!$C$61/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5638,19 +5587,19 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C21" s="35">
-        <f>(Assumptions!$C$40-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)</f>
+      <c r="C21" s="34">
+        <f>(Assumptions!$C$45-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>Book lens — implied value (base)</t>
         </is>
       </c>
-      <c r="C22" s="21">
-        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$47</f>
+      <c r="C22" s="32">
+        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5661,16 +5610,18 @@
         </is>
       </c>
       <c r="C23" s="15">
-        <f>(((Assumptions!$C$40)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$47</f>
+        <f>(((Assumptions!$C$45)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="D23" s="15">
-        <f>(((Assumptions!$C$40)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$47</f>
+        <f>(((Assumptions!$C$45)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5678,7 +5629,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5734,7 +5685,7 @@
           <t>Normalised risk-free rate rf*</t>
         </is>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="28">
         <f>Assumptions!$C$9-Assumptions!$C$10</f>
         <v/>
       </c>
@@ -5745,7 +5696,7 @@
           <t>Cost of equity Ke</t>
         </is>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="28">
         <f>C5+Assumptions!$C$12*Assumptions!$C$11</f>
         <v/>
       </c>
@@ -5756,7 +5707,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="28">
         <f>Assumptions!$C$13*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -5767,7 +5718,7 @@
           <t>Market capitalisation</t>
         </is>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="29">
         <f>Assumptions!$C$5*Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5778,18 +5729,18 @@
           <t>Net-debt weight</t>
         </is>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="28">
         <f>Assumptions!$C$7/(Assumptions!$C$7+C8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>WACC — explicit window</t>
         </is>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="35">
         <f>(1-C9)*C6+C9*C7</f>
         <v/>
       </c>
@@ -5800,7 +5751,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="28">
         <f>Assumptions!$C$16+Assumptions!$C$18*Assumptions!$C$17</f>
         <v/>
       </c>
@@ -5811,18 +5762,18 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="28">
         <f>Assumptions!$C$19*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>WACC — terminal</t>
         </is>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="35">
         <f>(1-Assumptions!$C$20)*C11+Assumptions!$C$20*C12</f>
         <v/>
       </c>
@@ -5880,24 +5831,24 @@
           <t>Glide fraction (from Kd path)</t>
         </is>
       </c>
-      <c r="C17" s="37">
-        <f>(Assumptions!C$32-Assumptions!C$32)/(Assumptions!C$32-Assumptions!G$32)</f>
-        <v/>
-      </c>
-      <c r="D17" s="37">
-        <f>(Assumptions!C$32-Assumptions!D$32)/(Assumptions!C$32-Assumptions!G$32)</f>
-        <v/>
-      </c>
-      <c r="E17" s="37">
-        <f>(Assumptions!C$32-Assumptions!E$32)/(Assumptions!C$32-Assumptions!G$32)</f>
-        <v/>
-      </c>
-      <c r="F17" s="37">
-        <f>(Assumptions!C$32-Assumptions!F$32)/(Assumptions!C$32-Assumptions!G$32)</f>
-        <v/>
-      </c>
-      <c r="G17" s="37">
-        <f>(Assumptions!C$32-Assumptions!G$32)/(Assumptions!C$32-Assumptions!G$32)</f>
+      <c r="C17" s="36">
+        <f>(Assumptions!C$38-Assumptions!C$38)/(Assumptions!C$38-Assumptions!G$38)</f>
+        <v/>
+      </c>
+      <c r="D17" s="36">
+        <f>(Assumptions!C$38-Assumptions!D$38)/(Assumptions!C$38-Assumptions!G$38)</f>
+        <v/>
+      </c>
+      <c r="E17" s="36">
+        <f>(Assumptions!C$38-Assumptions!E$38)/(Assumptions!C$38-Assumptions!G$38)</f>
+        <v/>
+      </c>
+      <c r="F17" s="36">
+        <f>(Assumptions!C$38-Assumptions!F$38)/(Assumptions!C$38-Assumptions!G$38)</f>
+        <v/>
+      </c>
+      <c r="G17" s="36">
+        <f>(Assumptions!C$38-Assumptions!G$38)/(Assumptions!C$38-Assumptions!G$38)</f>
         <v/>
       </c>
     </row>
@@ -5907,23 +5858,23 @@
           <t>Forward WACC</t>
         </is>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="28">
         <f>C10-(C10-C13)*C17</f>
         <v/>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="28">
         <f>C10-(C10-C13)*D17</f>
         <v/>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="28">
         <f>C10-(C10-C13)*E17</f>
         <v/>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="28">
         <f>C10-(C10-C13)*F17</f>
         <v/>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="28">
         <f>C10-(C10-C13)*G17</f>
         <v/>
       </c>
@@ -5934,23 +5885,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="36">
         <f>1/(1+C18)</f>
         <v/>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="36">
         <f>C19/(1+D18)</f>
         <v/>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="36">
         <f>D19/(1+E18)</f>
         <v/>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="36">
         <f>E19/(1+F18)</f>
         <v/>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="36">
         <f>F19/(1+G18)</f>
         <v/>
       </c>
@@ -5962,23 +5913,23 @@
         </is>
       </c>
       <c r="C20" s="14">
-        <f>Segments!C19</f>
+        <f>Segments!C31</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f>Segments!D19</f>
+        <f>Segments!D31</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>Segments!E19</f>
+        <f>Segments!E31</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>Segments!F19</f>
+        <f>Segments!F31</f>
         <v/>
       </c>
       <c r="G20" s="14">
-        <f>Segments!G19</f>
+        <f>Segments!G31</f>
         <v/>
       </c>
     </row>
@@ -5988,23 +5939,23 @@
           <t>NOPAT = EBIT x (1 - tax)</t>
         </is>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="29">
         <f>C20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="29">
         <f>D20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="29">
         <f>E20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="29">
         <f>F20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="29">
         <f>G20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -6016,23 +5967,23 @@
         </is>
       </c>
       <c r="C22" s="14">
-        <f>Segments!C18</f>
+        <f>Segments!C30</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>Segments!D18</f>
+        <f>Segments!D30</f>
         <v/>
       </c>
       <c r="E22" s="14">
-        <f>Segments!E18</f>
+        <f>Segments!E30</f>
         <v/>
       </c>
       <c r="F22" s="14">
-        <f>Segments!F18</f>
+        <f>Segments!F30</f>
         <v/>
       </c>
       <c r="G22" s="14">
-        <f>Segments!G18</f>
+        <f>Segments!G30</f>
         <v/>
       </c>
     </row>
@@ -6043,23 +5994,23 @@
         </is>
       </c>
       <c r="C23" s="14">
-        <f>Segments!C15</f>
+        <f>Segments!C25</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>Segments!D15</f>
+        <f>Segments!D25</f>
         <v/>
       </c>
       <c r="E23" s="14">
-        <f>Segments!E15</f>
+        <f>Segments!E25</f>
         <v/>
       </c>
       <c r="F23" s="14">
-        <f>Segments!F15</f>
+        <f>Segments!F25</f>
         <v/>
       </c>
       <c r="G23" s="14">
-        <f>Segments!G15</f>
+        <f>Segments!G25</f>
         <v/>
       </c>
     </row>
@@ -6069,24 +6020,24 @@
           <t>- Capital expenditure</t>
         </is>
       </c>
-      <c r="C24" s="19">
-        <f>Assumptions!C$30*C23</f>
-        <v/>
-      </c>
-      <c r="D24" s="19">
-        <f>Assumptions!D$30*D23</f>
-        <v/>
-      </c>
-      <c r="E24" s="19">
-        <f>Assumptions!E$30*E23</f>
-        <v/>
-      </c>
-      <c r="F24" s="19">
-        <f>Assumptions!F$30*F23</f>
-        <v/>
-      </c>
-      <c r="G24" s="19">
-        <f>Assumptions!G$30*G23</f>
+      <c r="C24" s="29">
+        <f>Assumptions!C$36*C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="29">
+        <f>Assumptions!D$36*D23</f>
+        <v/>
+      </c>
+      <c r="E24" s="29">
+        <f>Assumptions!E$36*E23</f>
+        <v/>
+      </c>
+      <c r="F24" s="29">
+        <f>Assumptions!F$36*F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="29">
+        <f>Assumptions!G$36*G23</f>
         <v/>
       </c>
     </row>
@@ -6096,24 +6047,24 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="C25" s="19">
-        <f>Assumptions!$C$31*C23</f>
-        <v/>
-      </c>
-      <c r="D25" s="19">
-        <f>Assumptions!$C$31*D23</f>
-        <v/>
-      </c>
-      <c r="E25" s="19">
-        <f>Assumptions!$C$31*E23</f>
-        <v/>
-      </c>
-      <c r="F25" s="19">
-        <f>Assumptions!$C$31*F23</f>
-        <v/>
-      </c>
-      <c r="G25" s="19">
-        <f>Assumptions!$C$31*G23</f>
+      <c r="C25" s="29">
+        <f>Assumptions!$C$37*C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="29">
+        <f>Assumptions!$C$37*D23</f>
+        <v/>
+      </c>
+      <c r="E25" s="29">
+        <f>Assumptions!$C$37*E23</f>
+        <v/>
+      </c>
+      <c r="F25" s="29">
+        <f>Assumptions!$C$37*F23</f>
+        <v/>
+      </c>
+      <c r="G25" s="29">
+        <f>Assumptions!$C$37*G23</f>
         <v/>
       </c>
     </row>
@@ -6123,50 +6074,50 @@
           <t>- Change in working capital</t>
         </is>
       </c>
-      <c r="C26" s="19">
-        <f>C25-Assumptions!$C$51</f>
-        <v/>
-      </c>
-      <c r="D26" s="19">
+      <c r="C26" s="29">
+        <f>C25-Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="D26" s="29">
         <f>D25-C25</f>
         <v/>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="29">
         <f>E25-D25</f>
         <v/>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="29">
         <f>F25-E25</f>
         <v/>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="29">
         <f>G25-F25</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Free cash flow to firm</t>
         </is>
       </c>
-      <c r="C27" s="38">
+      <c r="C27" s="37">
         <f>C21+C22-C24-C26</f>
         <v/>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="37">
         <f>D21+D22-D24-D26</f>
         <v/>
       </c>
-      <c r="E27" s="38">
+      <c r="E27" s="37">
         <f>E21+E22-E24-E26</f>
         <v/>
       </c>
-      <c r="F27" s="38">
+      <c r="F27" s="37">
         <f>F21+F22-F24-F26</f>
         <v/>
       </c>
-      <c r="G27" s="38">
+      <c r="G27" s="37">
         <f>G21+G22-G24-G26</f>
         <v/>
       </c>
@@ -6177,23 +6128,23 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="29">
         <f>C27*C19</f>
         <v/>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="29">
         <f>D27*D19</f>
         <v/>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="29">
         <f>E27*E19</f>
         <v/>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="29">
         <f>F27*F19</f>
         <v/>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="29">
         <f>G27*G19</f>
         <v/>
       </c>
@@ -6218,23 +6169,23 @@
           <t>PP&amp;E roll-forward</t>
         </is>
       </c>
-      <c r="C31" s="19">
-        <f>Assumptions!$C$52+C24-C22</f>
-        <v/>
-      </c>
-      <c r="D31" s="19">
+      <c r="C31" s="29">
+        <f>Assumptions!$C$59+C24-C22</f>
+        <v/>
+      </c>
+      <c r="D31" s="29">
         <f>C31+D24-D22</f>
         <v/>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="29">
         <f>D31+E24-E22</f>
         <v/>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="29">
         <f>E31+F24-F22</f>
         <v/>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="29">
         <f>F31+G24-G22</f>
         <v/>
       </c>
@@ -6245,23 +6196,23 @@
           <t>Invested capital = NWC + PP&amp;E</t>
         </is>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="29">
         <f>C25+C31</f>
         <v/>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="29">
         <f>D25+D31</f>
         <v/>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="29">
         <f>E25+E31</f>
         <v/>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="29">
         <f>F25+F31</f>
         <v/>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="29">
         <f>G25+G31</f>
         <v/>
       </c>
@@ -6272,23 +6223,23 @@
           <t>ROIC = NOPAT / invested capital</t>
         </is>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="28">
         <f>C21/C32</f>
         <v/>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="28">
         <f>D21/D32</f>
         <v/>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="28">
         <f>E21/E32</f>
         <v/>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="28">
         <f>F21/F32</f>
         <v/>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="28">
         <f>G21/G32</f>
         <v/>
       </c>
@@ -6299,7 +6250,7 @@
           <t>PV of explicit FCFF (5 years)</t>
         </is>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="29">
         <f>SUM(C28:G28)</f>
         <v/>
       </c>
@@ -6310,7 +6261,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="28">
         <f>G21*(1+Assumptions!$C$21)/G32</f>
         <v/>
       </c>
@@ -6321,7 +6272,7 @@
           <t>Terminal reinvestment rate = g / ROIC</t>
         </is>
       </c>
-      <c r="C37" s="33">
+      <c r="C37" s="28">
         <f>Assumptions!$C$21/C36</f>
         <v/>
       </c>
@@ -6332,7 +6283,7 @@
           <t>Terminal NOPAT (next year)</t>
         </is>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="29">
         <f>G21*(1+Assumptions!$C$21)</f>
         <v/>
       </c>
@@ -6343,7 +6294,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="C39" s="19">
+      <c r="C39" s="29">
         <f>C38*(1-C37)/(C13-Assumptions!$C$21)</f>
         <v/>
       </c>
@@ -6354,29 +6305,29 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C40" s="19">
+      <c r="C40" s="29">
         <f>C39*G19</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C41" s="38">
+      <c r="C41" s="37">
         <f>C35+C40</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="31" t="inlineStr">
         <is>
           <t>Terminal value as % of EV</t>
         </is>
       </c>
-      <c r="C42" s="39">
+      <c r="C42" s="38">
         <f>C40/C41</f>
         <v/>
       </c>
@@ -6401,7 +6352,7 @@
           <t>Less: net financial debt</t>
         </is>
       </c>
-      <c r="C45" s="19">
+      <c r="C45" s="29">
         <f>-Assumptions!$C$7</f>
         <v/>
       </c>
@@ -6412,8 +6363,8 @@
           <t>Add: associates + non-operating assets</t>
         </is>
       </c>
-      <c r="C46" s="19">
-        <f>Assumptions!$C$55+Assumptions!$C$56</f>
+      <c r="C46" s="29">
+        <f>Assumptions!$C$62+Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -6423,18 +6374,18 @@
           <t>Less: non-controlling interests</t>
         </is>
       </c>
-      <c r="C47" s="19">
-        <f>-Assumptions!$C$57</f>
+      <c r="C47" s="29">
+        <f>-Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="31" t="inlineStr">
         <is>
           <t>Equity attributable (31-Dec-2025)</t>
         </is>
       </c>
-      <c r="C48" s="38">
+      <c r="C48" s="37">
         <f>C41+C45+C46+C47</f>
         <v/>
       </c>
@@ -6456,19 +6407,19 @@
           <t>Anchor accretion factor</t>
         </is>
       </c>
-      <c r="C50" s="37">
-        <f>(1+C6)^(Assumptions!$C$46/365)</f>
+      <c r="C50" s="36">
+        <f>(1+C6)^(Assumptions!$C$51/365)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>Value per share at anchor (18-Aug-2026)</t>
         </is>
       </c>
-      <c r="C51" s="21">
-        <f>C49*C50-Assumptions!$C$47</f>
+      <c r="C51" s="32">
+        <f>C49*C50-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -6504,7 +6455,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>78.52014039378953</v>
+        <v>80.84906676286525</v>
       </c>
     </row>
     <row r="56">
@@ -6525,11 +6476,13 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>188.2848029277439</v>
+        <v>197.7603327814774</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6537,7 +6490,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6631,33 +6584,33 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="19" t="n">
         <v>7825.378127</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="19" t="n">
         <v>9007.360866999999</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="19" t="n">
         <v>10673.604262</v>
       </c>
       <c r="F5" s="14">
-        <f>Segments!C15</f>
+        <f>Segments!C25</f>
         <v/>
       </c>
       <c r="G5" s="14">
-        <f>Segments!D15</f>
+        <f>Segments!D25</f>
         <v/>
       </c>
       <c r="H5" s="14">
-        <f>Segments!E15</f>
+        <f>Segments!E25</f>
         <v/>
       </c>
       <c r="I5" s="14">
-        <f>Segments!F15</f>
+        <f>Segments!F25</f>
         <v/>
       </c>
       <c r="J5" s="14">
-        <f>Segments!G15</f>
+        <f>Segments!G25</f>
         <v/>
       </c>
     </row>
@@ -6667,33 +6620,33 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="19" t="n">
         <v>972.763438</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="19" t="n">
         <v>1286.522351</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="19" t="n">
         <v>1733.329855</v>
       </c>
       <c r="F6" s="14">
-        <f>Segments!C14</f>
+        <f>Segments!C26</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>Segments!D14</f>
+        <f>Segments!D26</f>
         <v/>
       </c>
       <c r="H6" s="14">
-        <f>Segments!E14</f>
+        <f>Segments!E26</f>
         <v/>
       </c>
       <c r="I6" s="14">
-        <f>Segments!F14</f>
+        <f>Segments!F26</f>
         <v/>
       </c>
       <c r="J6" s="14">
-        <f>Segments!G14</f>
+        <f>Segments!G26</f>
         <v/>
       </c>
     </row>
@@ -6703,35 +6656,35 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="28">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="28">
         <f>D6/D5</f>
         <v/>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="28">
         <f>E6/E5</f>
         <v/>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="28">
         <f>F6/F5</f>
         <v/>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="28">
         <f>G6/G5</f>
         <v/>
       </c>
-      <c r="H7" s="33">
+      <c r="H7" s="28">
         <f>H6/H5</f>
         <v/>
       </c>
-      <c r="I7" s="33">
+      <c r="I7" s="28">
         <f>I6/I5</f>
         <v/>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="28">
         <f>J6/J5</f>
         <v/>
       </c>
@@ -6742,36 +6695,36 @@
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="29">
         <f>C6-C11</f>
         <v/>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="29">
         <f>D6-D11</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="29">
         <f>E6-E11</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>Segments!C17</f>
+        <f>Segments!C29</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>Segments!D17</f>
+        <f>Segments!D29</f>
         <v/>
       </c>
       <c r="H8" s="14">
-        <f>Segments!E17</f>
+        <f>Segments!E29</f>
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>Segments!F17</f>
+        <f>Segments!F29</f>
         <v/>
       </c>
       <c r="J8" s="14">
-        <f>Segments!G17</f>
+        <f>Segments!G29</f>
         <v/>
       </c>
     </row>
@@ -6781,36 +6734,36 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="29">
         <f>C11+C10</f>
         <v/>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="29">
         <f>D11+D10</f>
         <v/>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="29">
         <f>E11+E10</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>Segments!C20</f>
+        <f>Segments!C32</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>Segments!D20</f>
+        <f>Segments!D32</f>
         <v/>
       </c>
       <c r="H9" s="14">
-        <f>Segments!E20</f>
+        <f>Segments!E32</f>
         <v/>
       </c>
       <c r="I9" s="14">
-        <f>Segments!F20</f>
+        <f>Segments!F32</f>
         <v/>
       </c>
       <c r="J9" s="14">
-        <f>Segments!G20</f>
+        <f>Segments!G32</f>
         <v/>
       </c>
     </row>
@@ -6820,33 +6773,33 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="19" t="n">
         <v>66.428122</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="19" t="n">
         <v>68.643861</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="19" t="n">
         <v>85.39563699999999</v>
       </c>
       <c r="F10" s="14">
-        <f>Segments!C18</f>
+        <f>Segments!C30</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Segments!D18</f>
+        <f>Segments!D30</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Segments!E18</f>
+        <f>Segments!E30</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Segments!F18</f>
+        <f>Segments!F30</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Segments!G18</f>
+        <f>Segments!G30</f>
         <v/>
       </c>
     </row>
@@ -6856,33 +6809,33 @@
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="19" t="n">
         <v>647.606782</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="19" t="n">
         <v>968.439154</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="19" t="n">
         <v>1266.636844</v>
       </c>
       <c r="F11" s="14">
-        <f>Segments!C19</f>
+        <f>Segments!C31</f>
         <v/>
       </c>
       <c r="G11" s="14">
-        <f>Segments!D19</f>
+        <f>Segments!D31</f>
         <v/>
       </c>
       <c r="H11" s="14">
-        <f>Segments!E19</f>
+        <f>Segments!E31</f>
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>Segments!F19</f>
+        <f>Segments!F31</f>
         <v/>
       </c>
       <c r="J11" s="14">
-        <f>Segments!G19</f>
+        <f>Segments!G31</f>
         <v/>
       </c>
     </row>
@@ -6892,13 +6845,13 @@
           <t>Net finance cost</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="19" t="n">
         <v>-89.01433400000001</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="19" t="n">
         <v>-87.66669899999999</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="19" t="n">
         <v>-74.15399499999999</v>
       </c>
       <c r="F12" s="14">
@@ -6928,35 +6881,35 @@
           <t>Profit before zakat</t>
         </is>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="29">
         <f>C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="29">
         <f>D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="29">
         <f>E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="29">
         <f>F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="29">
         <f>G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="29">
         <f>H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="29">
         <f>I11+I12</f>
         <v/>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="29">
         <f>J11+J12</f>
         <v/>
       </c>
@@ -6967,32 +6920,32 @@
           <t>Zakat &amp; income tax</t>
         </is>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="19" t="n">
         <v>-39.126206</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="19" t="n">
         <v>-63.891298</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="19" t="n">
         <v>-107.681788</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="29">
         <f>-F13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="29">
         <f>-G13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="29">
         <f>-H13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="29">
         <f>-I13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="29">
         <f>-J13*Assumptions!$C$14</f>
         <v/>
       </c>
@@ -7003,32 +6956,32 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="19" t="n">
         <v>518.492623</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="19" t="n">
         <v>816.881157</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="19" t="n">
         <v>1084.801061</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="29">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="29">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="29">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="29">
         <f>I13+I14</f>
         <v/>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="29">
         <f>J13+J14</f>
         <v/>
       </c>
@@ -7039,7 +6992,7 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="19" t="n">
         <v>1080.396042</v>
       </c>
       <c r="F16" s="14">
@@ -7064,6 +7017,8 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
+++ b/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
@@ -37,8 +37,8 @@
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
-    <numFmt numFmtId="169" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,22 +125,23 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,15 +149,15 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -902,13 +903,13 @@
           <t>Property, plant &amp; equipment</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="21" t="n">
         <v>1206.659875</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="21" t="n">
         <v>1336.038944</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="21" t="n">
         <v>1491.86312</v>
       </c>
       <c r="F5" s="14">
@@ -938,13 +939,13 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="21" t="n">
         <v>1909.11144</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="21" t="n">
         <v>2126.036688</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="21" t="n">
         <v>2411.049305</v>
       </c>
     </row>
@@ -954,13 +955,13 @@
           <t>Trade &amp; other receivables</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="21" t="n">
         <v>1418.920843</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="21" t="n">
         <v>2112.098567</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="21" t="n">
         <v>2712.677113</v>
       </c>
     </row>
@@ -970,13 +971,13 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="21" t="n">
         <v>150.051628</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="21" t="n">
         <v>90.672725</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="21" t="n">
         <v>236.043009</v>
       </c>
     </row>
@@ -986,13 +987,13 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="21" t="n">
         <v>4830.929068</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="21" t="n">
         <v>5811.584098</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="21" t="n">
         <v>7281.581695</v>
       </c>
     </row>
@@ -1002,33 +1003,33 @@
           <t>Gross borrowings incl. leases</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="21" t="n">
         <v>730.611837</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="21" t="n">
         <v>440.445599</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="21" t="n">
         <v>621.216217</v>
       </c>
       <c r="F10" s="14">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
@@ -1038,13 +1039,13 @@
           <t>Trade &amp; other payables</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="21" t="n">
         <v>1486.905974</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="21" t="n">
         <v>2040.707151</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="21" t="n">
         <v>2190.467493</v>
       </c>
     </row>
@@ -1054,13 +1055,13 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="21" t="n">
         <v>1841.126309</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="21" t="n">
         <v>2197.428104</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="21" t="n">
         <v>2933.258925</v>
       </c>
       <c r="F12" s="14">
@@ -1090,13 +1091,13 @@
           <t>Net financial debt</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="21" t="n">
         <v>580.560209</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="21" t="n">
         <v>349.772874</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="21" t="n">
         <v>385.173208</v>
       </c>
       <c r="F13" s="14">
@@ -1126,13 +1127,13 @@
           <t>Equity attributable</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="21" t="n">
         <v>2246.744341</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="21" t="n">
         <v>2624.35365</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="21" t="n">
         <v>3246.136935</v>
       </c>
       <c r="F14" s="14">
@@ -1157,20 +1158,20 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Forecast roll-forward (feeds the income statement &amp; lenses)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="11" t="n"/>
-      <c r="J16" s="11" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="10" t="n"/>
+      <c r="J16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1178,23 +1179,23 @@
           <t>Net debt, start of year</t>
         </is>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <f>Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <f>C24</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <f>D24</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <f>E24</f>
         <v/>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="30">
         <f>F24</f>
         <v/>
       </c>
@@ -1205,24 +1206,24 @@
           <t>Surplus cash</t>
         </is>
       </c>
-      <c r="C18" s="29">
-        <f>Assumptions!$C$60-C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="29">
-        <f>Assumptions!$C$60-D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="29">
-        <f>Assumptions!$C$60-E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="29">
-        <f>Assumptions!$C$60-F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="29">
-        <f>Assumptions!$C$60-G17</f>
+      <c r="C18" s="30">
+        <f>Assumptions!$C$56-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="30">
+        <f>Assumptions!$C$56-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="30">
+        <f>Assumptions!$C$56-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="30">
+        <f>Assumptions!$C$56-F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="30">
+        <f>Assumptions!$C$56-G17</f>
         <v/>
       </c>
     </row>
@@ -1232,24 +1233,24 @@
           <t>Net interest</t>
         </is>
       </c>
-      <c r="C19" s="29">
-        <f>Assumptions!C$38*Assumptions!$C$60-Assumptions!$C$40*MAX(C18,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="29">
-        <f>Assumptions!D$38*Assumptions!$C$60-Assumptions!$C$40*MAX(D18,0)</f>
-        <v/>
-      </c>
-      <c r="E19" s="29">
-        <f>Assumptions!E$38*Assumptions!$C$60-Assumptions!$C$40*MAX(E18,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="29">
-        <f>Assumptions!F$38*Assumptions!$C$60-Assumptions!$C$40*MAX(F18,0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="29">
-        <f>Assumptions!G$38*Assumptions!$C$60-Assumptions!$C$40*MAX(G18,0)</f>
+      <c r="C19" s="30">
+        <f>Assumptions!C$38*Assumptions!$C$56-Assumptions!$C$40*MAX(C18,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="30">
+        <f>Assumptions!D$38*Assumptions!$C$56-Assumptions!$C$40*MAX(D18,0)</f>
+        <v/>
+      </c>
+      <c r="E19" s="30">
+        <f>Assumptions!E$38*Assumptions!$C$56-Assumptions!$C$40*MAX(E18,0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="30">
+        <f>Assumptions!F$38*Assumptions!$C$56-Assumptions!$C$40*MAX(F18,0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="30">
+        <f>Assumptions!G$38*Assumptions!$C$56-Assumptions!$C$40*MAX(G18,0)</f>
         <v/>
       </c>
     </row>
@@ -1286,23 +1287,23 @@
           <t>Profit before zakat</t>
         </is>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <f>C20-C19</f>
         <v/>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <f>D20-D19</f>
         <v/>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <f>E20-E19</f>
         <v/>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <f>F20-F19</f>
         <v/>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <f>G20-G19</f>
         <v/>
       </c>
@@ -1313,23 +1314,23 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
         <v/>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
         <v/>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
         <v/>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
         <v/>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="30">
         <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
         <v/>
       </c>
@@ -1340,23 +1341,23 @@
           <t>Dividend</t>
         </is>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="30">
         <f>Assumptions!$C$39*C22</f>
         <v/>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <f>Assumptions!$C$39*D22</f>
         <v/>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <f>Assumptions!$C$39*E22</f>
         <v/>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <f>Assumptions!$C$39*F22</f>
         <v/>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <f>Assumptions!$C$39*G22</f>
         <v/>
       </c>
@@ -1367,23 +1368,23 @@
           <t>Net debt, end of year</t>
         </is>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <f>C17-(DCF!C27-C19*(1-Assumptions!$C$14))+C23</f>
         <v/>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <f>D17-(DCF!D27-D19*(1-Assumptions!$C$14))+D23</f>
         <v/>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <f>E17-(DCF!E27-E19*(1-Assumptions!$C$14))+E23</f>
         <v/>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <f>F17-(DCF!F27-F19*(1-Assumptions!$C$14))+F23</f>
         <v/>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <f>G17-(DCF!G27-G19*(1-Assumptions!$C$14))+G23</f>
         <v/>
       </c>
@@ -1394,23 +1395,23 @@
           <t>Equity attributable</t>
         </is>
       </c>
-      <c r="C25" s="29">
-        <f>Assumptions!$C$61+C22-C23</f>
-        <v/>
-      </c>
-      <c r="D25" s="29">
+      <c r="C25" s="30">
+        <f>Assumptions!$C$57+C22-C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="30">
         <f>C25+D22-D23</f>
         <v/>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <f>D25+E22-E23</f>
         <v/>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <f>E25+F22-F23</f>
         <v/>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="30">
         <f>F25+G22-G23</f>
         <v/>
       </c>
@@ -1663,23 +1664,23 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>C9*C10</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>D9*D10</f>
         <v/>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>E9*E10</f>
         <v/>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>F9*F10</f>
         <v/>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>G9*G10</f>
         <v/>
       </c>
@@ -1992,10 +1993,10 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="19" t="n">
         <v>87.21321014037129</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="19" t="n">
         <v>76.54888951524968</v>
       </c>
     </row>
@@ -2005,10 +2006,10 @@
           <t>P25</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="19" t="n">
         <v>97.61126202615651</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="19" t="n">
         <v>92.86909864606133</v>
       </c>
     </row>
@@ -2018,10 +2019,10 @@
           <t>P50</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="19" t="n">
         <v>104.7866044705799</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="19" t="n">
         <v>105.0593696127112</v>
       </c>
     </row>
@@ -2031,10 +2032,10 @@
           <t>P75</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="19" t="n">
         <v>112.6160892961509</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="19" t="n">
         <v>118.7094846328782</v>
       </c>
     </row>
@@ -2044,10 +2045,10 @@
           <t>P95</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="19" t="n">
         <v>126.1767140981632</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="19" t="n">
         <v>144.0563430692076</v>
       </c>
     </row>
@@ -2057,10 +2058,10 @@
           <t>Spot</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="19" t="n">
         <v>104.8</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="19" t="n">
         <v>104.8</v>
       </c>
     </row>
@@ -2070,10 +2071,10 @@
           <t>P(above spot)</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="40" t="n">
         <v>0.4997</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="40" t="n">
         <v>0.50542</v>
       </c>
     </row>
@@ -2083,10 +2084,10 @@
           <t>Annualised vol</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="40" t="n">
         <v>0.3614703996629836</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="40" t="n">
         <v>0.3670575648854793</v>
       </c>
     </row>
@@ -2145,7 +2146,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>DCF value per share: terminal WACC (rows) x terminal growth (cols)</t>
         </is>
@@ -2185,19 +2186,19 @@
           <t>WACC_t=7.48%</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="19" t="n">
         <v>141.7056057772044</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="19" t="n">
         <v>163.715865885987</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="19" t="n">
         <v>198.2042805447696</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="19" t="n">
         <v>260.2479130974581</v>
       </c>
-      <c r="F6" s="40" t="inlineStr">
+      <c r="F6" s="41" t="inlineStr">
         <is>
           <t>n.m.</t>
         </is>
@@ -2209,19 +2210,19 @@
           <t>WACC_t=8.48%</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="19" t="n">
         <v>120.4623841952295</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="19" t="n">
         <v>134.7210292900971</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="19" t="n">
         <v>155.2188360125738</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="19" t="n">
         <v>187.3299521235833</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="19" t="n">
         <v>245.0864687133326</v>
       </c>
     </row>
@@ -2231,19 +2232,19 @@
           <t>WACC_t=9.48%</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="19" t="n">
         <v>104.8967296610403</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="19" t="n">
         <v>114.6678051971448</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="19" t="n">
         <v>127.905424577565</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="19" t="n">
         <v>146.9294453787323</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="19" t="n">
         <v>176.7240270270523</v>
       </c>
     </row>
@@ -2253,19 +2254,19 @@
           <t>WACC_t=10.48%</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="19" t="n">
         <v>93.00059958544631</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="19" t="n">
         <v>99.97128853350969</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="19" t="n">
         <v>109.0117190503424</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="19" t="n">
         <v>121.2543672012037</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="19" t="n">
         <v>138.8421999218402</v>
       </c>
     </row>
@@ -2275,24 +2276,24 @@
           <t>WACC_t=11.48%</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="19" t="n">
         <v>83.61297829887353</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="19" t="n">
         <v>88.73699993247544</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="19" t="n">
         <v>95.16215451155131</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="19" t="n">
         <v>103.4905512602372</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="19" t="n">
         <v>114.7635647327278</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Beta sensitivity (DCF value/share)</t>
         </is>
@@ -2304,7 +2305,7 @@
           <t>0.7</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="19" t="n">
         <v>134.1012811749074</v>
       </c>
     </row>
@@ -2314,7 +2315,7 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="19" t="n">
         <v>131.1659864625187</v>
       </c>
     </row>
@@ -2324,7 +2325,7 @@
           <t>1.129</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="19" t="n">
         <v>127.905424577565</v>
       </c>
     </row>
@@ -2334,7 +2335,7 @@
           <t>1.3</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="19" t="n">
         <v>125.5381303609279</v>
       </c>
     </row>
@@ -2344,12 +2345,12 @@
           <t>1.5</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="19" t="n">
         <v>122.8400164516531</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Metal price x sensitivity (DCF value/share)</t>
         </is>
@@ -2361,7 +2362,7 @@
           <t>0.85</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="19" t="n">
         <v>139.3236347299058</v>
       </c>
     </row>
@@ -2371,7 +2372,7 @@
           <t>0.925</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="19" t="n">
         <v>133.6031807444171</v>
       </c>
     </row>
@@ -2381,7 +2382,7 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B22" s="19" t="n">
         <v>127.905424577565</v>
       </c>
     </row>
@@ -2391,7 +2392,7 @@
           <t>1.075</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="19" t="n">
         <v>122.2278357157988</v>
       </c>
     </row>
@@ -2401,12 +2402,12 @@
           <t>1.15</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n">
+      <c r="B24" s="19" t="n">
         <v>116.5683245327664</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Sustained gross margin sensitivity (DCF value/share)</t>
         </is>
@@ -2418,7 +2419,7 @@
           <t>0.14</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="19" t="n">
         <v>108.4540646253059</v>
       </c>
     </row>
@@ -2428,7 +2429,7 @@
           <t>0.145</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
+      <c r="B28" s="19" t="n">
         <v>116.1041350901616</v>
       </c>
     </row>
@@ -2438,7 +2439,7 @@
           <t>0.1526</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n">
+      <c r="B29" s="19" t="n">
         <v>127.905424577565</v>
       </c>
     </row>
@@ -2448,7 +2449,7 @@
           <t>0.155</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="19" t="n">
         <v>131.6763234351193</v>
       </c>
     </row>
@@ -2458,12 +2459,12 @@
           <t>0.16</t>
         </is>
       </c>
-      <c r="B31" s="17" t="n">
+      <c r="B31" s="19" t="n">
         <v>139.6016853407702</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>Volume x sensitivity (DCF value/share)</t>
         </is>
@@ -2475,7 +2476,7 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="B34" s="17" t="n">
+      <c r="B34" s="19" t="n">
         <v>117.0795645368853</v>
       </c>
     </row>
@@ -2485,7 +2486,7 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="B35" s="17" t="n">
+      <c r="B35" s="19" t="n">
         <v>122.4970935834225</v>
       </c>
     </row>
@@ -2495,7 +2496,7 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B36" s="17" t="n">
+      <c r="B36" s="19" t="n">
         <v>127.905424577565</v>
       </c>
     </row>
@@ -2505,7 +2506,7 @@
           <t>1.05</t>
         </is>
       </c>
-      <c r="B37" s="17" t="n">
+      <c r="B37" s="19" t="n">
         <v>133.3052385180974</v>
       </c>
     </row>
@@ -2515,12 +2516,12 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="B38" s="17" t="n">
+      <c r="B38" s="19" t="n">
         <v>138.6971354501409</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Net working capital / revenue sensitivity (DCF value/share)</t>
         </is>
@@ -2532,7 +2533,7 @@
           <t>0.24</t>
         </is>
       </c>
-      <c r="B41" s="17" t="n">
+      <c r="B41" s="19" t="n">
         <v>133.5580939831738</v>
       </c>
     </row>
@@ -2542,7 +2543,7 @@
           <t>0.26</t>
         </is>
       </c>
-      <c r="B42" s="17" t="n">
+      <c r="B42" s="19" t="n">
         <v>130.7317592803693</v>
       </c>
     </row>
@@ -2552,7 +2553,7 @@
           <t>0.28</t>
         </is>
       </c>
-      <c r="B43" s="17" t="n">
+      <c r="B43" s="19" t="n">
         <v>127.905424577565</v>
       </c>
     </row>
@@ -2562,7 +2563,7 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="B44" s="17" t="n">
+      <c r="B44" s="19" t="n">
         <v>125.0790898747605</v>
       </c>
     </row>
@@ -2572,7 +2573,7 @@
           <t>0.32</t>
         </is>
       </c>
-      <c r="B45" s="17" t="n">
+      <c r="B45" s="19" t="n">
         <v>122.2527551719562</v>
       </c>
     </row>
@@ -2659,23 +2660,23 @@
         <f>'Income Statement'!E16/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="18">
         <f>'Balance Sheet'!C22/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="18">
         <f>'Balance Sheet'!D22/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="18">
         <f>'Balance Sheet'!E22/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="18">
         <f>'Balance Sheet'!F22/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="18">
         <f>'Balance Sheet'!G22/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -2686,27 +2687,27 @@
           <t>Book value per share (SAR)</t>
         </is>
       </c>
-      <c r="B6" s="15">
-        <f>Assumptions!$C$61/Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="C6" s="15">
+      <c r="B6" s="18">
+        <f>Assumptions!$C$57/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C6" s="18">
         <f>'Balance Sheet'!F14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="18">
         <f>'Balance Sheet'!G14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="18">
         <f>'Balance Sheet'!H14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="18">
         <f>'Balance Sheet'!I14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="18">
         <f>'Balance Sheet'!J14/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -2717,7 +2718,7 @@
           <t>ROE (%) — attributable profit / average equity</t>
         </is>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="13">
         <f>'Income Statement'!E16/AVERAGE('Balance Sheet'!D14,'Balance Sheet'!E14)</f>
         <v/>
       </c>
@@ -2728,7 +2729,7 @@
           <t>Net debt / EBITDA (x)</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <f>Assumptions!$C$7/'Income Statement'!E9</f>
         <v/>
       </c>
@@ -2759,7 +2760,7 @@
           <t>Trailing EV/EBITDA (x)</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <f>(Assumptions!$C$5*Assumptions!$C$6+Assumptions!$C$7)/'Income Statement'!E9</f>
         <v/>
       </c>
@@ -2770,7 +2771,7 @@
           <t>Trailing P/E (x)</t>
         </is>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <f>Assumptions!$C$5/B5</f>
         <v/>
       </c>
@@ -2849,7 +2850,7 @@
           <t>Tadawul</t>
         </is>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>'Per-Share &amp; Ratios'!B9</f>
         <v/>
       </c>
@@ -2870,7 +2871,7 @@
           <t>Milan</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="24" t="n">
         <v>8.5</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2890,7 +2891,7 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="24" t="n">
         <v>7.5</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -2910,7 +2911,7 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="24" t="n">
         <v>26</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -2930,7 +2931,7 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="24" t="n">
         <v>24</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -3031,20 +3032,20 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>vs spot</t>
+          <t>vs price</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Discounted cash flow (primary)</t>
+          <t>Discounted cash flow (the answer)</t>
         </is>
       </c>
       <c r="B5" s="7">
@@ -3059,11 +3060,12 @@
         <f>'Fundamental Valuation'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="8">
-        <f>'Fundamental Valuation'!E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="9">
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the class primary</t>
+        </is>
+      </c>
+      <c r="G5" s="8">
         <f>C5/Assumptions!$C$5-1</f>
         <v/>
       </c>
@@ -3086,11 +3088,12 @@
         <f>'Fundamental Valuation'!D6</f>
         <v/>
       </c>
-      <c r="E6" s="8">
-        <f>'Fundamental Valuation'!E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="9">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>cross-check</t>
+        </is>
+      </c>
+      <c r="G6" s="8">
         <f>C6/Assumptions!$C$5-1</f>
         <v/>
       </c>
@@ -3113,11 +3116,12 @@
         <f>'Fundamental Valuation'!D7</f>
         <v/>
       </c>
-      <c r="E7" s="8">
-        <f>'Fundamental Valuation'!E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="9">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED — not a lens this class publishes</t>
+        </is>
+      </c>
+      <c r="G7" s="8">
         <f>C7/Assumptions!$C$5-1</f>
         <v/>
       </c>
@@ -3140,30 +3144,31 @@
         <f>'Fundamental Valuation'!D8</f>
         <v/>
       </c>
-      <c r="E8" s="8">
-        <f>'Fundamental Valuation'!E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="9">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>a disclosed floor, never weighted</t>
+        </is>
+      </c>
+      <c r="G8" s="8">
         <f>C8/Assumptions!$C$5-1</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Weighted central</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="12">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the cash-flow lens, not an average</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="11">
         <f>'Fundamental Valuation'!C9</f>
         <v/>
       </c>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="13">
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="12">
         <f>C9/Assumptions!$C$5-1</f>
         <v/>
       </c>
@@ -3174,7 +3179,7 @@
           <t>Terminal value as % of DCF EV</t>
         </is>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="13">
         <f>DCF!C42</f>
         <v/>
       </c>
@@ -3186,25 +3191,25 @@
         </is>
       </c>
       <c r="C11" s="7">
-        <f>'Fundamental Valuation'!C11</f>
+        <f>'Fundamental Valuation'!C13</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Market price (anchor)</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="12">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="11">
         <f>Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3230,7 +3235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3285,24 +3290,20 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>vs spot</t>
+          <t>vs price</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Discounted cash flow (primary)</t>
+          <t>Discounted cash flow (the answer)</t>
         </is>
       </c>
       <c r="B5" s="7">
@@ -3317,15 +3318,12 @@
         <f>DCF!C57</f>
         <v/>
       </c>
-      <c r="E5" s="8">
-        <f>Assumptions!$C$46</f>
-        <v/>
-      </c>
-      <c r="F5" s="15">
-        <f>C5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="9">
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the class primary</t>
+        </is>
+      </c>
+      <c r="G5" s="8">
         <f>C5/Assumptions!$C$5-1</f>
         <v/>
       </c>
@@ -3348,15 +3346,12 @@
         <f>'Relative &amp; Normalized'!D9</f>
         <v/>
       </c>
-      <c r="E6" s="8">
-        <f>Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="F6" s="15">
-        <f>C6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="9">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>cross-check</t>
+        </is>
+      </c>
+      <c r="G6" s="8">
         <f>C6/Assumptions!$C$5-1</f>
         <v/>
       </c>
@@ -3379,15 +3374,12 @@
         <f>'Relative &amp; Normalized'!D17</f>
         <v/>
       </c>
-      <c r="E7" s="8">
-        <f>Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="F7" s="15">
-        <f>C7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="9">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED — not a lens this class publishes</t>
+        </is>
+      </c>
+      <c r="G7" s="8">
         <f>C7/Assumptions!$C$5-1</f>
         <v/>
       </c>
@@ -3410,109 +3402,142 @@
         <f>'Relative &amp; Normalized'!D23</f>
         <v/>
       </c>
-      <c r="E8" s="8">
-        <f>Assumptions!$C$49</f>
-        <v/>
-      </c>
-      <c r="F8" s="15">
-        <f>C8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="9">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>a disclosed floor, never weighted</t>
+        </is>
+      </c>
+      <c r="G8" s="8">
         <f>C8/Assumptions!$C$5-1</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Weighted central</t>
-        </is>
-      </c>
-      <c r="B9" s="16">
-        <f>MIN(B5:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="16">
-        <f>SUM(F5:F8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="16">
-        <f>MAX(D5:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="13">
-        <f>SUM(E5:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="13">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the cash-flow lens, not an average</t>
+        </is>
+      </c>
+      <c r="B9" s="15">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="15">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>D5</f>
+        <v/>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>the class primary</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="12">
         <f>C9/Assumptions!$C$5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>NOT AVERAGED — the retired 45/20/20/15 blend, published unused</t>
+        </is>
+      </c>
+      <c r="C10" s="18">
+        <f>C5*0.45+C6*0.2+C7*0.2+C8*0.15</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>retired 04-Sep-2026</t>
+        </is>
+      </c>
+      <c r="G10" s="8">
+        <f>C10/Assumptions!$C$5-1</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>Span across the lenses (min/max) — a spread between METHODS, not a range around the answer</t>
+        </is>
+      </c>
+      <c r="B11" s="18">
+        <f>MIN(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="D11" s="18">
+        <f>MAX(D5:D8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>Expert panel median (whole-model — pasted)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C13" s="19" t="n">
         <v>125.9789008877625</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Market price (anchor)</t>
         </is>
       </c>
-      <c r="C12" s="7">
+      <c r="C14" s="7">
         <f>Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Central contested judgement — sustained gross margin, both ways</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>H1-2026 anchor (15.26%) — DCF value</t>
-        </is>
-      </c>
-      <c r="C15" s="7">
-        <f>DCF!C51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>FY2025-peak framing (16.0%) — DCF value (pasted re-run)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="n">
-        <v>139.6016853407702</v>
-      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>H1-2026 anchor (15.26%) — DCF value</t>
+        </is>
+      </c>
+      <c r="C17" s="7">
+        <f>DCF!C51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>FY2025-peak framing (16.0%) — DCF value (pasted re-run)</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>139.6016853407702</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
           <t>Further-compression framing (14.5%) — DCF value (pasted re-run)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C19" s="19" t="n">
         <v>116.1041350901616</v>
       </c>
     </row>
@@ -3529,7 +3554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3568,20 +3593,20 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Anchors &amp; market</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="11" t="n"/>
-      <c r="J4" s="11" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3589,7 +3614,7 @@
           <t>Spot price (SAR)</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="19" t="n">
         <v>104.8</v>
       </c>
     </row>
@@ -3599,7 +3624,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="20" t="n">
         <v>149.7175</v>
       </c>
     </row>
@@ -3609,25 +3634,25 @@
           <t>Net financial debt at FY2025 (SAR mn, disclosed)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="21" t="n">
         <v>385.173208</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Cost of capital — explicit window</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -3635,7 +3660,7 @@
           <t>Risk-free rate (10-year SAR sukuk)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="22" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -3645,7 +3670,7 @@
           <t>Sovereign default spread (netted out)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="22" t="n">
         <v>0.0048</v>
       </c>
     </row>
@@ -3655,7 +3680,7 @@
           <t>Equity risk premium (rating basis)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="22" t="n">
         <v>0.0494</v>
       </c>
     </row>
@@ -3665,7 +3690,7 @@
           <t>Beta (own-stock vs TASI)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="23" t="n">
         <v>1.129</v>
       </c>
     </row>
@@ -3675,7 +3700,7 @@
           <t>Cost of debt, marginal pre-tax</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="22" t="n">
         <v>0.059</v>
       </c>
     </row>
@@ -3685,25 +3710,25 @@
           <t>Effective zakat and income tax rate</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="22" t="n">
         <v>0.095</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Cost of capital — terminal</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -3711,7 +3736,7 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="22" t="n">
         <v>0.0502</v>
       </c>
     </row>
@@ -3721,7 +3746,7 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="22" t="n">
         <v>0.047</v>
       </c>
     </row>
@@ -3731,7 +3756,7 @@
           <t>Terminal beta</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3741,7 +3766,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="22" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -3751,7 +3776,7 @@
           <t>Terminal net-debt weight</t>
         </is>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="22" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -3761,25 +3786,25 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="22" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Forecast drivers — Cables &amp; wires leg (metal converter)</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="n"/>
-      <c r="I22" s="11" t="n"/>
-      <c r="J22" s="11" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -3787,19 +3812,19 @@
           <t>Cable volume index growth</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="22" t="n">
         <v>0.1</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="22" t="n">
         <v>0.075</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="22" t="n">
         <v>0.065</v>
       </c>
-      <c r="F23" s="20" t="n">
+      <c r="F23" s="22" t="n">
         <v>0.055</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="22" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -3809,19 +3834,19 @@
           <t>Metal content price growth</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="20" t="n">
+      <c r="E24" s="22" t="n">
         <v>0.01</v>
       </c>
-      <c r="F24" s="20" t="n">
+      <c r="F24" s="22" t="n">
         <v>0.01</v>
       </c>
-      <c r="G24" s="20" t="n">
+      <c r="G24" s="22" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3831,19 +3856,19 @@
           <t>Conversion cost inflation</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="D25" s="20" t="n">
+      <c r="D25" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="E25" s="20" t="n">
+      <c r="E25" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="F25" s="20" t="n">
+      <c r="F25" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="G25" s="20" t="n">
+      <c r="G25" s="22" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -3853,7 +3878,7 @@
           <t>Sustained gross margin (H1-2026 anchor)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="22" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -3863,37 +3888,37 @@
           <t>Gross-margin glide (added to anchor)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="23" t="n">
         <v>0.001</v>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E27" s="23" t="n">
         <v>0.001</v>
       </c>
-      <c r="F27" s="21" t="n">
+      <c r="F27" s="23" t="n">
         <v>0.0015</v>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="23" t="n">
         <v>0.0015</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Forecast drivers — HV turnkey &amp; Other legs</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="11" t="n"/>
-      <c r="I28" s="11" t="n"/>
-      <c r="J28" s="11" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="10" t="n"/>
+      <c r="J28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -3901,19 +3926,19 @@
           <t>HV turnkey revenue growth</t>
         </is>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="22" t="n">
         <v>0.1</v>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="22" t="n">
         <v>0.1</v>
       </c>
-      <c r="E29" s="20" t="n">
+      <c r="E29" s="22" t="n">
         <v>0.09</v>
       </c>
-      <c r="F29" s="20" t="n">
+      <c r="F29" s="22" t="n">
         <v>0.08</v>
       </c>
-      <c r="G29" s="20" t="n">
+      <c r="G29" s="22" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -3923,7 +3948,7 @@
           <t>HV turnkey segment margin</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="22" t="n">
         <v>0.08378233242821985</v>
       </c>
     </row>
@@ -3933,19 +3958,19 @@
           <t>Other segment revenue growth</t>
         </is>
       </c>
-      <c r="C31" s="20" t="n">
+      <c r="C31" s="22" t="n">
         <v>0.08</v>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="22" t="n">
         <v>0.08</v>
       </c>
-      <c r="E31" s="20" t="n">
+      <c r="E31" s="22" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F31" s="20" t="n">
+      <c r="F31" s="22" t="n">
         <v>0.06</v>
       </c>
-      <c r="G31" s="20" t="n">
+      <c r="G31" s="22" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -3955,25 +3980,25 @@
           <t>Other segment margin</t>
         </is>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="22" t="n">
         <v>0.5786820313464731</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Forecast drivers — group</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="11" t="n"/>
-      <c r="J33" s="11" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -3981,19 +4006,19 @@
           <t>Operating expenses / revenue</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n">
+      <c r="C34" s="22" t="n">
         <v>0.043</v>
       </c>
-      <c r="D34" s="20" t="n">
+      <c r="D34" s="22" t="n">
         <v>0.043</v>
       </c>
-      <c r="E34" s="20" t="n">
+      <c r="E34" s="22" t="n">
         <v>0.0425</v>
       </c>
-      <c r="F34" s="20" t="n">
+      <c r="F34" s="22" t="n">
         <v>0.042</v>
       </c>
-      <c r="G34" s="20" t="n">
+      <c r="G34" s="22" t="n">
         <v>0.042</v>
       </c>
     </row>
@@ -4003,7 +4028,7 @@
           <t>Depreciation and amortisation / revenue</t>
         </is>
       </c>
-      <c r="C35" s="20" t="n">
+      <c r="C35" s="22" t="n">
         <v>0.008500000000000001</v>
       </c>
     </row>
@@ -4013,19 +4038,19 @@
           <t>Capital expenditure / revenue</t>
         </is>
       </c>
-      <c r="C36" s="20" t="n">
+      <c r="C36" s="22" t="n">
         <v>0.019</v>
       </c>
-      <c r="D36" s="20" t="n">
+      <c r="D36" s="22" t="n">
         <v>0.018</v>
       </c>
-      <c r="E36" s="20" t="n">
+      <c r="E36" s="22" t="n">
         <v>0.017</v>
       </c>
-      <c r="F36" s="20" t="n">
+      <c r="F36" s="22" t="n">
         <v>0.016</v>
       </c>
-      <c r="G36" s="20" t="n">
+      <c r="G36" s="22" t="n">
         <v>0.016</v>
       </c>
     </row>
@@ -4035,7 +4060,7 @@
           <t>Net working capital / revenue</t>
         </is>
       </c>
-      <c r="C37" s="20" t="n">
+      <c r="C37" s="22" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -4045,19 +4070,19 @@
           <t>Cost-of-debt path</t>
         </is>
       </c>
-      <c r="C38" s="20" t="n">
+      <c r="C38" s="22" t="n">
         <v>0.059</v>
       </c>
-      <c r="D38" s="20" t="n">
+      <c r="D38" s="22" t="n">
         <v>0.058</v>
       </c>
-      <c r="E38" s="20" t="n">
+      <c r="E38" s="22" t="n">
         <v>0.057</v>
       </c>
-      <c r="F38" s="20" t="n">
+      <c r="F38" s="22" t="n">
         <v>0.056</v>
       </c>
-      <c r="G38" s="20" t="n">
+      <c r="G38" s="22" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -4067,7 +4092,7 @@
           <t>Forecast dividend payout ratio</t>
         </is>
       </c>
-      <c r="C39" s="20" t="n">
+      <c r="C39" s="22" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -4077,7 +4102,7 @@
           <t>Yield on surplus cash</t>
         </is>
       </c>
-      <c r="C40" s="20" t="n">
+      <c r="C40" s="22" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -4087,25 +4112,25 @@
           <t>NCI share of forecast profit</t>
         </is>
       </c>
-      <c r="C41" s="20" t="n">
+      <c r="C41" s="22" t="n">
         <v>0.004060669885351275</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Lens inputs</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="11" t="n"/>
-      <c r="H42" s="11" t="n"/>
-      <c r="I42" s="11" t="n"/>
-      <c r="J42" s="11" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -4113,7 +4138,7 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="C43" s="22" t="n">
+      <c r="C43" s="24" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -4123,7 +4148,7 @@
           <t>Justified price/earnings</t>
         </is>
       </c>
-      <c r="C44" s="22" t="n">
+      <c r="C44" s="24" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4133,209 +4158,169 @@
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C45" s="20" t="n">
+      <c r="C45" s="22" t="n">
         <v>0.28</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C46" s="23" t="n">
-        <v>0.45</v>
-      </c>
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Anchor roll</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="n">
-        <v>0.2</v>
+          <t>Days to the anchor</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>230</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C48" s="23" t="n">
-        <v>0.2</v>
+          <t>FY2025 dividend per share paid in window</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Weight — book</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>FY2025 disclosed base (audited)</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="10" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>Anchor roll</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n"/>
-      <c r="C50" s="11" t="n"/>
-      <c r="D50" s="11" t="n"/>
-      <c r="E50" s="11" t="n"/>
-      <c r="F50" s="11" t="n"/>
-      <c r="G50" s="11" t="n"/>
-      <c r="H50" s="11" t="n"/>
-      <c r="I50" s="11" t="n"/>
-      <c r="J50" s="11" t="n"/>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 cables metal content (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>8486.925676999999</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Days to the anchor</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="n">
-        <v>230</v>
+          <t>FY2025 cables conversion cost (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n">
+        <v>229.8024540000006</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>FY2025 dividend per share paid in window</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="n">
-        <v>2.25</v>
+          <t>FY2025 HV turnkey revenue (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n">
+        <v>230.839181</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>FY2025 disclosed base (audited)</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n"/>
-      <c r="C53" s="11" t="n"/>
-      <c r="D53" s="11" t="n"/>
-      <c r="E53" s="11" t="n"/>
-      <c r="F53" s="11" t="n"/>
-      <c r="G53" s="11" t="n"/>
-      <c r="H53" s="11" t="n"/>
-      <c r="I53" s="11" t="n"/>
-      <c r="J53" s="11" t="n"/>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 Other segment revenue (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>28.594413</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>FY2025 cables metal content (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="n">
-        <v>8486.925676999999</v>
+          <t>FY2025 net working capital (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n">
+        <v>2933.258925</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>FY2025 cables conversion cost (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="n">
-        <v>229.8024540000006</v>
+          <t>FY2025 PP&amp;E (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="n">
+        <v>1491.86312</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>FY2025 HV turnkey revenue (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C56" s="19" t="n">
-        <v>230.839181</v>
+          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="n">
+        <v>621.216217</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>FY2025 Other segment revenue (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C57" s="19" t="n">
-        <v>28.594413</v>
+          <t>FY2025 equity attributable (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="n">
+        <v>3246.136935</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>FY2025 net working capital (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C58" s="19" t="n">
-        <v>2933.258925</v>
+          <t>FY2025 associates carrying value (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="n">
+        <v>31.851877</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>FY2025 PP&amp;E (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C59" s="19" t="n">
-        <v>1491.86312</v>
+          <t>FY2025 non-operating assets (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C59" s="21" t="n">
+        <v>20.40064</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="n">
-        <v>621.216217</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 equity attributable (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="n">
-        <v>3246.136935</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 associates carrying value (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C62" s="19" t="n">
-        <v>31.851877</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 non-operating assets (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="n">
-        <v>20.40064</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
           <t>FY2025 NCI carrying value (SAR mn)</t>
         </is>
       </c>
-      <c r="C64" s="19" t="n">
+      <c r="C60" s="21" t="n">
         <v>62.737156</v>
       </c>
     </row>
@@ -4408,7 +4393,7 @@
           <t xml:space="preserve">  terminal value as % of EV</t>
         </is>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="13">
         <f>DCF!C42</f>
         <v/>
       </c>
@@ -4452,7 +4437,7 @@
           <t>Equity attributable (31-Dec-2025)</t>
         </is>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <f>DCF!C48</f>
         <v/>
       </c>
@@ -4463,7 +4448,7 @@
           <t>Value per share at anchor (SAR)</t>
         </is>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>DCF!C51</f>
         <v/>
       </c>
@@ -4553,18 +4538,18 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Cables &amp; wires — the metal converter</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4572,26 +4557,26 @@
           <t>Cable volume index (FY2025=100)</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <f>B6*(1+Assumptions!C$23)</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>C6*(1+Assumptions!D$23)</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f>D6*(1+Assumptions!E$23)</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <f>E6*(1+Assumptions!F$23)</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="27">
         <f>F6*(1+Assumptions!G$23)</f>
         <v/>
       </c>
@@ -4602,27 +4587,27 @@
           <t>Metal content per unit</t>
         </is>
       </c>
-      <c r="B7" s="27">
-        <f>Assumptions!$C$54/100.0</f>
-        <v/>
-      </c>
-      <c r="C7" s="27">
+      <c r="B7" s="28">
+        <f>Assumptions!$C$50/100.0</f>
+        <v/>
+      </c>
+      <c r="C7" s="28">
         <f>B7*(1+Assumptions!C$24)</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>C7*(1+Assumptions!D$24)</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <f>D7*(1+Assumptions!E$24)</f>
         <v/>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <f>E7*(1+Assumptions!F$24)</f>
         <v/>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="28">
         <f>F7*(1+Assumptions!G$24)</f>
         <v/>
       </c>
@@ -4633,27 +4618,27 @@
           <t>Conversion cost per unit</t>
         </is>
       </c>
-      <c r="B8" s="27">
-        <f>Assumptions!$C$55/100.0</f>
-        <v/>
-      </c>
-      <c r="C8" s="27">
+      <c r="B8" s="28">
+        <f>Assumptions!$C$51/100.0</f>
+        <v/>
+      </c>
+      <c r="C8" s="28">
         <f>B8*(1+Assumptions!C$25)</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>C8*(1+Assumptions!D$25)</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f>D8*(1+Assumptions!E$25)</f>
         <v/>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <f>E8*(1+Assumptions!F$25)</f>
         <v/>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="28">
         <f>F8*(1+Assumptions!G$25)</f>
         <v/>
       </c>
@@ -4664,23 +4649,23 @@
           <t>Target gross margin (anchor + glide)</t>
         </is>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <f>Assumptions!$C$26+Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <f>Assumptions!$C$26+Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <f>Assumptions!$C$26+Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <f>Assumptions!$C$26+Assumptions!F$27</f>
         <v/>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <f>Assumptions!$C$26+Assumptions!G$27</f>
         <v/>
       </c>
@@ -4691,27 +4676,27 @@
           <t>Gross profit per unit (conversion spread)</t>
         </is>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="28">
         <f>B13/B6</f>
         <v/>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="28">
         <f>C9/(1-C9)*(C7+C8)</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <f>D9/(1-D9)*(D7+D8)</f>
         <v/>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <f>E9/(1-E9)*(E7+E8)</f>
         <v/>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="28">
         <f>F9/(1-F9)*(F7+F8)</f>
         <v/>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="28">
         <f>G9/(1-G9)*(G7+G8)</f>
         <v/>
       </c>
@@ -4722,27 +4707,27 @@
           <t>Materials (metal leg)</t>
         </is>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>B6*B7</f>
         <v/>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>C6*C7</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>D6*D7</f>
         <v/>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>E6*E7</f>
         <v/>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>F6*F7</f>
         <v/>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>G6*G7</f>
         <v/>
       </c>
@@ -4753,27 +4738,27 @@
           <t>Conversion cost</t>
         </is>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <f>B6*B8</f>
         <v/>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>C6*C8</f>
         <v/>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>D6*D8</f>
         <v/>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>E6*E8</f>
         <v/>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>F6*F8</f>
         <v/>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="30">
         <f>G6*G8</f>
         <v/>
       </c>
@@ -4784,26 +4769,26 @@
           <t>Gross profit = volume x spread</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
+      <c r="B13" s="21" t="n">
         <v>1697.442537000001</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>C6*C10</f>
         <v/>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>D6*D10</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>E6*E10</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>F6*F10</f>
         <v/>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>G6*G10</f>
         <v/>
       </c>
@@ -4814,27 +4799,27 @@
           <t>Cables revenue = materials + conversion + gross profit</t>
         </is>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <f>B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <f>C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>F11+F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <f>G11+G12+G13</f>
         <v/>
       </c>
@@ -4845,44 +4830,44 @@
           <t>Cables gross margin (OUTPUT)</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="29">
         <f>B13/B14</f>
         <v/>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>C13/C14</f>
         <v/>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>D13/D14</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>E13/E14</f>
         <v/>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>F13/F14</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f>G13/G14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>HV turnkey projects — own growth, disclosed margin</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4890,27 +4875,27 @@
           <t>HV revenue (own growth path)</t>
         </is>
       </c>
-      <c r="B17" s="29">
-        <f>Assumptions!$C$56</f>
-        <v/>
-      </c>
-      <c r="C17" s="29">
+      <c r="B17" s="30">
+        <f>Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="C17" s="30">
         <f>B17*(1+Assumptions!C$29)</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <f>C17*(1+Assumptions!D$29)</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <f>D17*(1+Assumptions!E$29)</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <f>E17*(1+Assumptions!F$29)</f>
         <v/>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="30">
         <f>F17*(1+Assumptions!G$29)</f>
         <v/>
       </c>
@@ -4921,27 +4906,27 @@
           <t>HV segment margin</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="29">
         <f>Assumptions!$C$30</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f>Assumptions!$C$30</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f>Assumptions!$C$30</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="29">
         <f>Assumptions!$C$30</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <f>Assumptions!$C$30</f>
         <v/>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <f>Assumptions!$C$30</f>
         <v/>
       </c>
@@ -4952,44 +4937,44 @@
           <t>HV gross profit = revenue x margin</t>
         </is>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <f>B17*B18</f>
         <v/>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <f>C17*C18</f>
         <v/>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <f>D17*D18</f>
         <v/>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <f>E17*E18</f>
         <v/>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <f>F17*F18</f>
         <v/>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="30">
         <f>G17*G18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Other (telephone cables &amp; services) — own growth, disclosed margin</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -4997,27 +4982,27 @@
           <t>Other revenue (own growth path)</t>
         </is>
       </c>
-      <c r="B21" s="29">
-        <f>Assumptions!$C$57</f>
-        <v/>
-      </c>
-      <c r="C21" s="29">
+      <c r="B21" s="30">
+        <f>Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="C21" s="30">
         <f>B21*(1+Assumptions!C$31)</f>
         <v/>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <f>C21*(1+Assumptions!D$31)</f>
         <v/>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <f>D21*(1+Assumptions!E$31)</f>
         <v/>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <f>E21*(1+Assumptions!F$31)</f>
         <v/>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <f>F21*(1+Assumptions!G$31)</f>
         <v/>
       </c>
@@ -5028,27 +5013,27 @@
           <t>Other segment margin</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="29">
         <f>Assumptions!$C$32</f>
         <v/>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="29">
         <f>Assumptions!$C$32</f>
         <v/>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="29">
         <f>Assumptions!$C$32</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="29">
         <f>Assumptions!$C$32</f>
         <v/>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="29">
         <f>Assumptions!$C$32</f>
         <v/>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="29">
         <f>Assumptions!$C$32</f>
         <v/>
       </c>
@@ -5059,44 +5044,44 @@
           <t>Other gross profit = revenue x margin</t>
         </is>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="30">
         <f>B21*B22</f>
         <v/>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="30">
         <f>C21*C22</f>
         <v/>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <f>D21*D22</f>
         <v/>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <f>E21*E22</f>
         <v/>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <f>F21*F22</f>
         <v/>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <f>G21*G22</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Group — the sum of the three legs</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5104,27 +5089,27 @@
           <t>Revenue (group)</t>
         </is>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="30">
         <f>B14+B17+B21</f>
         <v/>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <f>C14+C17+C21</f>
         <v/>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <f>D14+D17+D21</f>
         <v/>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <f>E14+E17+E21</f>
         <v/>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <f>F14+F17+F21</f>
         <v/>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="30">
         <f>G14+G17+G21</f>
         <v/>
       </c>
@@ -5135,27 +5120,27 @@
           <t>Gross profit (group)</t>
         </is>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="30">
         <f>B13+B19+B23</f>
         <v/>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <f>C13+C19+C23</f>
         <v/>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <f>D13+D19+D23</f>
         <v/>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <f>E13+E19+E23</f>
         <v/>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="30">
         <f>F13+F19+F23</f>
         <v/>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="30">
         <f>G13+G19+G23</f>
         <v/>
       </c>
@@ -5166,27 +5151,27 @@
           <t>Cost of revenue (group)</t>
         </is>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="30">
         <f>B25-B26</f>
         <v/>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <f>C25-C26</f>
         <v/>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <f>D25-D26</f>
         <v/>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="30">
         <f>E25-E26</f>
         <v/>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="30">
         <f>F25-F26</f>
         <v/>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="30">
         <f>G25-G26</f>
         <v/>
       </c>
@@ -5197,27 +5182,27 @@
           <t>Gross margin (OUTPUT = group gross profit / group revenue)</t>
         </is>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="29">
         <f>B26/B25</f>
         <v/>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="29">
         <f>C26/C25</f>
         <v/>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="29">
         <f>D26/D25</f>
         <v/>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="29">
         <f>E26/E25</f>
         <v/>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="29">
         <f>F26/F25</f>
         <v/>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="29">
         <f>G26/G25</f>
         <v/>
       </c>
@@ -5228,23 +5213,23 @@
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <f>Assumptions!C$34*C25</f>
         <v/>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <f>Assumptions!D$34*D25</f>
         <v/>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <f>Assumptions!E$34*E25</f>
         <v/>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <f>Assumptions!F$34*F25</f>
         <v/>
       </c>
-      <c r="G29" s="29">
+      <c r="G29" s="30">
         <f>Assumptions!G$34*G25</f>
         <v/>
       </c>
@@ -5255,23 +5240,23 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="30">
         <f>Assumptions!$C$35*C25</f>
         <v/>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="30">
         <f>Assumptions!$C$35*D25</f>
         <v/>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="30">
         <f>Assumptions!$C$35*E25</f>
         <v/>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="30">
         <f>Assumptions!$C$35*F25</f>
         <v/>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="30">
         <f>Assumptions!$C$35*G25</f>
         <v/>
       </c>
@@ -5282,23 +5267,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="30">
         <f>C26-C29</f>
         <v/>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="30">
         <f>D26-D29</f>
         <v/>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="30">
         <f>E26-E29</f>
         <v/>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="30">
         <f>F26-F29</f>
         <v/>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="30">
         <f>G26-G29</f>
         <v/>
       </c>
@@ -5309,23 +5294,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="30">
         <f>C31+C30</f>
         <v/>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="30">
         <f>D31+D30</f>
         <v/>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="30">
         <f>E31+E30</f>
         <v/>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="30">
         <f>F31+F30</f>
         <v/>
       </c>
-      <c r="G32" s="29">
+      <c r="G32" s="30">
         <f>G31+G30</f>
         <v/>
       </c>
@@ -5336,23 +5321,23 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="29">
         <f>C32/C25</f>
         <v/>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="29">
         <f>D32/D25</f>
         <v/>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="29">
         <f>E32/E25</f>
         <v/>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="29">
         <f>F32/F25</f>
         <v/>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="29">
         <f>G32/G25</f>
         <v/>
       </c>
@@ -5403,17 +5388,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Relative — EV/EBITDA on FY2027E</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5432,7 +5417,7 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
@@ -5449,13 +5434,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Relative lens — implied value (base)</t>
         </is>
       </c>
       <c r="C8" s="32">
-        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
+        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$58+Assumptions!$C$59-Assumptions!$C$60)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$48</f>
         <v/>
       </c>
     </row>
@@ -5465,27 +5450,27 @@
           <t>Bear (7.5x) / Bull (11.0x)</t>
         </is>
       </c>
-      <c r="C9" s="15">
-        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
-        <v/>
-      </c>
-      <c r="D9" s="15">
-        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$52</f>
+      <c r="C9" s="18">
+        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$58+Assumptions!$C$59-Assumptions!$C$60)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$48</f>
+        <v/>
+      </c>
+      <c r="D9" s="18">
+        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$58+Assumptions!$C$59-Assumptions!$C$60)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$48</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Normalised earnings power</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5526,19 +5511,19 @@
           <t>Normalised EPS</t>
         </is>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="18">
         <f>((C12*C13-Assumptions!$C$35*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Normalised lens — implied value (base)</t>
         </is>
       </c>
       <c r="C16" s="32">
-        <f>(Assumptions!$C$44*C15)*DCF!$C$50-Assumptions!$C$52</f>
+        <f>(Assumptions!$C$44*C15)*DCF!$C$50-Assumptions!$C$48</f>
         <v/>
       </c>
     </row>
@@ -5548,27 +5533,27 @@
           <t>Bear (10x) / Bull (16x)</t>
         </is>
       </c>
-      <c r="C17" s="15">
-        <f>(10*C15)*DCF!$C$50-Assumptions!$C$52</f>
-        <v/>
-      </c>
-      <c r="D17" s="15">
-        <f>(16*C15)*DCF!$C$50-Assumptions!$C$52</f>
+      <c r="C17" s="18">
+        <f>(10*C15)*DCF!$C$50-Assumptions!$C$48</f>
+        <v/>
+      </c>
+      <c r="D17" s="18">
+        <f>(16*C15)*DCF!$C$50-Assumptions!$C$48</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Book value &amp; sustainable return</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -5576,8 +5561,8 @@
           <t>Book value per share</t>
         </is>
       </c>
-      <c r="C20" s="15">
-        <f>Assumptions!$C$61/Assumptions!$C$6</f>
+      <c r="C20" s="18">
+        <f>Assumptions!$C$57/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5593,13 +5578,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Book lens — implied value (base)</t>
         </is>
       </c>
       <c r="C22" s="32">
-        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$52</f>
+        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$48</f>
         <v/>
       </c>
     </row>
@@ -5609,12 +5594,12 @@
           <t>Bear / Bull</t>
         </is>
       </c>
-      <c r="C23" s="15">
-        <f>(((Assumptions!$C$45)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$52</f>
-        <v/>
-      </c>
-      <c r="D23" s="15">
-        <f>(((Assumptions!$C$45)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$52</f>
+      <c r="C23" s="18">
+        <f>(((Assumptions!$C$45)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$48</f>
+        <v/>
+      </c>
+      <c r="D23" s="18">
+        <f>(((Assumptions!$C$45)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$48</f>
         <v/>
       </c>
     </row>
@@ -5666,18 +5651,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Cost of capital</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="11" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5685,7 +5670,7 @@
           <t>Normalised risk-free rate rf*</t>
         </is>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="29">
         <f>Assumptions!$C$9-Assumptions!$C$10</f>
         <v/>
       </c>
@@ -5696,7 +5681,7 @@
           <t>Cost of equity Ke</t>
         </is>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="29">
         <f>C5+Assumptions!$C$12*Assumptions!$C$11</f>
         <v/>
       </c>
@@ -5707,7 +5692,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>Assumptions!$C$13*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -5718,7 +5703,7 @@
           <t>Market capitalisation</t>
         </is>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>Assumptions!$C$5*Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5729,13 +5714,13 @@
           <t>Net-debt weight</t>
         </is>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <f>Assumptions!$C$7/(Assumptions!$C$7+C8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>WACC — explicit window</t>
         </is>
@@ -5751,7 +5736,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <f>Assumptions!$C$16+Assumptions!$C$18*Assumptions!$C$17</f>
         <v/>
       </c>
@@ -5762,13 +5747,13 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>Assumptions!$C$19*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>WACC — terminal</t>
         </is>
@@ -5779,18 +5764,18 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Discount-rate glide &amp; waterfall</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -5858,23 +5843,23 @@
           <t>Forward WACC</t>
         </is>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f>C10-(C10-C13)*C17</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f>C10-(C10-C13)*D17</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="29">
         <f>C10-(C10-C13)*E17</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <f>C10-(C10-C13)*F17</f>
         <v/>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <f>C10-(C10-C13)*G17</f>
         <v/>
       </c>
@@ -5939,23 +5924,23 @@
           <t>NOPAT = EBIT x (1 - tax)</t>
         </is>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <f>C20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <f>D20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <f>E20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <f>F20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <f>G20*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -6020,23 +6005,23 @@
           <t>- Capital expenditure</t>
         </is>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <f>Assumptions!C$36*C23</f>
         <v/>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <f>Assumptions!D$36*D23</f>
         <v/>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <f>Assumptions!E$36*E23</f>
         <v/>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <f>Assumptions!F$36*F23</f>
         <v/>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <f>Assumptions!G$36*G23</f>
         <v/>
       </c>
@@ -6047,23 +6032,23 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <f>Assumptions!$C$37*C23</f>
         <v/>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <f>Assumptions!$C$37*D23</f>
         <v/>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <f>Assumptions!$C$37*E23</f>
         <v/>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <f>Assumptions!$C$37*F23</f>
         <v/>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="30">
         <f>Assumptions!$C$37*G23</f>
         <v/>
       </c>
@@ -6074,29 +6059,29 @@
           <t>- Change in working capital</t>
         </is>
       </c>
-      <c r="C26" s="29">
-        <f>C25-Assumptions!$C$58</f>
-        <v/>
-      </c>
-      <c r="D26" s="29">
+      <c r="C26" s="30">
+        <f>C25-Assumptions!$C$54</f>
+        <v/>
+      </c>
+      <c r="D26" s="30">
         <f>D25-C25</f>
         <v/>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <f>E25-D25</f>
         <v/>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="30">
         <f>F25-E25</f>
         <v/>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="30">
         <f>G25-F25</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Free cash flow to firm</t>
         </is>
@@ -6128,40 +6113,40 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="30">
         <f>C27*C19</f>
         <v/>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="30">
         <f>D27*D19</f>
         <v/>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="30">
         <f>E27*E19</f>
         <v/>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="30">
         <f>F27*F19</f>
         <v/>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="30">
         <f>G27*G19</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Invested capital &amp; terminal</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="11" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -6169,23 +6154,23 @@
           <t>PP&amp;E roll-forward</t>
         </is>
       </c>
-      <c r="C31" s="29">
-        <f>Assumptions!$C$59+C24-C22</f>
-        <v/>
-      </c>
-      <c r="D31" s="29">
+      <c r="C31" s="30">
+        <f>Assumptions!$C$55+C24-C22</f>
+        <v/>
+      </c>
+      <c r="D31" s="30">
         <f>C31+D24-D22</f>
         <v/>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="30">
         <f>D31+E24-E22</f>
         <v/>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="30">
         <f>E31+F24-F22</f>
         <v/>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="30">
         <f>F31+G24-G22</f>
         <v/>
       </c>
@@ -6196,23 +6181,23 @@
           <t>Invested capital = NWC + PP&amp;E</t>
         </is>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="30">
         <f>C25+C31</f>
         <v/>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="30">
         <f>D25+D31</f>
         <v/>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="30">
         <f>E25+E31</f>
         <v/>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="30">
         <f>F25+F31</f>
         <v/>
       </c>
-      <c r="G32" s="29">
+      <c r="G32" s="30">
         <f>G25+G31</f>
         <v/>
       </c>
@@ -6223,23 +6208,23 @@
           <t>ROIC = NOPAT / invested capital</t>
         </is>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="29">
         <f>C21/C32</f>
         <v/>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="29">
         <f>D21/D32</f>
         <v/>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="29">
         <f>E21/E32</f>
         <v/>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="29">
         <f>F21/F32</f>
         <v/>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="29">
         <f>G21/G32</f>
         <v/>
       </c>
@@ -6250,7 +6235,7 @@
           <t>PV of explicit FCFF (5 years)</t>
         </is>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="30">
         <f>SUM(C28:G28)</f>
         <v/>
       </c>
@@ -6261,7 +6246,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="29">
         <f>G21*(1+Assumptions!$C$21)/G32</f>
         <v/>
       </c>
@@ -6272,7 +6257,7 @@
           <t>Terminal reinvestment rate = g / ROIC</t>
         </is>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="29">
         <f>Assumptions!$C$21/C36</f>
         <v/>
       </c>
@@ -6283,7 +6268,7 @@
           <t>Terminal NOPAT (next year)</t>
         </is>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="30">
         <f>G21*(1+Assumptions!$C$21)</f>
         <v/>
       </c>
@@ -6294,7 +6279,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="30">
         <f>C38*(1-C37)/(C13-Assumptions!$C$21)</f>
         <v/>
       </c>
@@ -6305,13 +6290,13 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="30">
         <f>C39*G19</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
@@ -6322,7 +6307,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="31" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>Terminal value as % of EV</t>
         </is>
@@ -6333,18 +6318,18 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Enterprise value to equity</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="11" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -6352,7 +6337,7 @@
           <t>Less: net financial debt</t>
         </is>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="30">
         <f>-Assumptions!$C$7</f>
         <v/>
       </c>
@@ -6363,8 +6348,8 @@
           <t>Add: associates + non-operating assets</t>
         </is>
       </c>
-      <c r="C46" s="29">
-        <f>Assumptions!$C$62+Assumptions!$C$63</f>
+      <c r="C46" s="30">
+        <f>Assumptions!$C$58+Assumptions!$C$59</f>
         <v/>
       </c>
     </row>
@@ -6374,13 +6359,13 @@
           <t>Less: non-controlling interests</t>
         </is>
       </c>
-      <c r="C47" s="29">
-        <f>-Assumptions!$C$64</f>
+      <c r="C47" s="30">
+        <f>-Assumptions!$C$60</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Equity attributable (31-Dec-2025)</t>
         </is>
@@ -6396,7 +6381,7 @@
           <t>Value per share (31-Dec-2025)</t>
         </is>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="18">
         <f>C48/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6408,18 +6393,18 @@
         </is>
       </c>
       <c r="C50" s="36">
-        <f>(1+C6)^(Assumptions!$C$51/365)</f>
+        <f>(1+C6)^(Assumptions!$C$47/365)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Value per share at anchor (18-Aug-2026)</t>
         </is>
       </c>
       <c r="C51" s="32">
-        <f>C49*C50-Assumptions!$C$52</f>
+        <f>C49*C50-Assumptions!$C$48</f>
         <v/>
       </c>
     </row>
@@ -6429,24 +6414,24 @@
           <t>vs spot</t>
         </is>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="8">
         <f>C51/Assumptions!$C$5-1</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>DCF scenarios (whole-model re-runs — pasted)</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
-      <c r="C54" s="11" t="n"/>
-      <c r="D54" s="11" t="n"/>
-      <c r="E54" s="11" t="n"/>
-      <c r="F54" s="11" t="n"/>
-      <c r="G54" s="11" t="n"/>
-      <c r="H54" s="11" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -6454,7 +6439,7 @@
           <t>Bear</t>
         </is>
       </c>
-      <c r="C55" s="17" t="n">
+      <c r="C55" s="19" t="n">
         <v>80.84906676286525</v>
       </c>
     </row>
@@ -6475,7 +6460,7 @@
           <t>Bull</t>
         </is>
       </c>
-      <c r="C57" s="17" t="n">
+      <c r="C57" s="19" t="n">
         <v>197.7603327814774</v>
       </c>
     </row>
@@ -6584,13 +6569,13 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="21" t="n">
         <v>7825.378127</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="21" t="n">
         <v>9007.360866999999</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="21" t="n">
         <v>10673.604262</v>
       </c>
       <c r="F5" s="14">
@@ -6620,13 +6605,13 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="21" t="n">
         <v>972.763438</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="21" t="n">
         <v>1286.522351</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="21" t="n">
         <v>1733.329855</v>
       </c>
       <c r="F6" s="14">
@@ -6656,35 +6641,35 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <f>D6/D5</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="29">
         <f>E6/E5</f>
         <v/>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="29">
         <f>F6/F5</f>
         <v/>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="29">
         <f>G6/G5</f>
         <v/>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="29">
         <f>H6/H5</f>
         <v/>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="29">
         <f>I6/I5</f>
         <v/>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="29">
         <f>J6/J5</f>
         <v/>
       </c>
@@ -6695,15 +6680,15 @@
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>C6-C11</f>
         <v/>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>D6-D11</f>
         <v/>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>E6-E11</f>
         <v/>
       </c>
@@ -6734,15 +6719,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>C11+C10</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>D11+D10</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>E11+E10</f>
         <v/>
       </c>
@@ -6773,13 +6758,13 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="21" t="n">
         <v>66.428122</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="21" t="n">
         <v>68.643861</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="21" t="n">
         <v>85.39563699999999</v>
       </c>
       <c r="F10" s="14">
@@ -6809,13 +6794,13 @@
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="21" t="n">
         <v>647.606782</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="21" t="n">
         <v>968.439154</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="21" t="n">
         <v>1266.636844</v>
       </c>
       <c r="F11" s="14">
@@ -6845,13 +6830,13 @@
           <t>Net finance cost</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="21" t="n">
         <v>-89.01433400000001</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="21" t="n">
         <v>-87.66669899999999</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="21" t="n">
         <v>-74.15399499999999</v>
       </c>
       <c r="F12" s="14">
@@ -6881,35 +6866,35 @@
           <t>Profit before zakat</t>
         </is>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="30">
         <f>H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="30">
         <f>I11+I12</f>
         <v/>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="30">
         <f>J11+J12</f>
         <v/>
       </c>
@@ -6920,32 +6905,32 @@
           <t>Zakat &amp; income tax</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="21" t="n">
         <v>-39.126206</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="21" t="n">
         <v>-63.891298</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="21" t="n">
         <v>-107.681788</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>-F13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <f>-G13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <f>-H13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="30">
         <f>-I13*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="J14" s="29">
+      <c r="J14" s="30">
         <f>-J13*Assumptions!$C$14</f>
         <v/>
       </c>
@@ -6956,32 +6941,32 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="21" t="n">
         <v>518.492623</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="21" t="n">
         <v>816.881157</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="21" t="n">
         <v>1084.801061</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="30">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="30">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="30">
         <f>I13+I14</f>
         <v/>
       </c>
-      <c r="J15" s="29">
+      <c r="J15" s="30">
         <f>J13+J14</f>
         <v/>
       </c>
@@ -6992,7 +6977,7 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="21" t="n">
         <v>1080.396042</v>
       </c>
       <c r="F16" s="14">

--- a/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
+++ b/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
@@ -141,12 +141,12 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1013,23 +1013,23 @@
         <v>621.216217</v>
       </c>
       <c r="F10" s="14">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
     </row>
@@ -1207,23 +1207,23 @@
         </is>
       </c>
       <c r="C18" s="30">
-        <f>Assumptions!$C$56-C17</f>
+        <f>Assumptions!$C$59-C17</f>
         <v/>
       </c>
       <c r="D18" s="30">
-        <f>Assumptions!$C$56-D17</f>
+        <f>Assumptions!$C$59-D17</f>
         <v/>
       </c>
       <c r="E18" s="30">
-        <f>Assumptions!$C$56-E17</f>
+        <f>Assumptions!$C$59-E17</f>
         <v/>
       </c>
       <c r="F18" s="30">
-        <f>Assumptions!$C$56-F17</f>
+        <f>Assumptions!$C$59-F17</f>
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>Assumptions!$C$56-G17</f>
+        <f>Assumptions!$C$59-G17</f>
         <v/>
       </c>
     </row>
@@ -1234,23 +1234,23 @@
         </is>
       </c>
       <c r="C19" s="30">
-        <f>Assumptions!C$38*Assumptions!$C$56-Assumptions!$C$40*MAX(C18,0)</f>
+        <f>Assumptions!C$41*Assumptions!$C$59-Assumptions!$C$43*MAX(C18,0)</f>
         <v/>
       </c>
       <c r="D19" s="30">
-        <f>Assumptions!D$38*Assumptions!$C$56-Assumptions!$C$40*MAX(D18,0)</f>
+        <f>Assumptions!D$41*Assumptions!$C$59-Assumptions!$C$43*MAX(D18,0)</f>
         <v/>
       </c>
       <c r="E19" s="30">
-        <f>Assumptions!E$38*Assumptions!$C$56-Assumptions!$C$40*MAX(E18,0)</f>
+        <f>Assumptions!E$41*Assumptions!$C$59-Assumptions!$C$43*MAX(E18,0)</f>
         <v/>
       </c>
       <c r="F19" s="30">
-        <f>Assumptions!F$38*Assumptions!$C$56-Assumptions!$C$40*MAX(F18,0)</f>
+        <f>Assumptions!F$41*Assumptions!$C$59-Assumptions!$C$43*MAX(F18,0)</f>
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>Assumptions!G$38*Assumptions!$C$56-Assumptions!$C$40*MAX(G18,0)</f>
+        <f>Assumptions!G$41*Assumptions!$C$59-Assumptions!$C$43*MAX(G18,0)</f>
         <v/>
       </c>
     </row>
@@ -1315,23 +1315,23 @@
         </is>
       </c>
       <c r="C22" s="30">
-        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
+        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)</f>
         <v/>
       </c>
       <c r="D22" s="30">
-        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
+        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)</f>
         <v/>
       </c>
       <c r="E22" s="30">
-        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
+        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)</f>
         <v/>
       </c>
       <c r="F22" s="30">
-        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
+        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)</f>
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)</f>
+        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)</f>
         <v/>
       </c>
     </row>
@@ -1342,23 +1342,23 @@
         </is>
       </c>
       <c r="C23" s="30">
-        <f>Assumptions!$C$39*C22</f>
+        <f>Assumptions!$C$42*C22</f>
         <v/>
       </c>
       <c r="D23" s="30">
-        <f>Assumptions!$C$39*D22</f>
+        <f>Assumptions!$C$42*D22</f>
         <v/>
       </c>
       <c r="E23" s="30">
-        <f>Assumptions!$C$39*E22</f>
+        <f>Assumptions!$C$42*E22</f>
         <v/>
       </c>
       <c r="F23" s="30">
-        <f>Assumptions!$C$39*F22</f>
+        <f>Assumptions!$C$42*F22</f>
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>Assumptions!$C$39*G22</f>
+        <f>Assumptions!$C$42*G22</f>
         <v/>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="C25" s="30">
-        <f>Assumptions!$C$57+C22-C23</f>
+        <f>Assumptions!$C$60+C22-C23</f>
         <v/>
       </c>
       <c r="D25" s="30">
@@ -2187,16 +2187,16 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>141.7056057772044</v>
+        <v>142.5329983174736</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>163.715865885987</v>
+        <v>165.8900261351979</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>198.2042805447696</v>
+        <v>202.3566722281835</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>260.2479130974581</v>
+        <v>267.7660755948026</v>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>120.4623841952295</v>
+        <v>121.1462246885317</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>134.7210292900971</v>
+        <v>136.4581994122694</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>155.2188360125738</v>
+        <v>158.3715319493057</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>187.3299521235833</v>
+        <v>192.5675384208111</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>245.0864687133326</v>
+        <v>253.8803374388925</v>
       </c>
     </row>
     <row r="8">
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>104.8967296610403</v>
+        <v>105.4757919254231</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>114.6678051971448</v>
+        <v>116.1038048717173</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>127.905424577565</v>
+        <v>130.4248509123573</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>146.9294453787323</v>
+        <v>150.9067031915588</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>176.7240270270523</v>
+        <v>182.8513142532758</v>
       </c>
     </row>
     <row r="9">
@@ -2255,19 +2255,19 @@
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>93.00059958544631</v>
+        <v>93.49993194791615</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>99.97128853350969</v>
+        <v>101.1874536036779</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>109.0117190503424</v>
+        <v>111.0946812493539</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>121.2543672012037</v>
+        <v>124.4332246638776</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>138.8421999218402</v>
+        <v>143.4957942849643</v>
       </c>
     </row>
     <row r="10">
@@ -2277,19 +2277,19 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>83.61297829887353</v>
+        <v>84.04969368984855</v>
       </c>
       <c r="C10" s="19" t="n">
-        <v>88.73699993247544</v>
+        <v>89.78587482784923</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>95.16215451155131</v>
+        <v>96.92651079279665</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>103.4905512602372</v>
+        <v>106.1191088346631</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>114.7635647327278</v>
+        <v>118.483561402772</v>
       </c>
     </row>
     <row r="12">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B13" s="19" t="n">
-        <v>134.1012811749074</v>
+        <v>136.7426042395026</v>
       </c>
     </row>
     <row r="14">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="B14" s="19" t="n">
-        <v>131.1659864625187</v>
+        <v>133.7495488251624</v>
       </c>
     </row>
     <row r="15">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>127.905424577565</v>
+        <v>130.4248509123573</v>
       </c>
     </row>
     <row r="16">
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="B16" s="19" t="n">
-        <v>125.5381303609279</v>
+        <v>128.0110086639152</v>
       </c>
     </row>
     <row r="17">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>122.8400164516531</v>
+        <v>125.259860044495</v>
       </c>
     </row>
     <row r="19">
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="B20" s="19" t="n">
-        <v>139.3236347299058</v>
+        <v>142.6983003741912</v>
       </c>
     </row>
     <row r="21">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="B21" s="19" t="n">
-        <v>133.6031807444171</v>
+        <v>136.5505807795981</v>
       </c>
     </row>
     <row r="22">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="B22" s="19" t="n">
-        <v>127.905424577565</v>
+        <v>130.4248509123573</v>
       </c>
     </row>
     <row r="23">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>122.2278357157988</v>
+        <v>124.3186591109369</v>
       </c>
     </row>
     <row r="24">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>116.5683245327664</v>
+        <v>118.2299808722273</v>
       </c>
     </row>
     <row r="26">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="B27" s="19" t="n">
-        <v>108.4540646253059</v>
+        <v>110.4145045547937</v>
       </c>
     </row>
     <row r="28">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B28" s="19" t="n">
-        <v>116.1041350901616</v>
+        <v>118.2844198497204</v>
       </c>
     </row>
     <row r="29">
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="B29" s="19" t="n">
-        <v>127.905424577565</v>
+        <v>130.4248509123573</v>
       </c>
     </row>
     <row r="30">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="B30" s="19" t="n">
-        <v>131.6763234351193</v>
+        <v>134.3041167701747</v>
       </c>
     </row>
     <row r="31">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>139.6016853407702</v>
+        <v>142.457235668817</v>
       </c>
     </row>
     <row r="33">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="B34" s="19" t="n">
-        <v>117.0795645368853</v>
+        <v>119.6053719904985</v>
       </c>
     </row>
     <row r="35">
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>122.4970935834225</v>
+        <v>125.0198940084373</v>
       </c>
     </row>
     <row r="36">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="B36" s="19" t="n">
-        <v>127.905424577565</v>
+        <v>130.4248509123573</v>
       </c>
     </row>
     <row r="37">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="B37" s="19" t="n">
-        <v>133.3052385180974</v>
+        <v>135.8209510803724</v>
       </c>
     </row>
     <row r="38">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="B38" s="19" t="n">
-        <v>138.6971354501409</v>
+        <v>141.2088186686372</v>
       </c>
     </row>
     <row r="40">
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="B41" s="19" t="n">
-        <v>133.5580939831738</v>
+        <v>136.2160155850796</v>
       </c>
     </row>
     <row r="42">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B42" s="19" t="n">
-        <v>130.7317592803693</v>
+        <v>133.3204332487185</v>
       </c>
     </row>
     <row r="43">
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="B43" s="19" t="n">
-        <v>127.905424577565</v>
+        <v>130.4248509123573</v>
       </c>
     </row>
     <row r="44">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="B44" s="19" t="n">
-        <v>125.0790898747605</v>
+        <v>127.5292685759961</v>
       </c>
     </row>
     <row r="45">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>122.2527551719562</v>
+        <v>124.633686239635</v>
       </c>
     </row>
   </sheetData>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>Assumptions!$C$57/Assumptions!$C$6</f>
+        <f>Assumptions!$C$60/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C6" s="18">
@@ -2871,7 +2871,7 @@
           <t>Milan</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="25" t="n">
         <v>8.5</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2891,7 +2891,7 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="25" t="n">
         <v>7.5</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -2911,7 +2911,7 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="25" t="n">
         <v>26</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -2931,7 +2931,7 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="25" t="n">
         <v>24</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="C10" s="13">
-        <f>DCF!C42</f>
+        <f>DCF!C46</f>
         <v/>
       </c>
     </row>
@@ -3307,15 +3307,15 @@
         </is>
       </c>
       <c r="B5" s="7">
+        <f>DCF!C59</f>
+        <v/>
+      </c>
+      <c r="C5" s="7">
         <f>DCF!C55</f>
         <v/>
       </c>
-      <c r="C5" s="7">
-        <f>DCF!C51</f>
-        <v/>
-      </c>
       <c r="D5" s="7">
-        <f>DCF!C57</f>
+        <f>DCF!C61</f>
         <v/>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="C17" s="7">
-        <f>DCF!C51</f>
+        <f>DCF!C55</f>
         <v/>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="C18" s="19" t="n">
-        <v>139.6016853407702</v>
+        <v>142.457235668817</v>
       </c>
     </row>
     <row r="19">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="C19" s="19" t="n">
-        <v>116.1041350901616</v>
+        <v>118.2844198497204</v>
       </c>
     </row>
   </sheetData>
@@ -3554,7 +3554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3783,425 +3783,420 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Terminal inflation (house Saudi path)</t>
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Forecast drivers — Cables &amp; wires leg (metal converter)</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="10" t="n"/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Terminal real growth</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>0.0196078431372549</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Cable volume index growth</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D23" s="22" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="F23" s="22" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="G23" s="22" t="n">
-        <v>0.05</v>
+          <t>Terminal growth, nominal (derived)</t>
+        </is>
+      </c>
+      <c r="C23" s="24">
+        <f>(1+Assumptions!$C$21)*(1+Assumptions!$C$22)-1</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Metal content price growth</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F24" s="22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G24" s="22" t="n">
-        <v>0.01</v>
+          <t>Weighted asset life, years (derived from the notes)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="n">
+        <v>35.7565</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Conversion cost inflation</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D25" s="22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E25" s="22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F25" s="22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G25" s="22" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Forecast drivers — Cables &amp; wires leg (metal converter)</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Sustained gross margin (H1-2026 anchor)</t>
+          <t>Cable volume index growth</t>
         </is>
       </c>
       <c r="C26" s="22" t="n">
-        <v>0.1526</v>
+        <v>0.1</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="F26" s="22" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G26" s="22" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Gross-margin glide (added to anchor)</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="n">
+          <t>Metal content price growth</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D27" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="23" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E27" s="23" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F27" s="23" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="G27" s="23" t="n">
-        <v>0.0015</v>
+      <c r="E27" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F27" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G27" s="22" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Forecast drivers — HV turnkey &amp; Other legs</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="10" t="n"/>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Conversion cost inflation</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F28" s="22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G28" s="22" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>HV turnkey revenue growth</t>
+          <t>Sustained gross margin (H1-2026 anchor)</t>
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D29" s="22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E29" s="22" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F29" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G29" s="22" t="n">
-        <v>0.08</v>
+        <v>0.1526</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>HV turnkey segment margin</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="n">
-        <v>0.08378233242821985</v>
+          <t>Gross-margin glide (added to anchor)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F30" s="23" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="G30" s="23" t="n">
+        <v>0.0015</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Other segment revenue growth</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D31" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E31" s="22" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F31" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G31" s="22" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Forecast drivers — HV turnkey &amp; Other legs</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Other segment margin</t>
+          <t>HV turnkey revenue growth</t>
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.5786820313464731</v>
+        <v>0.1</v>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E32" s="22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F32" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G32" s="22" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Forecast drivers — group</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>HV turnkey segment margin</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="n">
+        <v>0.08378233242821985</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Operating expenses / revenue</t>
+          <t>Other segment revenue growth</t>
         </is>
       </c>
       <c r="C34" s="22" t="n">
-        <v>0.043</v>
+        <v>0.08</v>
       </c>
       <c r="D34" s="22" t="n">
-        <v>0.043</v>
+        <v>0.08</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>0.0425</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>0.042</v>
+        <v>0.06</v>
       </c>
       <c r="G34" s="22" t="n">
-        <v>0.042</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation / revenue</t>
+          <t>Other segment margin</t>
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.5786820313464731</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Capital expenditure / revenue</t>
-        </is>
-      </c>
-      <c r="C36" s="22" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="D36" s="22" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="E36" s="22" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="F36" s="22" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="G36" s="22" t="n">
-        <v>0.016</v>
-      </c>
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Forecast drivers — group</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Net working capital / revenue</t>
+          <t>Operating expenses / revenue</t>
         </is>
       </c>
       <c r="C37" s="22" t="n">
-        <v>0.28</v>
+        <v>0.043</v>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="E37" s="22" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="F37" s="22" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G37" s="22" t="n">
+        <v>0.042</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Cost-of-debt path</t>
+          <t>Depreciation and amortisation / revenue</t>
         </is>
       </c>
       <c r="C38" s="22" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="D38" s="22" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="E38" s="22" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="F38" s="22" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="G38" s="22" t="n">
-        <v>0.055</v>
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Forecast dividend payout ratio</t>
+          <t>Capital expenditure / revenue</t>
         </is>
       </c>
       <c r="C39" s="22" t="n">
-        <v>0.55</v>
+        <v>0.019</v>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E39" s="22" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F39" s="22" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G39" s="22" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Yield on surplus cash</t>
+          <t>Net working capital / revenue</t>
         </is>
       </c>
       <c r="C40" s="22" t="n">
-        <v>0.04</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>NCI share of forecast profit</t>
+          <t>Cost-of-debt path</t>
         </is>
       </c>
       <c r="C41" s="22" t="n">
-        <v>0.004060669885351275</v>
+        <v>0.059</v>
+      </c>
+      <c r="D41" s="22" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E41" s="22" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="F41" s="22" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="10" t="n"/>
-      <c r="I42" s="10" t="n"/>
-      <c r="J42" s="10" t="n"/>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Forecast dividend payout ratio</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="n">
-        <v>9.5</v>
+          <t>Yield on surplus cash</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="n">
-        <v>13</v>
+          <t>NCI share of forecast profit</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="n">
+        <v>0.004060669885351275</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C45" s="22" t="n">
-        <v>0.28</v>
-      </c>
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="10" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>Anchor roll</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Days to the anchor</t>
-        </is>
-      </c>
-      <c r="C47" s="21" t="n">
-        <v>230</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>FY2025 dividend per share paid in window</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="n">
-        <v>2.25</v>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>FY2025 disclosed base (audited)</t>
+          <t>Anchor roll</t>
         </is>
       </c>
       <c r="B49" s="10" t="n"/>
@@ -4217,110 +4212,146 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>FY2025 cables metal content (SAR mn)</t>
+          <t>Days to the anchor</t>
         </is>
       </c>
       <c r="C50" s="21" t="n">
-        <v>8486.925676999999</v>
+        <v>230</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>FY2025 cables conversion cost (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C51" s="21" t="n">
-        <v>229.8024540000006</v>
+          <t>FY2025 dividend per share paid in window</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 HV turnkey revenue (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C52" s="21" t="n">
-        <v>230.839181</v>
-      </c>
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>FY2025 disclosed base (audited)</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>FY2025 Other segment revenue (SAR mn)</t>
+          <t>FY2025 cables metal content (SAR mn)</t>
         </is>
       </c>
       <c r="C53" s="21" t="n">
-        <v>28.594413</v>
+        <v>8486.925676999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>FY2025 net working capital (SAR mn)</t>
+          <t>FY2025 cables conversion cost (SAR mn)</t>
         </is>
       </c>
       <c r="C54" s="21" t="n">
-        <v>2933.258925</v>
+        <v>229.8024540000006</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>FY2025 PP&amp;E (SAR mn)</t>
+          <t>FY2025 HV turnkey revenue (SAR mn)</t>
         </is>
       </c>
       <c r="C55" s="21" t="n">
-        <v>1491.86312</v>
+        <v>230.839181</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
+          <t>FY2025 Other segment revenue (SAR mn)</t>
         </is>
       </c>
       <c r="C56" s="21" t="n">
-        <v>621.216217</v>
+        <v>28.594413</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>FY2025 equity attributable (SAR mn)</t>
+          <t>FY2025 net working capital (SAR mn)</t>
         </is>
       </c>
       <c r="C57" s="21" t="n">
-        <v>3246.136935</v>
+        <v>2933.258925</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>FY2025 associates carrying value (SAR mn)</t>
+          <t>FY2025 PP&amp;E (SAR mn)</t>
         </is>
       </c>
       <c r="C58" s="21" t="n">
-        <v>31.851877</v>
+        <v>1491.86312</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>FY2025 non-operating assets (SAR mn)</t>
+          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
         </is>
       </c>
       <c r="C59" s="21" t="n">
-        <v>20.40064</v>
+        <v>621.216217</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>FY2025 equity attributable (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>3246.136935</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 associates carrying value (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="n">
+        <v>31.851877</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 non-operating assets (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C62" s="21" t="n">
+        <v>20.40064</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
           <t>FY2025 NCI carrying value (SAR mn)</t>
         </is>
       </c>
-      <c r="C60" s="21" t="n">
+      <c r="C63" s="21" t="n">
         <v>62.737156</v>
       </c>
     </row>
@@ -4372,7 +4403,7 @@
         </is>
       </c>
       <c r="C4" s="14">
-        <f>DCF!C41</f>
+        <f>DCF!C45</f>
         <v/>
       </c>
     </row>
@@ -4383,7 +4414,7 @@
         </is>
       </c>
       <c r="C5" s="14">
-        <f>DCF!C40</f>
+        <f>DCF!C44</f>
         <v/>
       </c>
     </row>
@@ -4394,7 +4425,7 @@
         </is>
       </c>
       <c r="C6" s="13">
-        <f>DCF!C42</f>
+        <f>DCF!C46</f>
         <v/>
       </c>
     </row>
@@ -4405,7 +4436,7 @@
         </is>
       </c>
       <c r="C7" s="14">
-        <f>DCF!C45</f>
+        <f>DCF!C49</f>
         <v/>
       </c>
     </row>
@@ -4416,7 +4447,7 @@
         </is>
       </c>
       <c r="C8" s="14">
-        <f>DCF!C46</f>
+        <f>DCF!C50</f>
         <v/>
       </c>
     </row>
@@ -4427,7 +4458,7 @@
         </is>
       </c>
       <c r="C9" s="14">
-        <f>DCF!C47</f>
+        <f>DCF!C51</f>
         <v/>
       </c>
     </row>
@@ -4437,8 +4468,8 @@
           <t>Equity attributable (31-Dec-2025)</t>
         </is>
       </c>
-      <c r="C10" s="25">
-        <f>DCF!C48</f>
+      <c r="C10" s="26">
+        <f>DCF!C52</f>
         <v/>
       </c>
     </row>
@@ -4448,8 +4479,8 @@
           <t>Value per share at anchor (SAR)</t>
         </is>
       </c>
-      <c r="C11" s="26">
-        <f>DCF!C51</f>
+      <c r="C11" s="27">
+        <f>DCF!C55</f>
         <v/>
       </c>
     </row>
@@ -4560,24 +4591,24 @@
       <c r="B6" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="C6" s="27">
-        <f>B6*(1+Assumptions!C$23)</f>
-        <v/>
-      </c>
-      <c r="D6" s="27">
-        <f>C6*(1+Assumptions!D$23)</f>
-        <v/>
-      </c>
-      <c r="E6" s="27">
-        <f>D6*(1+Assumptions!E$23)</f>
-        <v/>
-      </c>
-      <c r="F6" s="27">
-        <f>E6*(1+Assumptions!F$23)</f>
-        <v/>
-      </c>
-      <c r="G6" s="27">
-        <f>F6*(1+Assumptions!G$23)</f>
+      <c r="C6" s="28">
+        <f>B6*(1+Assumptions!C$26)</f>
+        <v/>
+      </c>
+      <c r="D6" s="28">
+        <f>C6*(1+Assumptions!D$26)</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>D6*(1+Assumptions!E$26)</f>
+        <v/>
+      </c>
+      <c r="F6" s="28">
+        <f>E6*(1+Assumptions!F$26)</f>
+        <v/>
+      </c>
+      <c r="G6" s="28">
+        <f>F6*(1+Assumptions!G$26)</f>
         <v/>
       </c>
     </row>
@@ -4587,28 +4618,28 @@
           <t>Metal content per unit</t>
         </is>
       </c>
-      <c r="B7" s="28">
-        <f>Assumptions!$C$50/100.0</f>
-        <v/>
-      </c>
-      <c r="C7" s="28">
-        <f>B7*(1+Assumptions!C$24)</f>
-        <v/>
-      </c>
-      <c r="D7" s="28">
-        <f>C7*(1+Assumptions!D$24)</f>
-        <v/>
-      </c>
-      <c r="E7" s="28">
-        <f>D7*(1+Assumptions!E$24)</f>
-        <v/>
-      </c>
-      <c r="F7" s="28">
-        <f>E7*(1+Assumptions!F$24)</f>
-        <v/>
-      </c>
-      <c r="G7" s="28">
-        <f>F7*(1+Assumptions!G$24)</f>
+      <c r="B7" s="29">
+        <f>Assumptions!$C$53/100.0</f>
+        <v/>
+      </c>
+      <c r="C7" s="29">
+        <f>B7*(1+Assumptions!C$27)</f>
+        <v/>
+      </c>
+      <c r="D7" s="29">
+        <f>C7*(1+Assumptions!D$27)</f>
+        <v/>
+      </c>
+      <c r="E7" s="29">
+        <f>D7*(1+Assumptions!E$27)</f>
+        <v/>
+      </c>
+      <c r="F7" s="29">
+        <f>E7*(1+Assumptions!F$27)</f>
+        <v/>
+      </c>
+      <c r="G7" s="29">
+        <f>F7*(1+Assumptions!G$27)</f>
         <v/>
       </c>
     </row>
@@ -4618,28 +4649,28 @@
           <t>Conversion cost per unit</t>
         </is>
       </c>
-      <c r="B8" s="28">
-        <f>Assumptions!$C$51/100.0</f>
-        <v/>
-      </c>
-      <c r="C8" s="28">
-        <f>B8*(1+Assumptions!C$25)</f>
-        <v/>
-      </c>
-      <c r="D8" s="28">
-        <f>C8*(1+Assumptions!D$25)</f>
-        <v/>
-      </c>
-      <c r="E8" s="28">
-        <f>D8*(1+Assumptions!E$25)</f>
-        <v/>
-      </c>
-      <c r="F8" s="28">
-        <f>E8*(1+Assumptions!F$25)</f>
-        <v/>
-      </c>
-      <c r="G8" s="28">
-        <f>F8*(1+Assumptions!G$25)</f>
+      <c r="B8" s="29">
+        <f>Assumptions!$C$54/100.0</f>
+        <v/>
+      </c>
+      <c r="C8" s="29">
+        <f>B8*(1+Assumptions!C$28)</f>
+        <v/>
+      </c>
+      <c r="D8" s="29">
+        <f>C8*(1+Assumptions!D$28)</f>
+        <v/>
+      </c>
+      <c r="E8" s="29">
+        <f>D8*(1+Assumptions!E$28)</f>
+        <v/>
+      </c>
+      <c r="F8" s="29">
+        <f>E8*(1+Assumptions!F$28)</f>
+        <v/>
+      </c>
+      <c r="G8" s="29">
+        <f>F8*(1+Assumptions!G$28)</f>
         <v/>
       </c>
     </row>
@@ -4649,24 +4680,24 @@
           <t>Target gross margin (anchor + glide)</t>
         </is>
       </c>
-      <c r="C9" s="29">
-        <f>Assumptions!$C$26+Assumptions!C$27</f>
-        <v/>
-      </c>
-      <c r="D9" s="29">
-        <f>Assumptions!$C$26+Assumptions!D$27</f>
-        <v/>
-      </c>
-      <c r="E9" s="29">
-        <f>Assumptions!$C$26+Assumptions!E$27</f>
-        <v/>
-      </c>
-      <c r="F9" s="29">
-        <f>Assumptions!$C$26+Assumptions!F$27</f>
-        <v/>
-      </c>
-      <c r="G9" s="29">
-        <f>Assumptions!$C$26+Assumptions!G$27</f>
+      <c r="C9" s="24">
+        <f>Assumptions!$C$29+Assumptions!C$30</f>
+        <v/>
+      </c>
+      <c r="D9" s="24">
+        <f>Assumptions!$C$29+Assumptions!D$30</f>
+        <v/>
+      </c>
+      <c r="E9" s="24">
+        <f>Assumptions!$C$29+Assumptions!E$30</f>
+        <v/>
+      </c>
+      <c r="F9" s="24">
+        <f>Assumptions!$C$29+Assumptions!F$30</f>
+        <v/>
+      </c>
+      <c r="G9" s="24">
+        <f>Assumptions!$C$29+Assumptions!G$30</f>
         <v/>
       </c>
     </row>
@@ -4676,27 +4707,27 @@
           <t>Gross profit per unit (conversion spread)</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>B13/B6</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>C9/(1-C9)*(C7+C8)</f>
         <v/>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>D9/(1-D9)*(D7+D8)</f>
         <v/>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>E9/(1-E9)*(E7+E8)</f>
         <v/>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>F9/(1-F9)*(F7+F8)</f>
         <v/>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>G9/(1-G9)*(G7+G8)</f>
         <v/>
       </c>
@@ -4830,27 +4861,27 @@
           <t>Cables gross margin (OUTPUT)</t>
         </is>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="24">
         <f>B13/B14</f>
         <v/>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="24">
         <f>C13/C14</f>
         <v/>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="24">
         <f>D13/D14</f>
         <v/>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="24">
         <f>E13/E14</f>
         <v/>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="24">
         <f>F13/F14</f>
         <v/>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="24">
         <f>G13/G14</f>
         <v/>
       </c>
@@ -4876,27 +4907,27 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="C17" s="30">
-        <f>B17*(1+Assumptions!C$29)</f>
+        <f>B17*(1+Assumptions!C$32)</f>
         <v/>
       </c>
       <c r="D17" s="30">
-        <f>C17*(1+Assumptions!D$29)</f>
+        <f>C17*(1+Assumptions!D$32)</f>
         <v/>
       </c>
       <c r="E17" s="30">
-        <f>D17*(1+Assumptions!E$29)</f>
+        <f>D17*(1+Assumptions!E$32)</f>
         <v/>
       </c>
       <c r="F17" s="30">
-        <f>E17*(1+Assumptions!F$29)</f>
+        <f>E17*(1+Assumptions!F$32)</f>
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>F17*(1+Assumptions!G$29)</f>
+        <f>F17*(1+Assumptions!G$32)</f>
         <v/>
       </c>
     </row>
@@ -4906,28 +4937,28 @@
           <t>HV segment margin</t>
         </is>
       </c>
-      <c r="B18" s="29">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="C18" s="29">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="D18" s="29">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="E18" s="29">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="F18" s="29">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="G18" s="29">
-        <f>Assumptions!$C$30</f>
+      <c r="B18" s="24">
+        <f>Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="C18" s="24">
+        <f>Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="D18" s="24">
+        <f>Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="F18" s="24">
+        <f>Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="G18" s="24">
+        <f>Assumptions!$C$33</f>
         <v/>
       </c>
     </row>
@@ -4983,27 +5014,27 @@
         </is>
       </c>
       <c r="B21" s="30">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="C21" s="30">
-        <f>B21*(1+Assumptions!C$31)</f>
+        <f>B21*(1+Assumptions!C$34)</f>
         <v/>
       </c>
       <c r="D21" s="30">
-        <f>C21*(1+Assumptions!D$31)</f>
+        <f>C21*(1+Assumptions!D$34)</f>
         <v/>
       </c>
       <c r="E21" s="30">
-        <f>D21*(1+Assumptions!E$31)</f>
+        <f>D21*(1+Assumptions!E$34)</f>
         <v/>
       </c>
       <c r="F21" s="30">
-        <f>E21*(1+Assumptions!F$31)</f>
+        <f>E21*(1+Assumptions!F$34)</f>
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>F21*(1+Assumptions!G$31)</f>
+        <f>F21*(1+Assumptions!G$34)</f>
         <v/>
       </c>
     </row>
@@ -5013,28 +5044,28 @@
           <t>Other segment margin</t>
         </is>
       </c>
-      <c r="B22" s="29">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="C22" s="29">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="D22" s="29">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="E22" s="29">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="F22" s="29">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="G22" s="29">
-        <f>Assumptions!$C$32</f>
+      <c r="B22" s="24">
+        <f>Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="C22" s="24">
+        <f>Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="D22" s="24">
+        <f>Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="F22" s="24">
+        <f>Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="G22" s="24">
+        <f>Assumptions!$C$35</f>
         <v/>
       </c>
     </row>
@@ -5182,27 +5213,27 @@
           <t>Gross margin (OUTPUT = group gross profit / group revenue)</t>
         </is>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="24">
         <f>B26/B25</f>
         <v/>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="24">
         <f>C26/C25</f>
         <v/>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="24">
         <f>D26/D25</f>
         <v/>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="24">
         <f>E26/E25</f>
         <v/>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="24">
         <f>F26/F25</f>
         <v/>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="24">
         <f>G26/G25</f>
         <v/>
       </c>
@@ -5214,23 +5245,23 @@
         </is>
       </c>
       <c r="C29" s="30">
-        <f>Assumptions!C$34*C25</f>
+        <f>Assumptions!C$37*C25</f>
         <v/>
       </c>
       <c r="D29" s="30">
-        <f>Assumptions!D$34*D25</f>
+        <f>Assumptions!D$37*D25</f>
         <v/>
       </c>
       <c r="E29" s="30">
-        <f>Assumptions!E$34*E25</f>
+        <f>Assumptions!E$37*E25</f>
         <v/>
       </c>
       <c r="F29" s="30">
-        <f>Assumptions!F$34*F25</f>
+        <f>Assumptions!F$37*F25</f>
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>Assumptions!G$34*G25</f>
+        <f>Assumptions!G$37*G25</f>
         <v/>
       </c>
     </row>
@@ -5241,23 +5272,23 @@
         </is>
       </c>
       <c r="C30" s="30">
-        <f>Assumptions!$C$35*C25</f>
+        <f>Assumptions!$C$38*C25</f>
         <v/>
       </c>
       <c r="D30" s="30">
-        <f>Assumptions!$C$35*D25</f>
+        <f>Assumptions!$C$38*D25</f>
         <v/>
       </c>
       <c r="E30" s="30">
-        <f>Assumptions!$C$35*E25</f>
+        <f>Assumptions!$C$38*E25</f>
         <v/>
       </c>
       <c r="F30" s="30">
-        <f>Assumptions!$C$35*F25</f>
+        <f>Assumptions!$C$38*F25</f>
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>Assumptions!$C$35*G25</f>
+        <f>Assumptions!$C$38*G25</f>
         <v/>
       </c>
     </row>
@@ -5321,23 +5352,23 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="24">
         <f>C32/C25</f>
         <v/>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="24">
         <f>D32/D25</f>
         <v/>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="24">
         <f>E32/E25</f>
         <v/>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="24">
         <f>F32/F25</f>
         <v/>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="24">
         <f>G32/G25</f>
         <v/>
       </c>
@@ -5418,7 +5449,7 @@
         </is>
       </c>
       <c r="C6" s="31">
-        <f>Assumptions!$C$43</f>
+        <f>Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -5440,7 +5471,7 @@
         </is>
       </c>
       <c r="C8" s="32">
-        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$58+Assumptions!$C$59-Assumptions!$C$60)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$48</f>
+        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$61+Assumptions!$C$62-Assumptions!$C$63)/Assumptions!$C$6)*DCF!$C$54-Assumptions!$C$51</f>
         <v/>
       </c>
     </row>
@@ -5451,11 +5482,11 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$58+Assumptions!$C$59-Assumptions!$C$60)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$48</f>
+        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$61+Assumptions!$C$62-Assumptions!$C$63)/Assumptions!$C$6)*DCF!$C$54-Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="D9" s="18">
-        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$58+Assumptions!$C$59-Assumptions!$C$60)/Assumptions!$C$6)*DCF!$C$50-Assumptions!$C$48</f>
+        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$61+Assumptions!$C$62-Assumptions!$C$63)/Assumptions!$C$6)*DCF!$C$54-Assumptions!$C$51</f>
         <v/>
       </c>
     </row>
@@ -5512,7 +5543,7 @@
         </is>
       </c>
       <c r="C15" s="18">
-        <f>((C12*C13-Assumptions!$C$35*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$41)/Assumptions!$C$6</f>
+        <f>((C12*C13-Assumptions!$C$38*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5523,7 +5554,7 @@
         </is>
       </c>
       <c r="C16" s="32">
-        <f>(Assumptions!$C$44*C15)*DCF!$C$50-Assumptions!$C$48</f>
+        <f>(Assumptions!$C$47*C15)*DCF!$C$54-Assumptions!$C$51</f>
         <v/>
       </c>
     </row>
@@ -5534,11 +5565,11 @@
         </is>
       </c>
       <c r="C17" s="18">
-        <f>(10*C15)*DCF!$C$50-Assumptions!$C$48</f>
+        <f>(10*C15)*DCF!$C$54-Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="D17" s="18">
-        <f>(16*C15)*DCF!$C$50-Assumptions!$C$48</f>
+        <f>(16*C15)*DCF!$C$54-Assumptions!$C$51</f>
         <v/>
       </c>
     </row>
@@ -5562,7 +5593,7 @@
         </is>
       </c>
       <c r="C20" s="18">
-        <f>Assumptions!$C$57/Assumptions!$C$6</f>
+        <f>Assumptions!$C$60/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5573,7 +5604,7 @@
         </is>
       </c>
       <c r="C21" s="34">
-        <f>(Assumptions!$C$45-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)</f>
+        <f>(Assumptions!$C$48-Assumptions!$C$23)/(DCF!C11-Assumptions!$C$23)</f>
         <v/>
       </c>
     </row>
@@ -5584,7 +5615,7 @@
         </is>
       </c>
       <c r="C22" s="32">
-        <f>(C21*C20)*DCF!$C$50-Assumptions!$C$48</f>
+        <f>(C21*C20)*DCF!$C$54-Assumptions!$C$51</f>
         <v/>
       </c>
     </row>
@@ -5595,11 +5626,11 @@
         </is>
       </c>
       <c r="C23" s="18">
-        <f>(((Assumptions!$C$45)-0.05-Assumptions!$C$21)/(DCF!C6-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$48</f>
+        <f>(((Assumptions!$C$48)-0.05-Assumptions!$C$23)/(DCF!C6-Assumptions!$C$23)*C20)*DCF!$C$54-Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="D23" s="18">
-        <f>(((Assumptions!$C$45)+0.03-Assumptions!$C$21)/(DCF!C11-Assumptions!$C$21)*C20)*DCF!$C$50-Assumptions!$C$48</f>
+        <f>(((Assumptions!$C$48)+0.03-Assumptions!$C$23)/(DCF!C11-Assumptions!$C$23)*C20)*DCF!$C$54-Assumptions!$C$51</f>
         <v/>
       </c>
     </row>
@@ -5616,7 +5647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5670,7 +5701,7 @@
           <t>Normalised risk-free rate rf*</t>
         </is>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="24">
         <f>Assumptions!$C$9-Assumptions!$C$10</f>
         <v/>
       </c>
@@ -5681,7 +5712,7 @@
           <t>Cost of equity Ke</t>
         </is>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="24">
         <f>C5+Assumptions!$C$12*Assumptions!$C$11</f>
         <v/>
       </c>
@@ -5692,7 +5723,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="24">
         <f>Assumptions!$C$13*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -5714,7 +5745,7 @@
           <t>Net-debt weight</t>
         </is>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="24">
         <f>Assumptions!$C$7/(Assumptions!$C$7+C8)</f>
         <v/>
       </c>
@@ -5736,7 +5767,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="24">
         <f>Assumptions!$C$16+Assumptions!$C$18*Assumptions!$C$17</f>
         <v/>
       </c>
@@ -5747,7 +5778,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="24">
         <f>Assumptions!$C$19*(1-Assumptions!$C$14)</f>
         <v/>
       </c>
@@ -5817,23 +5848,23 @@
         </is>
       </c>
       <c r="C17" s="36">
-        <f>(Assumptions!C$38-Assumptions!C$38)/(Assumptions!C$38-Assumptions!G$38)</f>
+        <f>(Assumptions!C$41-Assumptions!C$41)/(Assumptions!C$41-Assumptions!G$41)</f>
         <v/>
       </c>
       <c r="D17" s="36">
-        <f>(Assumptions!C$38-Assumptions!D$38)/(Assumptions!C$38-Assumptions!G$38)</f>
+        <f>(Assumptions!C$41-Assumptions!D$41)/(Assumptions!C$41-Assumptions!G$41)</f>
         <v/>
       </c>
       <c r="E17" s="36">
-        <f>(Assumptions!C$38-Assumptions!E$38)/(Assumptions!C$38-Assumptions!G$38)</f>
+        <f>(Assumptions!C$41-Assumptions!E$41)/(Assumptions!C$41-Assumptions!G$41)</f>
         <v/>
       </c>
       <c r="F17" s="36">
-        <f>(Assumptions!C$38-Assumptions!F$38)/(Assumptions!C$38-Assumptions!G$38)</f>
+        <f>(Assumptions!C$41-Assumptions!F$41)/(Assumptions!C$41-Assumptions!G$41)</f>
         <v/>
       </c>
       <c r="G17" s="36">
-        <f>(Assumptions!C$38-Assumptions!G$38)/(Assumptions!C$38-Assumptions!G$38)</f>
+        <f>(Assumptions!C$41-Assumptions!G$41)/(Assumptions!C$41-Assumptions!G$41)</f>
         <v/>
       </c>
     </row>
@@ -5843,23 +5874,23 @@
           <t>Forward WACC</t>
         </is>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="24">
         <f>C10-(C10-C13)*C17</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="24">
         <f>C10-(C10-C13)*D17</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="24">
         <f>C10-(C10-C13)*E17</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="24">
         <f>C10-(C10-C13)*F17</f>
         <v/>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="24">
         <f>C10-(C10-C13)*G17</f>
         <v/>
       </c>
@@ -6006,23 +6037,23 @@
         </is>
       </c>
       <c r="C24" s="30">
-        <f>Assumptions!C$36*C23</f>
+        <f>Assumptions!C$39*C23</f>
         <v/>
       </c>
       <c r="D24" s="30">
-        <f>Assumptions!D$36*D23</f>
+        <f>Assumptions!D$39*D23</f>
         <v/>
       </c>
       <c r="E24" s="30">
-        <f>Assumptions!E$36*E23</f>
+        <f>Assumptions!E$39*E23</f>
         <v/>
       </c>
       <c r="F24" s="30">
-        <f>Assumptions!F$36*F23</f>
+        <f>Assumptions!F$39*F23</f>
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>Assumptions!G$36*G23</f>
+        <f>Assumptions!G$39*G23</f>
         <v/>
       </c>
     </row>
@@ -6033,23 +6064,23 @@
         </is>
       </c>
       <c r="C25" s="30">
-        <f>Assumptions!$C$37*C23</f>
+        <f>Assumptions!$C$40*C23</f>
         <v/>
       </c>
       <c r="D25" s="30">
-        <f>Assumptions!$C$37*D23</f>
+        <f>Assumptions!$C$40*D23</f>
         <v/>
       </c>
       <c r="E25" s="30">
-        <f>Assumptions!$C$37*E23</f>
+        <f>Assumptions!$C$40*E23</f>
         <v/>
       </c>
       <c r="F25" s="30">
-        <f>Assumptions!$C$37*F23</f>
+        <f>Assumptions!$C$40*F23</f>
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>Assumptions!$C$37*G23</f>
+        <f>Assumptions!$C$40*G23</f>
         <v/>
       </c>
     </row>
@@ -6060,7 +6091,7 @@
         </is>
       </c>
       <c r="C26" s="30">
-        <f>C25-Assumptions!$C$54</f>
+        <f>C25-Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="D26" s="30">
@@ -6155,7 +6186,7 @@
         </is>
       </c>
       <c r="C31" s="30">
-        <f>Assumptions!$C$55+C24-C22</f>
+        <f>Assumptions!$C$58+C24-C22</f>
         <v/>
       </c>
       <c r="D31" s="30">
@@ -6208,23 +6239,23 @@
           <t>ROIC = NOPAT / invested capital</t>
         </is>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="24">
         <f>C21/C32</f>
         <v/>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="24">
         <f>D21/D32</f>
         <v/>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="24">
         <f>E21/E32</f>
         <v/>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="24">
         <f>F21/F32</f>
         <v/>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="24">
         <f>G21/G32</f>
         <v/>
       </c>
@@ -6243,225 +6274,269 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Terminal ROIC</t>
-        </is>
-      </c>
-      <c r="C36" s="29">
-        <f>G21*(1+Assumptions!$C$21)/G32</f>
+          <t>Terminal ROIC (reported, not used to build the terminal)</t>
+        </is>
+      </c>
+      <c r="C36" s="24">
+        <f>G21*(1+Assumptions!$C$23)/G32</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Terminal reinvestment rate = g / ROIC</t>
-        </is>
-      </c>
-      <c r="C37" s="29">
-        <f>Assumptions!$C$21/C36</f>
+          <t>Terminal NOPAT (next year)</t>
+        </is>
+      </c>
+      <c r="C37" s="30">
+        <f>G21*(1+Assumptions!$C$23)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Terminal NOPAT (next year)</t>
+          <t>Plus book depreciation and amortisation inside that profit</t>
         </is>
       </c>
       <c r="C38" s="30">
-        <f>G21*(1+Assumptions!$C$21)</f>
+        <f>G22*(1+Assumptions!$C$23)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Terminal value</t>
+          <t>Less capital maintenance at current cost</t>
         </is>
       </c>
       <c r="C39" s="30">
-        <f>C38*(1-C37)/(C13-Assumptions!$C$21)</f>
+        <f>-C38*(1+Assumptions!$C$21)^(Assumptions!$C$24/2)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>PV of terminal value</t>
+          <t>Less growth capital, for REAL growth only</t>
         </is>
       </c>
       <c r="C40" s="30">
-        <f>C39*G19</f>
+        <f>-Assumptions!$C$22*(G32)*(1+Assumptions!$C$23)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>Enterprise value</t>
-        </is>
-      </c>
-      <c r="C41" s="37">
-        <f>C35+C40</f>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Less inflation on working capital</t>
+        </is>
+      </c>
+      <c r="C41" s="30">
+        <f>-Assumptions!$C$21*G25*(1+Assumptions!$C$23)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
         <is>
+          <t>Terminal free cash flow</t>
+        </is>
+      </c>
+      <c r="C42" s="37">
+        <f>SUM(C37:C41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Terminal value</t>
+        </is>
+      </c>
+      <c r="C43" s="30">
+        <f>C42*(1+Assumptions!$C$23)/(C13-Assumptions!$C$23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="C44" s="30">
+        <f>C43*G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="C45" s="37">
+        <f>C35+C44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
           <t>Terminal value as % of EV</t>
         </is>
       </c>
-      <c r="C42" s="38">
-        <f>C40/C41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="C46" s="38">
+        <f>C44/C45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Enterprise value to equity</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
-      <c r="H44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Less: net financial debt</t>
-        </is>
-      </c>
-      <c r="C45" s="30">
-        <f>-Assumptions!$C$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Add: associates + non-operating assets</t>
-        </is>
-      </c>
-      <c r="C46" s="30">
-        <f>Assumptions!$C$58+Assumptions!$C$59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Less: non-controlling interests</t>
-        </is>
-      </c>
-      <c r="C47" s="30">
-        <f>-Assumptions!$C$60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t>Equity attributable (31-Dec-2025)</t>
-        </is>
-      </c>
-      <c r="C48" s="37">
-        <f>C41+C45+C46+C47</f>
-        <v/>
-      </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Value per share (31-Dec-2025)</t>
-        </is>
-      </c>
-      <c r="C49" s="18">
-        <f>C48/Assumptions!$C$6</f>
+          <t>Less: net financial debt</t>
+        </is>
+      </c>
+      <c r="C49" s="30">
+        <f>-Assumptions!$C$7</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
+          <t>Add: associates + non-operating assets</t>
+        </is>
+      </c>
+      <c r="C50" s="30">
+        <f>Assumptions!$C$61+Assumptions!$C$62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Less: non-controlling interests</t>
+        </is>
+      </c>
+      <c r="C51" s="30">
+        <f>-Assumptions!$C$63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>Equity attributable (31-Dec-2025)</t>
+        </is>
+      </c>
+      <c r="C52" s="37">
+        <f>C45+C49+C50+C51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Value per share (31-Dec-2025)</t>
+        </is>
+      </c>
+      <c r="C53" s="18">
+        <f>C52/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
           <t>Anchor accretion factor</t>
         </is>
       </c>
-      <c r="C50" s="36">
-        <f>(1+C6)^(Assumptions!$C$47/365)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="C54" s="36">
+        <f>(1+C6)^(Assumptions!$C$50/365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>Value per share at anchor (18-Aug-2026)</t>
         </is>
       </c>
-      <c r="C51" s="32">
-        <f>C49*C50-Assumptions!$C$48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>vs spot</t>
-        </is>
-      </c>
-      <c r="C52" s="8">
-        <f>C51/Assumptions!$C$5-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>DCF scenarios (whole-model re-runs — pasted)</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="10" t="n"/>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="10" t="n"/>
-      <c r="G54" s="10" t="n"/>
-      <c r="H54" s="10" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="n">
-        <v>80.84906676286525</v>
+      <c r="C55" s="32">
+        <f>C53*C54-Assumptions!$C$51</f>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
+          <t>vs spot</t>
+        </is>
+      </c>
+      <c r="C56" s="8">
+        <f>C55/Assumptions!$C$5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>DCF scenarios (whole-model re-runs — pasted)</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="n">
+        <v>81.9880979359901</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
           <t>Base (= value per share at anchor)</t>
         </is>
       </c>
-      <c r="C56" s="7">
-        <f>C51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="C60" s="7">
+        <f>C55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="C57" s="19" t="n">
-        <v>197.7603327814774</v>
+      <c r="C61" s="19" t="n">
+        <v>202.3740402967112</v>
       </c>
     </row>
   </sheetData>
@@ -6641,35 +6716,35 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="24">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="24">
         <f>D6/D5</f>
         <v/>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="24">
         <f>E6/E5</f>
         <v/>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="24">
         <f>F6/F5</f>
         <v/>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="24">
         <f>G6/G5</f>
         <v/>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="24">
         <f>H6/H5</f>
         <v/>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="24">
         <f>I6/I5</f>
         <v/>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="24">
         <f>J6/J5</f>
         <v/>
       </c>

--- a/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
+++ b/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
@@ -1013,23 +1013,23 @@
         <v>621.216217</v>
       </c>
       <c r="F10" s="14">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
     </row>
@@ -1207,23 +1207,23 @@
         </is>
       </c>
       <c r="C18" s="30">
-        <f>Assumptions!$C$59-C17</f>
+        <f>Assumptions!$C$60-C17</f>
         <v/>
       </c>
       <c r="D18" s="30">
-        <f>Assumptions!$C$59-D17</f>
+        <f>Assumptions!$C$60-D17</f>
         <v/>
       </c>
       <c r="E18" s="30">
-        <f>Assumptions!$C$59-E17</f>
+        <f>Assumptions!$C$60-E17</f>
         <v/>
       </c>
       <c r="F18" s="30">
-        <f>Assumptions!$C$59-F17</f>
+        <f>Assumptions!$C$60-F17</f>
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>Assumptions!$C$59-G17</f>
+        <f>Assumptions!$C$60-G17</f>
         <v/>
       </c>
     </row>
@@ -1234,23 +1234,23 @@
         </is>
       </c>
       <c r="C19" s="30">
-        <f>Assumptions!C$41*Assumptions!$C$59-Assumptions!$C$43*MAX(C18,0)</f>
+        <f>Assumptions!C$42*Assumptions!$C$60-Assumptions!$C$44*MAX(C18,0)</f>
         <v/>
       </c>
       <c r="D19" s="30">
-        <f>Assumptions!D$41*Assumptions!$C$59-Assumptions!$C$43*MAX(D18,0)</f>
+        <f>Assumptions!D$42*Assumptions!$C$60-Assumptions!$C$44*MAX(D18,0)</f>
         <v/>
       </c>
       <c r="E19" s="30">
-        <f>Assumptions!E$41*Assumptions!$C$59-Assumptions!$C$43*MAX(E18,0)</f>
+        <f>Assumptions!E$42*Assumptions!$C$60-Assumptions!$C$44*MAX(E18,0)</f>
         <v/>
       </c>
       <c r="F19" s="30">
-        <f>Assumptions!F$41*Assumptions!$C$59-Assumptions!$C$43*MAX(F18,0)</f>
+        <f>Assumptions!F$42*Assumptions!$C$60-Assumptions!$C$44*MAX(F18,0)</f>
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>Assumptions!G$41*Assumptions!$C$59-Assumptions!$C$43*MAX(G18,0)</f>
+        <f>Assumptions!G$42*Assumptions!$C$60-Assumptions!$C$44*MAX(G18,0)</f>
         <v/>
       </c>
     </row>
@@ -1315,23 +1315,23 @@
         </is>
       </c>
       <c r="C22" s="30">
-        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)</f>
+        <f>C21*(1-Assumptions!$C$14)*(1-Assumptions!$C$45)</f>
         <v/>
       </c>
       <c r="D22" s="30">
-        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)</f>
+        <f>D21*(1-Assumptions!$C$14)*(1-Assumptions!$C$45)</f>
         <v/>
       </c>
       <c r="E22" s="30">
-        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)</f>
+        <f>E21*(1-Assumptions!$C$14)*(1-Assumptions!$C$45)</f>
         <v/>
       </c>
       <c r="F22" s="30">
-        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)</f>
+        <f>F21*(1-Assumptions!$C$14)*(1-Assumptions!$C$45)</f>
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)</f>
+        <f>G21*(1-Assumptions!$C$14)*(1-Assumptions!$C$45)</f>
         <v/>
       </c>
     </row>
@@ -1342,23 +1342,23 @@
         </is>
       </c>
       <c r="C23" s="30">
-        <f>Assumptions!$C$42*C22</f>
+        <f>Assumptions!$C$43*C22</f>
         <v/>
       </c>
       <c r="D23" s="30">
-        <f>Assumptions!$C$42*D22</f>
+        <f>Assumptions!$C$43*D22</f>
         <v/>
       </c>
       <c r="E23" s="30">
-        <f>Assumptions!$C$42*E22</f>
+        <f>Assumptions!$C$43*E22</f>
         <v/>
       </c>
       <c r="F23" s="30">
-        <f>Assumptions!$C$42*F22</f>
+        <f>Assumptions!$C$43*F22</f>
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>Assumptions!$C$42*G22</f>
+        <f>Assumptions!$C$43*G22</f>
         <v/>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="C25" s="30">
-        <f>Assumptions!$C$60+C22-C23</f>
+        <f>Assumptions!$C$61+C22-C23</f>
         <v/>
       </c>
       <c r="D25" s="30">
@@ -2187,16 +2187,16 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>142.5329983174736</v>
+        <v>141.181821159505</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>165.8900261351979</v>
+        <v>164.2048778752795</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>202.3566722281835</v>
+        <v>200.1453649939247</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>267.7660755948026</v>
+        <v>264.6042053864718</v>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>121.1462246885317</v>
+        <v>120.0294758549692</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>136.4581994122694</v>
+        <v>135.1117534869411</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>158.3715319493057</v>
+        <v>156.6926008985187</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>192.5675384208111</v>
+        <v>190.36479698198</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>253.8803374388925</v>
+        <v>250.731286493416</v>
       </c>
     </row>
     <row r="8">
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>105.4757919254231</v>
+        <v>104.5301516560279</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>116.1038048717173</v>
+        <v>114.9907901554711</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>130.4248509123573</v>
+        <v>129.0831601218276</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>150.9067031915588</v>
+        <v>149.234010829074</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>182.8513142532758</v>
+        <v>180.6571560010763</v>
       </c>
     </row>
     <row r="9">
@@ -2255,19 +2255,19 @@
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>93.49993194791615</v>
+        <v>92.68449495813583</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>101.1874536036779</v>
+        <v>100.2448283061584</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>111.0946812493539</v>
+        <v>109.9854242884174</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>124.4332246638776</v>
+        <v>123.0963109284656</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>143.4957942849643</v>
+        <v>141.829359842241</v>
       </c>
     </row>
     <row r="10">
@@ -2277,19 +2277,19 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>84.04969368984855</v>
+        <v>83.33651363068722</v>
       </c>
       <c r="C10" s="19" t="n">
-        <v>89.78587482784923</v>
+        <v>88.97291280931691</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>96.92651079279665</v>
+        <v>95.98692365699924</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>106.1191088346631</v>
+        <v>105.0136315470419</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>118.483561402772</v>
+        <v>117.1514447432494</v>
       </c>
     </row>
     <row r="12">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B13" s="19" t="n">
-        <v>136.7426042395026</v>
+        <v>135.3359987826802</v>
       </c>
     </row>
     <row r="14">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="B14" s="19" t="n">
-        <v>133.7495488251624</v>
+        <v>132.373703149165</v>
       </c>
     </row>
     <row r="15">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>130.4248509123573</v>
+        <v>129.0831601218276</v>
       </c>
     </row>
     <row r="16">
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="B16" s="19" t="n">
-        <v>128.0110086639152</v>
+        <v>126.6941064789215</v>
       </c>
     </row>
     <row r="17">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>125.259860044495</v>
+        <v>123.9712008691094</v>
       </c>
     </row>
     <row r="19">
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="B20" s="19" t="n">
-        <v>142.6983003741912</v>
+        <v>141.5174478670757</v>
       </c>
     </row>
     <row r="21">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="B21" s="19" t="n">
-        <v>136.5505807795981</v>
+        <v>135.2893091307755</v>
       </c>
     </row>
     <row r="22">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="B22" s="19" t="n">
-        <v>130.4248509123573</v>
+        <v>129.0831601218276</v>
       </c>
     </row>
     <row r="23">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>124.3186591109369</v>
+        <v>122.8965491787002</v>
       </c>
     </row>
     <row r="24">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>118.2299808722273</v>
+        <v>116.7274517982834</v>
       </c>
     </row>
     <row r="26">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="B27" s="19" t="n">
-        <v>110.4145045547937</v>
+        <v>109.0919904282692</v>
       </c>
     </row>
     <row r="28">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B28" s="19" t="n">
-        <v>118.2844198497204</v>
+        <v>116.9543636973258</v>
       </c>
     </row>
     <row r="29">
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="B29" s="19" t="n">
-        <v>130.4248509123573</v>
+        <v>129.0831601218276</v>
       </c>
     </row>
     <row r="30">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="B30" s="19" t="n">
-        <v>134.3041167701747</v>
+        <v>132.9587083256414</v>
       </c>
     </row>
     <row r="31">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>142.457235668817</v>
+        <v>141.1040137589644</v>
       </c>
     </row>
     <row r="33">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="B34" s="19" t="n">
-        <v>119.6053719904985</v>
+        <v>118.3943412479728</v>
       </c>
     </row>
     <row r="35">
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>125.0198940084373</v>
+        <v>123.7435332419096</v>
       </c>
     </row>
     <row r="36">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="B36" s="19" t="n">
-        <v>130.4248509123573</v>
+        <v>129.0831601218276</v>
       </c>
     </row>
     <row r="37">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="B37" s="19" t="n">
-        <v>135.8209510803724</v>
+        <v>134.4139302658407</v>
       </c>
     </row>
     <row r="38">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="B38" s="19" t="n">
-        <v>141.2088186686372</v>
+        <v>139.7364678301035</v>
       </c>
     </row>
     <row r="40">
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="B41" s="19" t="n">
-        <v>136.2160155850796</v>
+        <v>134.87432479455</v>
       </c>
     </row>
     <row r="42">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B42" s="19" t="n">
-        <v>133.3204332487185</v>
+        <v>131.9787424581888</v>
       </c>
     </row>
     <row r="43">
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="B43" s="19" t="n">
-        <v>130.4248509123573</v>
+        <v>129.0831601218276</v>
       </c>
     </row>
     <row r="44">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="B44" s="19" t="n">
-        <v>127.5292685759961</v>
+        <v>126.1875777854665</v>
       </c>
     </row>
     <row r="45">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>124.633686239635</v>
+        <v>123.2919954491053</v>
       </c>
     </row>
   </sheetData>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>Assumptions!$C$60/Assumptions!$C$6</f>
+        <f>Assumptions!$C$61/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C6" s="18">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="C18" s="19" t="n">
-        <v>142.457235668817</v>
+        <v>141.1040137589644</v>
       </c>
     </row>
     <row r="19">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="C19" s="19" t="n">
-        <v>118.2844198497204</v>
+        <v>116.9543636973258</v>
       </c>
     </row>
   </sheetData>
@@ -3554,7 +3554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3822,536 +3822,546 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Average age of the base, years (measured from the notes)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>21.9518</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Forecast drivers — Cables &amp; wires leg (metal converter)</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="10" t="n"/>
-      <c r="J25" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Cable volume index growth</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D26" s="22" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E26" s="22" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="F26" s="22" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="G26" s="22" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="10" t="n"/>
+      <c r="J26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Metal content price growth</t>
+          <t>Cable volume index growth</t>
         </is>
       </c>
       <c r="C27" s="22" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D27" s="22" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>0.01</v>
+        <v>0.065</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>0.01</v>
+        <v>0.055</v>
       </c>
       <c r="G27" s="22" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Conversion cost inflation</t>
+          <t>Metal content price growth</t>
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="D28" s="22" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G28" s="22" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Sustained gross margin (H1-2026 anchor)</t>
+          <t>Conversion cost inflation</t>
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>0.1526</v>
+        <v>0.03</v>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F29" s="22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G29" s="22" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
+          <t>Sustained gross margin (H1-2026 anchor)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="n">
+        <v>0.1526</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>Gross-margin glide (added to anchor)</t>
         </is>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D31" s="23" t="n">
         <v>0.001</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E31" s="23" t="n">
         <v>0.001</v>
       </c>
-      <c r="F30" s="23" t="n">
+      <c r="F31" s="23" t="n">
         <v>0.0015</v>
       </c>
-      <c r="G30" s="23" t="n">
+      <c r="G31" s="23" t="n">
         <v>0.0015</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Forecast drivers — HV turnkey &amp; Other legs</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>HV turnkey revenue growth</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D32" s="22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E32" s="22" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F32" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G32" s="22" t="n">
-        <v>0.08</v>
-      </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>HV turnkey segment margin</t>
+          <t>HV turnkey revenue growth</t>
         </is>
       </c>
       <c r="C33" s="22" t="n">
-        <v>0.08378233242821985</v>
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E33" s="22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F33" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G33" s="22" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Other segment revenue growth</t>
+          <t>HV turnkey segment margin</t>
         </is>
       </c>
       <c r="C34" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D34" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E34" s="22" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F34" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G34" s="22" t="n">
-        <v>0.06</v>
+        <v>0.08378233242821985</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
+          <t>Other segment revenue growth</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E35" s="22" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F35" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G35" s="22" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
           <t>Other segment margin</t>
         </is>
       </c>
-      <c r="C35" s="22" t="n">
+      <c r="C36" s="22" t="n">
         <v>0.5786820313464731</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Forecast drivers — group</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
-      <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="n"/>
-      <c r="J36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Operating expenses / revenue</t>
-        </is>
-      </c>
-      <c r="C37" s="22" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D37" s="22" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="E37" s="22" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="F37" s="22" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="G37" s="22" t="n">
-        <v>0.042</v>
-      </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation / revenue</t>
+          <t>Operating expenses / revenue</t>
         </is>
       </c>
       <c r="C38" s="22" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.043</v>
+      </c>
+      <c r="D38" s="22" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="E38" s="22" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="F38" s="22" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>0.042</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure / revenue</t>
+          <t>Depreciation and amortisation / revenue</t>
         </is>
       </c>
       <c r="C39" s="22" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="D39" s="22" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="E39" s="22" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="F39" s="22" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="G39" s="22" t="n">
-        <v>0.016</v>
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Net working capital / revenue</t>
+          <t>Capital expenditure / revenue</t>
         </is>
       </c>
       <c r="C40" s="22" t="n">
-        <v>0.28</v>
+        <v>0.019</v>
+      </c>
+      <c r="D40" s="22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E40" s="22" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F40" s="22" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G40" s="22" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Cost-of-debt path</t>
+          <t>Net working capital / revenue</t>
         </is>
       </c>
       <c r="C41" s="22" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="D41" s="22" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="E41" s="22" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="F41" s="22" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="G41" s="22" t="n">
-        <v>0.055</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Forecast dividend payout ratio</t>
+          <t>Cost-of-debt path</t>
         </is>
       </c>
       <c r="C42" s="22" t="n">
-        <v>0.55</v>
+        <v>0.059</v>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E42" s="22" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="F42" s="22" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="G42" s="22" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Yield on surplus cash</t>
+          <t>Forecast dividend payout ratio</t>
         </is>
       </c>
       <c r="C43" s="22" t="n">
-        <v>0.04</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
+          <t>Yield on surplus cash</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
           <t>NCI share of forecast profit</t>
         </is>
       </c>
-      <c r="C44" s="22" t="n">
+      <c r="C45" s="22" t="n">
         <v>0.004060669885351275</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Lens inputs</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="10" t="n"/>
-      <c r="G45" s="10" t="n"/>
-      <c r="H45" s="10" t="n"/>
-      <c r="I45" s="10" t="n"/>
-      <c r="J45" s="10" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
+          <t>Justified EV/EBITDA</t>
         </is>
       </c>
       <c r="C47" s="25" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C48" s="25" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C48" s="22" t="n">
+      <c r="C49" s="22" t="n">
         <v>0.28</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>Anchor roll</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n"/>
-      <c r="J49" s="10" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Days to the anchor</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="n">
-        <v>230</v>
-      </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
+          <t>Days to the anchor</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>FY2025 dividend per share paid in window</t>
         </is>
       </c>
-      <c r="C51" s="19" t="n">
+      <c r="C52" s="19" t="n">
         <v>2.25</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>FY2025 disclosed base (audited)</t>
         </is>
       </c>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
-      <c r="J52" s="10" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 cables metal content (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C53" s="21" t="n">
-        <v>8486.925676999999</v>
-      </c>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>FY2025 cables conversion cost (SAR mn)</t>
+          <t>FY2025 cables metal content (SAR mn)</t>
         </is>
       </c>
       <c r="C54" s="21" t="n">
-        <v>229.8024540000006</v>
+        <v>8486.925676999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>FY2025 HV turnkey revenue (SAR mn)</t>
+          <t>FY2025 cables conversion cost (SAR mn)</t>
         </is>
       </c>
       <c r="C55" s="21" t="n">
-        <v>230.839181</v>
+        <v>229.8024540000006</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>FY2025 Other segment revenue (SAR mn)</t>
+          <t>FY2025 HV turnkey revenue (SAR mn)</t>
         </is>
       </c>
       <c r="C56" s="21" t="n">
-        <v>28.594413</v>
+        <v>230.839181</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>FY2025 net working capital (SAR mn)</t>
+          <t>FY2025 Other segment revenue (SAR mn)</t>
         </is>
       </c>
       <c r="C57" s="21" t="n">
-        <v>2933.258925</v>
+        <v>28.594413</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>FY2025 PP&amp;E (SAR mn)</t>
+          <t>FY2025 net working capital (SAR mn)</t>
         </is>
       </c>
       <c r="C58" s="21" t="n">
-        <v>1491.86312</v>
+        <v>2933.258925</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
+          <t>FY2025 PP&amp;E (SAR mn)</t>
         </is>
       </c>
       <c r="C59" s="21" t="n">
-        <v>621.216217</v>
+        <v>1491.86312</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>FY2025 equity attributable (SAR mn)</t>
+          <t>FY2025 gross borrowings incl. leases (SAR mn)</t>
         </is>
       </c>
       <c r="C60" s="21" t="n">
-        <v>3246.136935</v>
+        <v>621.216217</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>FY2025 associates carrying value (SAR mn)</t>
+          <t>FY2025 equity attributable (SAR mn)</t>
         </is>
       </c>
       <c r="C61" s="21" t="n">
-        <v>31.851877</v>
+        <v>3246.136935</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>FY2025 non-operating assets (SAR mn)</t>
+          <t>FY2025 associates carrying value (SAR mn)</t>
         </is>
       </c>
       <c r="C62" s="21" t="n">
-        <v>20.40064</v>
+        <v>31.851877</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
+          <t>FY2025 non-operating assets (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="n">
+        <v>20.40064</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
           <t>FY2025 NCI carrying value (SAR mn)</t>
         </is>
       </c>
-      <c r="C63" s="21" t="n">
+      <c r="C64" s="21" t="n">
         <v>62.737156</v>
       </c>
     </row>
@@ -4592,23 +4602,23 @@
         <v>100</v>
       </c>
       <c r="C6" s="28">
-        <f>B6*(1+Assumptions!C$26)</f>
+        <f>B6*(1+Assumptions!C$27)</f>
         <v/>
       </c>
       <c r="D6" s="28">
-        <f>C6*(1+Assumptions!D$26)</f>
+        <f>C6*(1+Assumptions!D$27)</f>
         <v/>
       </c>
       <c r="E6" s="28">
-        <f>D6*(1+Assumptions!E$26)</f>
+        <f>D6*(1+Assumptions!E$27)</f>
         <v/>
       </c>
       <c r="F6" s="28">
-        <f>E6*(1+Assumptions!F$26)</f>
+        <f>E6*(1+Assumptions!F$27)</f>
         <v/>
       </c>
       <c r="G6" s="28">
-        <f>F6*(1+Assumptions!G$26)</f>
+        <f>F6*(1+Assumptions!G$27)</f>
         <v/>
       </c>
     </row>
@@ -4619,27 +4629,27 @@
         </is>
       </c>
       <c r="B7" s="29">
-        <f>Assumptions!$C$53/100.0</f>
+        <f>Assumptions!$C$54/100.0</f>
         <v/>
       </c>
       <c r="C7" s="29">
-        <f>B7*(1+Assumptions!C$27)</f>
+        <f>B7*(1+Assumptions!C$28)</f>
         <v/>
       </c>
       <c r="D7" s="29">
-        <f>C7*(1+Assumptions!D$27)</f>
+        <f>C7*(1+Assumptions!D$28)</f>
         <v/>
       </c>
       <c r="E7" s="29">
-        <f>D7*(1+Assumptions!E$27)</f>
+        <f>D7*(1+Assumptions!E$28)</f>
         <v/>
       </c>
       <c r="F7" s="29">
-        <f>E7*(1+Assumptions!F$27)</f>
+        <f>E7*(1+Assumptions!F$28)</f>
         <v/>
       </c>
       <c r="G7" s="29">
-        <f>F7*(1+Assumptions!G$27)</f>
+        <f>F7*(1+Assumptions!G$28)</f>
         <v/>
       </c>
     </row>
@@ -4650,27 +4660,27 @@
         </is>
       </c>
       <c r="B8" s="29">
-        <f>Assumptions!$C$54/100.0</f>
+        <f>Assumptions!$C$55/100.0</f>
         <v/>
       </c>
       <c r="C8" s="29">
-        <f>B8*(1+Assumptions!C$28)</f>
+        <f>B8*(1+Assumptions!C$29)</f>
         <v/>
       </c>
       <c r="D8" s="29">
-        <f>C8*(1+Assumptions!D$28)</f>
+        <f>C8*(1+Assumptions!D$29)</f>
         <v/>
       </c>
       <c r="E8" s="29">
-        <f>D8*(1+Assumptions!E$28)</f>
+        <f>D8*(1+Assumptions!E$29)</f>
         <v/>
       </c>
       <c r="F8" s="29">
-        <f>E8*(1+Assumptions!F$28)</f>
+        <f>E8*(1+Assumptions!F$29)</f>
         <v/>
       </c>
       <c r="G8" s="29">
-        <f>F8*(1+Assumptions!G$28)</f>
+        <f>F8*(1+Assumptions!G$29)</f>
         <v/>
       </c>
     </row>
@@ -4681,23 +4691,23 @@
         </is>
       </c>
       <c r="C9" s="24">
-        <f>Assumptions!$C$29+Assumptions!C$30</f>
+        <f>Assumptions!$C$30+Assumptions!C$31</f>
         <v/>
       </c>
       <c r="D9" s="24">
-        <f>Assumptions!$C$29+Assumptions!D$30</f>
+        <f>Assumptions!$C$30+Assumptions!D$31</f>
         <v/>
       </c>
       <c r="E9" s="24">
-        <f>Assumptions!$C$29+Assumptions!E$30</f>
+        <f>Assumptions!$C$30+Assumptions!E$31</f>
         <v/>
       </c>
       <c r="F9" s="24">
-        <f>Assumptions!$C$29+Assumptions!F$30</f>
+        <f>Assumptions!$C$30+Assumptions!F$31</f>
         <v/>
       </c>
       <c r="G9" s="24">
-        <f>Assumptions!$C$29+Assumptions!G$30</f>
+        <f>Assumptions!$C$30+Assumptions!G$31</f>
         <v/>
       </c>
     </row>
@@ -4907,27 +4917,27 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>Assumptions!$C$55</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="C17" s="30">
-        <f>B17*(1+Assumptions!C$32)</f>
+        <f>B17*(1+Assumptions!C$33)</f>
         <v/>
       </c>
       <c r="D17" s="30">
-        <f>C17*(1+Assumptions!D$32)</f>
+        <f>C17*(1+Assumptions!D$33)</f>
         <v/>
       </c>
       <c r="E17" s="30">
-        <f>D17*(1+Assumptions!E$32)</f>
+        <f>D17*(1+Assumptions!E$33)</f>
         <v/>
       </c>
       <c r="F17" s="30">
-        <f>E17*(1+Assumptions!F$32)</f>
+        <f>E17*(1+Assumptions!F$33)</f>
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>F17*(1+Assumptions!G$32)</f>
+        <f>F17*(1+Assumptions!G$33)</f>
         <v/>
       </c>
     </row>
@@ -4938,27 +4948,27 @@
         </is>
       </c>
       <c r="B18" s="24">
-        <f>Assumptions!$C$33</f>
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
       <c r="C18" s="24">
-        <f>Assumptions!$C$33</f>
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
       <c r="D18" s="24">
-        <f>Assumptions!$C$33</f>
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
       <c r="E18" s="24">
-        <f>Assumptions!$C$33</f>
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
       <c r="F18" s="24">
-        <f>Assumptions!$C$33</f>
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
       <c r="G18" s="24">
-        <f>Assumptions!$C$33</f>
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
     </row>
@@ -5014,27 +5024,27 @@
         </is>
       </c>
       <c r="B21" s="30">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="C21" s="30">
-        <f>B21*(1+Assumptions!C$34)</f>
+        <f>B21*(1+Assumptions!C$35)</f>
         <v/>
       </c>
       <c r="D21" s="30">
-        <f>C21*(1+Assumptions!D$34)</f>
+        <f>C21*(1+Assumptions!D$35)</f>
         <v/>
       </c>
       <c r="E21" s="30">
-        <f>D21*(1+Assumptions!E$34)</f>
+        <f>D21*(1+Assumptions!E$35)</f>
         <v/>
       </c>
       <c r="F21" s="30">
-        <f>E21*(1+Assumptions!F$34)</f>
+        <f>E21*(1+Assumptions!F$35)</f>
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>F21*(1+Assumptions!G$34)</f>
+        <f>F21*(1+Assumptions!G$35)</f>
         <v/>
       </c>
     </row>
@@ -5045,27 +5055,27 @@
         </is>
       </c>
       <c r="B22" s="24">
-        <f>Assumptions!$C$35</f>
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
       <c r="C22" s="24">
-        <f>Assumptions!$C$35</f>
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
       <c r="D22" s="24">
-        <f>Assumptions!$C$35</f>
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
       <c r="E22" s="24">
-        <f>Assumptions!$C$35</f>
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
       <c r="F22" s="24">
-        <f>Assumptions!$C$35</f>
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
       <c r="G22" s="24">
-        <f>Assumptions!$C$35</f>
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
     </row>
@@ -5245,23 +5255,23 @@
         </is>
       </c>
       <c r="C29" s="30">
-        <f>Assumptions!C$37*C25</f>
+        <f>Assumptions!C$38*C25</f>
         <v/>
       </c>
       <c r="D29" s="30">
-        <f>Assumptions!D$37*D25</f>
+        <f>Assumptions!D$38*D25</f>
         <v/>
       </c>
       <c r="E29" s="30">
-        <f>Assumptions!E$37*E25</f>
+        <f>Assumptions!E$38*E25</f>
         <v/>
       </c>
       <c r="F29" s="30">
-        <f>Assumptions!F$37*F25</f>
+        <f>Assumptions!F$38*F25</f>
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>Assumptions!G$37*G25</f>
+        <f>Assumptions!G$38*G25</f>
         <v/>
       </c>
     </row>
@@ -5272,23 +5282,23 @@
         </is>
       </c>
       <c r="C30" s="30">
-        <f>Assumptions!$C$38*C25</f>
+        <f>Assumptions!$C$39*C25</f>
         <v/>
       </c>
       <c r="D30" s="30">
-        <f>Assumptions!$C$38*D25</f>
+        <f>Assumptions!$C$39*D25</f>
         <v/>
       </c>
       <c r="E30" s="30">
-        <f>Assumptions!$C$38*E25</f>
+        <f>Assumptions!$C$39*E25</f>
         <v/>
       </c>
       <c r="F30" s="30">
-        <f>Assumptions!$C$38*F25</f>
+        <f>Assumptions!$C$39*F25</f>
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>Assumptions!$C$38*G25</f>
+        <f>Assumptions!$C$39*G25</f>
         <v/>
       </c>
     </row>
@@ -5449,7 +5459,7 @@
         </is>
       </c>
       <c r="C6" s="31">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5471,7 +5481,7 @@
         </is>
       </c>
       <c r="C8" s="32">
-        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$61+Assumptions!$C$62-Assumptions!$C$63)/Assumptions!$C$6)*DCF!$C$54-Assumptions!$C$51</f>
+        <f>((C6*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$54-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5482,11 +5492,11 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$61+Assumptions!$C$62-Assumptions!$C$63)/Assumptions!$C$6)*DCF!$C$54-Assumptions!$C$51</f>
+        <f>((7.5*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$54-Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="D9" s="18">
-        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$61+Assumptions!$C$62-Assumptions!$C$63)/Assumptions!$C$6)*DCF!$C$54-Assumptions!$C$51</f>
+        <f>((11*C5*DCF!D19+C7-Assumptions!$C$7+Assumptions!$C$62+Assumptions!$C$63-Assumptions!$C$64)/Assumptions!$C$6)*DCF!$C$54-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5543,7 +5553,7 @@
         </is>
       </c>
       <c r="C15" s="18">
-        <f>((C12*C13-Assumptions!$C$38*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$44)/Assumptions!$C$6</f>
+        <f>((C12*C13-Assumptions!$C$39*C13)-C14)*(1-Assumptions!$C$14)*(1-Assumptions!$C$45)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5554,7 +5564,7 @@
         </is>
       </c>
       <c r="C16" s="32">
-        <f>(Assumptions!$C$47*C15)*DCF!$C$54-Assumptions!$C$51</f>
+        <f>(Assumptions!$C$48*C15)*DCF!$C$54-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5565,11 +5575,11 @@
         </is>
       </c>
       <c r="C17" s="18">
-        <f>(10*C15)*DCF!$C$54-Assumptions!$C$51</f>
+        <f>(10*C15)*DCF!$C$54-Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="D17" s="18">
-        <f>(16*C15)*DCF!$C$54-Assumptions!$C$51</f>
+        <f>(16*C15)*DCF!$C$54-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5593,7 +5603,7 @@
         </is>
       </c>
       <c r="C20" s="18">
-        <f>Assumptions!$C$60/Assumptions!$C$6</f>
+        <f>Assumptions!$C$61/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5604,7 +5614,7 @@
         </is>
       </c>
       <c r="C21" s="34">
-        <f>(Assumptions!$C$48-Assumptions!$C$23)/(DCF!C11-Assumptions!$C$23)</f>
+        <f>(Assumptions!$C$49-Assumptions!$C$23)/(DCF!C11-Assumptions!$C$23)</f>
         <v/>
       </c>
     </row>
@@ -5615,7 +5625,7 @@
         </is>
       </c>
       <c r="C22" s="32">
-        <f>(C21*C20)*DCF!$C$54-Assumptions!$C$51</f>
+        <f>(C21*C20)*DCF!$C$54-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5626,11 +5636,11 @@
         </is>
       </c>
       <c r="C23" s="18">
-        <f>(((Assumptions!$C$48)-0.05-Assumptions!$C$23)/(DCF!C6-Assumptions!$C$23)*C20)*DCF!$C$54-Assumptions!$C$51</f>
+        <f>(((Assumptions!$C$49)-0.05-Assumptions!$C$23)/(DCF!C6-Assumptions!$C$23)*C20)*DCF!$C$54-Assumptions!$C$52</f>
         <v/>
       </c>
       <c r="D23" s="18">
-        <f>(((Assumptions!$C$48)+0.03-Assumptions!$C$23)/(DCF!C11-Assumptions!$C$23)*C20)*DCF!$C$54-Assumptions!$C$51</f>
+        <f>(((Assumptions!$C$49)+0.03-Assumptions!$C$23)/(DCF!C11-Assumptions!$C$23)*C20)*DCF!$C$54-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -5848,23 +5858,23 @@
         </is>
       </c>
       <c r="C17" s="36">
-        <f>(Assumptions!C$41-Assumptions!C$41)/(Assumptions!C$41-Assumptions!G$41)</f>
+        <f>(Assumptions!C$42-Assumptions!C$42)/(Assumptions!C$42-Assumptions!G$42)</f>
         <v/>
       </c>
       <c r="D17" s="36">
-        <f>(Assumptions!C$41-Assumptions!D$41)/(Assumptions!C$41-Assumptions!G$41)</f>
+        <f>(Assumptions!C$42-Assumptions!D$42)/(Assumptions!C$42-Assumptions!G$42)</f>
         <v/>
       </c>
       <c r="E17" s="36">
-        <f>(Assumptions!C$41-Assumptions!E$41)/(Assumptions!C$41-Assumptions!G$41)</f>
+        <f>(Assumptions!C$42-Assumptions!E$42)/(Assumptions!C$42-Assumptions!G$42)</f>
         <v/>
       </c>
       <c r="F17" s="36">
-        <f>(Assumptions!C$41-Assumptions!F$41)/(Assumptions!C$41-Assumptions!G$41)</f>
+        <f>(Assumptions!C$42-Assumptions!F$42)/(Assumptions!C$42-Assumptions!G$42)</f>
         <v/>
       </c>
       <c r="G17" s="36">
-        <f>(Assumptions!C$41-Assumptions!G$41)/(Assumptions!C$41-Assumptions!G$41)</f>
+        <f>(Assumptions!C$42-Assumptions!G$42)/(Assumptions!C$42-Assumptions!G$42)</f>
         <v/>
       </c>
     </row>
@@ -6037,23 +6047,23 @@
         </is>
       </c>
       <c r="C24" s="30">
-        <f>Assumptions!C$39*C23</f>
+        <f>Assumptions!C$40*C23</f>
         <v/>
       </c>
       <c r="D24" s="30">
-        <f>Assumptions!D$39*D23</f>
+        <f>Assumptions!D$40*D23</f>
         <v/>
       </c>
       <c r="E24" s="30">
-        <f>Assumptions!E$39*E23</f>
+        <f>Assumptions!E$40*E23</f>
         <v/>
       </c>
       <c r="F24" s="30">
-        <f>Assumptions!F$39*F23</f>
+        <f>Assumptions!F$40*F23</f>
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>Assumptions!G$39*G23</f>
+        <f>Assumptions!G$40*G23</f>
         <v/>
       </c>
     </row>
@@ -6064,23 +6074,23 @@
         </is>
       </c>
       <c r="C25" s="30">
-        <f>Assumptions!$C$40*C23</f>
+        <f>Assumptions!$C$41*C23</f>
         <v/>
       </c>
       <c r="D25" s="30">
-        <f>Assumptions!$C$40*D23</f>
+        <f>Assumptions!$C$41*D23</f>
         <v/>
       </c>
       <c r="E25" s="30">
-        <f>Assumptions!$C$40*E23</f>
+        <f>Assumptions!$C$41*E23</f>
         <v/>
       </c>
       <c r="F25" s="30">
-        <f>Assumptions!$C$40*F23</f>
+        <f>Assumptions!$C$41*F23</f>
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>Assumptions!$C$40*G23</f>
+        <f>Assumptions!$C$41*G23</f>
         <v/>
       </c>
     </row>
@@ -6091,7 +6101,7 @@
         </is>
       </c>
       <c r="C26" s="30">
-        <f>C25-Assumptions!$C$57</f>
+        <f>C25-Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="D26" s="30">
@@ -6186,7 +6196,7 @@
         </is>
       </c>
       <c r="C31" s="30">
-        <f>Assumptions!$C$58+C24-C22</f>
+        <f>Assumptions!$C$59+C24-C22</f>
         <v/>
       </c>
       <c r="D31" s="30">
@@ -6311,7 +6321,7 @@
         </is>
       </c>
       <c r="C39" s="30">
-        <f>-C38*(1+Assumptions!$C$21)^(Assumptions!$C$24/2)</f>
+        <f>-C38*(1+Assumptions!$C$21)^Assumptions!$C$25</f>
         <v/>
       </c>
     </row>
@@ -6424,7 +6434,7 @@
         </is>
       </c>
       <c r="C50" s="30">
-        <f>Assumptions!$C$61+Assumptions!$C$62</f>
+        <f>Assumptions!$C$62+Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -6435,7 +6445,7 @@
         </is>
       </c>
       <c r="C51" s="30">
-        <f>-Assumptions!$C$63</f>
+        <f>-Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
@@ -6468,7 +6478,7 @@
         </is>
       </c>
       <c r="C54" s="36">
-        <f>(1+C6)^(Assumptions!$C$50/365)</f>
+        <f>(1+C6)^(Assumptions!$C$51/365)</f>
         <v/>
       </c>
     </row>
@@ -6479,7 +6489,7 @@
         </is>
       </c>
       <c r="C55" s="32">
-        <f>C53*C54-Assumptions!$C$51</f>
+        <f>C53*C54-Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
@@ -6515,7 +6525,7 @@
         </is>
       </c>
       <c r="C59" s="19" t="n">
-        <v>81.9880979359901</v>
+        <v>81.17493099821168</v>
       </c>
     </row>
     <row r="60">
@@ -6536,7 +6546,7 @@
         </is>
       </c>
       <c r="C61" s="19" t="n">
-        <v>202.3740402967112</v>
+        <v>200.3094466830363</v>
       </c>
     </row>
   </sheetData>

--- a/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
+++ b/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
@@ -2187,16 +2187,16 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>141.181821159505</v>
+        <v>138.8188086179422</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>164.2048778752795</v>
+        <v>160.024197399489</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>200.1453649939247</v>
+        <v>193.2423963995355</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>264.6042053864718</v>
+        <v>252.9882042509163</v>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>120.0294758549692</v>
+        <v>118.0764443935354</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>135.1117534869411</v>
+        <v>131.7713588607731</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>156.6926008985187</v>
+        <v>151.4515343763388</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>190.36479698198</v>
+        <v>182.2724195695924</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>250.731286493416</v>
+        <v>237.6950743138928</v>
       </c>
     </row>
     <row r="8">
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>104.5301516560279</v>
+        <v>102.8763642135678</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>114.9907901554711</v>
+        <v>112.2295144836776</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>129.0831601218276</v>
+        <v>124.8948459667789</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>149.234010829074</v>
+        <v>143.0889146986687</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>180.6571560010763</v>
+        <v>171.5739391759529</v>
       </c>
     </row>
     <row r="9">
@@ -2255,19 +2255,19 @@
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>92.68449495813583</v>
+        <v>91.25841413495058</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>100.2448283061584</v>
+        <v>97.90627135478546</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>109.9854242884174</v>
+        <v>106.5226915456201</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>123.0963109284656</v>
+        <v>118.1847900735714</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>141.829359842241</v>
+        <v>134.9307756799832</v>
       </c>
     </row>
     <row r="10">
@@ -2277,19 +2277,19 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>83.33651363068722</v>
+        <v>82.08926532260874</v>
       </c>
       <c r="C10" s="19" t="n">
-        <v>88.97291280931691</v>
+        <v>86.95603719114317</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>95.98692365699924</v>
+        <v>93.05384389783332</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>105.0136315470419</v>
+        <v>100.9523562314059</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>117.1514447432494</v>
+        <v>111.6368450361986</v>
       </c>
     </row>
     <row r="12">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B13" s="19" t="n">
-        <v>135.3359987826802</v>
+        <v>130.9450425452507</v>
       </c>
     </row>
     <row r="14">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="B14" s="19" t="n">
-        <v>132.373703149165</v>
+        <v>128.0787687569658</v>
       </c>
     </row>
     <row r="15">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>129.0831601218276</v>
+        <v>124.8948459667789</v>
       </c>
     </row>
     <row r="16">
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="B16" s="19" t="n">
-        <v>126.6941064789215</v>
+        <v>122.5831741380606</v>
       </c>
     </row>
     <row r="17">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>123.9712008691094</v>
+        <v>119.9484338475291</v>
       </c>
     </row>
     <row r="19">
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="B20" s="19" t="n">
-        <v>141.5174478670757</v>
+        <v>136.9997289262113</v>
       </c>
     </row>
     <row r="21">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="B21" s="19" t="n">
-        <v>135.2893091307755</v>
+        <v>130.9363079504094</v>
       </c>
     </row>
     <row r="22">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="B22" s="19" t="n">
-        <v>129.0831601218276</v>
+        <v>124.8948459667789</v>
       </c>
     </row>
     <row r="23">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>122.8965491787002</v>
+        <v>118.8728947364131</v>
       </c>
     </row>
     <row r="24">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>116.7274517982834</v>
+        <v>112.8684325829204</v>
       </c>
     </row>
     <row r="26">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="B27" s="19" t="n">
-        <v>109.0919904282692</v>
+        <v>105.5202482992868</v>
       </c>
     </row>
     <row r="28">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B28" s="19" t="n">
-        <v>116.9543636973258</v>
+        <v>113.1401288100613</v>
       </c>
     </row>
     <row r="29">
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="B29" s="19" t="n">
-        <v>129.0831601218276</v>
+        <v>124.8948459667789</v>
       </c>
     </row>
     <row r="30">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="B30" s="19" t="n">
-        <v>132.9587083256414</v>
+        <v>128.6508633970396</v>
       </c>
     </row>
     <row r="31">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>141.1040137589644</v>
+        <v>136.5449486906654</v>
       </c>
     </row>
     <row r="33">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="B34" s="19" t="n">
-        <v>118.3943412479728</v>
+        <v>114.6272837035758</v>
       </c>
     </row>
     <row r="35">
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>123.7435332419096</v>
+        <v>119.7658553584658</v>
       </c>
     </row>
     <row r="36">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="B36" s="19" t="n">
-        <v>129.0831601218276</v>
+        <v>124.8948459667789</v>
       </c>
     </row>
     <row r="37">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="B37" s="19" t="n">
-        <v>134.4139302658407</v>
+        <v>130.0149650950475</v>
       </c>
     </row>
     <row r="38">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="B38" s="19" t="n">
-        <v>139.7364678301035</v>
+        <v>135.1268379459818</v>
       </c>
     </row>
     <row r="40">
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="B41" s="19" t="n">
-        <v>134.87432479455</v>
+        <v>130.6056552326431</v>
       </c>
     </row>
     <row r="42">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B42" s="19" t="n">
-        <v>131.9787424581888</v>
+        <v>127.750250599711</v>
       </c>
     </row>
     <row r="43">
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="B43" s="19" t="n">
-        <v>129.0831601218276</v>
+        <v>124.8948459667789</v>
       </c>
     </row>
     <row r="44">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="B44" s="19" t="n">
-        <v>126.1875777854665</v>
+        <v>122.0394413338469</v>
       </c>
     </row>
     <row r="45">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>123.2919954491053</v>
+        <v>119.1840367009148</v>
       </c>
     </row>
   </sheetData>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="C18" s="19" t="n">
-        <v>141.1040137589644</v>
+        <v>136.5449486906654</v>
       </c>
     </row>
     <row r="19">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="C19" s="19" t="n">
-        <v>116.9543636973258</v>
+        <v>113.1401288100613</v>
       </c>
     </row>
   </sheetData>
@@ -6295,11 +6295,11 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Terminal NOPAT (next year)</t>
+          <t>FY2030 operating profit after tax</t>
         </is>
       </c>
       <c r="C37" s="30">
-        <f>G21*(1+Assumptions!$C$23)</f>
+        <f>G21</f>
         <v/>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="C38" s="30">
-        <f>G22*(1+Assumptions!$C$23)</f>
+        <f>G22</f>
         <v/>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="C40" s="30">
-        <f>-Assumptions!$C$22*(G32)*(1+Assumptions!$C$23)</f>
+        <f>-Assumptions!$C$22*(G32)</f>
         <v/>
       </c>
     </row>
@@ -6343,14 +6343,14 @@
         </is>
       </c>
       <c r="C41" s="30">
-        <f>-Assumptions!$C$21*G25*(1+Assumptions!$C$23)</f>
+        <f>-Assumptions!$C$21*G25</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>Terminal free cash flow</t>
+          <t>FY2030 free cash flow on this construction</t>
         </is>
       </c>
       <c r="C42" s="37">
@@ -6361,7 +6361,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Terminal value</t>
+          <t>Terminal value = that flow grown one year, capitalised</t>
         </is>
       </c>
       <c r="C43" s="30">
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="C59" s="19" t="n">
-        <v>81.17493099821168</v>
+        <v>79.31652798852629</v>
       </c>
     </row>
     <row r="60">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="C61" s="19" t="n">
-        <v>200.3094466830363</v>
+        <v>192.6858853006842</v>
       </c>
     </row>
   </sheetData>

--- a/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
+++ b/engine/riyadhcable_study/RIYADHCABLE_Valuation_Model_18082026_public.xlsx
@@ -2094,7 +2094,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>3-month calibration: PARITY vs the random walk; coverage 0.70/0.80/0.90; PIT mean 0.49.</t>
+          <t>Three-month record: over 10 resolved forecasts the price finished inside the 50/80/90% bands 0.70/0.80/0.90 of the time; PIT mean 0.49; the 90% band ran 1.19x a naive carry-anchored band.</t>
         </is>
       </c>
     </row>
